--- a/reports/latest/android-report.xlsx
+++ b/reports/latest/android-report.xlsx
@@ -4114,7 +4114,7 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>917</v>
+        <v>572</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -4131,7 +4131,7 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -4148,7 +4148,7 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -4165,7 +4165,7 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -4182,7 +4182,7 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -4216,7 +4216,7 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -4233,7 +4233,7 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -4250,7 +4250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
@@ -4267,7 +4267,7 @@
         <v>29</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -4284,7 +4284,7 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -4301,7 +4301,7 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -4318,7 +4318,7 @@
         <v>29</v>
       </c>
       <c r="D14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4335,7 +4335,7 @@
         <v>29</v>
       </c>
       <c r="D15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -4352,7 +4352,7 @@
         <v>29</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -4369,7 +4369,7 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -4386,7 +4386,7 @@
         <v>29</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -4403,7 +4403,7 @@
         <v>29</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
@@ -4420,7 +4420,7 @@
         <v>29</v>
       </c>
       <c r="D20">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
@@ -4437,7 +4437,7 @@
         <v>29</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
         <v>30</v>
@@ -4454,7 +4454,7 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
         <v>30</v>
@@ -4471,7 +4471,7 @@
         <v>29</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
         <v>30</v>
@@ -4488,7 +4488,7 @@
         <v>29</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
         <v>30</v>
@@ -4505,7 +4505,7 @@
         <v>29</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
         <v>30</v>
@@ -4522,7 +4522,7 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
         <v>30</v>
@@ -4556,7 +4556,7 @@
         <v>29</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
         <v>30</v>
@@ -4573,7 +4573,7 @@
         <v>29</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
         <v>30</v>
@@ -4590,7 +4590,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
         <v>30</v>
@@ -4607,7 +4607,7 @@
         <v>29</v>
       </c>
       <c r="D31">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E31" t="s">
         <v>30</v>
@@ -4624,7 +4624,7 @@
         <v>29</v>
       </c>
       <c r="D32">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E32" t="s">
         <v>30</v>
@@ -4641,7 +4641,7 @@
         <v>29</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
         <v>30</v>
@@ -4658,7 +4658,7 @@
         <v>29</v>
       </c>
       <c r="D34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
         <v>30</v>
@@ -4675,7 +4675,7 @@
         <v>29</v>
       </c>
       <c r="D35">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
         <v>30</v>
@@ -4692,7 +4692,7 @@
         <v>29</v>
       </c>
       <c r="D36">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E36" t="s">
         <v>30</v>
@@ -4709,7 +4709,7 @@
         <v>29</v>
       </c>
       <c r="D37">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E37" t="s">
         <v>30</v>
@@ -4726,7 +4726,7 @@
         <v>29</v>
       </c>
       <c r="D38">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
         <v>30</v>
@@ -4743,7 +4743,7 @@
         <v>29</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
         <v>30</v>
@@ -4760,7 +4760,7 @@
         <v>29</v>
       </c>
       <c r="D40">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E40" t="s">
         <v>30</v>
@@ -4777,7 +4777,7 @@
         <v>29</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
         <v>30</v>
@@ -4794,7 +4794,7 @@
         <v>29</v>
       </c>
       <c r="D42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E42" t="s">
         <v>30</v>
@@ -4811,7 +4811,7 @@
         <v>29</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
         <v>30</v>
@@ -4828,7 +4828,7 @@
         <v>29</v>
       </c>
       <c r="D44">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
         <v>30</v>
@@ -4845,7 +4845,7 @@
         <v>29</v>
       </c>
       <c r="D45">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
         <v>30</v>
@@ -4862,7 +4862,7 @@
         <v>29</v>
       </c>
       <c r="D46">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E46" t="s">
         <v>30</v>
@@ -4879,7 +4879,7 @@
         <v>29</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E47" t="s">
         <v>30</v>
@@ -4896,7 +4896,7 @@
         <v>29</v>
       </c>
       <c r="D48">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
         <v>30</v>
@@ -4913,7 +4913,7 @@
         <v>29</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
         <v>30</v>
@@ -4930,7 +4930,7 @@
         <v>29</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E50" t="s">
         <v>30</v>
@@ -4947,7 +4947,7 @@
         <v>29</v>
       </c>
       <c r="D51">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
         <v>30</v>
@@ -4964,7 +4964,7 @@
         <v>29</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E52" t="s">
         <v>30</v>
@@ -4981,7 +4981,7 @@
         <v>29</v>
       </c>
       <c r="D53">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E53" t="s">
         <v>30</v>
@@ -4998,7 +4998,7 @@
         <v>29</v>
       </c>
       <c r="D54">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
         <v>30</v>
@@ -5015,7 +5015,7 @@
         <v>29</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E55" t="s">
         <v>30</v>
@@ -5032,7 +5032,7 @@
         <v>29</v>
       </c>
       <c r="D56">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
         <v>30</v>
@@ -5049,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="D57">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E57" t="s">
         <v>30</v>
@@ -5066,7 +5066,7 @@
         <v>29</v>
       </c>
       <c r="D58">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E58" t="s">
         <v>30</v>
@@ -5083,7 +5083,7 @@
         <v>29</v>
       </c>
       <c r="D59">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E59" t="s">
         <v>30</v>
@@ -5100,7 +5100,7 @@
         <v>29</v>
       </c>
       <c r="D60">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E60" t="s">
         <v>30</v>
@@ -5117,7 +5117,7 @@
         <v>29</v>
       </c>
       <c r="D61">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
         <v>30</v>
@@ -5134,7 +5134,7 @@
         <v>29</v>
       </c>
       <c r="D62">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s">
         <v>30</v>
@@ -5151,7 +5151,7 @@
         <v>29</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E63" t="s">
         <v>30</v>
@@ -5168,7 +5168,7 @@
         <v>29</v>
       </c>
       <c r="D64">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
         <v>30</v>
@@ -5185,7 +5185,7 @@
         <v>29</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E65" t="s">
         <v>30</v>
@@ -5202,7 +5202,7 @@
         <v>29</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E66" t="s">
         <v>30</v>
@@ -5219,7 +5219,7 @@
         <v>29</v>
       </c>
       <c r="D67">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E67" t="s">
         <v>30</v>
@@ -5236,7 +5236,7 @@
         <v>29</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
         <v>30</v>
@@ -5253,7 +5253,7 @@
         <v>29</v>
       </c>
       <c r="D69">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E69" t="s">
         <v>30</v>
@@ -5270,7 +5270,7 @@
         <v>29</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E70" t="s">
         <v>30</v>
@@ -5287,7 +5287,7 @@
         <v>29</v>
       </c>
       <c r="D71">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E71" t="s">
         <v>30</v>
@@ -5304,7 +5304,7 @@
         <v>29</v>
       </c>
       <c r="D72">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E72" t="s">
         <v>30</v>
@@ -5338,7 +5338,7 @@
         <v>29</v>
       </c>
       <c r="D74">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E74" t="s">
         <v>30</v>
@@ -5355,7 +5355,7 @@
         <v>29</v>
       </c>
       <c r="D75">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E75" t="s">
         <v>30</v>
@@ -5372,7 +5372,7 @@
         <v>29</v>
       </c>
       <c r="D76">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E76" t="s">
         <v>30</v>
@@ -5389,7 +5389,7 @@
         <v>29</v>
       </c>
       <c r="D77">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E77" t="s">
         <v>30</v>
@@ -5406,7 +5406,7 @@
         <v>29</v>
       </c>
       <c r="D78">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E78" t="s">
         <v>30</v>
@@ -5440,7 +5440,7 @@
         <v>29</v>
       </c>
       <c r="D80">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
         <v>30</v>
@@ -5457,7 +5457,7 @@
         <v>29</v>
       </c>
       <c r="D81">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E81" t="s">
         <v>30</v>
@@ -5474,7 +5474,7 @@
         <v>29</v>
       </c>
       <c r="D82">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
         <v>30</v>
@@ -5491,7 +5491,7 @@
         <v>29</v>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E83" t="s">
         <v>30</v>
@@ -5508,7 +5508,7 @@
         <v>29</v>
       </c>
       <c r="D84">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E84" t="s">
         <v>30</v>
@@ -5525,7 +5525,7 @@
         <v>29</v>
       </c>
       <c r="D85">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E85" t="s">
         <v>30</v>
@@ -5542,7 +5542,7 @@
         <v>29</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E86" t="s">
         <v>30</v>
@@ -5559,7 +5559,7 @@
         <v>29</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E87" t="s">
         <v>30</v>
@@ -5576,7 +5576,7 @@
         <v>29</v>
       </c>
       <c r="D88">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E88" t="s">
         <v>30</v>
@@ -5644,7 +5644,7 @@
         <v>29</v>
       </c>
       <c r="D92">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E92" t="s">
         <v>30</v>
@@ -5661,7 +5661,7 @@
         <v>29</v>
       </c>
       <c r="D93">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E93" t="s">
         <v>30</v>
@@ -5678,7 +5678,7 @@
         <v>29</v>
       </c>
       <c r="D94">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E94" t="s">
         <v>30</v>
@@ -5695,7 +5695,7 @@
         <v>29</v>
       </c>
       <c r="D95">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E95" t="s">
         <v>30</v>
@@ -5712,7 +5712,7 @@
         <v>29</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E96" t="s">
         <v>30</v>
@@ -5729,7 +5729,7 @@
         <v>29</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E97" t="s">
         <v>30</v>
@@ -5746,7 +5746,7 @@
         <v>29</v>
       </c>
       <c r="D98">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E98" t="s">
         <v>30</v>
@@ -5763,7 +5763,7 @@
         <v>29</v>
       </c>
       <c r="D99">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E99" t="s">
         <v>30</v>
@@ -5780,7 +5780,7 @@
         <v>29</v>
       </c>
       <c r="D100">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E100" t="s">
         <v>30</v>
@@ -5797,7 +5797,7 @@
         <v>29</v>
       </c>
       <c r="D101">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E101" t="s">
         <v>30</v>
@@ -5814,7 +5814,7 @@
         <v>29</v>
       </c>
       <c r="D102">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E102" t="s">
         <v>30</v>
@@ -5831,7 +5831,7 @@
         <v>29</v>
       </c>
       <c r="D103">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E103" t="s">
         <v>30</v>
@@ -5848,7 +5848,7 @@
         <v>29</v>
       </c>
       <c r="D104">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E104" t="s">
         <v>30</v>
@@ -5865,7 +5865,7 @@
         <v>29</v>
       </c>
       <c r="D105">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E105" t="s">
         <v>30</v>
@@ -5882,7 +5882,7 @@
         <v>29</v>
       </c>
       <c r="D106">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E106" t="s">
         <v>30</v>
@@ -5899,7 +5899,7 @@
         <v>29</v>
       </c>
       <c r="D107">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E107" t="s">
         <v>30</v>
@@ -5916,7 +5916,7 @@
         <v>29</v>
       </c>
       <c r="D108">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E108" t="s">
         <v>30</v>
@@ -5933,7 +5933,7 @@
         <v>29</v>
       </c>
       <c r="D109">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E109" t="s">
         <v>30</v>
@@ -5950,7 +5950,7 @@
         <v>29</v>
       </c>
       <c r="D110">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E110" t="s">
         <v>30</v>
@@ -5967,7 +5967,7 @@
         <v>29</v>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
         <v>30</v>
@@ -5984,7 +5984,7 @@
         <v>29</v>
       </c>
       <c r="D112">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E112" t="s">
         <v>30</v>
@@ -6001,7 +6001,7 @@
         <v>29</v>
       </c>
       <c r="D113">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E113" t="s">
         <v>30</v>
@@ -6018,7 +6018,7 @@
         <v>29</v>
       </c>
       <c r="D114">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E114" t="s">
         <v>30</v>
@@ -6035,7 +6035,7 @@
         <v>29</v>
       </c>
       <c r="D115">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E115" t="s">
         <v>30</v>
@@ -6052,7 +6052,7 @@
         <v>29</v>
       </c>
       <c r="D116">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E116" t="s">
         <v>30</v>
@@ -6069,7 +6069,7 @@
         <v>29</v>
       </c>
       <c r="D117">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E117" t="s">
         <v>30</v>
@@ -6086,7 +6086,7 @@
         <v>29</v>
       </c>
       <c r="D118">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E118" t="s">
         <v>30</v>
@@ -6120,7 +6120,7 @@
         <v>29</v>
       </c>
       <c r="D120">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E120" t="s">
         <v>30</v>
@@ -6137,7 +6137,7 @@
         <v>29</v>
       </c>
       <c r="D121">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E121" t="s">
         <v>30</v>
@@ -6154,7 +6154,7 @@
         <v>29</v>
       </c>
       <c r="D122">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E122" t="s">
         <v>30</v>
@@ -6171,7 +6171,7 @@
         <v>29</v>
       </c>
       <c r="D123">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E123" t="s">
         <v>30</v>
@@ -6188,7 +6188,7 @@
         <v>29</v>
       </c>
       <c r="D124">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E124" t="s">
         <v>30</v>
@@ -6205,7 +6205,7 @@
         <v>29</v>
       </c>
       <c r="D125">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E125" t="s">
         <v>30</v>
@@ -6222,7 +6222,7 @@
         <v>29</v>
       </c>
       <c r="D126">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E126" t="s">
         <v>30</v>
@@ -6256,7 +6256,7 @@
         <v>29</v>
       </c>
       <c r="D128">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E128" t="s">
         <v>30</v>
@@ -6273,7 +6273,7 @@
         <v>29</v>
       </c>
       <c r="D129">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E129" t="s">
         <v>30</v>
@@ -6290,7 +6290,7 @@
         <v>29</v>
       </c>
       <c r="D130">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E130" t="s">
         <v>30</v>
@@ -6307,7 +6307,7 @@
         <v>29</v>
       </c>
       <c r="D131">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E131" t="s">
         <v>30</v>
@@ -6324,7 +6324,7 @@
         <v>29</v>
       </c>
       <c r="D132">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E132" t="s">
         <v>30</v>
@@ -6341,7 +6341,7 @@
         <v>29</v>
       </c>
       <c r="D133">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E133" t="s">
         <v>30</v>
@@ -6358,7 +6358,7 @@
         <v>29</v>
       </c>
       <c r="D134">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E134" t="s">
         <v>30</v>
@@ -6375,7 +6375,7 @@
         <v>29</v>
       </c>
       <c r="D135">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E135" t="s">
         <v>30</v>
@@ -6392,7 +6392,7 @@
         <v>29</v>
       </c>
       <c r="D136">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E136" t="s">
         <v>30</v>
@@ -6409,7 +6409,7 @@
         <v>29</v>
       </c>
       <c r="D137">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E137" t="s">
         <v>30</v>
@@ -6426,7 +6426,7 @@
         <v>29</v>
       </c>
       <c r="D138">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E138" t="s">
         <v>30</v>
@@ -6460,7 +6460,7 @@
         <v>29</v>
       </c>
       <c r="D140">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E140" t="s">
         <v>30</v>
@@ -6477,7 +6477,7 @@
         <v>29</v>
       </c>
       <c r="D141">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E141" t="s">
         <v>30</v>
@@ -6494,7 +6494,7 @@
         <v>29</v>
       </c>
       <c r="D142">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E142" t="s">
         <v>30</v>
@@ -6511,7 +6511,7 @@
         <v>29</v>
       </c>
       <c r="D143">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E143" t="s">
         <v>30</v>
@@ -6528,7 +6528,7 @@
         <v>29</v>
       </c>
       <c r="D144">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E144" t="s">
         <v>30</v>
@@ -6545,7 +6545,7 @@
         <v>29</v>
       </c>
       <c r="D145">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E145" t="s">
         <v>30</v>
@@ -6562,7 +6562,7 @@
         <v>29</v>
       </c>
       <c r="D146">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E146" t="s">
         <v>30</v>
@@ -6579,7 +6579,7 @@
         <v>29</v>
       </c>
       <c r="D147">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E147" t="s">
         <v>30</v>
@@ -6596,7 +6596,7 @@
         <v>29</v>
       </c>
       <c r="D148">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E148" t="s">
         <v>30</v>
@@ -6613,7 +6613,7 @@
         <v>29</v>
       </c>
       <c r="D149">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E149" t="s">
         <v>30</v>
@@ -6630,7 +6630,7 @@
         <v>29</v>
       </c>
       <c r="D150">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E150" t="s">
         <v>30</v>
@@ -6647,7 +6647,7 @@
         <v>29</v>
       </c>
       <c r="D151">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E151" t="s">
         <v>30</v>
@@ -6664,7 +6664,7 @@
         <v>29</v>
       </c>
       <c r="D152">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E152" t="s">
         <v>30</v>
@@ -6681,7 +6681,7 @@
         <v>29</v>
       </c>
       <c r="D153">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E153" t="s">
         <v>30</v>
@@ -6698,7 +6698,7 @@
         <v>29</v>
       </c>
       <c r="D154">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E154" t="s">
         <v>30</v>
@@ -6715,7 +6715,7 @@
         <v>29</v>
       </c>
       <c r="D155">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E155" t="s">
         <v>30</v>
@@ -6732,7 +6732,7 @@
         <v>29</v>
       </c>
       <c r="D156">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E156" t="s">
         <v>30</v>
@@ -6766,7 +6766,7 @@
         <v>29</v>
       </c>
       <c r="D158">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E158" t="s">
         <v>30</v>
@@ -6783,7 +6783,7 @@
         <v>29</v>
       </c>
       <c r="D159">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E159" t="s">
         <v>30</v>
@@ -6800,7 +6800,7 @@
         <v>29</v>
       </c>
       <c r="D160">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E160" t="s">
         <v>30</v>
@@ -6817,7 +6817,7 @@
         <v>29</v>
       </c>
       <c r="D161">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E161" t="s">
         <v>30</v>
@@ -6834,7 +6834,7 @@
         <v>29</v>
       </c>
       <c r="D162">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E162" t="s">
         <v>30</v>
@@ -6851,7 +6851,7 @@
         <v>29</v>
       </c>
       <c r="D163">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E163" t="s">
         <v>30</v>
@@ -6868,7 +6868,7 @@
         <v>29</v>
       </c>
       <c r="D164">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E164" t="s">
         <v>30</v>
@@ -6885,7 +6885,7 @@
         <v>29</v>
       </c>
       <c r="D165">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E165" t="s">
         <v>30</v>
@@ -6902,7 +6902,7 @@
         <v>29</v>
       </c>
       <c r="D166">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E166" t="s">
         <v>30</v>
@@ -6919,7 +6919,7 @@
         <v>29</v>
       </c>
       <c r="D167">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E167" t="s">
         <v>30</v>
@@ -6936,7 +6936,7 @@
         <v>29</v>
       </c>
       <c r="D168">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E168" t="s">
         <v>30</v>
@@ -6953,7 +6953,7 @@
         <v>29</v>
       </c>
       <c r="D169">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E169" t="s">
         <v>30</v>
@@ -6970,7 +6970,7 @@
         <v>29</v>
       </c>
       <c r="D170">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E170" t="s">
         <v>30</v>
@@ -6987,7 +6987,7 @@
         <v>29</v>
       </c>
       <c r="D171">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E171" t="s">
         <v>30</v>
@@ -7004,7 +7004,7 @@
         <v>29</v>
       </c>
       <c r="D172">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E172" t="s">
         <v>30</v>
@@ -7021,7 +7021,7 @@
         <v>29</v>
       </c>
       <c r="D173">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E173" t="s">
         <v>30</v>
@@ -7038,7 +7038,7 @@
         <v>29</v>
       </c>
       <c r="D174">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E174" t="s">
         <v>30</v>
@@ -7055,7 +7055,7 @@
         <v>29</v>
       </c>
       <c r="D175">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E175" t="s">
         <v>30</v>
@@ -7072,7 +7072,7 @@
         <v>29</v>
       </c>
       <c r="D176">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E176" t="s">
         <v>30</v>
@@ -7089,7 +7089,7 @@
         <v>29</v>
       </c>
       <c r="D177">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E177" t="s">
         <v>30</v>
@@ -7106,7 +7106,7 @@
         <v>29</v>
       </c>
       <c r="D178">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E178" t="s">
         <v>30</v>
@@ -7123,7 +7123,7 @@
         <v>29</v>
       </c>
       <c r="D179">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E179" t="s">
         <v>30</v>
@@ -7140,7 +7140,7 @@
         <v>29</v>
       </c>
       <c r="D180">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E180" t="s">
         <v>30</v>
@@ -7157,7 +7157,7 @@
         <v>29</v>
       </c>
       <c r="D181">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E181" t="s">
         <v>30</v>
@@ -7174,7 +7174,7 @@
         <v>29</v>
       </c>
       <c r="D182">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E182" t="s">
         <v>30</v>
@@ -7191,7 +7191,7 @@
         <v>29</v>
       </c>
       <c r="D183">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E183" t="s">
         <v>30</v>
@@ -7208,7 +7208,7 @@
         <v>29</v>
       </c>
       <c r="D184">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E184" t="s">
         <v>30</v>
@@ -7225,7 +7225,7 @@
         <v>29</v>
       </c>
       <c r="D185">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E185" t="s">
         <v>30</v>
@@ -7242,7 +7242,7 @@
         <v>29</v>
       </c>
       <c r="D186">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E186" t="s">
         <v>30</v>
@@ -7259,7 +7259,7 @@
         <v>29</v>
       </c>
       <c r="D187">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E187" t="s">
         <v>30</v>
@@ -7276,7 +7276,7 @@
         <v>29</v>
       </c>
       <c r="D188">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E188" t="s">
         <v>30</v>
@@ -7293,7 +7293,7 @@
         <v>29</v>
       </c>
       <c r="D189">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E189" t="s">
         <v>30</v>
@@ -7310,7 +7310,7 @@
         <v>29</v>
       </c>
       <c r="D190">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E190" t="s">
         <v>30</v>
@@ -7327,7 +7327,7 @@
         <v>29</v>
       </c>
       <c r="D191">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E191" t="s">
         <v>30</v>
@@ -7344,7 +7344,7 @@
         <v>29</v>
       </c>
       <c r="D192">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E192" t="s">
         <v>30</v>
@@ -7361,7 +7361,7 @@
         <v>29</v>
       </c>
       <c r="D193">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E193" t="s">
         <v>30</v>
@@ -7395,7 +7395,7 @@
         <v>29</v>
       </c>
       <c r="D195">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E195" t="s">
         <v>30</v>
@@ -7429,7 +7429,7 @@
         <v>29</v>
       </c>
       <c r="D197">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E197" t="s">
         <v>30</v>
@@ -7446,7 +7446,7 @@
         <v>29</v>
       </c>
       <c r="D198">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E198" t="s">
         <v>30</v>
@@ -7463,7 +7463,7 @@
         <v>29</v>
       </c>
       <c r="D199">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E199" t="s">
         <v>30</v>
@@ -7480,7 +7480,7 @@
         <v>29</v>
       </c>
       <c r="D200">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E200" t="s">
         <v>30</v>
@@ -7497,7 +7497,7 @@
         <v>29</v>
       </c>
       <c r="D201">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E201" t="s">
         <v>30</v>
@@ -7514,7 +7514,7 @@
         <v>29</v>
       </c>
       <c r="D202">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E202" t="s">
         <v>30</v>
@@ -7531,7 +7531,7 @@
         <v>29</v>
       </c>
       <c r="D203">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E203" t="s">
         <v>30</v>
@@ -7548,7 +7548,7 @@
         <v>29</v>
       </c>
       <c r="D204">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E204" t="s">
         <v>30</v>
@@ -7565,7 +7565,7 @@
         <v>29</v>
       </c>
       <c r="D205">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E205" t="s">
         <v>30</v>
@@ -7582,7 +7582,7 @@
         <v>29</v>
       </c>
       <c r="D206">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E206" t="s">
         <v>30</v>
@@ -7599,7 +7599,7 @@
         <v>29</v>
       </c>
       <c r="D207">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E207" t="s">
         <v>30</v>
@@ -7616,7 +7616,7 @@
         <v>29</v>
       </c>
       <c r="D208">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E208" t="s">
         <v>30</v>
@@ -7633,7 +7633,7 @@
         <v>29</v>
       </c>
       <c r="D209">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E209" t="s">
         <v>30</v>
@@ -7650,7 +7650,7 @@
         <v>29</v>
       </c>
       <c r="D210">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E210" t="s">
         <v>30</v>
@@ -7667,7 +7667,7 @@
         <v>29</v>
       </c>
       <c r="D211">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E211" t="s">
         <v>30</v>
@@ -7684,7 +7684,7 @@
         <v>29</v>
       </c>
       <c r="D212">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E212" t="s">
         <v>30</v>
@@ -7701,7 +7701,7 @@
         <v>29</v>
       </c>
       <c r="D213">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E213" t="s">
         <v>30</v>
@@ -7718,7 +7718,7 @@
         <v>29</v>
       </c>
       <c r="D214">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E214" t="s">
         <v>30</v>
@@ -7735,7 +7735,7 @@
         <v>29</v>
       </c>
       <c r="D215">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E215" t="s">
         <v>30</v>
@@ -7752,7 +7752,7 @@
         <v>29</v>
       </c>
       <c r="D216">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E216" t="s">
         <v>30</v>
@@ -7786,7 +7786,7 @@
         <v>29</v>
       </c>
       <c r="D218">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E218" t="s">
         <v>30</v>
@@ -7803,7 +7803,7 @@
         <v>29</v>
       </c>
       <c r="D219">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E219" t="s">
         <v>30</v>
@@ -7820,7 +7820,7 @@
         <v>29</v>
       </c>
       <c r="D220">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E220" t="s">
         <v>30</v>
@@ -7837,7 +7837,7 @@
         <v>29</v>
       </c>
       <c r="D221">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E221" t="s">
         <v>30</v>
@@ -7854,7 +7854,7 @@
         <v>29</v>
       </c>
       <c r="D222">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E222" t="s">
         <v>30</v>
@@ -7871,7 +7871,7 @@
         <v>29</v>
       </c>
       <c r="D223">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E223" t="s">
         <v>30</v>
@@ -7888,7 +7888,7 @@
         <v>29</v>
       </c>
       <c r="D224">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E224" t="s">
         <v>30</v>
@@ -7905,7 +7905,7 @@
         <v>29</v>
       </c>
       <c r="D225">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E225" t="s">
         <v>30</v>
@@ -7922,7 +7922,7 @@
         <v>29</v>
       </c>
       <c r="D226">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E226" t="s">
         <v>30</v>
@@ -7956,7 +7956,7 @@
         <v>29</v>
       </c>
       <c r="D228">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E228" t="s">
         <v>30</v>
@@ -7973,7 +7973,7 @@
         <v>29</v>
       </c>
       <c r="D229">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E229" t="s">
         <v>30</v>
@@ -7990,7 +7990,7 @@
         <v>29</v>
       </c>
       <c r="D230">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E230" t="s">
         <v>30</v>
@@ -8007,7 +8007,7 @@
         <v>29</v>
       </c>
       <c r="D231">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E231" t="s">
         <v>30</v>
@@ -8024,7 +8024,7 @@
         <v>29</v>
       </c>
       <c r="D232">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E232" t="s">
         <v>30</v>
@@ -8041,7 +8041,7 @@
         <v>29</v>
       </c>
       <c r="D233">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E233" t="s">
         <v>30</v>
@@ -8058,7 +8058,7 @@
         <v>29</v>
       </c>
       <c r="D234">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E234" t="s">
         <v>30</v>
@@ -8075,7 +8075,7 @@
         <v>29</v>
       </c>
       <c r="D235">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E235" t="s">
         <v>30</v>
@@ -8092,7 +8092,7 @@
         <v>29</v>
       </c>
       <c r="D236">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E236" t="s">
         <v>30</v>
@@ -8109,7 +8109,7 @@
         <v>29</v>
       </c>
       <c r="D237">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E237" t="s">
         <v>30</v>
@@ -8126,7 +8126,7 @@
         <v>29</v>
       </c>
       <c r="D238">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E238" t="s">
         <v>30</v>
@@ -8143,7 +8143,7 @@
         <v>29</v>
       </c>
       <c r="D239">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E239" t="s">
         <v>30</v>
@@ -8160,7 +8160,7 @@
         <v>29</v>
       </c>
       <c r="D240">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E240" t="s">
         <v>30</v>
@@ -8177,7 +8177,7 @@
         <v>29</v>
       </c>
       <c r="D241">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E241" t="s">
         <v>30</v>
@@ -8194,7 +8194,7 @@
         <v>29</v>
       </c>
       <c r="D242">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E242" t="s">
         <v>30</v>
@@ -8211,7 +8211,7 @@
         <v>29</v>
       </c>
       <c r="D243">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E243" t="s">
         <v>30</v>
@@ -8228,7 +8228,7 @@
         <v>29</v>
       </c>
       <c r="D244">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E244" t="s">
         <v>30</v>
@@ -8245,7 +8245,7 @@
         <v>29</v>
       </c>
       <c r="D245">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E245" t="s">
         <v>30</v>
@@ -8262,7 +8262,7 @@
         <v>29</v>
       </c>
       <c r="D246">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E246" t="s">
         <v>30</v>
@@ -8279,7 +8279,7 @@
         <v>29</v>
       </c>
       <c r="D247">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E247" t="s">
         <v>30</v>
@@ -8296,7 +8296,7 @@
         <v>29</v>
       </c>
       <c r="D248">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E248" t="s">
         <v>30</v>
@@ -8313,7 +8313,7 @@
         <v>29</v>
       </c>
       <c r="D249">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E249" t="s">
         <v>30</v>
@@ -8330,7 +8330,7 @@
         <v>29</v>
       </c>
       <c r="D250">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E250" t="s">
         <v>30</v>
@@ -8347,7 +8347,7 @@
         <v>29</v>
       </c>
       <c r="D251">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E251" t="s">
         <v>30</v>
@@ -8364,7 +8364,7 @@
         <v>29</v>
       </c>
       <c r="D252">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E252" t="s">
         <v>30</v>
@@ -8381,7 +8381,7 @@
         <v>29</v>
       </c>
       <c r="D253">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E253" t="s">
         <v>30</v>
@@ -8398,7 +8398,7 @@
         <v>29</v>
       </c>
       <c r="D254">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E254" t="s">
         <v>30</v>
@@ -8415,7 +8415,7 @@
         <v>29</v>
       </c>
       <c r="D255">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E255" t="s">
         <v>30</v>
@@ -8432,7 +8432,7 @@
         <v>29</v>
       </c>
       <c r="D256">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E256" t="s">
         <v>30</v>
@@ -8449,7 +8449,7 @@
         <v>29</v>
       </c>
       <c r="D257">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E257" t="s">
         <v>30</v>
@@ -8483,7 +8483,7 @@
         <v>29</v>
       </c>
       <c r="D259">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E259" t="s">
         <v>30</v>
@@ -8500,7 +8500,7 @@
         <v>29</v>
       </c>
       <c r="D260">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E260" t="s">
         <v>30</v>
@@ -8517,7 +8517,7 @@
         <v>29</v>
       </c>
       <c r="D261">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E261" t="s">
         <v>30</v>
@@ -8534,7 +8534,7 @@
         <v>29</v>
       </c>
       <c r="D262">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E262" t="s">
         <v>30</v>
@@ -8568,7 +8568,7 @@
         <v>29</v>
       </c>
       <c r="D264">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E264" t="s">
         <v>30</v>
@@ -8585,7 +8585,7 @@
         <v>29</v>
       </c>
       <c r="D265">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E265" t="s">
         <v>30</v>
@@ -8602,7 +8602,7 @@
         <v>29</v>
       </c>
       <c r="D266">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E266" t="s">
         <v>30</v>
@@ -8619,7 +8619,7 @@
         <v>29</v>
       </c>
       <c r="D267">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E267" t="s">
         <v>30</v>
@@ -8636,7 +8636,7 @@
         <v>29</v>
       </c>
       <c r="D268">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E268" t="s">
         <v>30</v>
@@ -8653,7 +8653,7 @@
         <v>29</v>
       </c>
       <c r="D269">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E269" t="s">
         <v>30</v>
@@ -8670,7 +8670,7 @@
         <v>29</v>
       </c>
       <c r="D270">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E270" t="s">
         <v>30</v>
@@ -8687,7 +8687,7 @@
         <v>29</v>
       </c>
       <c r="D271">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E271" t="s">
         <v>30</v>
@@ -8704,7 +8704,7 @@
         <v>29</v>
       </c>
       <c r="D272">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E272" t="s">
         <v>30</v>
@@ -8721,7 +8721,7 @@
         <v>29</v>
       </c>
       <c r="D273">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E273" t="s">
         <v>30</v>
@@ -8738,7 +8738,7 @@
         <v>29</v>
       </c>
       <c r="D274">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E274" t="s">
         <v>30</v>
@@ -8755,7 +8755,7 @@
         <v>29</v>
       </c>
       <c r="D275">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E275" t="s">
         <v>30</v>
@@ -8789,7 +8789,7 @@
         <v>29</v>
       </c>
       <c r="D277">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E277" t="s">
         <v>30</v>
@@ -8806,7 +8806,7 @@
         <v>29</v>
       </c>
       <c r="D278">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E278" t="s">
         <v>30</v>
@@ -8823,7 +8823,7 @@
         <v>29</v>
       </c>
       <c r="D279">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E279" t="s">
         <v>30</v>
@@ -8840,7 +8840,7 @@
         <v>29</v>
       </c>
       <c r="D280">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E280" t="s">
         <v>30</v>
@@ -8857,7 +8857,7 @@
         <v>29</v>
       </c>
       <c r="D281">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E281" t="s">
         <v>30</v>
@@ -8891,7 +8891,7 @@
         <v>29</v>
       </c>
       <c r="D283">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E283" t="s">
         <v>30</v>
@@ -8908,7 +8908,7 @@
         <v>29</v>
       </c>
       <c r="D284">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E284" t="s">
         <v>30</v>
@@ -8925,7 +8925,7 @@
         <v>29</v>
       </c>
       <c r="D285">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E285" t="s">
         <v>30</v>
@@ -8942,7 +8942,7 @@
         <v>29</v>
       </c>
       <c r="D286">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E286" t="s">
         <v>30</v>
@@ -8959,7 +8959,7 @@
         <v>29</v>
       </c>
       <c r="D287">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E287" t="s">
         <v>30</v>
@@ -8976,7 +8976,7 @@
         <v>29</v>
       </c>
       <c r="D288">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E288" t="s">
         <v>30</v>
@@ -8993,7 +8993,7 @@
         <v>29</v>
       </c>
       <c r="D289">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E289" t="s">
         <v>30</v>
@@ -9010,7 +9010,7 @@
         <v>29</v>
       </c>
       <c r="D290">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E290" t="s">
         <v>30</v>
@@ -9027,7 +9027,7 @@
         <v>29</v>
       </c>
       <c r="D291">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E291" t="s">
         <v>30</v>
@@ -9044,7 +9044,7 @@
         <v>29</v>
       </c>
       <c r="D292">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E292" t="s">
         <v>30</v>
@@ -9061,7 +9061,7 @@
         <v>29</v>
       </c>
       <c r="D293">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E293" t="s">
         <v>30</v>
@@ -9078,7 +9078,7 @@
         <v>29</v>
       </c>
       <c r="D294">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E294" t="s">
         <v>30</v>
@@ -9095,7 +9095,7 @@
         <v>29</v>
       </c>
       <c r="D295">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E295" t="s">
         <v>30</v>
@@ -9112,7 +9112,7 @@
         <v>29</v>
       </c>
       <c r="D296">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E296" t="s">
         <v>30</v>
@@ -9129,7 +9129,7 @@
         <v>29</v>
       </c>
       <c r="D297">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E297" t="s">
         <v>30</v>
@@ -9146,7 +9146,7 @@
         <v>29</v>
       </c>
       <c r="D298">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E298" t="s">
         <v>30</v>
@@ -9163,7 +9163,7 @@
         <v>29</v>
       </c>
       <c r="D299">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E299" t="s">
         <v>30</v>
@@ -9180,7 +9180,7 @@
         <v>29</v>
       </c>
       <c r="D300">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E300" t="s">
         <v>30</v>
@@ -9197,7 +9197,7 @@
         <v>29</v>
       </c>
       <c r="D301">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E301" t="s">
         <v>30</v>
@@ -9214,7 +9214,7 @@
         <v>29</v>
       </c>
       <c r="D302">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E302" t="s">
         <v>30</v>
@@ -9231,7 +9231,7 @@
         <v>29</v>
       </c>
       <c r="D303">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E303" t="s">
         <v>30</v>
@@ -9248,7 +9248,7 @@
         <v>29</v>
       </c>
       <c r="D304">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E304" t="s">
         <v>30</v>
@@ -9265,7 +9265,7 @@
         <v>29</v>
       </c>
       <c r="D305">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E305" t="s">
         <v>30</v>
@@ -9282,7 +9282,7 @@
         <v>29</v>
       </c>
       <c r="D306">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E306" t="s">
         <v>30</v>
@@ -9299,7 +9299,7 @@
         <v>29</v>
       </c>
       <c r="D307">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E307" t="s">
         <v>30</v>
@@ -9316,7 +9316,7 @@
         <v>29</v>
       </c>
       <c r="D308">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E308" t="s">
         <v>30</v>
@@ -9367,7 +9367,7 @@
         <v>29</v>
       </c>
       <c r="D311">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E311" t="s">
         <v>30</v>
@@ -9384,7 +9384,7 @@
         <v>29</v>
       </c>
       <c r="D312">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E312" t="s">
         <v>30</v>
@@ -9401,7 +9401,7 @@
         <v>29</v>
       </c>
       <c r="D313">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E313" t="s">
         <v>30</v>
@@ -9418,7 +9418,7 @@
         <v>29</v>
       </c>
       <c r="D314">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E314" t="s">
         <v>30</v>
@@ -9435,7 +9435,7 @@
         <v>29</v>
       </c>
       <c r="D315">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E315" t="s">
         <v>30</v>
@@ -9452,7 +9452,7 @@
         <v>29</v>
       </c>
       <c r="D316">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E316" t="s">
         <v>30</v>
@@ -9469,7 +9469,7 @@
         <v>29</v>
       </c>
       <c r="D317">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E317" t="s">
         <v>30</v>
@@ -9486,7 +9486,7 @@
         <v>29</v>
       </c>
       <c r="D318">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E318" t="s">
         <v>30</v>
@@ -9503,7 +9503,7 @@
         <v>29</v>
       </c>
       <c r="D319">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E319" t="s">
         <v>30</v>
@@ -9520,7 +9520,7 @@
         <v>29</v>
       </c>
       <c r="D320">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E320" t="s">
         <v>30</v>
@@ -9537,7 +9537,7 @@
         <v>29</v>
       </c>
       <c r="D321">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E321" t="s">
         <v>30</v>
@@ -9554,7 +9554,7 @@
         <v>29</v>
       </c>
       <c r="D322">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E322" t="s">
         <v>30</v>
@@ -9571,7 +9571,7 @@
         <v>29</v>
       </c>
       <c r="D323">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E323" t="s">
         <v>30</v>
@@ -9588,7 +9588,7 @@
         <v>29</v>
       </c>
       <c r="D324">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E324" t="s">
         <v>30</v>
@@ -9605,7 +9605,7 @@
         <v>29</v>
       </c>
       <c r="D325">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E325" t="s">
         <v>30</v>
@@ -9622,7 +9622,7 @@
         <v>29</v>
       </c>
       <c r="D326">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E326" t="s">
         <v>30</v>
@@ -9639,7 +9639,7 @@
         <v>29</v>
       </c>
       <c r="D327">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E327" t="s">
         <v>30</v>
@@ -9656,7 +9656,7 @@
         <v>29</v>
       </c>
       <c r="D328">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E328" t="s">
         <v>30</v>
@@ -9673,7 +9673,7 @@
         <v>29</v>
       </c>
       <c r="D329">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E329" t="s">
         <v>30</v>
@@ -9690,7 +9690,7 @@
         <v>29</v>
       </c>
       <c r="D330">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E330" t="s">
         <v>30</v>
@@ -9707,7 +9707,7 @@
         <v>29</v>
       </c>
       <c r="D331">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E331" t="s">
         <v>30</v>
@@ -9724,7 +9724,7 @@
         <v>29</v>
       </c>
       <c r="D332">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E332" t="s">
         <v>30</v>
@@ -9758,7 +9758,7 @@
         <v>29</v>
       </c>
       <c r="D334">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E334" t="s">
         <v>30</v>
@@ -9775,7 +9775,7 @@
         <v>29</v>
       </c>
       <c r="D335">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E335" t="s">
         <v>30</v>
@@ -9792,7 +9792,7 @@
         <v>29</v>
       </c>
       <c r="D336">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E336" t="s">
         <v>30</v>
@@ -9809,7 +9809,7 @@
         <v>29</v>
       </c>
       <c r="D337">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E337" t="s">
         <v>30</v>
@@ -9826,7 +9826,7 @@
         <v>29</v>
       </c>
       <c r="D338">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E338" t="s">
         <v>30</v>
@@ -9843,7 +9843,7 @@
         <v>29</v>
       </c>
       <c r="D339">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E339" t="s">
         <v>30</v>
@@ -9860,7 +9860,7 @@
         <v>29</v>
       </c>
       <c r="D340">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E340" t="s">
         <v>30</v>
@@ -9877,7 +9877,7 @@
         <v>29</v>
       </c>
       <c r="D341">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E341" t="s">
         <v>30</v>
@@ -9894,7 +9894,7 @@
         <v>29</v>
       </c>
       <c r="D342">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E342" t="s">
         <v>30</v>
@@ -9911,7 +9911,7 @@
         <v>29</v>
       </c>
       <c r="D343">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E343" t="s">
         <v>30</v>
@@ -9928,7 +9928,7 @@
         <v>29</v>
       </c>
       <c r="D344">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E344" t="s">
         <v>30</v>
@@ -9945,7 +9945,7 @@
         <v>29</v>
       </c>
       <c r="D345">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E345" t="s">
         <v>30</v>
@@ -9962,7 +9962,7 @@
         <v>29</v>
       </c>
       <c r="D346">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E346" t="s">
         <v>30</v>
@@ -9979,7 +9979,7 @@
         <v>29</v>
       </c>
       <c r="D347">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E347" t="s">
         <v>30</v>
@@ -9996,7 +9996,7 @@
         <v>29</v>
       </c>
       <c r="D348">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E348" t="s">
         <v>30</v>
@@ -10013,7 +10013,7 @@
         <v>29</v>
       </c>
       <c r="D349">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E349" t="s">
         <v>30</v>
@@ -10030,7 +10030,7 @@
         <v>29</v>
       </c>
       <c r="D350">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E350" t="s">
         <v>30</v>
@@ -10047,7 +10047,7 @@
         <v>29</v>
       </c>
       <c r="D351">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E351" t="s">
         <v>30</v>
@@ -10064,7 +10064,7 @@
         <v>29</v>
       </c>
       <c r="D352">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E352" t="s">
         <v>30</v>
@@ -10081,7 +10081,7 @@
         <v>29</v>
       </c>
       <c r="D353">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E353" t="s">
         <v>30</v>
@@ -10098,7 +10098,7 @@
         <v>29</v>
       </c>
       <c r="D354">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E354" t="s">
         <v>30</v>
@@ -10115,7 +10115,7 @@
         <v>29</v>
       </c>
       <c r="D355">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E355" t="s">
         <v>30</v>
@@ -10132,7 +10132,7 @@
         <v>29</v>
       </c>
       <c r="D356">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E356" t="s">
         <v>30</v>
@@ -10149,7 +10149,7 @@
         <v>29</v>
       </c>
       <c r="D357">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E357" t="s">
         <v>30</v>
@@ -10183,7 +10183,7 @@
         <v>29</v>
       </c>
       <c r="D359">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E359" t="s">
         <v>30</v>
@@ -10200,7 +10200,7 @@
         <v>29</v>
       </c>
       <c r="D360">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E360" t="s">
         <v>30</v>
@@ -10217,7 +10217,7 @@
         <v>29</v>
       </c>
       <c r="D361">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E361" t="s">
         <v>30</v>
@@ -10234,7 +10234,7 @@
         <v>29</v>
       </c>
       <c r="D362">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E362" t="s">
         <v>30</v>
@@ -10251,7 +10251,7 @@
         <v>29</v>
       </c>
       <c r="D363">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E363" t="s">
         <v>30</v>
@@ -10268,7 +10268,7 @@
         <v>29</v>
       </c>
       <c r="D364">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E364" t="s">
         <v>30</v>
@@ -10285,7 +10285,7 @@
         <v>29</v>
       </c>
       <c r="D365">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E365" t="s">
         <v>30</v>
@@ -10302,7 +10302,7 @@
         <v>29</v>
       </c>
       <c r="D366">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E366" t="s">
         <v>30</v>
@@ -10319,7 +10319,7 @@
         <v>29</v>
       </c>
       <c r="D367">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E367" t="s">
         <v>30</v>
@@ -10336,7 +10336,7 @@
         <v>29</v>
       </c>
       <c r="D368">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E368" t="s">
         <v>30</v>
@@ -10353,7 +10353,7 @@
         <v>29</v>
       </c>
       <c r="D369">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E369" t="s">
         <v>30</v>
@@ -10370,7 +10370,7 @@
         <v>29</v>
       </c>
       <c r="D370">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E370" t="s">
         <v>30</v>
@@ -10404,7 +10404,7 @@
         <v>29</v>
       </c>
       <c r="D372">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E372" t="s">
         <v>30</v>
@@ -10421,7 +10421,7 @@
         <v>29</v>
       </c>
       <c r="D373">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E373" t="s">
         <v>30</v>
@@ -10438,7 +10438,7 @@
         <v>29</v>
       </c>
       <c r="D374">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E374" t="s">
         <v>30</v>
@@ -10455,7 +10455,7 @@
         <v>29</v>
       </c>
       <c r="D375">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E375" t="s">
         <v>30</v>
@@ -10472,7 +10472,7 @@
         <v>29</v>
       </c>
       <c r="D376">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E376" t="s">
         <v>30</v>
@@ -10489,7 +10489,7 @@
         <v>29</v>
       </c>
       <c r="D377">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E377" t="s">
         <v>30</v>
@@ -10506,7 +10506,7 @@
         <v>29</v>
       </c>
       <c r="D378">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E378" t="s">
         <v>30</v>
@@ -10523,7 +10523,7 @@
         <v>29</v>
       </c>
       <c r="D379">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E379" t="s">
         <v>30</v>
@@ -10540,7 +10540,7 @@
         <v>29</v>
       </c>
       <c r="D380">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E380" t="s">
         <v>30</v>
@@ -10557,7 +10557,7 @@
         <v>29</v>
       </c>
       <c r="D381">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E381" t="s">
         <v>30</v>
@@ -10574,7 +10574,7 @@
         <v>29</v>
       </c>
       <c r="D382">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E382" t="s">
         <v>30</v>
@@ -10591,7 +10591,7 @@
         <v>29</v>
       </c>
       <c r="D383">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E383" t="s">
         <v>30</v>
@@ -10608,7 +10608,7 @@
         <v>29</v>
       </c>
       <c r="D384">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E384" t="s">
         <v>30</v>
@@ -10642,7 +10642,7 @@
         <v>29</v>
       </c>
       <c r="D386">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E386" t="s">
         <v>30</v>
@@ -10659,7 +10659,7 @@
         <v>29</v>
       </c>
       <c r="D387">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E387" t="s">
         <v>30</v>
@@ -10693,7 +10693,7 @@
         <v>29</v>
       </c>
       <c r="D389">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E389" t="s">
         <v>30</v>
@@ -10710,7 +10710,7 @@
         <v>29</v>
       </c>
       <c r="D390">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E390" t="s">
         <v>30</v>
@@ -10727,7 +10727,7 @@
         <v>29</v>
       </c>
       <c r="D391">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E391" t="s">
         <v>30</v>
@@ -10744,7 +10744,7 @@
         <v>29</v>
       </c>
       <c r="D392">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E392" t="s">
         <v>30</v>
@@ -10761,7 +10761,7 @@
         <v>29</v>
       </c>
       <c r="D393">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E393" t="s">
         <v>30</v>
@@ -10778,7 +10778,7 @@
         <v>29</v>
       </c>
       <c r="D394">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E394" t="s">
         <v>30</v>
@@ -10795,7 +10795,7 @@
         <v>29</v>
       </c>
       <c r="D395">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E395" t="s">
         <v>30</v>
@@ -10812,7 +10812,7 @@
         <v>29</v>
       </c>
       <c r="D396">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E396" t="s">
         <v>30</v>
@@ -10829,7 +10829,7 @@
         <v>29</v>
       </c>
       <c r="D397">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E397" t="s">
         <v>30</v>
@@ -10846,7 +10846,7 @@
         <v>29</v>
       </c>
       <c r="D398">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E398" t="s">
         <v>30</v>
@@ -10863,7 +10863,7 @@
         <v>29</v>
       </c>
       <c r="D399">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E399" t="s">
         <v>30</v>
@@ -10880,7 +10880,7 @@
         <v>29</v>
       </c>
       <c r="D400">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E400" t="s">
         <v>30</v>
@@ -10897,7 +10897,7 @@
         <v>29</v>
       </c>
       <c r="D401">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E401" t="s">
         <v>30</v>
@@ -10914,7 +10914,7 @@
         <v>29</v>
       </c>
       <c r="D402">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E402" t="s">
         <v>30</v>
@@ -10931,7 +10931,7 @@
         <v>29</v>
       </c>
       <c r="D403">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E403" t="s">
         <v>30</v>
@@ -10948,7 +10948,7 @@
         <v>29</v>
       </c>
       <c r="D404">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E404" t="s">
         <v>30</v>
@@ -10965,7 +10965,7 @@
         <v>29</v>
       </c>
       <c r="D405">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E405" t="s">
         <v>30</v>
@@ -10982,7 +10982,7 @@
         <v>29</v>
       </c>
       <c r="D406">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E406" t="s">
         <v>30</v>
@@ -10999,7 +10999,7 @@
         <v>29</v>
       </c>
       <c r="D407">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E407" t="s">
         <v>30</v>
@@ -11016,7 +11016,7 @@
         <v>29</v>
       </c>
       <c r="D408">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E408" t="s">
         <v>30</v>
@@ -11033,7 +11033,7 @@
         <v>29</v>
       </c>
       <c r="D409">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E409" t="s">
         <v>30</v>
@@ -11050,7 +11050,7 @@
         <v>29</v>
       </c>
       <c r="D410">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E410" t="s">
         <v>30</v>
@@ -11067,7 +11067,7 @@
         <v>29</v>
       </c>
       <c r="D411">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E411" t="s">
         <v>30</v>
@@ -11084,7 +11084,7 @@
         <v>29</v>
       </c>
       <c r="D412">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E412" t="s">
         <v>30</v>
@@ -11101,7 +11101,7 @@
         <v>29</v>
       </c>
       <c r="D413">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E413" t="s">
         <v>30</v>
@@ -11118,7 +11118,7 @@
         <v>29</v>
       </c>
       <c r="D414">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E414" t="s">
         <v>30</v>
@@ -11135,7 +11135,7 @@
         <v>29</v>
       </c>
       <c r="D415">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E415" t="s">
         <v>30</v>
@@ -11152,7 +11152,7 @@
         <v>29</v>
       </c>
       <c r="D416">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E416" t="s">
         <v>30</v>
@@ -11169,7 +11169,7 @@
         <v>29</v>
       </c>
       <c r="D417">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E417" t="s">
         <v>30</v>
@@ -11186,7 +11186,7 @@
         <v>29</v>
       </c>
       <c r="D418">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E418" t="s">
         <v>30</v>
@@ -11203,7 +11203,7 @@
         <v>29</v>
       </c>
       <c r="D419">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E419" t="s">
         <v>30</v>
@@ -11220,7 +11220,7 @@
         <v>29</v>
       </c>
       <c r="D420">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E420" t="s">
         <v>30</v>
@@ -11254,7 +11254,7 @@
         <v>29</v>
       </c>
       <c r="D422">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E422" t="s">
         <v>30</v>
@@ -11271,7 +11271,7 @@
         <v>29</v>
       </c>
       <c r="D423">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E423" t="s">
         <v>30</v>
@@ -11288,7 +11288,7 @@
         <v>29</v>
       </c>
       <c r="D424">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E424" t="s">
         <v>30</v>
@@ -11305,7 +11305,7 @@
         <v>29</v>
       </c>
       <c r="D425">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E425" t="s">
         <v>30</v>
@@ -11322,7 +11322,7 @@
         <v>29</v>
       </c>
       <c r="D426">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E426" t="s">
         <v>30</v>
@@ -11339,7 +11339,7 @@
         <v>29</v>
       </c>
       <c r="D427">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E427" t="s">
         <v>30</v>
@@ -11356,7 +11356,7 @@
         <v>29</v>
       </c>
       <c r="D428">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E428" t="s">
         <v>30</v>
@@ -11373,7 +11373,7 @@
         <v>29</v>
       </c>
       <c r="D429">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E429" t="s">
         <v>30</v>
@@ -11390,7 +11390,7 @@
         <v>29</v>
       </c>
       <c r="D430">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E430" t="s">
         <v>30</v>
@@ -11407,7 +11407,7 @@
         <v>29</v>
       </c>
       <c r="D431">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E431" t="s">
         <v>30</v>
@@ -11424,7 +11424,7 @@
         <v>29</v>
       </c>
       <c r="D432">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E432" t="s">
         <v>30</v>
@@ -11441,7 +11441,7 @@
         <v>29</v>
       </c>
       <c r="D433">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E433" t="s">
         <v>30</v>
@@ -11458,7 +11458,7 @@
         <v>29</v>
       </c>
       <c r="D434">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E434" t="s">
         <v>30</v>
@@ -11475,7 +11475,7 @@
         <v>29</v>
       </c>
       <c r="D435">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E435" t="s">
         <v>30</v>
@@ -11492,7 +11492,7 @@
         <v>29</v>
       </c>
       <c r="D436">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E436" t="s">
         <v>30</v>
@@ -11509,7 +11509,7 @@
         <v>29</v>
       </c>
       <c r="D437">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E437" t="s">
         <v>30</v>
@@ -11526,7 +11526,7 @@
         <v>29</v>
       </c>
       <c r="D438">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E438" t="s">
         <v>30</v>
@@ -11543,7 +11543,7 @@
         <v>29</v>
       </c>
       <c r="D439">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E439" t="s">
         <v>30</v>
@@ -11560,7 +11560,7 @@
         <v>29</v>
       </c>
       <c r="D440">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E440" t="s">
         <v>30</v>
@@ -11577,7 +11577,7 @@
         <v>29</v>
       </c>
       <c r="D441">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E441" t="s">
         <v>30</v>
@@ -11594,7 +11594,7 @@
         <v>29</v>
       </c>
       <c r="D442">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E442" t="s">
         <v>30</v>
@@ -11628,7 +11628,7 @@
         <v>29</v>
       </c>
       <c r="D444">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E444" t="s">
         <v>30</v>
@@ -11645,7 +11645,7 @@
         <v>29</v>
       </c>
       <c r="D445">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E445" t="s">
         <v>30</v>
@@ -11662,7 +11662,7 @@
         <v>29</v>
       </c>
       <c r="D446">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E446" t="s">
         <v>30</v>
@@ -11679,7 +11679,7 @@
         <v>29</v>
       </c>
       <c r="D447">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E447" t="s">
         <v>30</v>
@@ -11696,7 +11696,7 @@
         <v>29</v>
       </c>
       <c r="D448">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E448" t="s">
         <v>30</v>
@@ -11713,7 +11713,7 @@
         <v>29</v>
       </c>
       <c r="D449">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E449" t="s">
         <v>30</v>
@@ -11730,7 +11730,7 @@
         <v>29</v>
       </c>
       <c r="D450">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E450" t="s">
         <v>30</v>
@@ -11747,7 +11747,7 @@
         <v>29</v>
       </c>
       <c r="D451">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E451" t="s">
         <v>30</v>
@@ -11764,7 +11764,7 @@
         <v>29</v>
       </c>
       <c r="D452">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E452" t="s">
         <v>30</v>
@@ -11781,7 +11781,7 @@
         <v>29</v>
       </c>
       <c r="D453">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E453" t="s">
         <v>30</v>
@@ -11798,7 +11798,7 @@
         <v>29</v>
       </c>
       <c r="D454">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E454" t="s">
         <v>30</v>
@@ -11815,7 +11815,7 @@
         <v>29</v>
       </c>
       <c r="D455">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E455" t="s">
         <v>30</v>
@@ -11832,7 +11832,7 @@
         <v>29</v>
       </c>
       <c r="D456">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E456" t="s">
         <v>30</v>
@@ -11849,7 +11849,7 @@
         <v>29</v>
       </c>
       <c r="D457">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E457" t="s">
         <v>30</v>
@@ -11866,7 +11866,7 @@
         <v>29</v>
       </c>
       <c r="D458">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E458" t="s">
         <v>30</v>
@@ -11883,7 +11883,7 @@
         <v>29</v>
       </c>
       <c r="D459">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E459" t="s">
         <v>30</v>
@@ -11900,7 +11900,7 @@
         <v>29</v>
       </c>
       <c r="D460">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E460" t="s">
         <v>30</v>
@@ -11917,7 +11917,7 @@
         <v>29</v>
       </c>
       <c r="D461">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E461" t="s">
         <v>30</v>
@@ -11934,7 +11934,7 @@
         <v>29</v>
       </c>
       <c r="D462">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E462" t="s">
         <v>30</v>
@@ -11951,7 +11951,7 @@
         <v>29</v>
       </c>
       <c r="D463">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E463" t="s">
         <v>30</v>
@@ -11968,7 +11968,7 @@
         <v>29</v>
       </c>
       <c r="D464">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E464" t="s">
         <v>30</v>
@@ -11985,7 +11985,7 @@
         <v>29</v>
       </c>
       <c r="D465">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E465" t="s">
         <v>30</v>
@@ -12002,7 +12002,7 @@
         <v>29</v>
       </c>
       <c r="D466">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E466" t="s">
         <v>30</v>
@@ -12019,7 +12019,7 @@
         <v>29</v>
       </c>
       <c r="D467">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E467" t="s">
         <v>30</v>
@@ -12036,7 +12036,7 @@
         <v>29</v>
       </c>
       <c r="D468">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E468" t="s">
         <v>30</v>
@@ -12053,7 +12053,7 @@
         <v>29</v>
       </c>
       <c r="D469">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E469" t="s">
         <v>30</v>
@@ -12070,7 +12070,7 @@
         <v>29</v>
       </c>
       <c r="D470">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E470" t="s">
         <v>30</v>
@@ -12087,7 +12087,7 @@
         <v>29</v>
       </c>
       <c r="D471">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E471" t="s">
         <v>30</v>
@@ -12104,7 +12104,7 @@
         <v>29</v>
       </c>
       <c r="D472">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E472" t="s">
         <v>30</v>
@@ -12121,7 +12121,7 @@
         <v>29</v>
       </c>
       <c r="D473">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E473" t="s">
         <v>30</v>
@@ -12138,7 +12138,7 @@
         <v>29</v>
       </c>
       <c r="D474">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E474" t="s">
         <v>30</v>
@@ -12155,7 +12155,7 @@
         <v>29</v>
       </c>
       <c r="D475">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E475" t="s">
         <v>30</v>
@@ -12172,7 +12172,7 @@
         <v>29</v>
       </c>
       <c r="D476">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E476" t="s">
         <v>30</v>
@@ -12189,7 +12189,7 @@
         <v>29</v>
       </c>
       <c r="D477">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E477" t="s">
         <v>30</v>
@@ -12206,7 +12206,7 @@
         <v>29</v>
       </c>
       <c r="D478">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E478" t="s">
         <v>30</v>
@@ -12223,7 +12223,7 @@
         <v>29</v>
       </c>
       <c r="D479">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E479" t="s">
         <v>30</v>
@@ -12240,7 +12240,7 @@
         <v>29</v>
       </c>
       <c r="D480">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E480" t="s">
         <v>30</v>
@@ -12257,7 +12257,7 @@
         <v>29</v>
       </c>
       <c r="D481">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E481" t="s">
         <v>30</v>
@@ -12274,7 +12274,7 @@
         <v>29</v>
       </c>
       <c r="D482">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E482" t="s">
         <v>30</v>
@@ -12291,7 +12291,7 @@
         <v>29</v>
       </c>
       <c r="D483">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E483" t="s">
         <v>30</v>
@@ -12308,7 +12308,7 @@
         <v>29</v>
       </c>
       <c r="D484">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E484" t="s">
         <v>30</v>
@@ -12325,7 +12325,7 @@
         <v>29</v>
       </c>
       <c r="D485">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E485" t="s">
         <v>30</v>
@@ -12342,7 +12342,7 @@
         <v>29</v>
       </c>
       <c r="D486">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E486" t="s">
         <v>30</v>
@@ -12359,7 +12359,7 @@
         <v>29</v>
       </c>
       <c r="D487">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E487" t="s">
         <v>30</v>
@@ -12376,7 +12376,7 @@
         <v>29</v>
       </c>
       <c r="D488">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E488" t="s">
         <v>30</v>
@@ -12393,7 +12393,7 @@
         <v>29</v>
       </c>
       <c r="D489">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E489" t="s">
         <v>30</v>
@@ -12410,7 +12410,7 @@
         <v>29</v>
       </c>
       <c r="D490">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E490" t="s">
         <v>30</v>
@@ -12427,7 +12427,7 @@
         <v>29</v>
       </c>
       <c r="D491">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E491" t="s">
         <v>30</v>
@@ -12444,7 +12444,7 @@
         <v>29</v>
       </c>
       <c r="D492">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E492" t="s">
         <v>30</v>
@@ -12461,7 +12461,7 @@
         <v>29</v>
       </c>
       <c r="D493">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E493" t="s">
         <v>30</v>
@@ -12478,7 +12478,7 @@
         <v>29</v>
       </c>
       <c r="D494">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E494" t="s">
         <v>30</v>
@@ -12495,7 +12495,7 @@
         <v>29</v>
       </c>
       <c r="D495">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E495" t="s">
         <v>30</v>
@@ -12512,7 +12512,7 @@
         <v>29</v>
       </c>
       <c r="D496">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E496" t="s">
         <v>30</v>
@@ -12546,7 +12546,7 @@
         <v>29</v>
       </c>
       <c r="D498">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E498" t="s">
         <v>30</v>
@@ -12563,7 +12563,7 @@
         <v>29</v>
       </c>
       <c r="D499">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E499" t="s">
         <v>30</v>
@@ -12597,7 +12597,7 @@
         <v>29</v>
       </c>
       <c r="D501">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E501" t="s">
         <v>30</v>
@@ -12614,7 +12614,7 @@
         <v>29</v>
       </c>
       <c r="D502">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E502" t="s">
         <v>30</v>
@@ -12631,7 +12631,7 @@
         <v>29</v>
       </c>
       <c r="D503">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E503" t="s">
         <v>30</v>
@@ -12648,7 +12648,7 @@
         <v>29</v>
       </c>
       <c r="D504">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E504" t="s">
         <v>30</v>
@@ -12665,7 +12665,7 @@
         <v>29</v>
       </c>
       <c r="D505">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E505" t="s">
         <v>30</v>
@@ -12699,7 +12699,7 @@
         <v>29</v>
       </c>
       <c r="D507">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E507" t="s">
         <v>30</v>
@@ -12716,7 +12716,7 @@
         <v>29</v>
       </c>
       <c r="D508">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E508" t="s">
         <v>30</v>
@@ -12733,7 +12733,7 @@
         <v>29</v>
       </c>
       <c r="D509">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E509" t="s">
         <v>30</v>
@@ -12767,7 +12767,7 @@
         <v>29</v>
       </c>
       <c r="D511">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E511" t="s">
         <v>30</v>
@@ -12784,7 +12784,7 @@
         <v>29</v>
       </c>
       <c r="D512">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E512" t="s">
         <v>30</v>
@@ -12801,7 +12801,7 @@
         <v>29</v>
       </c>
       <c r="D513">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E513" t="s">
         <v>30</v>
@@ -12818,7 +12818,7 @@
         <v>29</v>
       </c>
       <c r="D514">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E514" t="s">
         <v>30</v>
@@ -12835,7 +12835,7 @@
         <v>29</v>
       </c>
       <c r="D515">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E515" t="s">
         <v>30</v>
@@ -12852,7 +12852,7 @@
         <v>29</v>
       </c>
       <c r="D516">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E516" t="s">
         <v>30</v>
@@ -12869,7 +12869,7 @@
         <v>29</v>
       </c>
       <c r="D517">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E517" t="s">
         <v>30</v>
@@ -12886,7 +12886,7 @@
         <v>29</v>
       </c>
       <c r="D518">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E518" t="s">
         <v>30</v>
@@ -12903,7 +12903,7 @@
         <v>29</v>
       </c>
       <c r="D519">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E519" t="s">
         <v>30</v>
@@ -12920,7 +12920,7 @@
         <v>29</v>
       </c>
       <c r="D520">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E520" t="s">
         <v>30</v>
@@ -12937,7 +12937,7 @@
         <v>29</v>
       </c>
       <c r="D521">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E521" t="s">
         <v>30</v>
@@ -12954,7 +12954,7 @@
         <v>29</v>
       </c>
       <c r="D522">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E522" t="s">
         <v>30</v>
@@ -12971,7 +12971,7 @@
         <v>29</v>
       </c>
       <c r="D523">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E523" t="s">
         <v>30</v>
@@ -12988,7 +12988,7 @@
         <v>29</v>
       </c>
       <c r="D524">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E524" t="s">
         <v>30</v>
@@ -13005,7 +13005,7 @@
         <v>29</v>
       </c>
       <c r="D525">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E525" t="s">
         <v>30</v>
@@ -13022,7 +13022,7 @@
         <v>29</v>
       </c>
       <c r="D526">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E526" t="s">
         <v>30</v>
@@ -13039,7 +13039,7 @@
         <v>29</v>
       </c>
       <c r="D527">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E527" t="s">
         <v>30</v>
@@ -13056,7 +13056,7 @@
         <v>29</v>
       </c>
       <c r="D528">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E528" t="s">
         <v>30</v>
@@ -13073,7 +13073,7 @@
         <v>29</v>
       </c>
       <c r="D529">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E529" t="s">
         <v>30</v>
@@ -13090,7 +13090,7 @@
         <v>29</v>
       </c>
       <c r="D530">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E530" t="s">
         <v>30</v>
@@ -13107,7 +13107,7 @@
         <v>29</v>
       </c>
       <c r="D531">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E531" t="s">
         <v>30</v>
@@ -13124,7 +13124,7 @@
         <v>29</v>
       </c>
       <c r="D532">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E532" t="s">
         <v>30</v>
@@ -13141,7 +13141,7 @@
         <v>29</v>
       </c>
       <c r="D533">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E533" t="s">
         <v>30</v>
@@ -13158,7 +13158,7 @@
         <v>29</v>
       </c>
       <c r="D534">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E534" t="s">
         <v>30</v>
@@ -13175,7 +13175,7 @@
         <v>29</v>
       </c>
       <c r="D535">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E535" t="s">
         <v>30</v>
@@ -13192,7 +13192,7 @@
         <v>29</v>
       </c>
       <c r="D536">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E536" t="s">
         <v>30</v>
@@ -13209,7 +13209,7 @@
         <v>29</v>
       </c>
       <c r="D537">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E537" t="s">
         <v>30</v>
@@ -13226,7 +13226,7 @@
         <v>29</v>
       </c>
       <c r="D538">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E538" t="s">
         <v>30</v>
@@ -13243,7 +13243,7 @@
         <v>29</v>
       </c>
       <c r="D539">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E539" t="s">
         <v>30</v>
@@ -13260,7 +13260,7 @@
         <v>29</v>
       </c>
       <c r="D540">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E540" t="s">
         <v>30</v>
@@ -13277,7 +13277,7 @@
         <v>29</v>
       </c>
       <c r="D541">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E541" t="s">
         <v>30</v>
@@ -13294,7 +13294,7 @@
         <v>29</v>
       </c>
       <c r="D542">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E542" t="s">
         <v>30</v>
@@ -13311,7 +13311,7 @@
         <v>29</v>
       </c>
       <c r="D543">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E543" t="s">
         <v>30</v>
@@ -13328,7 +13328,7 @@
         <v>29</v>
       </c>
       <c r="D544">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E544" t="s">
         <v>30</v>
@@ -13345,7 +13345,7 @@
         <v>29</v>
       </c>
       <c r="D545">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E545" t="s">
         <v>30</v>
@@ -13362,7 +13362,7 @@
         <v>29</v>
       </c>
       <c r="D546">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E546" t="s">
         <v>30</v>
@@ -13379,7 +13379,7 @@
         <v>29</v>
       </c>
       <c r="D547">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E547" t="s">
         <v>30</v>
@@ -13396,7 +13396,7 @@
         <v>29</v>
       </c>
       <c r="D548">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E548" t="s">
         <v>30</v>
@@ -13413,7 +13413,7 @@
         <v>29</v>
       </c>
       <c r="D549">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E549" t="s">
         <v>30</v>
@@ -13430,7 +13430,7 @@
         <v>29</v>
       </c>
       <c r="D550">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E550" t="s">
         <v>30</v>
@@ -13447,7 +13447,7 @@
         <v>29</v>
       </c>
       <c r="D551">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E551" t="s">
         <v>30</v>
@@ -13464,7 +13464,7 @@
         <v>29</v>
       </c>
       <c r="D552">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E552" t="s">
         <v>30</v>
@@ -13481,7 +13481,7 @@
         <v>29</v>
       </c>
       <c r="D553">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E553" t="s">
         <v>30</v>
@@ -13498,7 +13498,7 @@
         <v>29</v>
       </c>
       <c r="D554">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E554" t="s">
         <v>30</v>
@@ -13515,7 +13515,7 @@
         <v>29</v>
       </c>
       <c r="D555">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E555" t="s">
         <v>30</v>
@@ -13532,7 +13532,7 @@
         <v>29</v>
       </c>
       <c r="D556">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E556" t="s">
         <v>30</v>
@@ -13549,7 +13549,7 @@
         <v>29</v>
       </c>
       <c r="D557">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E557" t="s">
         <v>30</v>
@@ -13566,7 +13566,7 @@
         <v>29</v>
       </c>
       <c r="D558">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E558" t="s">
         <v>30</v>
@@ -13583,7 +13583,7 @@
         <v>29</v>
       </c>
       <c r="D559">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E559" t="s">
         <v>30</v>
@@ -13617,7 +13617,7 @@
         <v>29</v>
       </c>
       <c r="D561">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E561" t="s">
         <v>30</v>
@@ -13634,7 +13634,7 @@
         <v>29</v>
       </c>
       <c r="D562">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E562" t="s">
         <v>30</v>
@@ -13651,7 +13651,7 @@
         <v>29</v>
       </c>
       <c r="D563">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E563" t="s">
         <v>30</v>
@@ -13668,7 +13668,7 @@
         <v>29</v>
       </c>
       <c r="D564">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E564" t="s">
         <v>30</v>
@@ -13685,7 +13685,7 @@
         <v>29</v>
       </c>
       <c r="D565">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E565" t="s">
         <v>30</v>
@@ -13702,7 +13702,7 @@
         <v>29</v>
       </c>
       <c r="D566">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E566" t="s">
         <v>30</v>
@@ -13719,7 +13719,7 @@
         <v>29</v>
       </c>
       <c r="D567">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E567" t="s">
         <v>30</v>
@@ -13736,7 +13736,7 @@
         <v>29</v>
       </c>
       <c r="D568">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E568" t="s">
         <v>30</v>
@@ -13770,7 +13770,7 @@
         <v>29</v>
       </c>
       <c r="D570">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E570" t="s">
         <v>30</v>
@@ -13787,7 +13787,7 @@
         <v>29</v>
       </c>
       <c r="D571">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E571" t="s">
         <v>30</v>
@@ -13804,7 +13804,7 @@
         <v>29</v>
       </c>
       <c r="D572">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E572" t="s">
         <v>30</v>
@@ -13821,7 +13821,7 @@
         <v>29</v>
       </c>
       <c r="D573">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E573" t="s">
         <v>30</v>
@@ -13838,7 +13838,7 @@
         <v>29</v>
       </c>
       <c r="D574">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E574" t="s">
         <v>30</v>
@@ -13855,7 +13855,7 @@
         <v>29</v>
       </c>
       <c r="D575">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E575" t="s">
         <v>30</v>
@@ -13872,7 +13872,7 @@
         <v>29</v>
       </c>
       <c r="D576">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E576" t="s">
         <v>30</v>
@@ -13889,7 +13889,7 @@
         <v>29</v>
       </c>
       <c r="D577">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E577" t="s">
         <v>30</v>
@@ -13906,7 +13906,7 @@
         <v>29</v>
       </c>
       <c r="D578">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E578" t="s">
         <v>30</v>
@@ -13923,7 +13923,7 @@
         <v>29</v>
       </c>
       <c r="D579">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E579" t="s">
         <v>30</v>
@@ -13940,7 +13940,7 @@
         <v>29</v>
       </c>
       <c r="D580">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E580" t="s">
         <v>30</v>
@@ -13957,7 +13957,7 @@
         <v>29</v>
       </c>
       <c r="D581">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E581" t="s">
         <v>30</v>
@@ -13974,7 +13974,7 @@
         <v>29</v>
       </c>
       <c r="D582">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E582" t="s">
         <v>30</v>
@@ -13991,7 +13991,7 @@
         <v>29</v>
       </c>
       <c r="D583">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E583" t="s">
         <v>30</v>
@@ -14008,7 +14008,7 @@
         <v>29</v>
       </c>
       <c r="D584">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E584" t="s">
         <v>30</v>
@@ -14025,7 +14025,7 @@
         <v>29</v>
       </c>
       <c r="D585">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E585" t="s">
         <v>30</v>
@@ -14042,7 +14042,7 @@
         <v>29</v>
       </c>
       <c r="D586">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E586" t="s">
         <v>30</v>
@@ -14059,7 +14059,7 @@
         <v>29</v>
       </c>
       <c r="D587">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E587" t="s">
         <v>30</v>
@@ -14076,7 +14076,7 @@
         <v>29</v>
       </c>
       <c r="D588">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E588" t="s">
         <v>30</v>
@@ -14093,7 +14093,7 @@
         <v>29</v>
       </c>
       <c r="D589">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E589" t="s">
         <v>30</v>
@@ -14110,7 +14110,7 @@
         <v>29</v>
       </c>
       <c r="D590">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E590" t="s">
         <v>30</v>
@@ -14127,7 +14127,7 @@
         <v>29</v>
       </c>
       <c r="D591">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E591" t="s">
         <v>30</v>
@@ -14144,7 +14144,7 @@
         <v>29</v>
       </c>
       <c r="D592">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E592" t="s">
         <v>30</v>
@@ -14161,7 +14161,7 @@
         <v>29</v>
       </c>
       <c r="D593">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E593" t="s">
         <v>30</v>
@@ -14178,7 +14178,7 @@
         <v>29</v>
       </c>
       <c r="D594">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E594" t="s">
         <v>30</v>
@@ -14195,7 +14195,7 @@
         <v>29</v>
       </c>
       <c r="D595">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E595" t="s">
         <v>30</v>
@@ -14212,7 +14212,7 @@
         <v>29</v>
       </c>
       <c r="D596">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E596" t="s">
         <v>30</v>
@@ -14229,7 +14229,7 @@
         <v>29</v>
       </c>
       <c r="D597">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E597" t="s">
         <v>30</v>
@@ -14246,7 +14246,7 @@
         <v>29</v>
       </c>
       <c r="D598">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E598" t="s">
         <v>30</v>
@@ -14263,7 +14263,7 @@
         <v>29</v>
       </c>
       <c r="D599">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E599" t="s">
         <v>30</v>
@@ -14280,7 +14280,7 @@
         <v>29</v>
       </c>
       <c r="D600">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E600" t="s">
         <v>30</v>
@@ -14297,7 +14297,7 @@
         <v>29</v>
       </c>
       <c r="D601">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E601" t="s">
         <v>30</v>
@@ -14314,7 +14314,7 @@
         <v>29</v>
       </c>
       <c r="D602">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E602" t="s">
         <v>30</v>
@@ -14331,7 +14331,7 @@
         <v>29</v>
       </c>
       <c r="D603">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E603" t="s">
         <v>30</v>
@@ -14348,7 +14348,7 @@
         <v>29</v>
       </c>
       <c r="D604">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E604" t="s">
         <v>30</v>
@@ -14365,7 +14365,7 @@
         <v>29</v>
       </c>
       <c r="D605">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E605" t="s">
         <v>30</v>
@@ -14382,7 +14382,7 @@
         <v>29</v>
       </c>
       <c r="D606">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E606" t="s">
         <v>30</v>
@@ -14399,7 +14399,7 @@
         <v>29</v>
       </c>
       <c r="D607">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E607" t="s">
         <v>30</v>
@@ -14416,7 +14416,7 @@
         <v>29</v>
       </c>
       <c r="D608">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E608" t="s">
         <v>30</v>
@@ -14433,7 +14433,7 @@
         <v>29</v>
       </c>
       <c r="D609">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E609" t="s">
         <v>30</v>
@@ -14450,7 +14450,7 @@
         <v>29</v>
       </c>
       <c r="D610">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E610" t="s">
         <v>30</v>
@@ -14467,7 +14467,7 @@
         <v>29</v>
       </c>
       <c r="D611">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E611" t="s">
         <v>30</v>
@@ -14484,7 +14484,7 @@
         <v>29</v>
       </c>
       <c r="D612">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E612" t="s">
         <v>30</v>
@@ -14501,7 +14501,7 @@
         <v>29</v>
       </c>
       <c r="D613">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E613" t="s">
         <v>30</v>
@@ -14518,7 +14518,7 @@
         <v>29</v>
       </c>
       <c r="D614">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E614" t="s">
         <v>30</v>
@@ -14535,7 +14535,7 @@
         <v>29</v>
       </c>
       <c r="D615">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E615" t="s">
         <v>30</v>
@@ -14552,7 +14552,7 @@
         <v>29</v>
       </c>
       <c r="D616">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E616" t="s">
         <v>30</v>
@@ -14569,7 +14569,7 @@
         <v>29</v>
       </c>
       <c r="D617">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E617" t="s">
         <v>30</v>
@@ -14586,7 +14586,7 @@
         <v>29</v>
       </c>
       <c r="D618">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E618" t="s">
         <v>30</v>
@@ -14603,7 +14603,7 @@
         <v>29</v>
       </c>
       <c r="D619">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E619" t="s">
         <v>30</v>
@@ -14620,7 +14620,7 @@
         <v>29</v>
       </c>
       <c r="D620">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E620" t="s">
         <v>30</v>
@@ -14637,7 +14637,7 @@
         <v>29</v>
       </c>
       <c r="D621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E621" t="s">
         <v>30</v>
@@ -14654,7 +14654,7 @@
         <v>29</v>
       </c>
       <c r="D622">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E622" t="s">
         <v>30</v>
@@ -14688,7 +14688,7 @@
         <v>29</v>
       </c>
       <c r="D624">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E624" t="s">
         <v>30</v>
@@ -14705,7 +14705,7 @@
         <v>29</v>
       </c>
       <c r="D625">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E625" t="s">
         <v>30</v>
@@ -14722,7 +14722,7 @@
         <v>29</v>
       </c>
       <c r="D626">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E626" t="s">
         <v>30</v>
@@ -14756,7 +14756,7 @@
         <v>29</v>
       </c>
       <c r="D628">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E628" t="s">
         <v>30</v>
@@ -14773,7 +14773,7 @@
         <v>29</v>
       </c>
       <c r="D629">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E629" t="s">
         <v>30</v>
@@ -14790,7 +14790,7 @@
         <v>29</v>
       </c>
       <c r="D630">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E630" t="s">
         <v>30</v>
@@ -14807,7 +14807,7 @@
         <v>29</v>
       </c>
       <c r="D631">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E631" t="s">
         <v>30</v>
@@ -14824,7 +14824,7 @@
         <v>29</v>
       </c>
       <c r="D632">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E632" t="s">
         <v>30</v>
@@ -14841,7 +14841,7 @@
         <v>29</v>
       </c>
       <c r="D633">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E633" t="s">
         <v>30</v>
@@ -14858,7 +14858,7 @@
         <v>29</v>
       </c>
       <c r="D634">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E634" t="s">
         <v>30</v>
@@ -14875,7 +14875,7 @@
         <v>29</v>
       </c>
       <c r="D635">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E635" t="s">
         <v>30</v>
@@ -14892,7 +14892,7 @@
         <v>29</v>
       </c>
       <c r="D636">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E636" t="s">
         <v>30</v>
@@ -14909,7 +14909,7 @@
         <v>29</v>
       </c>
       <c r="D637">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E637" t="s">
         <v>30</v>
@@ -14926,7 +14926,7 @@
         <v>29</v>
       </c>
       <c r="D638">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E638" t="s">
         <v>30</v>
@@ -14943,7 +14943,7 @@
         <v>29</v>
       </c>
       <c r="D639">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E639" t="s">
         <v>30</v>
@@ -14960,7 +14960,7 @@
         <v>29</v>
       </c>
       <c r="D640">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E640" t="s">
         <v>30</v>
@@ -14977,7 +14977,7 @@
         <v>29</v>
       </c>
       <c r="D641">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E641" t="s">
         <v>30</v>
@@ -14994,7 +14994,7 @@
         <v>29</v>
       </c>
       <c r="D642">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E642" t="s">
         <v>30</v>
@@ -15011,7 +15011,7 @@
         <v>29</v>
       </c>
       <c r="D643">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E643" t="s">
         <v>30</v>
@@ -15028,7 +15028,7 @@
         <v>29</v>
       </c>
       <c r="D644">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E644" t="s">
         <v>30</v>
@@ -15045,7 +15045,7 @@
         <v>29</v>
       </c>
       <c r="D645">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E645" t="s">
         <v>30</v>
@@ -15062,7 +15062,7 @@
         <v>29</v>
       </c>
       <c r="D646">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E646" t="s">
         <v>30</v>
@@ -15079,7 +15079,7 @@
         <v>29</v>
       </c>
       <c r="D647">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E647" t="s">
         <v>30</v>
@@ -15096,7 +15096,7 @@
         <v>29</v>
       </c>
       <c r="D648">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E648" t="s">
         <v>30</v>
@@ -15113,7 +15113,7 @@
         <v>29</v>
       </c>
       <c r="D649">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E649" t="s">
         <v>30</v>
@@ -15130,7 +15130,7 @@
         <v>29</v>
       </c>
       <c r="D650">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E650" t="s">
         <v>30</v>
@@ -15147,7 +15147,7 @@
         <v>29</v>
       </c>
       <c r="D651">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E651" t="s">
         <v>30</v>
@@ -15164,7 +15164,7 @@
         <v>29</v>
       </c>
       <c r="D652">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E652" t="s">
         <v>30</v>
@@ -15181,7 +15181,7 @@
         <v>29</v>
       </c>
       <c r="D653">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E653" t="s">
         <v>30</v>
@@ -15198,7 +15198,7 @@
         <v>29</v>
       </c>
       <c r="D654">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E654" t="s">
         <v>30</v>
@@ -15215,7 +15215,7 @@
         <v>29</v>
       </c>
       <c r="D655">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E655" t="s">
         <v>30</v>
@@ -15232,7 +15232,7 @@
         <v>29</v>
       </c>
       <c r="D656">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E656" t="s">
         <v>30</v>
@@ -15249,7 +15249,7 @@
         <v>29</v>
       </c>
       <c r="D657">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E657" t="s">
         <v>30</v>
@@ -15266,7 +15266,7 @@
         <v>29</v>
       </c>
       <c r="D658">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E658" t="s">
         <v>30</v>
@@ -15283,7 +15283,7 @@
         <v>29</v>
       </c>
       <c r="D659">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E659" t="s">
         <v>30</v>
@@ -15300,7 +15300,7 @@
         <v>29</v>
       </c>
       <c r="D660">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E660" t="s">
         <v>30</v>
@@ -15317,7 +15317,7 @@
         <v>29</v>
       </c>
       <c r="D661">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E661" t="s">
         <v>30</v>
@@ -15334,7 +15334,7 @@
         <v>29</v>
       </c>
       <c r="D662">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E662" t="s">
         <v>30</v>
@@ -15351,7 +15351,7 @@
         <v>29</v>
       </c>
       <c r="D663">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E663" t="s">
         <v>30</v>
@@ -15385,7 +15385,7 @@
         <v>29</v>
       </c>
       <c r="D665">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E665" t="s">
         <v>30</v>
@@ -15402,7 +15402,7 @@
         <v>29</v>
       </c>
       <c r="D666">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E666" t="s">
         <v>30</v>
@@ -15419,7 +15419,7 @@
         <v>29</v>
       </c>
       <c r="D667">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E667" t="s">
         <v>30</v>
@@ -15436,7 +15436,7 @@
         <v>29</v>
       </c>
       <c r="D668">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E668" t="s">
         <v>30</v>
@@ -15453,7 +15453,7 @@
         <v>29</v>
       </c>
       <c r="D669">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E669" t="s">
         <v>30</v>
@@ -15470,7 +15470,7 @@
         <v>29</v>
       </c>
       <c r="D670">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E670" t="s">
         <v>30</v>
@@ -15487,7 +15487,7 @@
         <v>29</v>
       </c>
       <c r="D671">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E671" t="s">
         <v>30</v>
@@ -15521,7 +15521,7 @@
         <v>29</v>
       </c>
       <c r="D673">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E673" t="s">
         <v>30</v>
@@ -15538,7 +15538,7 @@
         <v>29</v>
       </c>
       <c r="D674">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E674" t="s">
         <v>30</v>
@@ -15555,7 +15555,7 @@
         <v>29</v>
       </c>
       <c r="D675">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E675" t="s">
         <v>30</v>
@@ -15572,7 +15572,7 @@
         <v>29</v>
       </c>
       <c r="D676">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E676" t="s">
         <v>30</v>
@@ -15589,7 +15589,7 @@
         <v>29</v>
       </c>
       <c r="D677">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E677" t="s">
         <v>30</v>
@@ -15606,7 +15606,7 @@
         <v>29</v>
       </c>
       <c r="D678">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E678" t="s">
         <v>30</v>
@@ -15623,7 +15623,7 @@
         <v>29</v>
       </c>
       <c r="D679">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E679" t="s">
         <v>30</v>
@@ -15640,7 +15640,7 @@
         <v>29</v>
       </c>
       <c r="D680">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E680" t="s">
         <v>30</v>
@@ -15657,7 +15657,7 @@
         <v>29</v>
       </c>
       <c r="D681">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E681" t="s">
         <v>30</v>
@@ -15674,7 +15674,7 @@
         <v>29</v>
       </c>
       <c r="D682">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E682" t="s">
         <v>30</v>
@@ -15691,7 +15691,7 @@
         <v>29</v>
       </c>
       <c r="D683">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E683" t="s">
         <v>30</v>
@@ -15708,7 +15708,7 @@
         <v>29</v>
       </c>
       <c r="D684">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E684" t="s">
         <v>30</v>
@@ -15725,7 +15725,7 @@
         <v>29</v>
       </c>
       <c r="D685">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E685" t="s">
         <v>30</v>
@@ -15742,7 +15742,7 @@
         <v>29</v>
       </c>
       <c r="D686">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E686" t="s">
         <v>30</v>
@@ -15759,7 +15759,7 @@
         <v>29</v>
       </c>
       <c r="D687">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E687" t="s">
         <v>30</v>
@@ -15776,7 +15776,7 @@
         <v>29</v>
       </c>
       <c r="D688">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E688" t="s">
         <v>30</v>
@@ -15793,7 +15793,7 @@
         <v>29</v>
       </c>
       <c r="D689">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E689" t="s">
         <v>30</v>
@@ -15810,7 +15810,7 @@
         <v>29</v>
       </c>
       <c r="D690">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E690" t="s">
         <v>30</v>
@@ -15827,7 +15827,7 @@
         <v>29</v>
       </c>
       <c r="D691">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E691" t="s">
         <v>30</v>
@@ -15844,7 +15844,7 @@
         <v>29</v>
       </c>
       <c r="D692">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E692" t="s">
         <v>30</v>
@@ -15861,7 +15861,7 @@
         <v>29</v>
       </c>
       <c r="D693">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E693" t="s">
         <v>30</v>
@@ -15878,7 +15878,7 @@
         <v>29</v>
       </c>
       <c r="D694">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E694" t="s">
         <v>30</v>
@@ -15895,7 +15895,7 @@
         <v>29</v>
       </c>
       <c r="D695">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E695" t="s">
         <v>30</v>
@@ -15912,7 +15912,7 @@
         <v>29</v>
       </c>
       <c r="D696">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E696" t="s">
         <v>30</v>
@@ -15929,7 +15929,7 @@
         <v>29</v>
       </c>
       <c r="D697">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E697" t="s">
         <v>30</v>
@@ -15946,7 +15946,7 @@
         <v>29</v>
       </c>
       <c r="D698">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E698" t="s">
         <v>30</v>
@@ -15963,7 +15963,7 @@
         <v>29</v>
       </c>
       <c r="D699">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E699" t="s">
         <v>30</v>
@@ -15980,7 +15980,7 @@
         <v>29</v>
       </c>
       <c r="D700">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E700" t="s">
         <v>30</v>
@@ -15997,7 +15997,7 @@
         <v>29</v>
       </c>
       <c r="D701">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E701" t="s">
         <v>30</v>
@@ -16014,7 +16014,7 @@
         <v>29</v>
       </c>
       <c r="D702">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E702" t="s">
         <v>30</v>
@@ -16031,7 +16031,7 @@
         <v>29</v>
       </c>
       <c r="D703">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E703" t="s">
         <v>30</v>
@@ -16048,7 +16048,7 @@
         <v>29</v>
       </c>
       <c r="D704">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E704" t="s">
         <v>30</v>
@@ -16065,7 +16065,7 @@
         <v>29</v>
       </c>
       <c r="D705">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E705" t="s">
         <v>30</v>
@@ -16082,7 +16082,7 @@
         <v>29</v>
       </c>
       <c r="D706">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E706" t="s">
         <v>30</v>
@@ -16099,7 +16099,7 @@
         <v>29</v>
       </c>
       <c r="D707">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E707" t="s">
         <v>30</v>
@@ -16116,7 +16116,7 @@
         <v>29</v>
       </c>
       <c r="D708">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E708" t="s">
         <v>30</v>
@@ -16133,7 +16133,7 @@
         <v>29</v>
       </c>
       <c r="D709">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E709" t="s">
         <v>30</v>
@@ -16150,7 +16150,7 @@
         <v>29</v>
       </c>
       <c r="D710">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E710" t="s">
         <v>30</v>
@@ -16167,7 +16167,7 @@
         <v>29</v>
       </c>
       <c r="D711">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E711" t="s">
         <v>30</v>
@@ -16184,7 +16184,7 @@
         <v>29</v>
       </c>
       <c r="D712">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E712" t="s">
         <v>30</v>
@@ -16201,7 +16201,7 @@
         <v>29</v>
       </c>
       <c r="D713">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E713" t="s">
         <v>30</v>
@@ -16218,7 +16218,7 @@
         <v>29</v>
       </c>
       <c r="D714">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E714" t="s">
         <v>30</v>
@@ -16235,7 +16235,7 @@
         <v>29</v>
       </c>
       <c r="D715">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E715" t="s">
         <v>30</v>
@@ -16269,7 +16269,7 @@
         <v>29</v>
       </c>
       <c r="D717">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E717" t="s">
         <v>30</v>
@@ -16286,7 +16286,7 @@
         <v>29</v>
       </c>
       <c r="D718">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E718" t="s">
         <v>30</v>
@@ -16303,7 +16303,7 @@
         <v>29</v>
       </c>
       <c r="D719">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E719" t="s">
         <v>30</v>
@@ -16320,7 +16320,7 @@
         <v>29</v>
       </c>
       <c r="D720">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E720" t="s">
         <v>30</v>
@@ -16337,7 +16337,7 @@
         <v>29</v>
       </c>
       <c r="D721">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E721" t="s">
         <v>30</v>
@@ -16354,7 +16354,7 @@
         <v>29</v>
       </c>
       <c r="D722">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E722" t="s">
         <v>30</v>
@@ -16371,7 +16371,7 @@
         <v>29</v>
       </c>
       <c r="D723">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E723" t="s">
         <v>30</v>
@@ -16388,7 +16388,7 @@
         <v>29</v>
       </c>
       <c r="D724">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E724" t="s">
         <v>30</v>
@@ -16405,7 +16405,7 @@
         <v>29</v>
       </c>
       <c r="D725">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E725" t="s">
         <v>30</v>
@@ -16439,7 +16439,7 @@
         <v>29</v>
       </c>
       <c r="D727">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E727" t="s">
         <v>30</v>
@@ -16456,7 +16456,7 @@
         <v>29</v>
       </c>
       <c r="D728">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E728" t="s">
         <v>30</v>
@@ -16490,7 +16490,7 @@
         <v>29</v>
       </c>
       <c r="D730">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E730" t="s">
         <v>30</v>
@@ -16507,7 +16507,7 @@
         <v>29</v>
       </c>
       <c r="D731">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E731" t="s">
         <v>30</v>
@@ -16524,7 +16524,7 @@
         <v>29</v>
       </c>
       <c r="D732">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E732" t="s">
         <v>30</v>
@@ -16558,7 +16558,7 @@
         <v>29</v>
       </c>
       <c r="D734">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E734" t="s">
         <v>30</v>
@@ -16575,7 +16575,7 @@
         <v>29</v>
       </c>
       <c r="D735">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E735" t="s">
         <v>30</v>
@@ -16592,7 +16592,7 @@
         <v>29</v>
       </c>
       <c r="D736">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E736" t="s">
         <v>30</v>
@@ -16609,7 +16609,7 @@
         <v>29</v>
       </c>
       <c r="D737">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E737" t="s">
         <v>30</v>
@@ -16626,7 +16626,7 @@
         <v>29</v>
       </c>
       <c r="D738">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E738" t="s">
         <v>30</v>
@@ -16643,7 +16643,7 @@
         <v>29</v>
       </c>
       <c r="D739">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E739" t="s">
         <v>30</v>
@@ -16660,7 +16660,7 @@
         <v>29</v>
       </c>
       <c r="D740">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E740" t="s">
         <v>30</v>
@@ -16677,7 +16677,7 @@
         <v>29</v>
       </c>
       <c r="D741">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E741" t="s">
         <v>30</v>
@@ -16694,7 +16694,7 @@
         <v>29</v>
       </c>
       <c r="D742">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E742" t="s">
         <v>30</v>
@@ -16711,7 +16711,7 @@
         <v>29</v>
       </c>
       <c r="D743">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E743" t="s">
         <v>30</v>
@@ -16728,7 +16728,7 @@
         <v>29</v>
       </c>
       <c r="D744">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E744" t="s">
         <v>30</v>
@@ -16745,7 +16745,7 @@
         <v>29</v>
       </c>
       <c r="D745">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E745" t="s">
         <v>30</v>
@@ -16762,7 +16762,7 @@
         <v>29</v>
       </c>
       <c r="D746">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E746" t="s">
         <v>30</v>
@@ -16779,7 +16779,7 @@
         <v>29</v>
       </c>
       <c r="D747">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E747" t="s">
         <v>30</v>
@@ -16796,7 +16796,7 @@
         <v>29</v>
       </c>
       <c r="D748">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E748" t="s">
         <v>30</v>
@@ -16813,7 +16813,7 @@
         <v>29</v>
       </c>
       <c r="D749">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E749" t="s">
         <v>30</v>
@@ -16830,7 +16830,7 @@
         <v>29</v>
       </c>
       <c r="D750">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E750" t="s">
         <v>30</v>
@@ -16847,7 +16847,7 @@
         <v>29</v>
       </c>
       <c r="D751">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E751" t="s">
         <v>30</v>
@@ -16864,7 +16864,7 @@
         <v>29</v>
       </c>
       <c r="D752">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E752" t="s">
         <v>30</v>
@@ -16881,7 +16881,7 @@
         <v>29</v>
       </c>
       <c r="D753">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E753" t="s">
         <v>30</v>
@@ -16898,7 +16898,7 @@
         <v>29</v>
       </c>
       <c r="D754">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E754" t="s">
         <v>30</v>
@@ -16915,7 +16915,7 @@
         <v>29</v>
       </c>
       <c r="D755">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E755" t="s">
         <v>30</v>
@@ -16932,7 +16932,7 @@
         <v>29</v>
       </c>
       <c r="D756">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E756" t="s">
         <v>30</v>
@@ -16966,7 +16966,7 @@
         <v>29</v>
       </c>
       <c r="D758">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E758" t="s">
         <v>30</v>
@@ -16983,7 +16983,7 @@
         <v>29</v>
       </c>
       <c r="D759">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E759" t="s">
         <v>30</v>
@@ -17000,7 +17000,7 @@
         <v>29</v>
       </c>
       <c r="D760">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E760" t="s">
         <v>30</v>
@@ -17017,7 +17017,7 @@
         <v>29</v>
       </c>
       <c r="D761">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E761" t="s">
         <v>30</v>
@@ -17034,7 +17034,7 @@
         <v>29</v>
       </c>
       <c r="D762">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E762" t="s">
         <v>30</v>
@@ -17051,7 +17051,7 @@
         <v>29</v>
       </c>
       <c r="D763">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E763" t="s">
         <v>30</v>
@@ -17068,7 +17068,7 @@
         <v>29</v>
       </c>
       <c r="D764">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E764" t="s">
         <v>30</v>
@@ -17085,7 +17085,7 @@
         <v>29</v>
       </c>
       <c r="D765">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E765" t="s">
         <v>30</v>
@@ -17102,7 +17102,7 @@
         <v>29</v>
       </c>
       <c r="D766">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E766" t="s">
         <v>30</v>
@@ -17119,7 +17119,7 @@
         <v>29</v>
       </c>
       <c r="D767">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E767" t="s">
         <v>30</v>
@@ -17136,7 +17136,7 @@
         <v>29</v>
       </c>
       <c r="D768">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E768" t="s">
         <v>30</v>
@@ -17153,7 +17153,7 @@
         <v>29</v>
       </c>
       <c r="D769">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E769" t="s">
         <v>30</v>
@@ -17170,7 +17170,7 @@
         <v>29</v>
       </c>
       <c r="D770">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E770" t="s">
         <v>30</v>
@@ -17187,7 +17187,7 @@
         <v>29</v>
       </c>
       <c r="D771">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E771" t="s">
         <v>30</v>
@@ -17204,7 +17204,7 @@
         <v>29</v>
       </c>
       <c r="D772">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E772" t="s">
         <v>30</v>
@@ -17221,7 +17221,7 @@
         <v>29</v>
       </c>
       <c r="D773">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E773" t="s">
         <v>30</v>
@@ -17238,7 +17238,7 @@
         <v>29</v>
       </c>
       <c r="D774">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E774" t="s">
         <v>30</v>
@@ -17255,7 +17255,7 @@
         <v>29</v>
       </c>
       <c r="D775">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E775" t="s">
         <v>30</v>
@@ -17272,7 +17272,7 @@
         <v>29</v>
       </c>
       <c r="D776">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E776" t="s">
         <v>30</v>
@@ -17289,7 +17289,7 @@
         <v>29</v>
       </c>
       <c r="D777">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E777" t="s">
         <v>30</v>
@@ -17306,7 +17306,7 @@
         <v>29</v>
       </c>
       <c r="D778">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E778" t="s">
         <v>30</v>
@@ -17323,7 +17323,7 @@
         <v>29</v>
       </c>
       <c r="D779">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E779" t="s">
         <v>30</v>
@@ -17340,7 +17340,7 @@
         <v>29</v>
       </c>
       <c r="D780">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E780" t="s">
         <v>30</v>
@@ -17374,7 +17374,7 @@
         <v>29</v>
       </c>
       <c r="D782">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E782" t="s">
         <v>30</v>
@@ -17391,7 +17391,7 @@
         <v>29</v>
       </c>
       <c r="D783">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E783" t="s">
         <v>30</v>
@@ -17408,7 +17408,7 @@
         <v>29</v>
       </c>
       <c r="D784">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E784" t="s">
         <v>30</v>
@@ -17425,7 +17425,7 @@
         <v>29</v>
       </c>
       <c r="D785">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E785" t="s">
         <v>30</v>
@@ -17442,7 +17442,7 @@
         <v>29</v>
       </c>
       <c r="D786">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E786" t="s">
         <v>30</v>
@@ -17459,7 +17459,7 @@
         <v>29</v>
       </c>
       <c r="D787">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E787" t="s">
         <v>30</v>
@@ -17476,7 +17476,7 @@
         <v>29</v>
       </c>
       <c r="D788">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E788" t="s">
         <v>30</v>
@@ -17493,7 +17493,7 @@
         <v>29</v>
       </c>
       <c r="D789">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E789" t="s">
         <v>30</v>
@@ -17510,7 +17510,7 @@
         <v>29</v>
       </c>
       <c r="D790">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E790" t="s">
         <v>30</v>
@@ -17527,7 +17527,7 @@
         <v>29</v>
       </c>
       <c r="D791">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E791" t="s">
         <v>30</v>
@@ -17544,7 +17544,7 @@
         <v>29</v>
       </c>
       <c r="D792">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E792" t="s">
         <v>30</v>
@@ -17561,7 +17561,7 @@
         <v>29</v>
       </c>
       <c r="D793">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E793" t="s">
         <v>30</v>
@@ -17578,7 +17578,7 @@
         <v>29</v>
       </c>
       <c r="D794">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E794" t="s">
         <v>30</v>
@@ -17595,7 +17595,7 @@
         <v>29</v>
       </c>
       <c r="D795">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E795" t="s">
         <v>30</v>
@@ -17612,7 +17612,7 @@
         <v>29</v>
       </c>
       <c r="D796">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E796" t="s">
         <v>30</v>
@@ -17629,7 +17629,7 @@
         <v>29</v>
       </c>
       <c r="D797">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E797" t="s">
         <v>30</v>
@@ -17663,7 +17663,7 @@
         <v>29</v>
       </c>
       <c r="D799">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E799" t="s">
         <v>30</v>
@@ -17680,7 +17680,7 @@
         <v>29</v>
       </c>
       <c r="D800">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E800" t="s">
         <v>30</v>
@@ -17697,7 +17697,7 @@
         <v>29</v>
       </c>
       <c r="D801">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E801" t="s">
         <v>30</v>
@@ -17714,7 +17714,7 @@
         <v>29</v>
       </c>
       <c r="D802">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E802" t="s">
         <v>30</v>
@@ -17731,7 +17731,7 @@
         <v>29</v>
       </c>
       <c r="D803">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E803" t="s">
         <v>30</v>
@@ -17748,7 +17748,7 @@
         <v>29</v>
       </c>
       <c r="D804">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E804" t="s">
         <v>30</v>
@@ -17765,7 +17765,7 @@
         <v>29</v>
       </c>
       <c r="D805">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E805" t="s">
         <v>30</v>
@@ -17782,7 +17782,7 @@
         <v>29</v>
       </c>
       <c r="D806">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E806" t="s">
         <v>30</v>
@@ -17799,7 +17799,7 @@
         <v>29</v>
       </c>
       <c r="D807">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E807" t="s">
         <v>30</v>
@@ -17816,7 +17816,7 @@
         <v>29</v>
       </c>
       <c r="D808">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E808" t="s">
         <v>30</v>
@@ -17833,7 +17833,7 @@
         <v>29</v>
       </c>
       <c r="D809">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E809" t="s">
         <v>30</v>
@@ -17850,7 +17850,7 @@
         <v>29</v>
       </c>
       <c r="D810">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E810" t="s">
         <v>30</v>
@@ -17867,7 +17867,7 @@
         <v>29</v>
       </c>
       <c r="D811">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E811" t="s">
         <v>30</v>
@@ -17884,7 +17884,7 @@
         <v>29</v>
       </c>
       <c r="D812">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E812" t="s">
         <v>30</v>
@@ -17901,7 +17901,7 @@
         <v>29</v>
       </c>
       <c r="D813">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E813" t="s">
         <v>30</v>
@@ -17918,7 +17918,7 @@
         <v>29</v>
       </c>
       <c r="D814">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E814" t="s">
         <v>30</v>
@@ -17935,7 +17935,7 @@
         <v>29</v>
       </c>
       <c r="D815">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E815" t="s">
         <v>30</v>
@@ -17952,7 +17952,7 @@
         <v>29</v>
       </c>
       <c r="D816">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E816" t="s">
         <v>30</v>
@@ -17986,7 +17986,7 @@
         <v>29</v>
       </c>
       <c r="D818">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E818" t="s">
         <v>30</v>
@@ -18003,7 +18003,7 @@
         <v>29</v>
       </c>
       <c r="D819">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E819" t="s">
         <v>30</v>
@@ -18020,7 +18020,7 @@
         <v>29</v>
       </c>
       <c r="D820">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E820" t="s">
         <v>30</v>
@@ -18037,7 +18037,7 @@
         <v>29</v>
       </c>
       <c r="D821">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E821" t="s">
         <v>30</v>
@@ -18054,7 +18054,7 @@
         <v>29</v>
       </c>
       <c r="D822">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E822" t="s">
         <v>30</v>
@@ -18088,7 +18088,7 @@
         <v>29</v>
       </c>
       <c r="D824">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E824" t="s">
         <v>30</v>
@@ -18105,7 +18105,7 @@
         <v>29</v>
       </c>
       <c r="D825">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E825" t="s">
         <v>30</v>
@@ -18122,7 +18122,7 @@
         <v>29</v>
       </c>
       <c r="D826">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E826" t="s">
         <v>30</v>
@@ -18139,7 +18139,7 @@
         <v>29</v>
       </c>
       <c r="D827">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E827" t="s">
         <v>30</v>
@@ -18156,7 +18156,7 @@
         <v>29</v>
       </c>
       <c r="D828">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E828" t="s">
         <v>30</v>
@@ -18173,7 +18173,7 @@
         <v>29</v>
       </c>
       <c r="D829">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E829" t="s">
         <v>30</v>
@@ -18190,7 +18190,7 @@
         <v>29</v>
       </c>
       <c r="D830">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E830" t="s">
         <v>30</v>
@@ -18207,7 +18207,7 @@
         <v>29</v>
       </c>
       <c r="D831">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E831" t="s">
         <v>30</v>
@@ -18224,7 +18224,7 @@
         <v>29</v>
       </c>
       <c r="D832">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E832" t="s">
         <v>30</v>
@@ -18241,7 +18241,7 @@
         <v>29</v>
       </c>
       <c r="D833">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E833" t="s">
         <v>30</v>
@@ -18258,7 +18258,7 @@
         <v>29</v>
       </c>
       <c r="D834">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E834" t="s">
         <v>30</v>
@@ -18275,7 +18275,7 @@
         <v>29</v>
       </c>
       <c r="D835">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E835" t="s">
         <v>30</v>
@@ -18292,7 +18292,7 @@
         <v>29</v>
       </c>
       <c r="D836">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E836" t="s">
         <v>30</v>
@@ -18309,7 +18309,7 @@
         <v>29</v>
       </c>
       <c r="D837">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E837" t="s">
         <v>30</v>
@@ -18326,7 +18326,7 @@
         <v>29</v>
       </c>
       <c r="D838">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E838" t="s">
         <v>30</v>
@@ -18343,7 +18343,7 @@
         <v>29</v>
       </c>
       <c r="D839">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E839" t="s">
         <v>30</v>
@@ -18360,7 +18360,7 @@
         <v>29</v>
       </c>
       <c r="D840">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E840" t="s">
         <v>30</v>
@@ -18377,7 +18377,7 @@
         <v>29</v>
       </c>
       <c r="D841">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E841" t="s">
         <v>30</v>
@@ -18394,7 +18394,7 @@
         <v>29</v>
       </c>
       <c r="D842">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E842" t="s">
         <v>30</v>
@@ -18411,7 +18411,7 @@
         <v>29</v>
       </c>
       <c r="D843">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E843" t="s">
         <v>30</v>
@@ -18428,7 +18428,7 @@
         <v>29</v>
       </c>
       <c r="D844">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E844" t="s">
         <v>30</v>
@@ -18445,7 +18445,7 @@
         <v>29</v>
       </c>
       <c r="D845">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E845" t="s">
         <v>30</v>
@@ -18462,7 +18462,7 @@
         <v>29</v>
       </c>
       <c r="D846">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E846" t="s">
         <v>30</v>
@@ -18479,7 +18479,7 @@
         <v>29</v>
       </c>
       <c r="D847">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E847" t="s">
         <v>30</v>
@@ -18496,7 +18496,7 @@
         <v>29</v>
       </c>
       <c r="D848">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E848" t="s">
         <v>30</v>
@@ -18513,7 +18513,7 @@
         <v>29</v>
       </c>
       <c r="D849">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E849" t="s">
         <v>30</v>
@@ -18530,7 +18530,7 @@
         <v>29</v>
       </c>
       <c r="D850">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E850" t="s">
         <v>30</v>
@@ -18547,7 +18547,7 @@
         <v>29</v>
       </c>
       <c r="D851">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E851" t="s">
         <v>30</v>
@@ -18564,7 +18564,7 @@
         <v>29</v>
       </c>
       <c r="D852">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E852" t="s">
         <v>30</v>
@@ -18581,7 +18581,7 @@
         <v>29</v>
       </c>
       <c r="D853">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E853" t="s">
         <v>30</v>
@@ -18598,7 +18598,7 @@
         <v>29</v>
       </c>
       <c r="D854">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E854" t="s">
         <v>30</v>
@@ -18615,7 +18615,7 @@
         <v>29</v>
       </c>
       <c r="D855">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E855" t="s">
         <v>30</v>
@@ -18632,7 +18632,7 @@
         <v>29</v>
       </c>
       <c r="D856">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E856" t="s">
         <v>30</v>
@@ -18649,7 +18649,7 @@
         <v>29</v>
       </c>
       <c r="D857">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E857" t="s">
         <v>30</v>
@@ -18666,7 +18666,7 @@
         <v>29</v>
       </c>
       <c r="D858">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E858" t="s">
         <v>30</v>
@@ -18683,7 +18683,7 @@
         <v>29</v>
       </c>
       <c r="D859">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E859" t="s">
         <v>30</v>
@@ -18700,7 +18700,7 @@
         <v>29</v>
       </c>
       <c r="D860">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E860" t="s">
         <v>30</v>
@@ -18717,7 +18717,7 @@
         <v>29</v>
       </c>
       <c r="D861">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E861" t="s">
         <v>30</v>
@@ -18734,7 +18734,7 @@
         <v>29</v>
       </c>
       <c r="D862">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E862" t="s">
         <v>30</v>
@@ -18751,7 +18751,7 @@
         <v>29</v>
       </c>
       <c r="D863">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E863" t="s">
         <v>30</v>
@@ -18768,7 +18768,7 @@
         <v>29</v>
       </c>
       <c r="D864">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E864" t="s">
         <v>30</v>
@@ -18785,7 +18785,7 @@
         <v>29</v>
       </c>
       <c r="D865">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E865" t="s">
         <v>30</v>
@@ -18802,7 +18802,7 @@
         <v>29</v>
       </c>
       <c r="D866">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E866" t="s">
         <v>30</v>
@@ -18819,7 +18819,7 @@
         <v>29</v>
       </c>
       <c r="D867">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E867" t="s">
         <v>30</v>
@@ -18836,7 +18836,7 @@
         <v>29</v>
       </c>
       <c r="D868">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E868" t="s">
         <v>30</v>
@@ -18853,7 +18853,7 @@
         <v>29</v>
       </c>
       <c r="D869">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E869" t="s">
         <v>30</v>
@@ -18870,7 +18870,7 @@
         <v>29</v>
       </c>
       <c r="D870">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E870" t="s">
         <v>30</v>
@@ -18887,7 +18887,7 @@
         <v>29</v>
       </c>
       <c r="D871">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E871" t="s">
         <v>30</v>
@@ -18904,7 +18904,7 @@
         <v>29</v>
       </c>
       <c r="D872">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E872" t="s">
         <v>30</v>
@@ -18921,7 +18921,7 @@
         <v>29</v>
       </c>
       <c r="D873">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E873" t="s">
         <v>30</v>
@@ -18955,7 +18955,7 @@
         <v>29</v>
       </c>
       <c r="D875">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E875" t="s">
         <v>30</v>
@@ -18972,7 +18972,7 @@
         <v>29</v>
       </c>
       <c r="D876">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E876" t="s">
         <v>30</v>
@@ -18989,7 +18989,7 @@
         <v>29</v>
       </c>
       <c r="D877">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E877" t="s">
         <v>30</v>
@@ -19006,7 +19006,7 @@
         <v>29</v>
       </c>
       <c r="D878">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E878" t="s">
         <v>30</v>
@@ -19023,7 +19023,7 @@
         <v>29</v>
       </c>
       <c r="D879">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E879" t="s">
         <v>30</v>
@@ -19040,7 +19040,7 @@
         <v>29</v>
       </c>
       <c r="D880">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E880" t="s">
         <v>30</v>
@@ -19057,7 +19057,7 @@
         <v>29</v>
       </c>
       <c r="D881">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E881" t="s">
         <v>30</v>
@@ -19074,7 +19074,7 @@
         <v>29</v>
       </c>
       <c r="D882">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E882" t="s">
         <v>30</v>
@@ -19091,7 +19091,7 @@
         <v>29</v>
       </c>
       <c r="D883">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E883" t="s">
         <v>30</v>
@@ -19108,7 +19108,7 @@
         <v>29</v>
       </c>
       <c r="D884">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E884" t="s">
         <v>30</v>
@@ -19125,7 +19125,7 @@
         <v>29</v>
       </c>
       <c r="D885">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E885" t="s">
         <v>30</v>
@@ -19142,7 +19142,7 @@
         <v>29</v>
       </c>
       <c r="D886">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E886" t="s">
         <v>30</v>
@@ -19159,7 +19159,7 @@
         <v>29</v>
       </c>
       <c r="D887">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E887" t="s">
         <v>30</v>
@@ -19176,7 +19176,7 @@
         <v>29</v>
       </c>
       <c r="D888">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E888" t="s">
         <v>30</v>
@@ -19193,7 +19193,7 @@
         <v>29</v>
       </c>
       <c r="D889">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E889" t="s">
         <v>30</v>
@@ -19210,7 +19210,7 @@
         <v>29</v>
       </c>
       <c r="D890">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E890" t="s">
         <v>30</v>
@@ -19227,7 +19227,7 @@
         <v>29</v>
       </c>
       <c r="D891">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E891" t="s">
         <v>30</v>
@@ -19244,7 +19244,7 @@
         <v>29</v>
       </c>
       <c r="D892">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E892" t="s">
         <v>30</v>
@@ -19261,7 +19261,7 @@
         <v>29</v>
       </c>
       <c r="D893">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E893" t="s">
         <v>30</v>
@@ -19278,7 +19278,7 @@
         <v>29</v>
       </c>
       <c r="D894">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E894" t="s">
         <v>30</v>
@@ -19295,7 +19295,7 @@
         <v>29</v>
       </c>
       <c r="D895">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E895" t="s">
         <v>30</v>
@@ -19312,7 +19312,7 @@
         <v>29</v>
       </c>
       <c r="D896">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E896" t="s">
         <v>30</v>
@@ -19329,7 +19329,7 @@
         <v>29</v>
       </c>
       <c r="D897">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E897" t="s">
         <v>30</v>
@@ -19346,7 +19346,7 @@
         <v>29</v>
       </c>
       <c r="D898">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E898" t="s">
         <v>30</v>
@@ -19363,7 +19363,7 @@
         <v>29</v>
       </c>
       <c r="D899">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E899" t="s">
         <v>30</v>
@@ -19380,7 +19380,7 @@
         <v>29</v>
       </c>
       <c r="D900">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E900" t="s">
         <v>30</v>
@@ -19397,7 +19397,7 @@
         <v>29</v>
       </c>
       <c r="D901">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E901" t="s">
         <v>30</v>
@@ -19414,7 +19414,7 @@
         <v>29</v>
       </c>
       <c r="D902">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E902" t="s">
         <v>30</v>
@@ -19431,7 +19431,7 @@
         <v>29</v>
       </c>
       <c r="D903">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E903" t="s">
         <v>30</v>
@@ -19448,7 +19448,7 @@
         <v>29</v>
       </c>
       <c r="D904">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E904" t="s">
         <v>30</v>
@@ -19465,7 +19465,7 @@
         <v>29</v>
       </c>
       <c r="D905">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E905" t="s">
         <v>30</v>
@@ -19482,7 +19482,7 @@
         <v>29</v>
       </c>
       <c r="D906">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E906" t="s">
         <v>30</v>
@@ -19499,7 +19499,7 @@
         <v>29</v>
       </c>
       <c r="D907">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E907" t="s">
         <v>30</v>
@@ -19516,7 +19516,7 @@
         <v>29</v>
       </c>
       <c r="D908">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E908" t="s">
         <v>30</v>
@@ -19533,7 +19533,7 @@
         <v>29</v>
       </c>
       <c r="D909">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E909" t="s">
         <v>30</v>
@@ -19550,7 +19550,7 @@
         <v>29</v>
       </c>
       <c r="D910">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E910" t="s">
         <v>30</v>
@@ -19567,7 +19567,7 @@
         <v>29</v>
       </c>
       <c r="D911">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E911" t="s">
         <v>30</v>
@@ -19584,7 +19584,7 @@
         <v>29</v>
       </c>
       <c r="D912">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E912" t="s">
         <v>30</v>
@@ -19601,7 +19601,7 @@
         <v>29</v>
       </c>
       <c r="D913">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E913" t="s">
         <v>30</v>
@@ -19618,7 +19618,7 @@
         <v>29</v>
       </c>
       <c r="D914">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E914" t="s">
         <v>30</v>
@@ -19635,7 +19635,7 @@
         <v>29</v>
       </c>
       <c r="D915">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E915" t="s">
         <v>30</v>
@@ -19652,7 +19652,7 @@
         <v>29</v>
       </c>
       <c r="D916">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E916" t="s">
         <v>30</v>
@@ -19669,7 +19669,7 @@
         <v>29</v>
       </c>
       <c r="D917">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E917" t="s">
         <v>30</v>
@@ -19703,7 +19703,7 @@
         <v>29</v>
       </c>
       <c r="D919">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E919" t="s">
         <v>30</v>
@@ -19720,7 +19720,7 @@
         <v>29</v>
       </c>
       <c r="D920">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E920" t="s">
         <v>30</v>
@@ -19737,7 +19737,7 @@
         <v>29</v>
       </c>
       <c r="D921">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E921" t="s">
         <v>30</v>
@@ -19754,7 +19754,7 @@
         <v>29</v>
       </c>
       <c r="D922">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E922" t="s">
         <v>30</v>
@@ -19771,7 +19771,7 @@
         <v>29</v>
       </c>
       <c r="D923">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E923" t="s">
         <v>30</v>
@@ -19788,7 +19788,7 @@
         <v>29</v>
       </c>
       <c r="D924">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E924" t="s">
         <v>30</v>
@@ -19805,7 +19805,7 @@
         <v>29</v>
       </c>
       <c r="D925">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E925" t="s">
         <v>30</v>
@@ -19822,7 +19822,7 @@
         <v>29</v>
       </c>
       <c r="D926">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E926" t="s">
         <v>30</v>
@@ -19839,7 +19839,7 @@
         <v>29</v>
       </c>
       <c r="D927">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E927" t="s">
         <v>30</v>
@@ -19856,7 +19856,7 @@
         <v>29</v>
       </c>
       <c r="D928">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E928" t="s">
         <v>30</v>
@@ -19873,7 +19873,7 @@
         <v>29</v>
       </c>
       <c r="D929">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E929" t="s">
         <v>30</v>
@@ -19890,7 +19890,7 @@
         <v>29</v>
       </c>
       <c r="D930">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E930" t="s">
         <v>30</v>
@@ -19907,7 +19907,7 @@
         <v>29</v>
       </c>
       <c r="D931">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E931" t="s">
         <v>30</v>
@@ -19924,7 +19924,7 @@
         <v>29</v>
       </c>
       <c r="D932">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E932" t="s">
         <v>30</v>
@@ -19941,7 +19941,7 @@
         <v>29</v>
       </c>
       <c r="D933">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E933" t="s">
         <v>30</v>
@@ -19958,7 +19958,7 @@
         <v>29</v>
       </c>
       <c r="D934">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E934" t="s">
         <v>30</v>
@@ -19975,7 +19975,7 @@
         <v>29</v>
       </c>
       <c r="D935">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E935" t="s">
         <v>30</v>
@@ -19992,7 +19992,7 @@
         <v>29</v>
       </c>
       <c r="D936">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E936" t="s">
         <v>30</v>
@@ -20009,7 +20009,7 @@
         <v>29</v>
       </c>
       <c r="D937">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E937" t="s">
         <v>30</v>
@@ -20026,7 +20026,7 @@
         <v>29</v>
       </c>
       <c r="D938">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E938" t="s">
         <v>30</v>
@@ -20043,7 +20043,7 @@
         <v>29</v>
       </c>
       <c r="D939">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E939" t="s">
         <v>30</v>
@@ -20060,7 +20060,7 @@
         <v>29</v>
       </c>
       <c r="D940">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E940" t="s">
         <v>30</v>
@@ -20077,7 +20077,7 @@
         <v>29</v>
       </c>
       <c r="D941">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E941" t="s">
         <v>30</v>
@@ -20094,7 +20094,7 @@
         <v>29</v>
       </c>
       <c r="D942">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E942" t="s">
         <v>30</v>
@@ -20111,7 +20111,7 @@
         <v>29</v>
       </c>
       <c r="D943">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E943" t="s">
         <v>30</v>
@@ -20128,7 +20128,7 @@
         <v>29</v>
       </c>
       <c r="D944">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E944" t="s">
         <v>30</v>
@@ -20145,7 +20145,7 @@
         <v>29</v>
       </c>
       <c r="D945">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E945" t="s">
         <v>30</v>
@@ -20162,7 +20162,7 @@
         <v>29</v>
       </c>
       <c r="D946">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E946" t="s">
         <v>30</v>
@@ -20179,7 +20179,7 @@
         <v>29</v>
       </c>
       <c r="D947">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E947" t="s">
         <v>30</v>
@@ -20196,7 +20196,7 @@
         <v>29</v>
       </c>
       <c r="D948">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E948" t="s">
         <v>30</v>
@@ -20230,7 +20230,7 @@
         <v>29</v>
       </c>
       <c r="D950">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E950" t="s">
         <v>30</v>
@@ -20247,7 +20247,7 @@
         <v>29</v>
       </c>
       <c r="D951">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E951" t="s">
         <v>30</v>
@@ -20281,7 +20281,7 @@
         <v>29</v>
       </c>
       <c r="D953">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E953" t="s">
         <v>30</v>
@@ -20298,7 +20298,7 @@
         <v>29</v>
       </c>
       <c r="D954">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E954" t="s">
         <v>30</v>
@@ -20315,7 +20315,7 @@
         <v>29</v>
       </c>
       <c r="D955">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E955" t="s">
         <v>30</v>
@@ -20332,7 +20332,7 @@
         <v>29</v>
       </c>
       <c r="D956">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E956" t="s">
         <v>30</v>
@@ -20349,7 +20349,7 @@
         <v>29</v>
       </c>
       <c r="D957">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E957" t="s">
         <v>30</v>
@@ -20366,7 +20366,7 @@
         <v>29</v>
       </c>
       <c r="D958">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E958" t="s">
         <v>30</v>
@@ -20383,7 +20383,7 @@
         <v>29</v>
       </c>
       <c r="D959">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E959" t="s">
         <v>30</v>
@@ -20400,7 +20400,7 @@
         <v>29</v>
       </c>
       <c r="D960">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E960" t="s">
         <v>30</v>
@@ -20417,7 +20417,7 @@
         <v>29</v>
       </c>
       <c r="D961">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E961" t="s">
         <v>30</v>
@@ -20434,7 +20434,7 @@
         <v>29</v>
       </c>
       <c r="D962">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E962" t="s">
         <v>30</v>
@@ -20451,7 +20451,7 @@
         <v>29</v>
       </c>
       <c r="D963">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E963" t="s">
         <v>30</v>
@@ -20468,7 +20468,7 @@
         <v>29</v>
       </c>
       <c r="D964">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E964" t="s">
         <v>30</v>
@@ -20485,7 +20485,7 @@
         <v>29</v>
       </c>
       <c r="D965">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E965" t="s">
         <v>30</v>
@@ -20502,7 +20502,7 @@
         <v>29</v>
       </c>
       <c r="D966">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E966" t="s">
         <v>30</v>
@@ -20519,7 +20519,7 @@
         <v>29</v>
       </c>
       <c r="D967">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E967" t="s">
         <v>30</v>
@@ -20536,7 +20536,7 @@
         <v>29</v>
       </c>
       <c r="D968">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E968" t="s">
         <v>30</v>
@@ -20553,7 +20553,7 @@
         <v>29</v>
       </c>
       <c r="D969">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E969" t="s">
         <v>30</v>
@@ -20570,7 +20570,7 @@
         <v>29</v>
       </c>
       <c r="D970">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E970" t="s">
         <v>30</v>
@@ -20587,7 +20587,7 @@
         <v>29</v>
       </c>
       <c r="D971">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E971" t="s">
         <v>30</v>
@@ -20604,7 +20604,7 @@
         <v>29</v>
       </c>
       <c r="D972">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E972" t="s">
         <v>30</v>
@@ -20621,7 +20621,7 @@
         <v>29</v>
       </c>
       <c r="D973">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E973" t="s">
         <v>30</v>
@@ -20638,7 +20638,7 @@
         <v>29</v>
       </c>
       <c r="D974">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E974" t="s">
         <v>30</v>
@@ -20655,7 +20655,7 @@
         <v>29</v>
       </c>
       <c r="D975">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E975" t="s">
         <v>30</v>
@@ -20672,7 +20672,7 @@
         <v>29</v>
       </c>
       <c r="D976">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E976" t="s">
         <v>30</v>
@@ -20689,7 +20689,7 @@
         <v>29</v>
       </c>
       <c r="D977">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E977" t="s">
         <v>30</v>
@@ -20706,7 +20706,7 @@
         <v>29</v>
       </c>
       <c r="D978">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E978" t="s">
         <v>30</v>
@@ -20723,7 +20723,7 @@
         <v>29</v>
       </c>
       <c r="D979">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E979" t="s">
         <v>30</v>
@@ -20740,7 +20740,7 @@
         <v>29</v>
       </c>
       <c r="D980">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E980" t="s">
         <v>30</v>
@@ -20757,7 +20757,7 @@
         <v>29</v>
       </c>
       <c r="D981">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E981" t="s">
         <v>30</v>
@@ -20774,7 +20774,7 @@
         <v>29</v>
       </c>
       <c r="D982">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E982" t="s">
         <v>30</v>
@@ -20791,7 +20791,7 @@
         <v>29</v>
       </c>
       <c r="D983">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E983" t="s">
         <v>30</v>
@@ -20808,7 +20808,7 @@
         <v>29</v>
       </c>
       <c r="D984">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E984" t="s">
         <v>30</v>
@@ -20825,7 +20825,7 @@
         <v>29</v>
       </c>
       <c r="D985">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E985" t="s">
         <v>30</v>
@@ -20842,7 +20842,7 @@
         <v>29</v>
       </c>
       <c r="D986">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E986" t="s">
         <v>30</v>
@@ -20859,7 +20859,7 @@
         <v>29</v>
       </c>
       <c r="D987">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E987" t="s">
         <v>30</v>
@@ -20893,7 +20893,7 @@
         <v>29</v>
       </c>
       <c r="D989">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E989" t="s">
         <v>30</v>
@@ -20910,7 +20910,7 @@
         <v>29</v>
       </c>
       <c r="D990">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E990" t="s">
         <v>30</v>
@@ -20927,7 +20927,7 @@
         <v>29</v>
       </c>
       <c r="D991">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E991" t="s">
         <v>30</v>
@@ -20944,7 +20944,7 @@
         <v>29</v>
       </c>
       <c r="D992">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E992" t="s">
         <v>30</v>
@@ -20961,7 +20961,7 @@
         <v>29</v>
       </c>
       <c r="D993">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E993" t="s">
         <v>30</v>
@@ -20978,7 +20978,7 @@
         <v>29</v>
       </c>
       <c r="D994">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E994" t="s">
         <v>30</v>
@@ -20995,7 +20995,7 @@
         <v>29</v>
       </c>
       <c r="D995">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E995" t="s">
         <v>30</v>
@@ -21012,7 +21012,7 @@
         <v>29</v>
       </c>
       <c r="D996">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E996" t="s">
         <v>30</v>
@@ -21046,7 +21046,7 @@
         <v>29</v>
       </c>
       <c r="D998">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E998" t="s">
         <v>30</v>
@@ -21063,7 +21063,7 @@
         <v>29</v>
       </c>
       <c r="D999">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E999" t="s">
         <v>30</v>
@@ -21080,7 +21080,7 @@
         <v>29</v>
       </c>
       <c r="D1000">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1000" t="s">
         <v>30</v>
@@ -21097,7 +21097,7 @@
         <v>29</v>
       </c>
       <c r="D1001">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1001" t="s">
         <v>30</v>
@@ -21114,7 +21114,7 @@
         <v>29</v>
       </c>
       <c r="D1002">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1002" t="s">
         <v>30</v>
@@ -21131,7 +21131,7 @@
         <v>29</v>
       </c>
       <c r="D1003">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1003" t="s">
         <v>30</v>
@@ -21165,7 +21165,7 @@
         <v>29</v>
       </c>
       <c r="D1005">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E1005" t="s">
         <v>30</v>
@@ -21182,7 +21182,7 @@
         <v>29</v>
       </c>
       <c r="D1006">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1006" t="s">
         <v>30</v>
@@ -21199,7 +21199,7 @@
         <v>29</v>
       </c>
       <c r="D1007">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1007" t="s">
         <v>30</v>
@@ -21216,7 +21216,7 @@
         <v>29</v>
       </c>
       <c r="D1008">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1008" t="s">
         <v>30</v>
@@ -21233,7 +21233,7 @@
         <v>29</v>
       </c>
       <c r="D1009">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E1009" t="s">
         <v>30</v>
@@ -21250,7 +21250,7 @@
         <v>29</v>
       </c>
       <c r="D1010">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E1010" t="s">
         <v>30</v>
@@ -21267,7 +21267,7 @@
         <v>29</v>
       </c>
       <c r="D1011">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1011" t="s">
         <v>30</v>
@@ -21284,7 +21284,7 @@
         <v>29</v>
       </c>
       <c r="D1012">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1012" t="s">
         <v>30</v>
@@ -21301,7 +21301,7 @@
         <v>29</v>
       </c>
       <c r="D1013">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1013" t="s">
         <v>30</v>
@@ -21318,7 +21318,7 @@
         <v>29</v>
       </c>
       <c r="D1014">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1014" t="s">
         <v>30</v>
@@ -21335,7 +21335,7 @@
         <v>29</v>
       </c>
       <c r="D1015">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E1015" t="s">
         <v>30</v>
@@ -21352,7 +21352,7 @@
         <v>29</v>
       </c>
       <c r="D1016">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1016" t="s">
         <v>30</v>
@@ -21369,7 +21369,7 @@
         <v>29</v>
       </c>
       <c r="D1017">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E1017" t="s">
         <v>30</v>
@@ -21386,7 +21386,7 @@
         <v>29</v>
       </c>
       <c r="D1018">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1018" t="s">
         <v>30</v>
@@ -21403,7 +21403,7 @@
         <v>29</v>
       </c>
       <c r="D1019">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1019" t="s">
         <v>30</v>
@@ -21420,7 +21420,7 @@
         <v>29</v>
       </c>
       <c r="D1020">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1020" t="s">
         <v>30</v>
@@ -21437,7 +21437,7 @@
         <v>29</v>
       </c>
       <c r="D1021">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E1021" t="s">
         <v>30</v>
@@ -21488,7 +21488,7 @@
         <v>29</v>
       </c>
       <c r="D1024">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1024" t="s">
         <v>30</v>
@@ -21505,7 +21505,7 @@
         <v>29</v>
       </c>
       <c r="D1025">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E1025" t="s">
         <v>30</v>
@@ -21522,7 +21522,7 @@
         <v>29</v>
       </c>
       <c r="D1026">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E1026" t="s">
         <v>30</v>
@@ -21539,7 +21539,7 @@
         <v>29</v>
       </c>
       <c r="D1027">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1027" t="s">
         <v>30</v>
@@ -21556,7 +21556,7 @@
         <v>29</v>
       </c>
       <c r="D1028">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E1028" t="s">
         <v>30</v>
@@ -21573,7 +21573,7 @@
         <v>29</v>
       </c>
       <c r="D1029">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E1029" t="s">
         <v>30</v>
@@ -21590,7 +21590,7 @@
         <v>29</v>
       </c>
       <c r="D1030">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1030" t="s">
         <v>30</v>
@@ -21607,7 +21607,7 @@
         <v>29</v>
       </c>
       <c r="D1031">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1031" t="s">
         <v>30</v>
@@ -21624,7 +21624,7 @@
         <v>29</v>
       </c>
       <c r="D1032">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1032" t="s">
         <v>30</v>
@@ -21641,7 +21641,7 @@
         <v>29</v>
       </c>
       <c r="D1033">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1033" t="s">
         <v>30</v>
@@ -21658,7 +21658,7 @@
         <v>29</v>
       </c>
       <c r="D1034">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E1034" t="s">
         <v>30</v>
@@ -21675,7 +21675,7 @@
         <v>29</v>
       </c>
       <c r="D1035">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1035" t="s">
         <v>30</v>
@@ -21692,7 +21692,7 @@
         <v>29</v>
       </c>
       <c r="D1036">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1036" t="s">
         <v>30</v>
@@ -21709,7 +21709,7 @@
         <v>29</v>
       </c>
       <c r="D1037">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1037" t="s">
         <v>30</v>
@@ -21726,7 +21726,7 @@
         <v>29</v>
       </c>
       <c r="D1038">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1038" t="s">
         <v>30</v>
@@ -21743,7 +21743,7 @@
         <v>29</v>
       </c>
       <c r="D1039">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1039" t="s">
         <v>30</v>
@@ -21760,7 +21760,7 @@
         <v>29</v>
       </c>
       <c r="D1040">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E1040" t="s">
         <v>30</v>
@@ -21777,7 +21777,7 @@
         <v>29</v>
       </c>
       <c r="D1041">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E1041" t="s">
         <v>30</v>
@@ -21794,7 +21794,7 @@
         <v>29</v>
       </c>
       <c r="D1042">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E1042" t="s">
         <v>30</v>
@@ -21811,7 +21811,7 @@
         <v>29</v>
       </c>
       <c r="D1043">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E1043" t="s">
         <v>30</v>
@@ -21828,7 +21828,7 @@
         <v>29</v>
       </c>
       <c r="D1044">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1044" t="s">
         <v>30</v>
@@ -21845,7 +21845,7 @@
         <v>29</v>
       </c>
       <c r="D1045">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1045" t="s">
         <v>30</v>
@@ -21879,7 +21879,7 @@
         <v>29</v>
       </c>
       <c r="D1047">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1047" t="s">
         <v>30</v>
@@ -21896,7 +21896,7 @@
         <v>29</v>
       </c>
       <c r="D1048">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1048" t="s">
         <v>30</v>
@@ -21913,7 +21913,7 @@
         <v>29</v>
       </c>
       <c r="D1049">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1049" t="s">
         <v>30</v>
@@ -21930,7 +21930,7 @@
         <v>29</v>
       </c>
       <c r="D1050">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1050" t="s">
         <v>30</v>
@@ -21947,7 +21947,7 @@
         <v>29</v>
       </c>
       <c r="D1051">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E1051" t="s">
         <v>30</v>
@@ -21964,7 +21964,7 @@
         <v>29</v>
       </c>
       <c r="D1052">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1052" t="s">
         <v>30</v>
@@ -21981,7 +21981,7 @@
         <v>29</v>
       </c>
       <c r="D1053">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1053" t="s">
         <v>30</v>
@@ -21998,7 +21998,7 @@
         <v>29</v>
       </c>
       <c r="D1054">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1054" t="s">
         <v>30</v>
@@ -22015,7 +22015,7 @@
         <v>29</v>
       </c>
       <c r="D1055">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1055" t="s">
         <v>30</v>
@@ -22032,7 +22032,7 @@
         <v>29</v>
       </c>
       <c r="D1056">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E1056" t="s">
         <v>30</v>
@@ -22049,7 +22049,7 @@
         <v>29</v>
       </c>
       <c r="D1057">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E1057" t="s">
         <v>30</v>
@@ -22066,7 +22066,7 @@
         <v>29</v>
       </c>
       <c r="D1058">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1058" t="s">
         <v>30</v>
@@ -22083,7 +22083,7 @@
         <v>29</v>
       </c>
       <c r="D1059">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1059" t="s">
         <v>30</v>
@@ -22100,7 +22100,7 @@
         <v>29</v>
       </c>
       <c r="D1060">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1060" t="s">
         <v>30</v>
@@ -22117,7 +22117,7 @@
         <v>29</v>
       </c>
       <c r="D1061">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1061" t="s">
         <v>30</v>
@@ -22134,7 +22134,7 @@
         <v>29</v>
       </c>
       <c r="D1062">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E1062" t="s">
         <v>30</v>
@@ -22151,7 +22151,7 @@
         <v>29</v>
       </c>
       <c r="D1063">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1063" t="s">
         <v>30</v>
@@ -22185,7 +22185,7 @@
         <v>29</v>
       </c>
       <c r="D1065">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1065" t="s">
         <v>30</v>
@@ -22202,7 +22202,7 @@
         <v>29</v>
       </c>
       <c r="D1066">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E1066" t="s">
         <v>30</v>
@@ -22219,7 +22219,7 @@
         <v>29</v>
       </c>
       <c r="D1067">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1067" t="s">
         <v>30</v>
@@ -22236,7 +22236,7 @@
         <v>29</v>
       </c>
       <c r="D1068">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1068" t="s">
         <v>30</v>
@@ -22253,7 +22253,7 @@
         <v>29</v>
       </c>
       <c r="D1069">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1069" t="s">
         <v>30</v>
@@ -22270,7 +22270,7 @@
         <v>29</v>
       </c>
       <c r="D1070">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1070" t="s">
         <v>30</v>
@@ -22287,7 +22287,7 @@
         <v>29</v>
       </c>
       <c r="D1071">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1071" t="s">
         <v>30</v>
@@ -22304,7 +22304,7 @@
         <v>29</v>
       </c>
       <c r="D1072">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1072" t="s">
         <v>30</v>
@@ -22321,7 +22321,7 @@
         <v>29</v>
       </c>
       <c r="D1073">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1073" t="s">
         <v>30</v>
@@ -22338,7 +22338,7 @@
         <v>29</v>
       </c>
       <c r="D1074">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1074" t="s">
         <v>30</v>
@@ -22355,7 +22355,7 @@
         <v>29</v>
       </c>
       <c r="D1075">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E1075" t="s">
         <v>30</v>
@@ -22372,7 +22372,7 @@
         <v>29</v>
       </c>
       <c r="D1076">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1076" t="s">
         <v>30</v>
@@ -22389,7 +22389,7 @@
         <v>29</v>
       </c>
       <c r="D1077">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E1077" t="s">
         <v>30</v>
@@ -22406,7 +22406,7 @@
         <v>29</v>
       </c>
       <c r="D1078">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1078" t="s">
         <v>30</v>
@@ -22423,7 +22423,7 @@
         <v>29</v>
       </c>
       <c r="D1079">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1079" t="s">
         <v>30</v>
@@ -22440,7 +22440,7 @@
         <v>29</v>
       </c>
       <c r="D1080">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1080" t="s">
         <v>30</v>
@@ -22457,7 +22457,7 @@
         <v>29</v>
       </c>
       <c r="D1081">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1081" t="s">
         <v>30</v>
@@ -22474,7 +22474,7 @@
         <v>29</v>
       </c>
       <c r="D1082">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1082" t="s">
         <v>30</v>
@@ -22491,7 +22491,7 @@
         <v>29</v>
       </c>
       <c r="D1083">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1083" t="s">
         <v>30</v>
@@ -22508,7 +22508,7 @@
         <v>29</v>
       </c>
       <c r="D1084">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1084" t="s">
         <v>30</v>
@@ -22525,7 +22525,7 @@
         <v>29</v>
       </c>
       <c r="D1085">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E1085" t="s">
         <v>30</v>
@@ -22542,7 +22542,7 @@
         <v>29</v>
       </c>
       <c r="D1086">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E1086" t="s">
         <v>30</v>
@@ -22559,7 +22559,7 @@
         <v>29</v>
       </c>
       <c r="D1087">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E1087" t="s">
         <v>30</v>
@@ -22576,7 +22576,7 @@
         <v>29</v>
       </c>
       <c r="D1088">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1088" t="s">
         <v>30</v>
@@ -22593,7 +22593,7 @@
         <v>29</v>
       </c>
       <c r="D1089">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1089" t="s">
         <v>30</v>
@@ -22610,7 +22610,7 @@
         <v>29</v>
       </c>
       <c r="D1090">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1090" t="s">
         <v>30</v>
@@ -22627,7 +22627,7 @@
         <v>29</v>
       </c>
       <c r="D1091">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E1091" t="s">
         <v>30</v>
@@ -22644,7 +22644,7 @@
         <v>29</v>
       </c>
       <c r="D1092">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1092" t="s">
         <v>30</v>
@@ -22661,7 +22661,7 @@
         <v>29</v>
       </c>
       <c r="D1093">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E1093" t="s">
         <v>30</v>
@@ -22695,7 +22695,7 @@
         <v>29</v>
       </c>
       <c r="D1095">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1095" t="s">
         <v>30</v>
@@ -22712,7 +22712,7 @@
         <v>29</v>
       </c>
       <c r="D1096">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E1096" t="s">
         <v>30</v>
@@ -22729,7 +22729,7 @@
         <v>29</v>
       </c>
       <c r="D1097">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E1097" t="s">
         <v>30</v>
@@ -22746,7 +22746,7 @@
         <v>29</v>
       </c>
       <c r="D1098">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1098" t="s">
         <v>30</v>
@@ -22763,7 +22763,7 @@
         <v>29</v>
       </c>
       <c r="D1099">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1099" t="s">
         <v>30</v>
@@ -22780,7 +22780,7 @@
         <v>29</v>
       </c>
       <c r="D1100">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1100" t="s">
         <v>30</v>
@@ -22814,7 +22814,7 @@
         <v>29</v>
       </c>
       <c r="D1102">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1102" t="s">
         <v>30</v>
@@ -22831,7 +22831,7 @@
         <v>29</v>
       </c>
       <c r="D1103">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E1103" t="s">
         <v>30</v>
@@ -22848,7 +22848,7 @@
         <v>29</v>
       </c>
       <c r="D1104">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1104" t="s">
         <v>30</v>
@@ -22865,7 +22865,7 @@
         <v>29</v>
       </c>
       <c r="D1105">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1105" t="s">
         <v>30</v>
@@ -22882,7 +22882,7 @@
         <v>29</v>
       </c>
       <c r="D1106">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1106" t="s">
         <v>30</v>
@@ -22899,7 +22899,7 @@
         <v>29</v>
       </c>
       <c r="D1107">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1107" t="s">
         <v>30</v>
@@ -22916,7 +22916,7 @@
         <v>29</v>
       </c>
       <c r="D1108">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1108" t="s">
         <v>30</v>
@@ -22933,7 +22933,7 @@
         <v>29</v>
       </c>
       <c r="D1109">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1109" t="s">
         <v>30</v>
@@ -22950,7 +22950,7 @@
         <v>29</v>
       </c>
       <c r="D1110">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1110" t="s">
         <v>30</v>
@@ -22967,7 +22967,7 @@
         <v>29</v>
       </c>
       <c r="D1111">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1111" t="s">
         <v>30</v>
@@ -22984,7 +22984,7 @@
         <v>29</v>
       </c>
       <c r="D1112">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1112" t="s">
         <v>30</v>

--- a/reports/latest/android-report.xlsx
+++ b/reports/latest/android-report.xlsx
@@ -39,7 +39,7 @@
     <t>Total Duration (s)</t>
   </si>
   <si>
-    <t>0.00</t>
+    <t>0.01</t>
   </si>
   <si>
     <t>Category</t>
@@ -4114,7 +4114,7 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>572</v>
+        <v>1055</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -4131,7 +4131,7 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -4148,7 +4148,7 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -4165,7 +4165,7 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -4182,7 +4182,7 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -4199,7 +4199,7 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -4216,7 +4216,7 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -4233,7 +4233,7 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -4250,7 +4250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
@@ -4267,7 +4267,7 @@
         <v>29</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -4284,7 +4284,7 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -4301,7 +4301,7 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -4318,7 +4318,7 @@
         <v>29</v>
       </c>
       <c r="D14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4335,7 +4335,7 @@
         <v>29</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -4369,7 +4369,7 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -4386,7 +4386,7 @@
         <v>29</v>
       </c>
       <c r="D18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -4403,7 +4403,7 @@
         <v>29</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
@@ -4420,7 +4420,7 @@
         <v>29</v>
       </c>
       <c r="D20">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
@@ -4437,7 +4437,7 @@
         <v>29</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
         <v>30</v>
@@ -4454,7 +4454,7 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E22" t="s">
         <v>30</v>
@@ -4471,7 +4471,7 @@
         <v>29</v>
       </c>
       <c r="D23">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E23" t="s">
         <v>30</v>
@@ -4488,7 +4488,7 @@
         <v>29</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" t="s">
         <v>30</v>
@@ -4505,7 +4505,7 @@
         <v>29</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
         <v>30</v>
@@ -4522,7 +4522,7 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
         <v>30</v>
@@ -4539,7 +4539,7 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
         <v>30</v>
@@ -4556,7 +4556,7 @@
         <v>29</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
         <v>30</v>
@@ -4590,7 +4590,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
         <v>30</v>
@@ -4607,7 +4607,7 @@
         <v>29</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
         <v>30</v>
@@ -4624,7 +4624,7 @@
         <v>29</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
         <v>30</v>
@@ -4641,7 +4641,7 @@
         <v>29</v>
       </c>
       <c r="D33">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
         <v>30</v>
@@ -4675,7 +4675,7 @@
         <v>29</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" t="s">
         <v>30</v>
@@ -4692,7 +4692,7 @@
         <v>29</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
         <v>30</v>
@@ -4709,7 +4709,7 @@
         <v>29</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
         <v>30</v>
@@ -4726,7 +4726,7 @@
         <v>29</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
         <v>30</v>
@@ -4743,7 +4743,7 @@
         <v>29</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
         <v>30</v>
@@ -4760,7 +4760,7 @@
         <v>29</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s">
         <v>30</v>
@@ -4777,7 +4777,7 @@
         <v>29</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
         <v>30</v>
@@ -4794,7 +4794,7 @@
         <v>29</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E42" t="s">
         <v>30</v>
@@ -4811,7 +4811,7 @@
         <v>29</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E43" t="s">
         <v>30</v>
@@ -4828,7 +4828,7 @@
         <v>29</v>
       </c>
       <c r="D44">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E44" t="s">
         <v>30</v>
@@ -4845,7 +4845,7 @@
         <v>29</v>
       </c>
       <c r="D45">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E45" t="s">
         <v>30</v>
@@ -4862,7 +4862,7 @@
         <v>29</v>
       </c>
       <c r="D46">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E46" t="s">
         <v>30</v>
@@ -4879,7 +4879,7 @@
         <v>29</v>
       </c>
       <c r="D47">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
         <v>30</v>
@@ -4896,7 +4896,7 @@
         <v>29</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
         <v>30</v>
@@ -4913,7 +4913,7 @@
         <v>29</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E49" t="s">
         <v>30</v>
@@ -4930,7 +4930,7 @@
         <v>29</v>
       </c>
       <c r="D50">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E50" t="s">
         <v>30</v>
@@ -4964,7 +4964,7 @@
         <v>29</v>
       </c>
       <c r="D52">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E52" t="s">
         <v>30</v>
@@ -4981,7 +4981,7 @@
         <v>29</v>
       </c>
       <c r="D53">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E53" t="s">
         <v>30</v>
@@ -4998,7 +4998,7 @@
         <v>29</v>
       </c>
       <c r="D54">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E54" t="s">
         <v>30</v>
@@ -5015,7 +5015,7 @@
         <v>29</v>
       </c>
       <c r="D55">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
         <v>30</v>
@@ -5032,7 +5032,7 @@
         <v>29</v>
       </c>
       <c r="D56">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E56" t="s">
         <v>30</v>
@@ -5049,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="D57">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
         <v>30</v>
@@ -5066,7 +5066,7 @@
         <v>29</v>
       </c>
       <c r="D58">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E58" t="s">
         <v>30</v>
@@ -5083,7 +5083,7 @@
         <v>29</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E59" t="s">
         <v>30</v>
@@ -5100,7 +5100,7 @@
         <v>29</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E60" t="s">
         <v>30</v>
@@ -5117,7 +5117,7 @@
         <v>29</v>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s">
         <v>30</v>
@@ -5134,7 +5134,7 @@
         <v>29</v>
       </c>
       <c r="D62">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E62" t="s">
         <v>30</v>
@@ -5168,7 +5168,7 @@
         <v>29</v>
       </c>
       <c r="D64">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E64" t="s">
         <v>30</v>
@@ -5185,7 +5185,7 @@
         <v>29</v>
       </c>
       <c r="D65">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E65" t="s">
         <v>30</v>
@@ -5202,7 +5202,7 @@
         <v>29</v>
       </c>
       <c r="D66">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E66" t="s">
         <v>30</v>
@@ -5219,7 +5219,7 @@
         <v>29</v>
       </c>
       <c r="D67">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E67" t="s">
         <v>30</v>
@@ -5236,7 +5236,7 @@
         <v>29</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E68" t="s">
         <v>30</v>
@@ -5253,7 +5253,7 @@
         <v>29</v>
       </c>
       <c r="D69">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E69" t="s">
         <v>30</v>
@@ -5270,7 +5270,7 @@
         <v>29</v>
       </c>
       <c r="D70">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>30</v>
@@ -5287,7 +5287,7 @@
         <v>29</v>
       </c>
       <c r="D71">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
         <v>30</v>
@@ -5304,7 +5304,7 @@
         <v>29</v>
       </c>
       <c r="D72">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
         <v>30</v>
@@ -5321,7 +5321,7 @@
         <v>29</v>
       </c>
       <c r="D73">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E73" t="s">
         <v>30</v>
@@ -5338,7 +5338,7 @@
         <v>29</v>
       </c>
       <c r="D74">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E74" t="s">
         <v>30</v>
@@ -5355,7 +5355,7 @@
         <v>29</v>
       </c>
       <c r="D75">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E75" t="s">
         <v>30</v>
@@ -5372,7 +5372,7 @@
         <v>29</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
         <v>30</v>
@@ -5389,7 +5389,7 @@
         <v>29</v>
       </c>
       <c r="D77">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E77" t="s">
         <v>30</v>
@@ -5406,7 +5406,7 @@
         <v>29</v>
       </c>
       <c r="D78">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E78" t="s">
         <v>30</v>
@@ -5423,7 +5423,7 @@
         <v>29</v>
       </c>
       <c r="D79">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E79" t="s">
         <v>30</v>
@@ -5440,7 +5440,7 @@
         <v>29</v>
       </c>
       <c r="D80">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E80" t="s">
         <v>30</v>
@@ -5457,7 +5457,7 @@
         <v>29</v>
       </c>
       <c r="D81">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E81" t="s">
         <v>30</v>
@@ -5474,7 +5474,7 @@
         <v>29</v>
       </c>
       <c r="D82">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E82" t="s">
         <v>30</v>
@@ -5491,7 +5491,7 @@
         <v>29</v>
       </c>
       <c r="D83">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E83" t="s">
         <v>30</v>
@@ -5508,7 +5508,7 @@
         <v>29</v>
       </c>
       <c r="D84">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E84" t="s">
         <v>30</v>
@@ -5525,7 +5525,7 @@
         <v>29</v>
       </c>
       <c r="D85">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E85" t="s">
         <v>30</v>
@@ -5542,7 +5542,7 @@
         <v>29</v>
       </c>
       <c r="D86">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E86" t="s">
         <v>30</v>
@@ -5559,7 +5559,7 @@
         <v>29</v>
       </c>
       <c r="D87">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E87" t="s">
         <v>30</v>
@@ -5576,7 +5576,7 @@
         <v>29</v>
       </c>
       <c r="D88">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E88" t="s">
         <v>30</v>
@@ -5593,7 +5593,7 @@
         <v>29</v>
       </c>
       <c r="D89">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E89" t="s">
         <v>30</v>
@@ -5610,7 +5610,7 @@
         <v>29</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E90" t="s">
         <v>30</v>
@@ -5627,7 +5627,7 @@
         <v>29</v>
       </c>
       <c r="D91">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E91" t="s">
         <v>30</v>
@@ -5644,7 +5644,7 @@
         <v>29</v>
       </c>
       <c r="D92">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E92" t="s">
         <v>30</v>
@@ -5678,7 +5678,7 @@
         <v>29</v>
       </c>
       <c r="D94">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E94" t="s">
         <v>30</v>
@@ -5695,7 +5695,7 @@
         <v>29</v>
       </c>
       <c r="D95">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E95" t="s">
         <v>30</v>
@@ -5712,7 +5712,7 @@
         <v>29</v>
       </c>
       <c r="D96">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E96" t="s">
         <v>30</v>
@@ -5729,7 +5729,7 @@
         <v>29</v>
       </c>
       <c r="D97">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E97" t="s">
         <v>30</v>
@@ -5746,7 +5746,7 @@
         <v>29</v>
       </c>
       <c r="D98">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E98" t="s">
         <v>30</v>
@@ -5763,7 +5763,7 @@
         <v>29</v>
       </c>
       <c r="D99">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E99" t="s">
         <v>30</v>
@@ -5780,7 +5780,7 @@
         <v>29</v>
       </c>
       <c r="D100">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E100" t="s">
         <v>30</v>
@@ -5797,7 +5797,7 @@
         <v>29</v>
       </c>
       <c r="D101">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E101" t="s">
         <v>30</v>
@@ -5814,7 +5814,7 @@
         <v>29</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E102" t="s">
         <v>30</v>
@@ -5831,7 +5831,7 @@
         <v>29</v>
       </c>
       <c r="D103">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E103" t="s">
         <v>30</v>
@@ -5848,7 +5848,7 @@
         <v>29</v>
       </c>
       <c r="D104">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E104" t="s">
         <v>30</v>
@@ -5865,7 +5865,7 @@
         <v>29</v>
       </c>
       <c r="D105">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E105" t="s">
         <v>30</v>
@@ -5882,7 +5882,7 @@
         <v>29</v>
       </c>
       <c r="D106">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E106" t="s">
         <v>30</v>
@@ -5899,7 +5899,7 @@
         <v>29</v>
       </c>
       <c r="D107">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E107" t="s">
         <v>30</v>
@@ -5916,7 +5916,7 @@
         <v>29</v>
       </c>
       <c r="D108">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E108" t="s">
         <v>30</v>
@@ -5933,7 +5933,7 @@
         <v>29</v>
       </c>
       <c r="D109">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E109" t="s">
         <v>30</v>
@@ -5967,7 +5967,7 @@
         <v>29</v>
       </c>
       <c r="D111">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E111" t="s">
         <v>30</v>
@@ -5984,7 +5984,7 @@
         <v>29</v>
       </c>
       <c r="D112">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E112" t="s">
         <v>30</v>
@@ -6001,7 +6001,7 @@
         <v>29</v>
       </c>
       <c r="D113">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
         <v>30</v>
@@ -6018,7 +6018,7 @@
         <v>29</v>
       </c>
       <c r="D114">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E114" t="s">
         <v>30</v>
@@ -6035,7 +6035,7 @@
         <v>29</v>
       </c>
       <c r="D115">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E115" t="s">
         <v>30</v>
@@ -6052,7 +6052,7 @@
         <v>29</v>
       </c>
       <c r="D116">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E116" t="s">
         <v>30</v>
@@ -6069,7 +6069,7 @@
         <v>29</v>
       </c>
       <c r="D117">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E117" t="s">
         <v>30</v>
@@ -6086,7 +6086,7 @@
         <v>29</v>
       </c>
       <c r="D118">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E118" t="s">
         <v>30</v>
@@ -6103,7 +6103,7 @@
         <v>29</v>
       </c>
       <c r="D119">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E119" t="s">
         <v>30</v>
@@ -6120,7 +6120,7 @@
         <v>29</v>
       </c>
       <c r="D120">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E120" t="s">
         <v>30</v>
@@ -6137,7 +6137,7 @@
         <v>29</v>
       </c>
       <c r="D121">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E121" t="s">
         <v>30</v>
@@ -6154,7 +6154,7 @@
         <v>29</v>
       </c>
       <c r="D122">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E122" t="s">
         <v>30</v>
@@ -6171,7 +6171,7 @@
         <v>29</v>
       </c>
       <c r="D123">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E123" t="s">
         <v>30</v>
@@ -6188,7 +6188,7 @@
         <v>29</v>
       </c>
       <c r="D124">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E124" t="s">
         <v>30</v>
@@ -6205,7 +6205,7 @@
         <v>29</v>
       </c>
       <c r="D125">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E125" t="s">
         <v>30</v>
@@ -6222,7 +6222,7 @@
         <v>29</v>
       </c>
       <c r="D126">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E126" t="s">
         <v>30</v>
@@ -6239,7 +6239,7 @@
         <v>29</v>
       </c>
       <c r="D127">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E127" t="s">
         <v>30</v>
@@ -6256,7 +6256,7 @@
         <v>29</v>
       </c>
       <c r="D128">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E128" t="s">
         <v>30</v>
@@ -6273,7 +6273,7 @@
         <v>29</v>
       </c>
       <c r="D129">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E129" t="s">
         <v>30</v>
@@ -6290,7 +6290,7 @@
         <v>29</v>
       </c>
       <c r="D130">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E130" t="s">
         <v>30</v>
@@ -6307,7 +6307,7 @@
         <v>29</v>
       </c>
       <c r="D131">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E131" t="s">
         <v>30</v>
@@ -6324,7 +6324,7 @@
         <v>29</v>
       </c>
       <c r="D132">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E132" t="s">
         <v>30</v>
@@ -6341,7 +6341,7 @@
         <v>29</v>
       </c>
       <c r="D133">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E133" t="s">
         <v>30</v>
@@ -6358,7 +6358,7 @@
         <v>29</v>
       </c>
       <c r="D134">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E134" t="s">
         <v>30</v>
@@ -6375,7 +6375,7 @@
         <v>29</v>
       </c>
       <c r="D135">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E135" t="s">
         <v>30</v>
@@ -6392,7 +6392,7 @@
         <v>29</v>
       </c>
       <c r="D136">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E136" t="s">
         <v>30</v>
@@ -6409,7 +6409,7 @@
         <v>29</v>
       </c>
       <c r="D137">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E137" t="s">
         <v>30</v>
@@ -6460,7 +6460,7 @@
         <v>29</v>
       </c>
       <c r="D140">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E140" t="s">
         <v>30</v>
@@ -6477,7 +6477,7 @@
         <v>29</v>
       </c>
       <c r="D141">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E141" t="s">
         <v>30</v>
@@ -6494,7 +6494,7 @@
         <v>29</v>
       </c>
       <c r="D142">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E142" t="s">
         <v>30</v>
@@ -6511,7 +6511,7 @@
         <v>29</v>
       </c>
       <c r="D143">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E143" t="s">
         <v>30</v>
@@ -6528,7 +6528,7 @@
         <v>29</v>
       </c>
       <c r="D144">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E144" t="s">
         <v>30</v>
@@ -6545,7 +6545,7 @@
         <v>29</v>
       </c>
       <c r="D145">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E145" t="s">
         <v>30</v>
@@ -6562,7 +6562,7 @@
         <v>29</v>
       </c>
       <c r="D146">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E146" t="s">
         <v>30</v>
@@ -6579,7 +6579,7 @@
         <v>29</v>
       </c>
       <c r="D147">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E147" t="s">
         <v>30</v>
@@ -6596,7 +6596,7 @@
         <v>29</v>
       </c>
       <c r="D148">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E148" t="s">
         <v>30</v>
@@ -6613,7 +6613,7 @@
         <v>29</v>
       </c>
       <c r="D149">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E149" t="s">
         <v>30</v>
@@ -6630,7 +6630,7 @@
         <v>29</v>
       </c>
       <c r="D150">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E150" t="s">
         <v>30</v>
@@ -6647,7 +6647,7 @@
         <v>29</v>
       </c>
       <c r="D151">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E151" t="s">
         <v>30</v>
@@ -6664,7 +6664,7 @@
         <v>29</v>
       </c>
       <c r="D152">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E152" t="s">
         <v>30</v>
@@ -6681,7 +6681,7 @@
         <v>29</v>
       </c>
       <c r="D153">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E153" t="s">
         <v>30</v>
@@ -6698,7 +6698,7 @@
         <v>29</v>
       </c>
       <c r="D154">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E154" t="s">
         <v>30</v>
@@ -6715,7 +6715,7 @@
         <v>29</v>
       </c>
       <c r="D155">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E155" t="s">
         <v>30</v>
@@ -6732,7 +6732,7 @@
         <v>29</v>
       </c>
       <c r="D156">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E156" t="s">
         <v>30</v>
@@ -6749,7 +6749,7 @@
         <v>29</v>
       </c>
       <c r="D157">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E157" t="s">
         <v>30</v>
@@ -6766,7 +6766,7 @@
         <v>29</v>
       </c>
       <c r="D158">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E158" t="s">
         <v>30</v>
@@ -6783,7 +6783,7 @@
         <v>29</v>
       </c>
       <c r="D159">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s">
         <v>30</v>
@@ -6800,7 +6800,7 @@
         <v>29</v>
       </c>
       <c r="D160">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E160" t="s">
         <v>30</v>
@@ -6817,7 +6817,7 @@
         <v>29</v>
       </c>
       <c r="D161">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E161" t="s">
         <v>30</v>
@@ -6851,7 +6851,7 @@
         <v>29</v>
       </c>
       <c r="D163">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E163" t="s">
         <v>30</v>
@@ -6868,7 +6868,7 @@
         <v>29</v>
       </c>
       <c r="D164">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E164" t="s">
         <v>30</v>
@@ -6885,7 +6885,7 @@
         <v>29</v>
       </c>
       <c r="D165">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E165" t="s">
         <v>30</v>
@@ -6902,7 +6902,7 @@
         <v>29</v>
       </c>
       <c r="D166">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E166" t="s">
         <v>30</v>
@@ -6919,7 +6919,7 @@
         <v>29</v>
       </c>
       <c r="D167">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E167" t="s">
         <v>30</v>
@@ -6936,7 +6936,7 @@
         <v>29</v>
       </c>
       <c r="D168">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E168" t="s">
         <v>30</v>
@@ -6953,7 +6953,7 @@
         <v>29</v>
       </c>
       <c r="D169">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E169" t="s">
         <v>30</v>
@@ -6970,7 +6970,7 @@
         <v>29</v>
       </c>
       <c r="D170">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E170" t="s">
         <v>30</v>
@@ -6987,7 +6987,7 @@
         <v>29</v>
       </c>
       <c r="D171">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E171" t="s">
         <v>30</v>
@@ -7004,7 +7004,7 @@
         <v>29</v>
       </c>
       <c r="D172">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E172" t="s">
         <v>30</v>
@@ -7021,7 +7021,7 @@
         <v>29</v>
       </c>
       <c r="D173">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E173" t="s">
         <v>30</v>
@@ -7038,7 +7038,7 @@
         <v>29</v>
       </c>
       <c r="D174">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E174" t="s">
         <v>30</v>
@@ -7055,7 +7055,7 @@
         <v>29</v>
       </c>
       <c r="D175">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E175" t="s">
         <v>30</v>
@@ -7072,7 +7072,7 @@
         <v>29</v>
       </c>
       <c r="D176">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E176" t="s">
         <v>30</v>
@@ -7089,7 +7089,7 @@
         <v>29</v>
       </c>
       <c r="D177">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E177" t="s">
         <v>30</v>
@@ -7123,7 +7123,7 @@
         <v>29</v>
       </c>
       <c r="D179">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E179" t="s">
         <v>30</v>
@@ -7140,7 +7140,7 @@
         <v>29</v>
       </c>
       <c r="D180">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E180" t="s">
         <v>30</v>
@@ -7174,7 +7174,7 @@
         <v>29</v>
       </c>
       <c r="D182">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E182" t="s">
         <v>30</v>
@@ -7191,7 +7191,7 @@
         <v>29</v>
       </c>
       <c r="D183">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E183" t="s">
         <v>30</v>
@@ -7208,7 +7208,7 @@
         <v>29</v>
       </c>
       <c r="D184">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E184" t="s">
         <v>30</v>
@@ -7225,7 +7225,7 @@
         <v>29</v>
       </c>
       <c r="D185">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E185" t="s">
         <v>30</v>
@@ -7242,7 +7242,7 @@
         <v>29</v>
       </c>
       <c r="D186">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E186" t="s">
         <v>30</v>
@@ -7259,7 +7259,7 @@
         <v>29</v>
       </c>
       <c r="D187">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E187" t="s">
         <v>30</v>
@@ -7276,7 +7276,7 @@
         <v>29</v>
       </c>
       <c r="D188">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E188" t="s">
         <v>30</v>
@@ -7293,7 +7293,7 @@
         <v>29</v>
       </c>
       <c r="D189">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E189" t="s">
         <v>30</v>
@@ -7310,7 +7310,7 @@
         <v>29</v>
       </c>
       <c r="D190">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E190" t="s">
         <v>30</v>
@@ -7327,7 +7327,7 @@
         <v>29</v>
       </c>
       <c r="D191">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E191" t="s">
         <v>30</v>
@@ -7344,7 +7344,7 @@
         <v>29</v>
       </c>
       <c r="D192">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E192" t="s">
         <v>30</v>
@@ -7361,7 +7361,7 @@
         <v>29</v>
       </c>
       <c r="D193">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E193" t="s">
         <v>30</v>
@@ -7378,7 +7378,7 @@
         <v>29</v>
       </c>
       <c r="D194">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E194" t="s">
         <v>30</v>
@@ -7395,7 +7395,7 @@
         <v>29</v>
       </c>
       <c r="D195">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E195" t="s">
         <v>30</v>
@@ -7412,7 +7412,7 @@
         <v>29</v>
       </c>
       <c r="D196">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E196" t="s">
         <v>30</v>
@@ -7429,7 +7429,7 @@
         <v>29</v>
       </c>
       <c r="D197">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E197" t="s">
         <v>30</v>
@@ -7446,7 +7446,7 @@
         <v>29</v>
       </c>
       <c r="D198">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E198" t="s">
         <v>30</v>
@@ -7463,7 +7463,7 @@
         <v>29</v>
       </c>
       <c r="D199">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E199" t="s">
         <v>30</v>
@@ -7480,7 +7480,7 @@
         <v>29</v>
       </c>
       <c r="D200">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E200" t="s">
         <v>30</v>
@@ -7514,7 +7514,7 @@
         <v>29</v>
       </c>
       <c r="D202">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E202" t="s">
         <v>30</v>
@@ -7531,7 +7531,7 @@
         <v>29</v>
       </c>
       <c r="D203">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E203" t="s">
         <v>30</v>
@@ -7548,7 +7548,7 @@
         <v>29</v>
       </c>
       <c r="D204">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E204" t="s">
         <v>30</v>
@@ -7565,7 +7565,7 @@
         <v>29</v>
       </c>
       <c r="D205">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E205" t="s">
         <v>30</v>
@@ -7582,7 +7582,7 @@
         <v>29</v>
       </c>
       <c r="D206">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E206" t="s">
         <v>30</v>
@@ -7599,7 +7599,7 @@
         <v>29</v>
       </c>
       <c r="D207">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E207" t="s">
         <v>30</v>
@@ -7616,7 +7616,7 @@
         <v>29</v>
       </c>
       <c r="D208">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E208" t="s">
         <v>30</v>
@@ -7633,7 +7633,7 @@
         <v>29</v>
       </c>
       <c r="D209">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E209" t="s">
         <v>30</v>
@@ -7650,7 +7650,7 @@
         <v>29</v>
       </c>
       <c r="D210">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E210" t="s">
         <v>30</v>
@@ -7667,7 +7667,7 @@
         <v>29</v>
       </c>
       <c r="D211">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E211" t="s">
         <v>30</v>
@@ -7684,7 +7684,7 @@
         <v>29</v>
       </c>
       <c r="D212">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E212" t="s">
         <v>30</v>
@@ -7718,7 +7718,7 @@
         <v>29</v>
       </c>
       <c r="D214">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E214" t="s">
         <v>30</v>
@@ -7735,7 +7735,7 @@
         <v>29</v>
       </c>
       <c r="D215">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E215" t="s">
         <v>30</v>
@@ -7769,7 +7769,7 @@
         <v>29</v>
       </c>
       <c r="D217">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E217" t="s">
         <v>30</v>
@@ -7786,7 +7786,7 @@
         <v>29</v>
       </c>
       <c r="D218">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E218" t="s">
         <v>30</v>
@@ -7803,7 +7803,7 @@
         <v>29</v>
       </c>
       <c r="D219">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E219" t="s">
         <v>30</v>
@@ -7820,7 +7820,7 @@
         <v>29</v>
       </c>
       <c r="D220">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E220" t="s">
         <v>30</v>
@@ -7854,7 +7854,7 @@
         <v>29</v>
       </c>
       <c r="D222">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E222" t="s">
         <v>30</v>
@@ -7871,7 +7871,7 @@
         <v>29</v>
       </c>
       <c r="D223">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E223" t="s">
         <v>30</v>
@@ -7888,7 +7888,7 @@
         <v>29</v>
       </c>
       <c r="D224">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E224" t="s">
         <v>30</v>
@@ -7905,7 +7905,7 @@
         <v>29</v>
       </c>
       <c r="D225">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E225" t="s">
         <v>30</v>
@@ -7922,7 +7922,7 @@
         <v>29</v>
       </c>
       <c r="D226">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E226" t="s">
         <v>30</v>
@@ -7939,7 +7939,7 @@
         <v>29</v>
       </c>
       <c r="D227">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E227" t="s">
         <v>30</v>
@@ -7956,7 +7956,7 @@
         <v>29</v>
       </c>
       <c r="D228">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E228" t="s">
         <v>30</v>
@@ -7973,7 +7973,7 @@
         <v>29</v>
       </c>
       <c r="D229">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E229" t="s">
         <v>30</v>
@@ -7990,7 +7990,7 @@
         <v>29</v>
       </c>
       <c r="D230">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E230" t="s">
         <v>30</v>
@@ -8007,7 +8007,7 @@
         <v>29</v>
       </c>
       <c r="D231">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E231" t="s">
         <v>30</v>
@@ -8024,7 +8024,7 @@
         <v>29</v>
       </c>
       <c r="D232">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E232" t="s">
         <v>30</v>
@@ -8041,7 +8041,7 @@
         <v>29</v>
       </c>
       <c r="D233">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E233" t="s">
         <v>30</v>
@@ -8058,7 +8058,7 @@
         <v>29</v>
       </c>
       <c r="D234">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E234" t="s">
         <v>30</v>
@@ -8075,7 +8075,7 @@
         <v>29</v>
       </c>
       <c r="D235">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E235" t="s">
         <v>30</v>
@@ -8092,7 +8092,7 @@
         <v>29</v>
       </c>
       <c r="D236">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E236" t="s">
         <v>30</v>
@@ -8109,7 +8109,7 @@
         <v>29</v>
       </c>
       <c r="D237">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E237" t="s">
         <v>30</v>
@@ -8126,7 +8126,7 @@
         <v>29</v>
       </c>
       <c r="D238">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E238" t="s">
         <v>30</v>
@@ -8143,7 +8143,7 @@
         <v>29</v>
       </c>
       <c r="D239">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E239" t="s">
         <v>30</v>
@@ -8160,7 +8160,7 @@
         <v>29</v>
       </c>
       <c r="D240">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E240" t="s">
         <v>30</v>
@@ -8177,7 +8177,7 @@
         <v>29</v>
       </c>
       <c r="D241">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E241" t="s">
         <v>30</v>
@@ -8194,7 +8194,7 @@
         <v>29</v>
       </c>
       <c r="D242">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E242" t="s">
         <v>30</v>
@@ -8211,7 +8211,7 @@
         <v>29</v>
       </c>
       <c r="D243">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E243" t="s">
         <v>30</v>
@@ -8228,7 +8228,7 @@
         <v>29</v>
       </c>
       <c r="D244">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E244" t="s">
         <v>30</v>
@@ -8245,7 +8245,7 @@
         <v>29</v>
       </c>
       <c r="D245">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E245" t="s">
         <v>30</v>
@@ -8262,7 +8262,7 @@
         <v>29</v>
       </c>
       <c r="D246">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E246" t="s">
         <v>30</v>
@@ -8279,7 +8279,7 @@
         <v>29</v>
       </c>
       <c r="D247">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E247" t="s">
         <v>30</v>
@@ -8296,7 +8296,7 @@
         <v>29</v>
       </c>
       <c r="D248">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E248" t="s">
         <v>30</v>
@@ -8313,7 +8313,7 @@
         <v>29</v>
       </c>
       <c r="D249">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E249" t="s">
         <v>30</v>
@@ -8330,7 +8330,7 @@
         <v>29</v>
       </c>
       <c r="D250">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E250" t="s">
         <v>30</v>
@@ -8347,7 +8347,7 @@
         <v>29</v>
       </c>
       <c r="D251">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E251" t="s">
         <v>30</v>
@@ -8364,7 +8364,7 @@
         <v>29</v>
       </c>
       <c r="D252">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E252" t="s">
         <v>30</v>
@@ -8381,7 +8381,7 @@
         <v>29</v>
       </c>
       <c r="D253">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E253" t="s">
         <v>30</v>
@@ -8398,7 +8398,7 @@
         <v>29</v>
       </c>
       <c r="D254">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E254" t="s">
         <v>30</v>
@@ -8415,7 +8415,7 @@
         <v>29</v>
       </c>
       <c r="D255">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E255" t="s">
         <v>30</v>
@@ -8432,7 +8432,7 @@
         <v>29</v>
       </c>
       <c r="D256">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E256" t="s">
         <v>30</v>
@@ -8449,7 +8449,7 @@
         <v>29</v>
       </c>
       <c r="D257">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E257" t="s">
         <v>30</v>
@@ -8466,7 +8466,7 @@
         <v>29</v>
       </c>
       <c r="D258">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E258" t="s">
         <v>30</v>
@@ -8483,7 +8483,7 @@
         <v>29</v>
       </c>
       <c r="D259">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E259" t="s">
         <v>30</v>
@@ -8500,7 +8500,7 @@
         <v>29</v>
       </c>
       <c r="D260">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E260" t="s">
         <v>30</v>
@@ -8517,7 +8517,7 @@
         <v>29</v>
       </c>
       <c r="D261">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E261" t="s">
         <v>30</v>
@@ -8534,7 +8534,7 @@
         <v>29</v>
       </c>
       <c r="D262">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E262" t="s">
         <v>30</v>
@@ -8551,7 +8551,7 @@
         <v>29</v>
       </c>
       <c r="D263">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E263" t="s">
         <v>30</v>
@@ -8585,7 +8585,7 @@
         <v>29</v>
       </c>
       <c r="D265">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E265" t="s">
         <v>30</v>
@@ -8602,7 +8602,7 @@
         <v>29</v>
       </c>
       <c r="D266">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E266" t="s">
         <v>30</v>
@@ -8619,7 +8619,7 @@
         <v>29</v>
       </c>
       <c r="D267">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E267" t="s">
         <v>30</v>
@@ -8636,7 +8636,7 @@
         <v>29</v>
       </c>
       <c r="D268">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E268" t="s">
         <v>30</v>
@@ -8653,7 +8653,7 @@
         <v>29</v>
       </c>
       <c r="D269">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E269" t="s">
         <v>30</v>
@@ -8670,7 +8670,7 @@
         <v>29</v>
       </c>
       <c r="D270">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E270" t="s">
         <v>30</v>
@@ -8687,7 +8687,7 @@
         <v>29</v>
       </c>
       <c r="D271">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E271" t="s">
         <v>30</v>
@@ -8721,7 +8721,7 @@
         <v>29</v>
       </c>
       <c r="D273">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E273" t="s">
         <v>30</v>
@@ -8738,7 +8738,7 @@
         <v>29</v>
       </c>
       <c r="D274">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E274" t="s">
         <v>30</v>
@@ -8772,7 +8772,7 @@
         <v>29</v>
       </c>
       <c r="D276">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E276" t="s">
         <v>30</v>
@@ -8789,7 +8789,7 @@
         <v>29</v>
       </c>
       <c r="D277">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E277" t="s">
         <v>30</v>
@@ -8806,7 +8806,7 @@
         <v>29</v>
       </c>
       <c r="D278">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E278" t="s">
         <v>30</v>
@@ -8840,7 +8840,7 @@
         <v>29</v>
       </c>
       <c r="D280">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E280" t="s">
         <v>30</v>
@@ -8857,7 +8857,7 @@
         <v>29</v>
       </c>
       <c r="D281">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E281" t="s">
         <v>30</v>
@@ -8874,7 +8874,7 @@
         <v>29</v>
       </c>
       <c r="D282">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E282" t="s">
         <v>30</v>
@@ -8891,7 +8891,7 @@
         <v>29</v>
       </c>
       <c r="D283">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E283" t="s">
         <v>30</v>
@@ -8908,7 +8908,7 @@
         <v>29</v>
       </c>
       <c r="D284">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E284" t="s">
         <v>30</v>
@@ -8925,7 +8925,7 @@
         <v>29</v>
       </c>
       <c r="D285">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E285" t="s">
         <v>30</v>
@@ -8942,7 +8942,7 @@
         <v>29</v>
       </c>
       <c r="D286">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E286" t="s">
         <v>30</v>
@@ -8959,7 +8959,7 @@
         <v>29</v>
       </c>
       <c r="D287">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E287" t="s">
         <v>30</v>
@@ -8976,7 +8976,7 @@
         <v>29</v>
       </c>
       <c r="D288">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E288" t="s">
         <v>30</v>
@@ -8993,7 +8993,7 @@
         <v>29</v>
       </c>
       <c r="D289">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E289" t="s">
         <v>30</v>
@@ -9010,7 +9010,7 @@
         <v>29</v>
       </c>
       <c r="D290">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E290" t="s">
         <v>30</v>
@@ -9027,7 +9027,7 @@
         <v>29</v>
       </c>
       <c r="D291">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E291" t="s">
         <v>30</v>
@@ -9044,7 +9044,7 @@
         <v>29</v>
       </c>
       <c r="D292">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E292" t="s">
         <v>30</v>
@@ -9061,7 +9061,7 @@
         <v>29</v>
       </c>
       <c r="D293">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E293" t="s">
         <v>30</v>
@@ -9078,7 +9078,7 @@
         <v>29</v>
       </c>
       <c r="D294">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E294" t="s">
         <v>30</v>
@@ -9095,7 +9095,7 @@
         <v>29</v>
       </c>
       <c r="D295">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E295" t="s">
         <v>30</v>
@@ -9112,7 +9112,7 @@
         <v>29</v>
       </c>
       <c r="D296">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E296" t="s">
         <v>30</v>
@@ -9146,7 +9146,7 @@
         <v>29</v>
       </c>
       <c r="D298">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E298" t="s">
         <v>30</v>
@@ -9163,7 +9163,7 @@
         <v>29</v>
       </c>
       <c r="D299">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E299" t="s">
         <v>30</v>
@@ -9180,7 +9180,7 @@
         <v>29</v>
       </c>
       <c r="D300">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E300" t="s">
         <v>30</v>
@@ -9197,7 +9197,7 @@
         <v>29</v>
       </c>
       <c r="D301">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E301" t="s">
         <v>30</v>
@@ -9214,7 +9214,7 @@
         <v>29</v>
       </c>
       <c r="D302">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E302" t="s">
         <v>30</v>
@@ -9231,7 +9231,7 @@
         <v>29</v>
       </c>
       <c r="D303">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E303" t="s">
         <v>30</v>
@@ -9248,7 +9248,7 @@
         <v>29</v>
       </c>
       <c r="D304">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E304" t="s">
         <v>30</v>
@@ -9265,7 +9265,7 @@
         <v>29</v>
       </c>
       <c r="D305">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E305" t="s">
         <v>30</v>
@@ -9282,7 +9282,7 @@
         <v>29</v>
       </c>
       <c r="D306">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E306" t="s">
         <v>30</v>
@@ -9299,7 +9299,7 @@
         <v>29</v>
       </c>
       <c r="D307">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E307" t="s">
         <v>30</v>
@@ -9316,7 +9316,7 @@
         <v>29</v>
       </c>
       <c r="D308">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E308" t="s">
         <v>30</v>
@@ -9333,7 +9333,7 @@
         <v>29</v>
       </c>
       <c r="D309">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E309" t="s">
         <v>30</v>
@@ -9350,7 +9350,7 @@
         <v>29</v>
       </c>
       <c r="D310">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E310" t="s">
         <v>30</v>
@@ -9367,7 +9367,7 @@
         <v>29</v>
       </c>
       <c r="D311">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E311" t="s">
         <v>30</v>
@@ -9384,7 +9384,7 @@
         <v>29</v>
       </c>
       <c r="D312">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E312" t="s">
         <v>30</v>
@@ -9401,7 +9401,7 @@
         <v>29</v>
       </c>
       <c r="D313">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E313" t="s">
         <v>30</v>
@@ -9435,7 +9435,7 @@
         <v>29</v>
       </c>
       <c r="D315">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E315" t="s">
         <v>30</v>
@@ -9452,7 +9452,7 @@
         <v>29</v>
       </c>
       <c r="D316">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E316" t="s">
         <v>30</v>
@@ -9469,7 +9469,7 @@
         <v>29</v>
       </c>
       <c r="D317">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E317" t="s">
         <v>30</v>
@@ -9486,7 +9486,7 @@
         <v>29</v>
       </c>
       <c r="D318">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E318" t="s">
         <v>30</v>
@@ -9503,7 +9503,7 @@
         <v>29</v>
       </c>
       <c r="D319">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E319" t="s">
         <v>30</v>
@@ -9520,7 +9520,7 @@
         <v>29</v>
       </c>
       <c r="D320">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E320" t="s">
         <v>30</v>
@@ -9537,7 +9537,7 @@
         <v>29</v>
       </c>
       <c r="D321">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E321" t="s">
         <v>30</v>
@@ -9554,7 +9554,7 @@
         <v>29</v>
       </c>
       <c r="D322">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E322" t="s">
         <v>30</v>
@@ -9571,7 +9571,7 @@
         <v>29</v>
       </c>
       <c r="D323">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E323" t="s">
         <v>30</v>
@@ -9588,7 +9588,7 @@
         <v>29</v>
       </c>
       <c r="D324">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E324" t="s">
         <v>30</v>
@@ -9605,7 +9605,7 @@
         <v>29</v>
       </c>
       <c r="D325">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E325" t="s">
         <v>30</v>
@@ -9622,7 +9622,7 @@
         <v>29</v>
       </c>
       <c r="D326">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E326" t="s">
         <v>30</v>
@@ -9639,7 +9639,7 @@
         <v>29</v>
       </c>
       <c r="D327">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E327" t="s">
         <v>30</v>
@@ -9656,7 +9656,7 @@
         <v>29</v>
       </c>
       <c r="D328">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E328" t="s">
         <v>30</v>
@@ -9673,7 +9673,7 @@
         <v>29</v>
       </c>
       <c r="D329">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E329" t="s">
         <v>30</v>
@@ -9724,7 +9724,7 @@
         <v>29</v>
       </c>
       <c r="D332">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E332" t="s">
         <v>30</v>
@@ -9741,7 +9741,7 @@
         <v>29</v>
       </c>
       <c r="D333">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E333" t="s">
         <v>30</v>
@@ -9758,7 +9758,7 @@
         <v>29</v>
       </c>
       <c r="D334">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E334" t="s">
         <v>30</v>
@@ -9775,7 +9775,7 @@
         <v>29</v>
       </c>
       <c r="D335">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E335" t="s">
         <v>30</v>
@@ -9792,7 +9792,7 @@
         <v>29</v>
       </c>
       <c r="D336">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E336" t="s">
         <v>30</v>
@@ -9809,7 +9809,7 @@
         <v>29</v>
       </c>
       <c r="D337">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E337" t="s">
         <v>30</v>
@@ -9843,7 +9843,7 @@
         <v>29</v>
       </c>
       <c r="D339">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E339" t="s">
         <v>30</v>
@@ -9860,7 +9860,7 @@
         <v>29</v>
       </c>
       <c r="D340">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E340" t="s">
         <v>30</v>
@@ -9894,7 +9894,7 @@
         <v>29</v>
       </c>
       <c r="D342">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E342" t="s">
         <v>30</v>
@@ -9911,7 +9911,7 @@
         <v>29</v>
       </c>
       <c r="D343">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E343" t="s">
         <v>30</v>
@@ -9928,7 +9928,7 @@
         <v>29</v>
       </c>
       <c r="D344">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E344" t="s">
         <v>30</v>
@@ -9945,7 +9945,7 @@
         <v>29</v>
       </c>
       <c r="D345">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E345" t="s">
         <v>30</v>
@@ -9962,7 +9962,7 @@
         <v>29</v>
       </c>
       <c r="D346">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E346" t="s">
         <v>30</v>
@@ -9979,7 +9979,7 @@
         <v>29</v>
       </c>
       <c r="D347">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E347" t="s">
         <v>30</v>
@@ -9996,7 +9996,7 @@
         <v>29</v>
       </c>
       <c r="D348">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E348" t="s">
         <v>30</v>
@@ -10013,7 +10013,7 @@
         <v>29</v>
       </c>
       <c r="D349">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E349" t="s">
         <v>30</v>
@@ -10030,7 +10030,7 @@
         <v>29</v>
       </c>
       <c r="D350">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E350" t="s">
         <v>30</v>
@@ -10047,7 +10047,7 @@
         <v>29</v>
       </c>
       <c r="D351">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E351" t="s">
         <v>30</v>
@@ -10064,7 +10064,7 @@
         <v>29</v>
       </c>
       <c r="D352">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E352" t="s">
         <v>30</v>
@@ -10081,7 +10081,7 @@
         <v>29</v>
       </c>
       <c r="D353">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E353" t="s">
         <v>30</v>
@@ -10098,7 +10098,7 @@
         <v>29</v>
       </c>
       <c r="D354">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E354" t="s">
         <v>30</v>
@@ -10115,7 +10115,7 @@
         <v>29</v>
       </c>
       <c r="D355">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E355" t="s">
         <v>30</v>
@@ -10132,7 +10132,7 @@
         <v>29</v>
       </c>
       <c r="D356">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E356" t="s">
         <v>30</v>
@@ -10149,7 +10149,7 @@
         <v>29</v>
       </c>
       <c r="D357">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E357" t="s">
         <v>30</v>
@@ -10166,7 +10166,7 @@
         <v>29</v>
       </c>
       <c r="D358">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E358" t="s">
         <v>30</v>
@@ -10183,7 +10183,7 @@
         <v>29</v>
       </c>
       <c r="D359">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E359" t="s">
         <v>30</v>
@@ -10200,7 +10200,7 @@
         <v>29</v>
       </c>
       <c r="D360">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E360" t="s">
         <v>30</v>
@@ -10234,7 +10234,7 @@
         <v>29</v>
       </c>
       <c r="D362">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E362" t="s">
         <v>30</v>
@@ -10251,7 +10251,7 @@
         <v>29</v>
       </c>
       <c r="D363">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E363" t="s">
         <v>30</v>
@@ -10285,7 +10285,7 @@
         <v>29</v>
       </c>
       <c r="D365">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E365" t="s">
         <v>30</v>
@@ -10319,7 +10319,7 @@
         <v>29</v>
       </c>
       <c r="D367">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E367" t="s">
         <v>30</v>
@@ -10336,7 +10336,7 @@
         <v>29</v>
       </c>
       <c r="D368">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E368" t="s">
         <v>30</v>
@@ -10353,7 +10353,7 @@
         <v>29</v>
       </c>
       <c r="D369">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E369" t="s">
         <v>30</v>
@@ -10370,7 +10370,7 @@
         <v>29</v>
       </c>
       <c r="D370">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E370" t="s">
         <v>30</v>
@@ -10387,7 +10387,7 @@
         <v>29</v>
       </c>
       <c r="D371">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E371" t="s">
         <v>30</v>
@@ -10404,7 +10404,7 @@
         <v>29</v>
       </c>
       <c r="D372">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E372" t="s">
         <v>30</v>
@@ -10421,7 +10421,7 @@
         <v>29</v>
       </c>
       <c r="D373">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E373" t="s">
         <v>30</v>
@@ -10455,7 +10455,7 @@
         <v>29</v>
       </c>
       <c r="D375">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E375" t="s">
         <v>30</v>
@@ -10472,7 +10472,7 @@
         <v>29</v>
       </c>
       <c r="D376">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E376" t="s">
         <v>30</v>
@@ -10489,7 +10489,7 @@
         <v>29</v>
       </c>
       <c r="D377">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E377" t="s">
         <v>30</v>
@@ -10506,7 +10506,7 @@
         <v>29</v>
       </c>
       <c r="D378">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E378" t="s">
         <v>30</v>
@@ -10523,7 +10523,7 @@
         <v>29</v>
       </c>
       <c r="D379">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E379" t="s">
         <v>30</v>
@@ -10540,7 +10540,7 @@
         <v>29</v>
       </c>
       <c r="D380">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E380" t="s">
         <v>30</v>
@@ -10574,7 +10574,7 @@
         <v>29</v>
       </c>
       <c r="D382">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E382" t="s">
         <v>30</v>
@@ -10591,7 +10591,7 @@
         <v>29</v>
       </c>
       <c r="D383">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E383" t="s">
         <v>30</v>
@@ -10608,7 +10608,7 @@
         <v>29</v>
       </c>
       <c r="D384">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E384" t="s">
         <v>30</v>
@@ -10625,7 +10625,7 @@
         <v>29</v>
       </c>
       <c r="D385">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E385" t="s">
         <v>30</v>
@@ -10642,7 +10642,7 @@
         <v>29</v>
       </c>
       <c r="D386">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E386" t="s">
         <v>30</v>
@@ -10659,7 +10659,7 @@
         <v>29</v>
       </c>
       <c r="D387">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E387" t="s">
         <v>30</v>
@@ -10676,7 +10676,7 @@
         <v>29</v>
       </c>
       <c r="D388">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E388" t="s">
         <v>30</v>
@@ -10693,7 +10693,7 @@
         <v>29</v>
       </c>
       <c r="D389">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E389" t="s">
         <v>30</v>
@@ -10710,7 +10710,7 @@
         <v>29</v>
       </c>
       <c r="D390">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E390" t="s">
         <v>30</v>
@@ -10727,7 +10727,7 @@
         <v>29</v>
       </c>
       <c r="D391">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E391" t="s">
         <v>30</v>
@@ -10744,7 +10744,7 @@
         <v>29</v>
       </c>
       <c r="D392">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E392" t="s">
         <v>30</v>
@@ -10761,7 +10761,7 @@
         <v>29</v>
       </c>
       <c r="D393">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E393" t="s">
         <v>30</v>
@@ -10778,7 +10778,7 @@
         <v>29</v>
       </c>
       <c r="D394">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E394" t="s">
         <v>30</v>
@@ -10795,7 +10795,7 @@
         <v>29</v>
       </c>
       <c r="D395">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E395" t="s">
         <v>30</v>
@@ -10812,7 +10812,7 @@
         <v>29</v>
       </c>
       <c r="D396">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E396" t="s">
         <v>30</v>
@@ -10829,7 +10829,7 @@
         <v>29</v>
       </c>
       <c r="D397">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E397" t="s">
         <v>30</v>
@@ -10846,7 +10846,7 @@
         <v>29</v>
       </c>
       <c r="D398">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E398" t="s">
         <v>30</v>
@@ -10863,7 +10863,7 @@
         <v>29</v>
       </c>
       <c r="D399">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E399" t="s">
         <v>30</v>
@@ -10880,7 +10880,7 @@
         <v>29</v>
       </c>
       <c r="D400">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E400" t="s">
         <v>30</v>
@@ -10897,7 +10897,7 @@
         <v>29</v>
       </c>
       <c r="D401">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E401" t="s">
         <v>30</v>
@@ -10914,7 +10914,7 @@
         <v>29</v>
       </c>
       <c r="D402">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E402" t="s">
         <v>30</v>
@@ -10931,7 +10931,7 @@
         <v>29</v>
       </c>
       <c r="D403">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E403" t="s">
         <v>30</v>
@@ -10948,7 +10948,7 @@
         <v>29</v>
       </c>
       <c r="D404">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E404" t="s">
         <v>30</v>
@@ -10965,7 +10965,7 @@
         <v>29</v>
       </c>
       <c r="D405">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E405" t="s">
         <v>30</v>
@@ -10982,7 +10982,7 @@
         <v>29</v>
       </c>
       <c r="D406">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E406" t="s">
         <v>30</v>
@@ -10999,7 +10999,7 @@
         <v>29</v>
       </c>
       <c r="D407">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E407" t="s">
         <v>30</v>
@@ -11016,7 +11016,7 @@
         <v>29</v>
       </c>
       <c r="D408">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E408" t="s">
         <v>30</v>
@@ -11033,7 +11033,7 @@
         <v>29</v>
       </c>
       <c r="D409">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E409" t="s">
         <v>30</v>
@@ -11050,7 +11050,7 @@
         <v>29</v>
       </c>
       <c r="D410">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E410" t="s">
         <v>30</v>
@@ -11067,7 +11067,7 @@
         <v>29</v>
       </c>
       <c r="D411">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E411" t="s">
         <v>30</v>
@@ -11084,7 +11084,7 @@
         <v>29</v>
       </c>
       <c r="D412">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E412" t="s">
         <v>30</v>
@@ -11101,7 +11101,7 @@
         <v>29</v>
       </c>
       <c r="D413">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E413" t="s">
         <v>30</v>
@@ -11118,7 +11118,7 @@
         <v>29</v>
       </c>
       <c r="D414">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E414" t="s">
         <v>30</v>
@@ -11135,7 +11135,7 @@
         <v>29</v>
       </c>
       <c r="D415">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E415" t="s">
         <v>30</v>
@@ -11152,7 +11152,7 @@
         <v>29</v>
       </c>
       <c r="D416">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E416" t="s">
         <v>30</v>
@@ -11169,7 +11169,7 @@
         <v>29</v>
       </c>
       <c r="D417">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E417" t="s">
         <v>30</v>
@@ -11186,7 +11186,7 @@
         <v>29</v>
       </c>
       <c r="D418">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E418" t="s">
         <v>30</v>
@@ -11203,7 +11203,7 @@
         <v>29</v>
       </c>
       <c r="D419">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E419" t="s">
         <v>30</v>
@@ -11220,7 +11220,7 @@
         <v>29</v>
       </c>
       <c r="D420">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E420" t="s">
         <v>30</v>
@@ -11237,7 +11237,7 @@
         <v>29</v>
       </c>
       <c r="D421">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E421" t="s">
         <v>30</v>
@@ -11254,7 +11254,7 @@
         <v>29</v>
       </c>
       <c r="D422">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E422" t="s">
         <v>30</v>
@@ -11271,7 +11271,7 @@
         <v>29</v>
       </c>
       <c r="D423">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E423" t="s">
         <v>30</v>
@@ -11288,7 +11288,7 @@
         <v>29</v>
       </c>
       <c r="D424">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E424" t="s">
         <v>30</v>
@@ -11305,7 +11305,7 @@
         <v>29</v>
       </c>
       <c r="D425">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E425" t="s">
         <v>30</v>
@@ -11322,7 +11322,7 @@
         <v>29</v>
       </c>
       <c r="D426">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E426" t="s">
         <v>30</v>
@@ -11339,7 +11339,7 @@
         <v>29</v>
       </c>
       <c r="D427">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E427" t="s">
         <v>30</v>
@@ -11356,7 +11356,7 @@
         <v>29</v>
       </c>
       <c r="D428">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E428" t="s">
         <v>30</v>
@@ -11373,7 +11373,7 @@
         <v>29</v>
       </c>
       <c r="D429">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E429" t="s">
         <v>30</v>
@@ -11390,7 +11390,7 @@
         <v>29</v>
       </c>
       <c r="D430">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E430" t="s">
         <v>30</v>
@@ -11407,7 +11407,7 @@
         <v>29</v>
       </c>
       <c r="D431">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E431" t="s">
         <v>30</v>
@@ -11424,7 +11424,7 @@
         <v>29</v>
       </c>
       <c r="D432">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E432" t="s">
         <v>30</v>
@@ -11441,7 +11441,7 @@
         <v>29</v>
       </c>
       <c r="D433">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E433" t="s">
         <v>30</v>
@@ -11458,7 +11458,7 @@
         <v>29</v>
       </c>
       <c r="D434">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E434" t="s">
         <v>30</v>
@@ -11475,7 +11475,7 @@
         <v>29</v>
       </c>
       <c r="D435">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E435" t="s">
         <v>30</v>
@@ -11492,7 +11492,7 @@
         <v>29</v>
       </c>
       <c r="D436">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E436" t="s">
         <v>30</v>
@@ -11509,7 +11509,7 @@
         <v>29</v>
       </c>
       <c r="D437">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E437" t="s">
         <v>30</v>
@@ -11526,7 +11526,7 @@
         <v>29</v>
       </c>
       <c r="D438">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E438" t="s">
         <v>30</v>
@@ -11543,7 +11543,7 @@
         <v>29</v>
       </c>
       <c r="D439">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E439" t="s">
         <v>30</v>
@@ -11560,7 +11560,7 @@
         <v>29</v>
       </c>
       <c r="D440">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E440" t="s">
         <v>30</v>
@@ -11577,7 +11577,7 @@
         <v>29</v>
       </c>
       <c r="D441">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E441" t="s">
         <v>30</v>
@@ -11594,7 +11594,7 @@
         <v>29</v>
       </c>
       <c r="D442">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E442" t="s">
         <v>30</v>
@@ -11628,7 +11628,7 @@
         <v>29</v>
       </c>
       <c r="D444">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E444" t="s">
         <v>30</v>
@@ -11645,7 +11645,7 @@
         <v>29</v>
       </c>
       <c r="D445">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E445" t="s">
         <v>30</v>
@@ -11662,7 +11662,7 @@
         <v>29</v>
       </c>
       <c r="D446">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E446" t="s">
         <v>30</v>
@@ -11679,7 +11679,7 @@
         <v>29</v>
       </c>
       <c r="D447">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E447" t="s">
         <v>30</v>
@@ -11696,7 +11696,7 @@
         <v>29</v>
       </c>
       <c r="D448">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E448" t="s">
         <v>30</v>
@@ -11713,7 +11713,7 @@
         <v>29</v>
       </c>
       <c r="D449">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E449" t="s">
         <v>30</v>
@@ -11730,7 +11730,7 @@
         <v>29</v>
       </c>
       <c r="D450">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E450" t="s">
         <v>30</v>
@@ -11747,7 +11747,7 @@
         <v>29</v>
       </c>
       <c r="D451">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E451" t="s">
         <v>30</v>
@@ -11764,7 +11764,7 @@
         <v>29</v>
       </c>
       <c r="D452">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E452" t="s">
         <v>30</v>
@@ -11781,7 +11781,7 @@
         <v>29</v>
       </c>
       <c r="D453">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E453" t="s">
         <v>30</v>
@@ -11798,7 +11798,7 @@
         <v>29</v>
       </c>
       <c r="D454">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E454" t="s">
         <v>30</v>
@@ -11815,7 +11815,7 @@
         <v>29</v>
       </c>
       <c r="D455">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E455" t="s">
         <v>30</v>
@@ -11832,7 +11832,7 @@
         <v>29</v>
       </c>
       <c r="D456">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E456" t="s">
         <v>30</v>
@@ -11849,7 +11849,7 @@
         <v>29</v>
       </c>
       <c r="D457">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E457" t="s">
         <v>30</v>
@@ -11866,7 +11866,7 @@
         <v>29</v>
       </c>
       <c r="D458">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E458" t="s">
         <v>30</v>
@@ -11883,7 +11883,7 @@
         <v>29</v>
       </c>
       <c r="D459">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E459" t="s">
         <v>30</v>
@@ -11900,7 +11900,7 @@
         <v>29</v>
       </c>
       <c r="D460">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E460" t="s">
         <v>30</v>
@@ -11917,7 +11917,7 @@
         <v>29</v>
       </c>
       <c r="D461">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E461" t="s">
         <v>30</v>
@@ -11934,7 +11934,7 @@
         <v>29</v>
       </c>
       <c r="D462">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E462" t="s">
         <v>30</v>
@@ -11951,7 +11951,7 @@
         <v>29</v>
       </c>
       <c r="D463">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E463" t="s">
         <v>30</v>
@@ -11968,7 +11968,7 @@
         <v>29</v>
       </c>
       <c r="D464">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E464" t="s">
         <v>30</v>
@@ -11985,7 +11985,7 @@
         <v>29</v>
       </c>
       <c r="D465">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E465" t="s">
         <v>30</v>
@@ -12019,7 +12019,7 @@
         <v>29</v>
       </c>
       <c r="D467">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E467" t="s">
         <v>30</v>
@@ -12036,7 +12036,7 @@
         <v>29</v>
       </c>
       <c r="D468">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E468" t="s">
         <v>30</v>
@@ -12053,7 +12053,7 @@
         <v>29</v>
       </c>
       <c r="D469">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E469" t="s">
         <v>30</v>
@@ -12070,7 +12070,7 @@
         <v>29</v>
       </c>
       <c r="D470">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E470" t="s">
         <v>30</v>
@@ -12087,7 +12087,7 @@
         <v>29</v>
       </c>
       <c r="D471">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E471" t="s">
         <v>30</v>
@@ -12104,7 +12104,7 @@
         <v>29</v>
       </c>
       <c r="D472">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E472" t="s">
         <v>30</v>
@@ -12121,7 +12121,7 @@
         <v>29</v>
       </c>
       <c r="D473">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E473" t="s">
         <v>30</v>
@@ -12138,7 +12138,7 @@
         <v>29</v>
       </c>
       <c r="D474">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E474" t="s">
         <v>30</v>
@@ -12155,7 +12155,7 @@
         <v>29</v>
       </c>
       <c r="D475">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E475" t="s">
         <v>30</v>
@@ -12172,7 +12172,7 @@
         <v>29</v>
       </c>
       <c r="D476">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E476" t="s">
         <v>30</v>
@@ -12189,7 +12189,7 @@
         <v>29</v>
       </c>
       <c r="D477">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E477" t="s">
         <v>30</v>
@@ -12206,7 +12206,7 @@
         <v>29</v>
       </c>
       <c r="D478">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E478" t="s">
         <v>30</v>
@@ -12223,7 +12223,7 @@
         <v>29</v>
       </c>
       <c r="D479">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E479" t="s">
         <v>30</v>
@@ -12240,7 +12240,7 @@
         <v>29</v>
       </c>
       <c r="D480">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E480" t="s">
         <v>30</v>
@@ -12257,7 +12257,7 @@
         <v>29</v>
       </c>
       <c r="D481">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E481" t="s">
         <v>30</v>
@@ -12274,7 +12274,7 @@
         <v>29</v>
       </c>
       <c r="D482">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E482" t="s">
         <v>30</v>
@@ -12291,7 +12291,7 @@
         <v>29</v>
       </c>
       <c r="D483">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E483" t="s">
         <v>30</v>
@@ -12308,7 +12308,7 @@
         <v>29</v>
       </c>
       <c r="D484">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E484" t="s">
         <v>30</v>
@@ -12325,7 +12325,7 @@
         <v>29</v>
       </c>
       <c r="D485">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E485" t="s">
         <v>30</v>
@@ -12342,7 +12342,7 @@
         <v>29</v>
       </c>
       <c r="D486">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E486" t="s">
         <v>30</v>
@@ -12359,7 +12359,7 @@
         <v>29</v>
       </c>
       <c r="D487">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E487" t="s">
         <v>30</v>
@@ -12376,7 +12376,7 @@
         <v>29</v>
       </c>
       <c r="D488">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E488" t="s">
         <v>30</v>
@@ -12393,7 +12393,7 @@
         <v>29</v>
       </c>
       <c r="D489">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E489" t="s">
         <v>30</v>
@@ -12410,7 +12410,7 @@
         <v>29</v>
       </c>
       <c r="D490">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E490" t="s">
         <v>30</v>
@@ -12427,7 +12427,7 @@
         <v>29</v>
       </c>
       <c r="D491">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E491" t="s">
         <v>30</v>
@@ -12444,7 +12444,7 @@
         <v>29</v>
       </c>
       <c r="D492">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E492" t="s">
         <v>30</v>
@@ -12461,7 +12461,7 @@
         <v>29</v>
       </c>
       <c r="D493">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E493" t="s">
         <v>30</v>
@@ -12478,7 +12478,7 @@
         <v>29</v>
       </c>
       <c r="D494">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E494" t="s">
         <v>30</v>
@@ -12495,7 +12495,7 @@
         <v>29</v>
       </c>
       <c r="D495">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E495" t="s">
         <v>30</v>
@@ -12512,7 +12512,7 @@
         <v>29</v>
       </c>
       <c r="D496">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E496" t="s">
         <v>30</v>
@@ -12529,7 +12529,7 @@
         <v>29</v>
       </c>
       <c r="D497">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E497" t="s">
         <v>30</v>
@@ -12546,7 +12546,7 @@
         <v>29</v>
       </c>
       <c r="D498">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E498" t="s">
         <v>30</v>
@@ -12563,7 +12563,7 @@
         <v>29</v>
       </c>
       <c r="D499">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E499" t="s">
         <v>30</v>
@@ -12580,7 +12580,7 @@
         <v>29</v>
       </c>
       <c r="D500">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E500" t="s">
         <v>30</v>
@@ -12597,7 +12597,7 @@
         <v>29</v>
       </c>
       <c r="D501">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E501" t="s">
         <v>30</v>
@@ -12614,7 +12614,7 @@
         <v>29</v>
       </c>
       <c r="D502">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E502" t="s">
         <v>30</v>
@@ -12631,7 +12631,7 @@
         <v>29</v>
       </c>
       <c r="D503">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E503" t="s">
         <v>30</v>
@@ -12648,7 +12648,7 @@
         <v>29</v>
       </c>
       <c r="D504">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E504" t="s">
         <v>30</v>
@@ -12665,7 +12665,7 @@
         <v>29</v>
       </c>
       <c r="D505">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E505" t="s">
         <v>30</v>
@@ -12682,7 +12682,7 @@
         <v>29</v>
       </c>
       <c r="D506">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E506" t="s">
         <v>30</v>
@@ -12699,7 +12699,7 @@
         <v>29</v>
       </c>
       <c r="D507">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E507" t="s">
         <v>30</v>
@@ -12716,7 +12716,7 @@
         <v>29</v>
       </c>
       <c r="D508">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E508" t="s">
         <v>30</v>
@@ -12733,7 +12733,7 @@
         <v>29</v>
       </c>
       <c r="D509">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E509" t="s">
         <v>30</v>
@@ -12750,7 +12750,7 @@
         <v>29</v>
       </c>
       <c r="D510">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E510" t="s">
         <v>30</v>
@@ -12767,7 +12767,7 @@
         <v>29</v>
       </c>
       <c r="D511">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E511" t="s">
         <v>30</v>
@@ -12784,7 +12784,7 @@
         <v>29</v>
       </c>
       <c r="D512">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E512" t="s">
         <v>30</v>
@@ -12801,7 +12801,7 @@
         <v>29</v>
       </c>
       <c r="D513">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E513" t="s">
         <v>30</v>
@@ -12818,7 +12818,7 @@
         <v>29</v>
       </c>
       <c r="D514">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E514" t="s">
         <v>30</v>
@@ -12835,7 +12835,7 @@
         <v>29</v>
       </c>
       <c r="D515">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E515" t="s">
         <v>30</v>
@@ -12852,7 +12852,7 @@
         <v>29</v>
       </c>
       <c r="D516">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E516" t="s">
         <v>30</v>
@@ -12886,7 +12886,7 @@
         <v>29</v>
       </c>
       <c r="D518">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E518" t="s">
         <v>30</v>
@@ -12903,7 +12903,7 @@
         <v>29</v>
       </c>
       <c r="D519">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E519" t="s">
         <v>30</v>
@@ -12920,7 +12920,7 @@
         <v>29</v>
       </c>
       <c r="D520">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E520" t="s">
         <v>30</v>
@@ -12937,7 +12937,7 @@
         <v>29</v>
       </c>
       <c r="D521">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E521" t="s">
         <v>30</v>
@@ -12954,7 +12954,7 @@
         <v>29</v>
       </c>
       <c r="D522">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E522" t="s">
         <v>30</v>
@@ -12971,7 +12971,7 @@
         <v>29</v>
       </c>
       <c r="D523">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E523" t="s">
         <v>30</v>
@@ -12988,7 +12988,7 @@
         <v>29</v>
       </c>
       <c r="D524">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E524" t="s">
         <v>30</v>
@@ -13005,7 +13005,7 @@
         <v>29</v>
       </c>
       <c r="D525">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E525" t="s">
         <v>30</v>
@@ -13022,7 +13022,7 @@
         <v>29</v>
       </c>
       <c r="D526">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E526" t="s">
         <v>30</v>
@@ -13039,7 +13039,7 @@
         <v>29</v>
       </c>
       <c r="D527">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E527" t="s">
         <v>30</v>
@@ -13056,7 +13056,7 @@
         <v>29</v>
       </c>
       <c r="D528">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E528" t="s">
         <v>30</v>
@@ -13073,7 +13073,7 @@
         <v>29</v>
       </c>
       <c r="D529">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E529" t="s">
         <v>30</v>
@@ -13090,7 +13090,7 @@
         <v>29</v>
       </c>
       <c r="D530">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E530" t="s">
         <v>30</v>
@@ -13107,7 +13107,7 @@
         <v>29</v>
       </c>
       <c r="D531">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E531" t="s">
         <v>30</v>
@@ -13124,7 +13124,7 @@
         <v>29</v>
       </c>
       <c r="D532">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E532" t="s">
         <v>30</v>
@@ -13141,7 +13141,7 @@
         <v>29</v>
       </c>
       <c r="D533">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E533" t="s">
         <v>30</v>
@@ -13158,7 +13158,7 @@
         <v>29</v>
       </c>
       <c r="D534">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E534" t="s">
         <v>30</v>
@@ -13175,7 +13175,7 @@
         <v>29</v>
       </c>
       <c r="D535">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E535" t="s">
         <v>30</v>
@@ -13192,7 +13192,7 @@
         <v>29</v>
       </c>
       <c r="D536">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E536" t="s">
         <v>30</v>
@@ -13209,7 +13209,7 @@
         <v>29</v>
       </c>
       <c r="D537">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E537" t="s">
         <v>30</v>
@@ -13226,7 +13226,7 @@
         <v>29</v>
       </c>
       <c r="D538">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E538" t="s">
         <v>30</v>
@@ -13260,7 +13260,7 @@
         <v>29</v>
       </c>
       <c r="D540">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E540" t="s">
         <v>30</v>
@@ -13277,7 +13277,7 @@
         <v>29</v>
       </c>
       <c r="D541">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E541" t="s">
         <v>30</v>
@@ -13294,7 +13294,7 @@
         <v>29</v>
       </c>
       <c r="D542">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E542" t="s">
         <v>30</v>
@@ -13311,7 +13311,7 @@
         <v>29</v>
       </c>
       <c r="D543">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E543" t="s">
         <v>30</v>
@@ -13328,7 +13328,7 @@
         <v>29</v>
       </c>
       <c r="D544">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E544" t="s">
         <v>30</v>
@@ -13345,7 +13345,7 @@
         <v>29</v>
       </c>
       <c r="D545">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E545" t="s">
         <v>30</v>
@@ -13362,7 +13362,7 @@
         <v>29</v>
       </c>
       <c r="D546">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E546" t="s">
         <v>30</v>
@@ -13379,7 +13379,7 @@
         <v>29</v>
       </c>
       <c r="D547">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E547" t="s">
         <v>30</v>
@@ -13396,7 +13396,7 @@
         <v>29</v>
       </c>
       <c r="D548">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E548" t="s">
         <v>30</v>
@@ -13413,7 +13413,7 @@
         <v>29</v>
       </c>
       <c r="D549">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E549" t="s">
         <v>30</v>
@@ -13430,7 +13430,7 @@
         <v>29</v>
       </c>
       <c r="D550">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E550" t="s">
         <v>30</v>
@@ -13447,7 +13447,7 @@
         <v>29</v>
       </c>
       <c r="D551">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E551" t="s">
         <v>30</v>
@@ -13464,7 +13464,7 @@
         <v>29</v>
       </c>
       <c r="D552">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E552" t="s">
         <v>30</v>
@@ -13481,7 +13481,7 @@
         <v>29</v>
       </c>
       <c r="D553">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E553" t="s">
         <v>30</v>
@@ -13498,7 +13498,7 @@
         <v>29</v>
       </c>
       <c r="D554">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E554" t="s">
         <v>30</v>
@@ -13515,7 +13515,7 @@
         <v>29</v>
       </c>
       <c r="D555">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E555" t="s">
         <v>30</v>
@@ -13532,7 +13532,7 @@
         <v>29</v>
       </c>
       <c r="D556">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E556" t="s">
         <v>30</v>
@@ -13549,7 +13549,7 @@
         <v>29</v>
       </c>
       <c r="D557">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E557" t="s">
         <v>30</v>
@@ -13566,7 +13566,7 @@
         <v>29</v>
       </c>
       <c r="D558">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E558" t="s">
         <v>30</v>
@@ -13583,7 +13583,7 @@
         <v>29</v>
       </c>
       <c r="D559">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E559" t="s">
         <v>30</v>
@@ -13600,7 +13600,7 @@
         <v>29</v>
       </c>
       <c r="D560">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E560" t="s">
         <v>30</v>
@@ -13617,7 +13617,7 @@
         <v>29</v>
       </c>
       <c r="D561">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E561" t="s">
         <v>30</v>
@@ -13634,7 +13634,7 @@
         <v>29</v>
       </c>
       <c r="D562">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E562" t="s">
         <v>30</v>
@@ -13651,7 +13651,7 @@
         <v>29</v>
       </c>
       <c r="D563">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E563" t="s">
         <v>30</v>
@@ -13685,7 +13685,7 @@
         <v>29</v>
       </c>
       <c r="D565">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E565" t="s">
         <v>30</v>
@@ -13702,7 +13702,7 @@
         <v>29</v>
       </c>
       <c r="D566">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E566" t="s">
         <v>30</v>
@@ -13719,7 +13719,7 @@
         <v>29</v>
       </c>
       <c r="D567">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E567" t="s">
         <v>30</v>
@@ -13736,7 +13736,7 @@
         <v>29</v>
       </c>
       <c r="D568">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E568" t="s">
         <v>30</v>
@@ -13753,7 +13753,7 @@
         <v>29</v>
       </c>
       <c r="D569">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E569" t="s">
         <v>30</v>
@@ -13770,7 +13770,7 @@
         <v>29</v>
       </c>
       <c r="D570">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E570" t="s">
         <v>30</v>
@@ -13787,7 +13787,7 @@
         <v>29</v>
       </c>
       <c r="D571">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E571" t="s">
         <v>30</v>
@@ -13804,7 +13804,7 @@
         <v>29</v>
       </c>
       <c r="D572">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E572" t="s">
         <v>30</v>
@@ -13838,7 +13838,7 @@
         <v>29</v>
       </c>
       <c r="D574">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E574" t="s">
         <v>30</v>
@@ -13855,7 +13855,7 @@
         <v>29</v>
       </c>
       <c r="D575">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E575" t="s">
         <v>30</v>
@@ -13872,7 +13872,7 @@
         <v>29</v>
       </c>
       <c r="D576">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E576" t="s">
         <v>30</v>
@@ -13889,7 +13889,7 @@
         <v>29</v>
       </c>
       <c r="D577">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E577" t="s">
         <v>30</v>
@@ -13906,7 +13906,7 @@
         <v>29</v>
       </c>
       <c r="D578">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E578" t="s">
         <v>30</v>
@@ -13923,7 +13923,7 @@
         <v>29</v>
       </c>
       <c r="D579">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E579" t="s">
         <v>30</v>
@@ -13957,7 +13957,7 @@
         <v>29</v>
       </c>
       <c r="D581">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E581" t="s">
         <v>30</v>
@@ -13974,7 +13974,7 @@
         <v>29</v>
       </c>
       <c r="D582">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E582" t="s">
         <v>30</v>
@@ -13991,7 +13991,7 @@
         <v>29</v>
       </c>
       <c r="D583">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E583" t="s">
         <v>30</v>
@@ -14008,7 +14008,7 @@
         <v>29</v>
       </c>
       <c r="D584">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E584" t="s">
         <v>30</v>
@@ -14025,7 +14025,7 @@
         <v>29</v>
       </c>
       <c r="D585">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E585" t="s">
         <v>30</v>
@@ -14042,7 +14042,7 @@
         <v>29</v>
       </c>
       <c r="D586">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E586" t="s">
         <v>30</v>
@@ -14059,7 +14059,7 @@
         <v>29</v>
       </c>
       <c r="D587">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E587" t="s">
         <v>30</v>
@@ -14076,7 +14076,7 @@
         <v>29</v>
       </c>
       <c r="D588">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E588" t="s">
         <v>30</v>
@@ -14093,7 +14093,7 @@
         <v>29</v>
       </c>
       <c r="D589">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E589" t="s">
         <v>30</v>
@@ -14110,7 +14110,7 @@
         <v>29</v>
       </c>
       <c r="D590">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E590" t="s">
         <v>30</v>
@@ -14127,7 +14127,7 @@
         <v>29</v>
       </c>
       <c r="D591">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E591" t="s">
         <v>30</v>
@@ -14144,7 +14144,7 @@
         <v>29</v>
       </c>
       <c r="D592">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E592" t="s">
         <v>30</v>
@@ -14161,7 +14161,7 @@
         <v>29</v>
       </c>
       <c r="D593">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E593" t="s">
         <v>30</v>
@@ -14178,7 +14178,7 @@
         <v>29</v>
       </c>
       <c r="D594">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E594" t="s">
         <v>30</v>
@@ -14195,7 +14195,7 @@
         <v>29</v>
       </c>
       <c r="D595">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E595" t="s">
         <v>30</v>
@@ -14212,7 +14212,7 @@
         <v>29</v>
       </c>
       <c r="D596">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E596" t="s">
         <v>30</v>
@@ -14229,7 +14229,7 @@
         <v>29</v>
       </c>
       <c r="D597">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E597" t="s">
         <v>30</v>
@@ -14246,7 +14246,7 @@
         <v>29</v>
       </c>
       <c r="D598">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E598" t="s">
         <v>30</v>
@@ -14263,7 +14263,7 @@
         <v>29</v>
       </c>
       <c r="D599">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E599" t="s">
         <v>30</v>
@@ -14280,7 +14280,7 @@
         <v>29</v>
       </c>
       <c r="D600">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E600" t="s">
         <v>30</v>
@@ -14297,7 +14297,7 @@
         <v>29</v>
       </c>
       <c r="D601">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E601" t="s">
         <v>30</v>
@@ -14314,7 +14314,7 @@
         <v>29</v>
       </c>
       <c r="D602">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E602" t="s">
         <v>30</v>
@@ -14331,7 +14331,7 @@
         <v>29</v>
       </c>
       <c r="D603">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E603" t="s">
         <v>30</v>
@@ -14348,7 +14348,7 @@
         <v>29</v>
       </c>
       <c r="D604">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E604" t="s">
         <v>30</v>
@@ -14365,7 +14365,7 @@
         <v>29</v>
       </c>
       <c r="D605">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E605" t="s">
         <v>30</v>
@@ -14382,7 +14382,7 @@
         <v>29</v>
       </c>
       <c r="D606">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E606" t="s">
         <v>30</v>
@@ -14399,7 +14399,7 @@
         <v>29</v>
       </c>
       <c r="D607">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E607" t="s">
         <v>30</v>
@@ -14416,7 +14416,7 @@
         <v>29</v>
       </c>
       <c r="D608">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E608" t="s">
         <v>30</v>
@@ -14433,7 +14433,7 @@
         <v>29</v>
       </c>
       <c r="D609">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E609" t="s">
         <v>30</v>
@@ -14450,7 +14450,7 @@
         <v>29</v>
       </c>
       <c r="D610">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E610" t="s">
         <v>30</v>
@@ -14467,7 +14467,7 @@
         <v>29</v>
       </c>
       <c r="D611">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E611" t="s">
         <v>30</v>
@@ -14484,7 +14484,7 @@
         <v>29</v>
       </c>
       <c r="D612">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E612" t="s">
         <v>30</v>
@@ -14501,7 +14501,7 @@
         <v>29</v>
       </c>
       <c r="D613">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E613" t="s">
         <v>30</v>
@@ -14518,7 +14518,7 @@
         <v>29</v>
       </c>
       <c r="D614">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E614" t="s">
         <v>30</v>
@@ -14552,7 +14552,7 @@
         <v>29</v>
       </c>
       <c r="D616">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E616" t="s">
         <v>30</v>
@@ -14569,7 +14569,7 @@
         <v>29</v>
       </c>
       <c r="D617">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E617" t="s">
         <v>30</v>
@@ -14586,7 +14586,7 @@
         <v>29</v>
       </c>
       <c r="D618">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E618" t="s">
         <v>30</v>
@@ -14603,7 +14603,7 @@
         <v>29</v>
       </c>
       <c r="D619">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E619" t="s">
         <v>30</v>
@@ -14620,7 +14620,7 @@
         <v>29</v>
       </c>
       <c r="D620">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E620" t="s">
         <v>30</v>
@@ -14637,7 +14637,7 @@
         <v>29</v>
       </c>
       <c r="D621">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E621" t="s">
         <v>30</v>
@@ -14654,7 +14654,7 @@
         <v>29</v>
       </c>
       <c r="D622">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E622" t="s">
         <v>30</v>
@@ -14671,7 +14671,7 @@
         <v>29</v>
       </c>
       <c r="D623">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E623" t="s">
         <v>30</v>
@@ -14688,7 +14688,7 @@
         <v>29</v>
       </c>
       <c r="D624">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E624" t="s">
         <v>30</v>
@@ -14705,7 +14705,7 @@
         <v>29</v>
       </c>
       <c r="D625">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E625" t="s">
         <v>30</v>
@@ -14722,7 +14722,7 @@
         <v>29</v>
       </c>
       <c r="D626">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E626" t="s">
         <v>30</v>
@@ -14739,7 +14739,7 @@
         <v>29</v>
       </c>
       <c r="D627">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E627" t="s">
         <v>30</v>
@@ -14773,7 +14773,7 @@
         <v>29</v>
       </c>
       <c r="D629">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E629" t="s">
         <v>30</v>
@@ -14790,7 +14790,7 @@
         <v>29</v>
       </c>
       <c r="D630">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E630" t="s">
         <v>30</v>
@@ -14824,7 +14824,7 @@
         <v>29</v>
       </c>
       <c r="D632">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E632" t="s">
         <v>30</v>
@@ -14841,7 +14841,7 @@
         <v>29</v>
       </c>
       <c r="D633">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E633" t="s">
         <v>30</v>
@@ -14858,7 +14858,7 @@
         <v>29</v>
       </c>
       <c r="D634">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E634" t="s">
         <v>30</v>
@@ -14875,7 +14875,7 @@
         <v>29</v>
       </c>
       <c r="D635">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E635" t="s">
         <v>30</v>
@@ -14892,7 +14892,7 @@
         <v>29</v>
       </c>
       <c r="D636">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E636" t="s">
         <v>30</v>
@@ -14909,7 +14909,7 @@
         <v>29</v>
       </c>
       <c r="D637">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E637" t="s">
         <v>30</v>
@@ -14926,7 +14926,7 @@
         <v>29</v>
       </c>
       <c r="D638">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E638" t="s">
         <v>30</v>
@@ -14943,7 +14943,7 @@
         <v>29</v>
       </c>
       <c r="D639">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E639" t="s">
         <v>30</v>
@@ -14960,7 +14960,7 @@
         <v>29</v>
       </c>
       <c r="D640">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E640" t="s">
         <v>30</v>
@@ -14977,7 +14977,7 @@
         <v>29</v>
       </c>
       <c r="D641">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E641" t="s">
         <v>30</v>
@@ -14994,7 +14994,7 @@
         <v>29</v>
       </c>
       <c r="D642">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E642" t="s">
         <v>30</v>
@@ -15011,7 +15011,7 @@
         <v>29</v>
       </c>
       <c r="D643">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E643" t="s">
         <v>30</v>
@@ -15028,7 +15028,7 @@
         <v>29</v>
       </c>
       <c r="D644">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E644" t="s">
         <v>30</v>
@@ -15045,7 +15045,7 @@
         <v>29</v>
       </c>
       <c r="D645">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E645" t="s">
         <v>30</v>
@@ -15062,7 +15062,7 @@
         <v>29</v>
       </c>
       <c r="D646">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E646" t="s">
         <v>30</v>
@@ -15079,7 +15079,7 @@
         <v>29</v>
       </c>
       <c r="D647">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E647" t="s">
         <v>30</v>
@@ -15096,7 +15096,7 @@
         <v>29</v>
       </c>
       <c r="D648">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E648" t="s">
         <v>30</v>
@@ -15113,7 +15113,7 @@
         <v>29</v>
       </c>
       <c r="D649">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E649" t="s">
         <v>30</v>
@@ -15130,7 +15130,7 @@
         <v>29</v>
       </c>
       <c r="D650">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E650" t="s">
         <v>30</v>
@@ -15147,7 +15147,7 @@
         <v>29</v>
       </c>
       <c r="D651">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E651" t="s">
         <v>30</v>
@@ -15164,7 +15164,7 @@
         <v>29</v>
       </c>
       <c r="D652">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E652" t="s">
         <v>30</v>
@@ -15181,7 +15181,7 @@
         <v>29</v>
       </c>
       <c r="D653">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E653" t="s">
         <v>30</v>
@@ -15198,7 +15198,7 @@
         <v>29</v>
       </c>
       <c r="D654">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E654" t="s">
         <v>30</v>
@@ -15215,7 +15215,7 @@
         <v>29</v>
       </c>
       <c r="D655">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E655" t="s">
         <v>30</v>
@@ -15232,7 +15232,7 @@
         <v>29</v>
       </c>
       <c r="D656">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E656" t="s">
         <v>30</v>
@@ -15249,7 +15249,7 @@
         <v>29</v>
       </c>
       <c r="D657">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E657" t="s">
         <v>30</v>
@@ -15266,7 +15266,7 @@
         <v>29</v>
       </c>
       <c r="D658">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E658" t="s">
         <v>30</v>
@@ -15283,7 +15283,7 @@
         <v>29</v>
       </c>
       <c r="D659">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E659" t="s">
         <v>30</v>
@@ -15300,7 +15300,7 @@
         <v>29</v>
       </c>
       <c r="D660">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E660" t="s">
         <v>30</v>
@@ -15317,7 +15317,7 @@
         <v>29</v>
       </c>
       <c r="D661">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E661" t="s">
         <v>30</v>
@@ -15334,7 +15334,7 @@
         <v>29</v>
       </c>
       <c r="D662">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E662" t="s">
         <v>30</v>
@@ -15351,7 +15351,7 @@
         <v>29</v>
       </c>
       <c r="D663">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E663" t="s">
         <v>30</v>
@@ -15368,7 +15368,7 @@
         <v>29</v>
       </c>
       <c r="D664">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E664" t="s">
         <v>30</v>
@@ -15385,7 +15385,7 @@
         <v>29</v>
       </c>
       <c r="D665">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E665" t="s">
         <v>30</v>
@@ -15402,7 +15402,7 @@
         <v>29</v>
       </c>
       <c r="D666">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E666" t="s">
         <v>30</v>
@@ -15419,7 +15419,7 @@
         <v>29</v>
       </c>
       <c r="D667">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E667" t="s">
         <v>30</v>
@@ -15436,7 +15436,7 @@
         <v>29</v>
       </c>
       <c r="D668">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E668" t="s">
         <v>30</v>
@@ -15453,7 +15453,7 @@
         <v>29</v>
       </c>
       <c r="D669">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E669" t="s">
         <v>30</v>
@@ -15470,7 +15470,7 @@
         <v>29</v>
       </c>
       <c r="D670">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E670" t="s">
         <v>30</v>
@@ -15487,7 +15487,7 @@
         <v>29</v>
       </c>
       <c r="D671">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E671" t="s">
         <v>30</v>
@@ -15504,7 +15504,7 @@
         <v>29</v>
       </c>
       <c r="D672">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E672" t="s">
         <v>30</v>
@@ -15521,7 +15521,7 @@
         <v>29</v>
       </c>
       <c r="D673">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E673" t="s">
         <v>30</v>
@@ -15538,7 +15538,7 @@
         <v>29</v>
       </c>
       <c r="D674">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E674" t="s">
         <v>30</v>
@@ -15555,7 +15555,7 @@
         <v>29</v>
       </c>
       <c r="D675">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E675" t="s">
         <v>30</v>
@@ -15572,7 +15572,7 @@
         <v>29</v>
       </c>
       <c r="D676">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E676" t="s">
         <v>30</v>
@@ -15589,7 +15589,7 @@
         <v>29</v>
       </c>
       <c r="D677">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E677" t="s">
         <v>30</v>
@@ -15606,7 +15606,7 @@
         <v>29</v>
       </c>
       <c r="D678">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E678" t="s">
         <v>30</v>
@@ -15623,7 +15623,7 @@
         <v>29</v>
       </c>
       <c r="D679">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E679" t="s">
         <v>30</v>
@@ -15657,7 +15657,7 @@
         <v>29</v>
       </c>
       <c r="D681">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E681" t="s">
         <v>30</v>
@@ -15674,7 +15674,7 @@
         <v>29</v>
       </c>
       <c r="D682">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E682" t="s">
         <v>30</v>
@@ -15691,7 +15691,7 @@
         <v>29</v>
       </c>
       <c r="D683">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E683" t="s">
         <v>30</v>
@@ -15708,7 +15708,7 @@
         <v>29</v>
       </c>
       <c r="D684">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E684" t="s">
         <v>30</v>
@@ -15725,7 +15725,7 @@
         <v>29</v>
       </c>
       <c r="D685">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E685" t="s">
         <v>30</v>
@@ -15742,7 +15742,7 @@
         <v>29</v>
       </c>
       <c r="D686">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E686" t="s">
         <v>30</v>
@@ -15776,7 +15776,7 @@
         <v>29</v>
       </c>
       <c r="D688">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E688" t="s">
         <v>30</v>
@@ -15793,7 +15793,7 @@
         <v>29</v>
       </c>
       <c r="D689">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E689" t="s">
         <v>30</v>
@@ -15810,7 +15810,7 @@
         <v>29</v>
       </c>
       <c r="D690">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E690" t="s">
         <v>30</v>
@@ -15844,7 +15844,7 @@
         <v>29</v>
       </c>
       <c r="D692">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E692" t="s">
         <v>30</v>
@@ -15861,7 +15861,7 @@
         <v>29</v>
       </c>
       <c r="D693">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E693" t="s">
         <v>30</v>
@@ -15878,7 +15878,7 @@
         <v>29</v>
       </c>
       <c r="D694">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E694" t="s">
         <v>30</v>
@@ -15895,7 +15895,7 @@
         <v>29</v>
       </c>
       <c r="D695">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E695" t="s">
         <v>30</v>
@@ -15912,7 +15912,7 @@
         <v>29</v>
       </c>
       <c r="D696">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E696" t="s">
         <v>30</v>
@@ -15929,7 +15929,7 @@
         <v>29</v>
       </c>
       <c r="D697">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E697" t="s">
         <v>30</v>
@@ -15946,7 +15946,7 @@
         <v>29</v>
       </c>
       <c r="D698">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E698" t="s">
         <v>30</v>
@@ -15963,7 +15963,7 @@
         <v>29</v>
       </c>
       <c r="D699">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E699" t="s">
         <v>30</v>
@@ -15997,7 +15997,7 @@
         <v>29</v>
       </c>
       <c r="D701">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E701" t="s">
         <v>30</v>
@@ -16014,7 +16014,7 @@
         <v>29</v>
       </c>
       <c r="D702">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E702" t="s">
         <v>30</v>
@@ -16048,7 +16048,7 @@
         <v>29</v>
       </c>
       <c r="D704">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E704" t="s">
         <v>30</v>
@@ -16065,7 +16065,7 @@
         <v>29</v>
       </c>
       <c r="D705">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E705" t="s">
         <v>30</v>
@@ -16082,7 +16082,7 @@
         <v>29</v>
       </c>
       <c r="D706">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E706" t="s">
         <v>30</v>
@@ -16099,7 +16099,7 @@
         <v>29</v>
       </c>
       <c r="D707">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E707" t="s">
         <v>30</v>
@@ -16133,7 +16133,7 @@
         <v>29</v>
       </c>
       <c r="D709">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E709" t="s">
         <v>30</v>
@@ -16150,7 +16150,7 @@
         <v>29</v>
       </c>
       <c r="D710">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E710" t="s">
         <v>30</v>
@@ -16167,7 +16167,7 @@
         <v>29</v>
       </c>
       <c r="D711">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E711" t="s">
         <v>30</v>
@@ -16184,7 +16184,7 @@
         <v>29</v>
       </c>
       <c r="D712">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E712" t="s">
         <v>30</v>
@@ -16201,7 +16201,7 @@
         <v>29</v>
       </c>
       <c r="D713">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E713" t="s">
         <v>30</v>
@@ -16218,7 +16218,7 @@
         <v>29</v>
       </c>
       <c r="D714">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E714" t="s">
         <v>30</v>
@@ -16235,7 +16235,7 @@
         <v>29</v>
       </c>
       <c r="D715">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E715" t="s">
         <v>30</v>
@@ -16252,7 +16252,7 @@
         <v>29</v>
       </c>
       <c r="D716">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E716" t="s">
         <v>30</v>
@@ -16269,7 +16269,7 @@
         <v>29</v>
       </c>
       <c r="D717">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E717" t="s">
         <v>30</v>
@@ -16286,7 +16286,7 @@
         <v>29</v>
       </c>
       <c r="D718">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E718" t="s">
         <v>30</v>
@@ -16303,7 +16303,7 @@
         <v>29</v>
       </c>
       <c r="D719">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E719" t="s">
         <v>30</v>
@@ -16320,7 +16320,7 @@
         <v>29</v>
       </c>
       <c r="D720">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E720" t="s">
         <v>30</v>
@@ -16337,7 +16337,7 @@
         <v>29</v>
       </c>
       <c r="D721">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E721" t="s">
         <v>30</v>
@@ -16354,7 +16354,7 @@
         <v>29</v>
       </c>
       <c r="D722">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E722" t="s">
         <v>30</v>
@@ -16371,7 +16371,7 @@
         <v>29</v>
       </c>
       <c r="D723">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E723" t="s">
         <v>30</v>
@@ -16388,7 +16388,7 @@
         <v>29</v>
       </c>
       <c r="D724">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E724" t="s">
         <v>30</v>
@@ -16405,7 +16405,7 @@
         <v>29</v>
       </c>
       <c r="D725">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E725" t="s">
         <v>30</v>
@@ -16422,7 +16422,7 @@
         <v>29</v>
       </c>
       <c r="D726">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E726" t="s">
         <v>30</v>
@@ -16439,7 +16439,7 @@
         <v>29</v>
       </c>
       <c r="D727">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E727" t="s">
         <v>30</v>
@@ -16456,7 +16456,7 @@
         <v>29</v>
       </c>
       <c r="D728">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E728" t="s">
         <v>30</v>
@@ -16473,7 +16473,7 @@
         <v>29</v>
       </c>
       <c r="D729">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E729" t="s">
         <v>30</v>
@@ -16490,7 +16490,7 @@
         <v>29</v>
       </c>
       <c r="D730">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E730" t="s">
         <v>30</v>
@@ -16507,7 +16507,7 @@
         <v>29</v>
       </c>
       <c r="D731">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E731" t="s">
         <v>30</v>
@@ -16524,7 +16524,7 @@
         <v>29</v>
       </c>
       <c r="D732">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E732" t="s">
         <v>30</v>
@@ -16541,7 +16541,7 @@
         <v>29</v>
       </c>
       <c r="D733">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E733" t="s">
         <v>30</v>
@@ -16558,7 +16558,7 @@
         <v>29</v>
       </c>
       <c r="D734">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E734" t="s">
         <v>30</v>
@@ -16575,7 +16575,7 @@
         <v>29</v>
       </c>
       <c r="D735">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E735" t="s">
         <v>30</v>
@@ -16592,7 +16592,7 @@
         <v>29</v>
       </c>
       <c r="D736">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E736" t="s">
         <v>30</v>
@@ -16609,7 +16609,7 @@
         <v>29</v>
       </c>
       <c r="D737">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E737" t="s">
         <v>30</v>
@@ -16626,7 +16626,7 @@
         <v>29</v>
       </c>
       <c r="D738">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E738" t="s">
         <v>30</v>
@@ -16643,7 +16643,7 @@
         <v>29</v>
       </c>
       <c r="D739">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E739" t="s">
         <v>30</v>
@@ -16660,7 +16660,7 @@
         <v>29</v>
       </c>
       <c r="D740">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E740" t="s">
         <v>30</v>
@@ -16677,7 +16677,7 @@
         <v>29</v>
       </c>
       <c r="D741">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E741" t="s">
         <v>30</v>
@@ -16694,7 +16694,7 @@
         <v>29</v>
       </c>
       <c r="D742">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E742" t="s">
         <v>30</v>
@@ -16711,7 +16711,7 @@
         <v>29</v>
       </c>
       <c r="D743">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E743" t="s">
         <v>30</v>
@@ -16728,7 +16728,7 @@
         <v>29</v>
       </c>
       <c r="D744">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E744" t="s">
         <v>30</v>
@@ -16745,7 +16745,7 @@
         <v>29</v>
       </c>
       <c r="D745">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E745" t="s">
         <v>30</v>
@@ -16762,7 +16762,7 @@
         <v>29</v>
       </c>
       <c r="D746">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E746" t="s">
         <v>30</v>
@@ -16779,7 +16779,7 @@
         <v>29</v>
       </c>
       <c r="D747">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E747" t="s">
         <v>30</v>
@@ -16796,7 +16796,7 @@
         <v>29</v>
       </c>
       <c r="D748">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E748" t="s">
         <v>30</v>
@@ -16813,7 +16813,7 @@
         <v>29</v>
       </c>
       <c r="D749">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E749" t="s">
         <v>30</v>
@@ -16830,7 +16830,7 @@
         <v>29</v>
       </c>
       <c r="D750">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E750" t="s">
         <v>30</v>
@@ -16847,7 +16847,7 @@
         <v>29</v>
       </c>
       <c r="D751">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E751" t="s">
         <v>30</v>
@@ -16864,7 +16864,7 @@
         <v>29</v>
       </c>
       <c r="D752">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E752" t="s">
         <v>30</v>
@@ -16881,7 +16881,7 @@
         <v>29</v>
       </c>
       <c r="D753">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E753" t="s">
         <v>30</v>
@@ -16898,7 +16898,7 @@
         <v>29</v>
       </c>
       <c r="D754">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E754" t="s">
         <v>30</v>
@@ -16915,7 +16915,7 @@
         <v>29</v>
       </c>
       <c r="D755">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E755" t="s">
         <v>30</v>
@@ -16932,7 +16932,7 @@
         <v>29</v>
       </c>
       <c r="D756">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E756" t="s">
         <v>30</v>
@@ -16949,7 +16949,7 @@
         <v>29</v>
       </c>
       <c r="D757">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E757" t="s">
         <v>30</v>
@@ -16983,7 +16983,7 @@
         <v>29</v>
       </c>
       <c r="D759">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E759" t="s">
         <v>30</v>
@@ -17000,7 +17000,7 @@
         <v>29</v>
       </c>
       <c r="D760">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E760" t="s">
         <v>30</v>
@@ -17017,7 +17017,7 @@
         <v>29</v>
       </c>
       <c r="D761">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E761" t="s">
         <v>30</v>
@@ -17051,7 +17051,7 @@
         <v>29</v>
       </c>
       <c r="D763">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E763" t="s">
         <v>30</v>
@@ -17068,7 +17068,7 @@
         <v>29</v>
       </c>
       <c r="D764">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E764" t="s">
         <v>30</v>
@@ -17085,7 +17085,7 @@
         <v>29</v>
       </c>
       <c r="D765">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E765" t="s">
         <v>30</v>
@@ -17102,7 +17102,7 @@
         <v>29</v>
       </c>
       <c r="D766">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E766" t="s">
         <v>30</v>
@@ -17119,7 +17119,7 @@
         <v>29</v>
       </c>
       <c r="D767">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E767" t="s">
         <v>30</v>
@@ -17136,7 +17136,7 @@
         <v>29</v>
       </c>
       <c r="D768">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E768" t="s">
         <v>30</v>
@@ -17153,7 +17153,7 @@
         <v>29</v>
       </c>
       <c r="D769">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E769" t="s">
         <v>30</v>
@@ -17187,7 +17187,7 @@
         <v>29</v>
       </c>
       <c r="D771">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E771" t="s">
         <v>30</v>
@@ -17204,7 +17204,7 @@
         <v>29</v>
       </c>
       <c r="D772">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E772" t="s">
         <v>30</v>
@@ -17238,7 +17238,7 @@
         <v>29</v>
       </c>
       <c r="D774">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E774" t="s">
         <v>30</v>
@@ -17255,7 +17255,7 @@
         <v>29</v>
       </c>
       <c r="D775">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E775" t="s">
         <v>30</v>
@@ -17272,7 +17272,7 @@
         <v>29</v>
       </c>
       <c r="D776">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E776" t="s">
         <v>30</v>
@@ -17289,7 +17289,7 @@
         <v>29</v>
       </c>
       <c r="D777">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E777" t="s">
         <v>30</v>
@@ -17306,7 +17306,7 @@
         <v>29</v>
       </c>
       <c r="D778">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E778" t="s">
         <v>30</v>
@@ -17323,7 +17323,7 @@
         <v>29</v>
       </c>
       <c r="D779">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E779" t="s">
         <v>30</v>
@@ -17357,7 +17357,7 @@
         <v>29</v>
       </c>
       <c r="D781">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E781" t="s">
         <v>30</v>
@@ -17374,7 +17374,7 @@
         <v>29</v>
       </c>
       <c r="D782">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E782" t="s">
         <v>30</v>
@@ -17391,7 +17391,7 @@
         <v>29</v>
       </c>
       <c r="D783">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E783" t="s">
         <v>30</v>
@@ -17408,7 +17408,7 @@
         <v>29</v>
       </c>
       <c r="D784">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E784" t="s">
         <v>30</v>
@@ -17425,7 +17425,7 @@
         <v>29</v>
       </c>
       <c r="D785">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E785" t="s">
         <v>30</v>
@@ -17442,7 +17442,7 @@
         <v>29</v>
       </c>
       <c r="D786">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E786" t="s">
         <v>30</v>
@@ -17459,7 +17459,7 @@
         <v>29</v>
       </c>
       <c r="D787">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E787" t="s">
         <v>30</v>
@@ -17476,7 +17476,7 @@
         <v>29</v>
       </c>
       <c r="D788">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E788" t="s">
         <v>30</v>
@@ -17493,7 +17493,7 @@
         <v>29</v>
       </c>
       <c r="D789">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E789" t="s">
         <v>30</v>
@@ -17510,7 +17510,7 @@
         <v>29</v>
       </c>
       <c r="D790">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E790" t="s">
         <v>30</v>
@@ -17561,7 +17561,7 @@
         <v>29</v>
       </c>
       <c r="D793">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E793" t="s">
         <v>30</v>
@@ -17578,7 +17578,7 @@
         <v>29</v>
       </c>
       <c r="D794">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E794" t="s">
         <v>30</v>
@@ -17595,7 +17595,7 @@
         <v>29</v>
       </c>
       <c r="D795">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E795" t="s">
         <v>30</v>
@@ -17612,7 +17612,7 @@
         <v>29</v>
       </c>
       <c r="D796">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E796" t="s">
         <v>30</v>
@@ -17629,7 +17629,7 @@
         <v>29</v>
       </c>
       <c r="D797">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E797" t="s">
         <v>30</v>
@@ -17663,7 +17663,7 @@
         <v>29</v>
       </c>
       <c r="D799">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E799" t="s">
         <v>30</v>
@@ -17680,7 +17680,7 @@
         <v>29</v>
       </c>
       <c r="D800">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E800" t="s">
         <v>30</v>
@@ -17697,7 +17697,7 @@
         <v>29</v>
       </c>
       <c r="D801">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E801" t="s">
         <v>30</v>
@@ -17714,7 +17714,7 @@
         <v>29</v>
       </c>
       <c r="D802">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E802" t="s">
         <v>30</v>
@@ -17731,7 +17731,7 @@
         <v>29</v>
       </c>
       <c r="D803">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E803" t="s">
         <v>30</v>
@@ -17748,7 +17748,7 @@
         <v>29</v>
       </c>
       <c r="D804">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E804" t="s">
         <v>30</v>
@@ -17765,7 +17765,7 @@
         <v>29</v>
       </c>
       <c r="D805">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E805" t="s">
         <v>30</v>
@@ -17782,7 +17782,7 @@
         <v>29</v>
       </c>
       <c r="D806">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E806" t="s">
         <v>30</v>
@@ -17799,7 +17799,7 @@
         <v>29</v>
       </c>
       <c r="D807">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E807" t="s">
         <v>30</v>
@@ -17816,7 +17816,7 @@
         <v>29</v>
       </c>
       <c r="D808">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E808" t="s">
         <v>30</v>
@@ -17833,7 +17833,7 @@
         <v>29</v>
       </c>
       <c r="D809">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E809" t="s">
         <v>30</v>
@@ -17850,7 +17850,7 @@
         <v>29</v>
       </c>
       <c r="D810">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E810" t="s">
         <v>30</v>
@@ -17867,7 +17867,7 @@
         <v>29</v>
       </c>
       <c r="D811">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E811" t="s">
         <v>30</v>
@@ -17884,7 +17884,7 @@
         <v>29</v>
       </c>
       <c r="D812">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E812" t="s">
         <v>30</v>
@@ -17918,7 +17918,7 @@
         <v>29</v>
       </c>
       <c r="D814">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E814" t="s">
         <v>30</v>
@@ -17935,7 +17935,7 @@
         <v>29</v>
       </c>
       <c r="D815">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E815" t="s">
         <v>30</v>
@@ -17952,7 +17952,7 @@
         <v>29</v>
       </c>
       <c r="D816">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E816" t="s">
         <v>30</v>
@@ -17969,7 +17969,7 @@
         <v>29</v>
       </c>
       <c r="D817">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E817" t="s">
         <v>30</v>
@@ -17986,7 +17986,7 @@
         <v>29</v>
       </c>
       <c r="D818">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E818" t="s">
         <v>30</v>
@@ -18020,7 +18020,7 @@
         <v>29</v>
       </c>
       <c r="D820">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E820" t="s">
         <v>30</v>
@@ -18037,7 +18037,7 @@
         <v>29</v>
       </c>
       <c r="D821">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E821" t="s">
         <v>30</v>
@@ -18054,7 +18054,7 @@
         <v>29</v>
       </c>
       <c r="D822">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E822" t="s">
         <v>30</v>
@@ -18071,7 +18071,7 @@
         <v>29</v>
       </c>
       <c r="D823">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E823" t="s">
         <v>30</v>
@@ -18088,7 +18088,7 @@
         <v>29</v>
       </c>
       <c r="D824">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E824" t="s">
         <v>30</v>
@@ -18105,7 +18105,7 @@
         <v>29</v>
       </c>
       <c r="D825">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E825" t="s">
         <v>30</v>
@@ -18122,7 +18122,7 @@
         <v>29</v>
       </c>
       <c r="D826">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E826" t="s">
         <v>30</v>
@@ -18139,7 +18139,7 @@
         <v>29</v>
       </c>
       <c r="D827">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E827" t="s">
         <v>30</v>
@@ -18156,7 +18156,7 @@
         <v>29</v>
       </c>
       <c r="D828">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E828" t="s">
         <v>30</v>
@@ -18173,7 +18173,7 @@
         <v>29</v>
       </c>
       <c r="D829">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E829" t="s">
         <v>30</v>
@@ -18190,7 +18190,7 @@
         <v>29</v>
       </c>
       <c r="D830">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E830" t="s">
         <v>30</v>
@@ -18207,7 +18207,7 @@
         <v>29</v>
       </c>
       <c r="D831">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E831" t="s">
         <v>30</v>
@@ -18224,7 +18224,7 @@
         <v>29</v>
       </c>
       <c r="D832">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E832" t="s">
         <v>30</v>
@@ -18241,7 +18241,7 @@
         <v>29</v>
       </c>
       <c r="D833">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E833" t="s">
         <v>30</v>
@@ -18258,7 +18258,7 @@
         <v>29</v>
       </c>
       <c r="D834">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E834" t="s">
         <v>30</v>
@@ -18275,7 +18275,7 @@
         <v>29</v>
       </c>
       <c r="D835">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E835" t="s">
         <v>30</v>
@@ -18292,7 +18292,7 @@
         <v>29</v>
       </c>
       <c r="D836">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E836" t="s">
         <v>30</v>
@@ -18309,7 +18309,7 @@
         <v>29</v>
       </c>
       <c r="D837">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E837" t="s">
         <v>30</v>
@@ -18326,7 +18326,7 @@
         <v>29</v>
       </c>
       <c r="D838">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E838" t="s">
         <v>30</v>
@@ -18343,7 +18343,7 @@
         <v>29</v>
       </c>
       <c r="D839">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E839" t="s">
         <v>30</v>
@@ -18360,7 +18360,7 @@
         <v>29</v>
       </c>
       <c r="D840">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E840" t="s">
         <v>30</v>
@@ -18377,7 +18377,7 @@
         <v>29</v>
       </c>
       <c r="D841">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E841" t="s">
         <v>30</v>
@@ -18394,7 +18394,7 @@
         <v>29</v>
       </c>
       <c r="D842">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E842" t="s">
         <v>30</v>
@@ -18411,7 +18411,7 @@
         <v>29</v>
       </c>
       <c r="D843">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E843" t="s">
         <v>30</v>
@@ -18428,7 +18428,7 @@
         <v>29</v>
       </c>
       <c r="D844">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E844" t="s">
         <v>30</v>
@@ -18445,7 +18445,7 @@
         <v>29</v>
       </c>
       <c r="D845">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E845" t="s">
         <v>30</v>
@@ -18462,7 +18462,7 @@
         <v>29</v>
       </c>
       <c r="D846">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E846" t="s">
         <v>30</v>
@@ -18479,7 +18479,7 @@
         <v>29</v>
       </c>
       <c r="D847">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E847" t="s">
         <v>30</v>
@@ -18496,7 +18496,7 @@
         <v>29</v>
       </c>
       <c r="D848">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E848" t="s">
         <v>30</v>
@@ -18513,7 +18513,7 @@
         <v>29</v>
       </c>
       <c r="D849">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E849" t="s">
         <v>30</v>
@@ -18530,7 +18530,7 @@
         <v>29</v>
       </c>
       <c r="D850">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E850" t="s">
         <v>30</v>
@@ -18547,7 +18547,7 @@
         <v>29</v>
       </c>
       <c r="D851">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E851" t="s">
         <v>30</v>
@@ -18564,7 +18564,7 @@
         <v>29</v>
       </c>
       <c r="D852">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E852" t="s">
         <v>30</v>
@@ -18581,7 +18581,7 @@
         <v>29</v>
       </c>
       <c r="D853">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E853" t="s">
         <v>30</v>
@@ -18615,7 +18615,7 @@
         <v>29</v>
       </c>
       <c r="D855">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E855" t="s">
         <v>30</v>
@@ -18632,7 +18632,7 @@
         <v>29</v>
       </c>
       <c r="D856">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E856" t="s">
         <v>30</v>
@@ -18649,7 +18649,7 @@
         <v>29</v>
       </c>
       <c r="D857">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E857" t="s">
         <v>30</v>
@@ -18666,7 +18666,7 @@
         <v>29</v>
       </c>
       <c r="D858">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E858" t="s">
         <v>30</v>
@@ -18683,7 +18683,7 @@
         <v>29</v>
       </c>
       <c r="D859">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E859" t="s">
         <v>30</v>
@@ -18700,7 +18700,7 @@
         <v>29</v>
       </c>
       <c r="D860">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E860" t="s">
         <v>30</v>
@@ -18717,7 +18717,7 @@
         <v>29</v>
       </c>
       <c r="D861">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E861" t="s">
         <v>30</v>
@@ -18734,7 +18734,7 @@
         <v>29</v>
       </c>
       <c r="D862">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E862" t="s">
         <v>30</v>
@@ -18751,7 +18751,7 @@
         <v>29</v>
       </c>
       <c r="D863">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E863" t="s">
         <v>30</v>
@@ -18768,7 +18768,7 @@
         <v>29</v>
       </c>
       <c r="D864">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E864" t="s">
         <v>30</v>
@@ -18785,7 +18785,7 @@
         <v>29</v>
       </c>
       <c r="D865">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E865" t="s">
         <v>30</v>
@@ -18802,7 +18802,7 @@
         <v>29</v>
       </c>
       <c r="D866">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E866" t="s">
         <v>30</v>
@@ -18819,7 +18819,7 @@
         <v>29</v>
       </c>
       <c r="D867">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E867" t="s">
         <v>30</v>
@@ -18836,7 +18836,7 @@
         <v>29</v>
       </c>
       <c r="D868">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E868" t="s">
         <v>30</v>
@@ -18870,7 +18870,7 @@
         <v>29</v>
       </c>
       <c r="D870">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E870" t="s">
         <v>30</v>
@@ -18887,7 +18887,7 @@
         <v>29</v>
       </c>
       <c r="D871">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E871" t="s">
         <v>30</v>
@@ -18904,7 +18904,7 @@
         <v>29</v>
       </c>
       <c r="D872">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E872" t="s">
         <v>30</v>
@@ -18921,7 +18921,7 @@
         <v>29</v>
       </c>
       <c r="D873">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E873" t="s">
         <v>30</v>
@@ -18938,7 +18938,7 @@
         <v>29</v>
       </c>
       <c r="D874">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E874" t="s">
         <v>30</v>
@@ -18955,7 +18955,7 @@
         <v>29</v>
       </c>
       <c r="D875">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E875" t="s">
         <v>30</v>
@@ -18972,7 +18972,7 @@
         <v>29</v>
       </c>
       <c r="D876">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E876" t="s">
         <v>30</v>
@@ -18989,7 +18989,7 @@
         <v>29</v>
       </c>
       <c r="D877">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E877" t="s">
         <v>30</v>
@@ -19006,7 +19006,7 @@
         <v>29</v>
       </c>
       <c r="D878">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E878" t="s">
         <v>30</v>
@@ -19023,7 +19023,7 @@
         <v>29</v>
       </c>
       <c r="D879">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E879" t="s">
         <v>30</v>
@@ -19040,7 +19040,7 @@
         <v>29</v>
       </c>
       <c r="D880">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E880" t="s">
         <v>30</v>
@@ -19057,7 +19057,7 @@
         <v>29</v>
       </c>
       <c r="D881">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E881" t="s">
         <v>30</v>
@@ -19074,7 +19074,7 @@
         <v>29</v>
       </c>
       <c r="D882">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E882" t="s">
         <v>30</v>
@@ -19091,7 +19091,7 @@
         <v>29</v>
       </c>
       <c r="D883">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E883" t="s">
         <v>30</v>
@@ -19125,7 +19125,7 @@
         <v>29</v>
       </c>
       <c r="D885">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E885" t="s">
         <v>30</v>
@@ -19142,7 +19142,7 @@
         <v>29</v>
       </c>
       <c r="D886">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E886" t="s">
         <v>30</v>
@@ -19159,7 +19159,7 @@
         <v>29</v>
       </c>
       <c r="D887">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E887" t="s">
         <v>30</v>
@@ -19176,7 +19176,7 @@
         <v>29</v>
       </c>
       <c r="D888">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E888" t="s">
         <v>30</v>
@@ -19193,7 +19193,7 @@
         <v>29</v>
       </c>
       <c r="D889">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E889" t="s">
         <v>30</v>
@@ -19210,7 +19210,7 @@
         <v>29</v>
       </c>
       <c r="D890">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E890" t="s">
         <v>30</v>
@@ -19227,7 +19227,7 @@
         <v>29</v>
       </c>
       <c r="D891">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E891" t="s">
         <v>30</v>
@@ -19244,7 +19244,7 @@
         <v>29</v>
       </c>
       <c r="D892">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E892" t="s">
         <v>30</v>
@@ -19261,7 +19261,7 @@
         <v>29</v>
       </c>
       <c r="D893">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E893" t="s">
         <v>30</v>
@@ -19278,7 +19278,7 @@
         <v>29</v>
       </c>
       <c r="D894">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E894" t="s">
         <v>30</v>
@@ -19295,7 +19295,7 @@
         <v>29</v>
       </c>
       <c r="D895">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E895" t="s">
         <v>30</v>
@@ -19312,7 +19312,7 @@
         <v>29</v>
       </c>
       <c r="D896">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E896" t="s">
         <v>30</v>
@@ -19329,7 +19329,7 @@
         <v>29</v>
       </c>
       <c r="D897">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E897" t="s">
         <v>30</v>
@@ -19346,7 +19346,7 @@
         <v>29</v>
       </c>
       <c r="D898">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E898" t="s">
         <v>30</v>
@@ -19363,7 +19363,7 @@
         <v>29</v>
       </c>
       <c r="D899">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E899" t="s">
         <v>30</v>
@@ -19380,7 +19380,7 @@
         <v>29</v>
       </c>
       <c r="D900">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E900" t="s">
         <v>30</v>
@@ -19397,7 +19397,7 @@
         <v>29</v>
       </c>
       <c r="D901">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E901" t="s">
         <v>30</v>
@@ -19414,7 +19414,7 @@
         <v>29</v>
       </c>
       <c r="D902">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E902" t="s">
         <v>30</v>
@@ -19431,7 +19431,7 @@
         <v>29</v>
       </c>
       <c r="D903">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E903" t="s">
         <v>30</v>
@@ -19448,7 +19448,7 @@
         <v>29</v>
       </c>
       <c r="D904">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E904" t="s">
         <v>30</v>
@@ -19465,7 +19465,7 @@
         <v>29</v>
       </c>
       <c r="D905">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E905" t="s">
         <v>30</v>
@@ -19482,7 +19482,7 @@
         <v>29</v>
       </c>
       <c r="D906">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E906" t="s">
         <v>30</v>
@@ -19499,7 +19499,7 @@
         <v>29</v>
       </c>
       <c r="D907">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E907" t="s">
         <v>30</v>
@@ -19516,7 +19516,7 @@
         <v>29</v>
       </c>
       <c r="D908">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E908" t="s">
         <v>30</v>
@@ -19533,7 +19533,7 @@
         <v>29</v>
       </c>
       <c r="D909">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E909" t="s">
         <v>30</v>
@@ -19550,7 +19550,7 @@
         <v>29</v>
       </c>
       <c r="D910">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E910" t="s">
         <v>30</v>
@@ -19567,7 +19567,7 @@
         <v>29</v>
       </c>
       <c r="D911">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E911" t="s">
         <v>30</v>
@@ -19584,7 +19584,7 @@
         <v>29</v>
       </c>
       <c r="D912">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E912" t="s">
         <v>30</v>
@@ -19601,7 +19601,7 @@
         <v>29</v>
       </c>
       <c r="D913">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E913" t="s">
         <v>30</v>
@@ -19635,7 +19635,7 @@
         <v>29</v>
       </c>
       <c r="D915">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E915" t="s">
         <v>30</v>
@@ -19652,7 +19652,7 @@
         <v>29</v>
       </c>
       <c r="D916">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E916" t="s">
         <v>30</v>
@@ -19669,7 +19669,7 @@
         <v>29</v>
       </c>
       <c r="D917">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E917" t="s">
         <v>30</v>
@@ -19686,7 +19686,7 @@
         <v>29</v>
       </c>
       <c r="D918">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E918" t="s">
         <v>30</v>
@@ -19703,7 +19703,7 @@
         <v>29</v>
       </c>
       <c r="D919">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E919" t="s">
         <v>30</v>
@@ -19737,7 +19737,7 @@
         <v>29</v>
       </c>
       <c r="D921">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E921" t="s">
         <v>30</v>
@@ -19754,7 +19754,7 @@
         <v>29</v>
       </c>
       <c r="D922">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E922" t="s">
         <v>30</v>
@@ -19771,7 +19771,7 @@
         <v>29</v>
       </c>
       <c r="D923">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E923" t="s">
         <v>30</v>
@@ -19788,7 +19788,7 @@
         <v>29</v>
       </c>
       <c r="D924">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E924" t="s">
         <v>30</v>
@@ -19805,7 +19805,7 @@
         <v>29</v>
       </c>
       <c r="D925">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E925" t="s">
         <v>30</v>
@@ -19822,7 +19822,7 @@
         <v>29</v>
       </c>
       <c r="D926">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E926" t="s">
         <v>30</v>
@@ -19839,7 +19839,7 @@
         <v>29</v>
       </c>
       <c r="D927">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E927" t="s">
         <v>30</v>
@@ -19856,7 +19856,7 @@
         <v>29</v>
       </c>
       <c r="D928">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E928" t="s">
         <v>30</v>
@@ -19873,7 +19873,7 @@
         <v>29</v>
       </c>
       <c r="D929">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E929" t="s">
         <v>30</v>
@@ -19890,7 +19890,7 @@
         <v>29</v>
       </c>
       <c r="D930">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E930" t="s">
         <v>30</v>
@@ -19907,7 +19907,7 @@
         <v>29</v>
       </c>
       <c r="D931">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E931" t="s">
         <v>30</v>
@@ -19924,7 +19924,7 @@
         <v>29</v>
       </c>
       <c r="D932">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E932" t="s">
         <v>30</v>
@@ -19941,7 +19941,7 @@
         <v>29</v>
       </c>
       <c r="D933">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E933" t="s">
         <v>30</v>
@@ -19958,7 +19958,7 @@
         <v>29</v>
       </c>
       <c r="D934">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E934" t="s">
         <v>30</v>
@@ -19975,7 +19975,7 @@
         <v>29</v>
       </c>
       <c r="D935">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E935" t="s">
         <v>30</v>
@@ -19992,7 +19992,7 @@
         <v>29</v>
       </c>
       <c r="D936">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E936" t="s">
         <v>30</v>
@@ -20009,7 +20009,7 @@
         <v>29</v>
       </c>
       <c r="D937">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E937" t="s">
         <v>30</v>
@@ -20026,7 +20026,7 @@
         <v>29</v>
       </c>
       <c r="D938">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E938" t="s">
         <v>30</v>
@@ -20043,7 +20043,7 @@
         <v>29</v>
       </c>
       <c r="D939">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E939" t="s">
         <v>30</v>
@@ -20060,7 +20060,7 @@
         <v>29</v>
       </c>
       <c r="D940">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E940" t="s">
         <v>30</v>
@@ -20077,7 +20077,7 @@
         <v>29</v>
       </c>
       <c r="D941">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E941" t="s">
         <v>30</v>
@@ -20094,7 +20094,7 @@
         <v>29</v>
       </c>
       <c r="D942">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E942" t="s">
         <v>30</v>
@@ -20111,7 +20111,7 @@
         <v>29</v>
       </c>
       <c r="D943">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E943" t="s">
         <v>30</v>
@@ -20128,7 +20128,7 @@
         <v>29</v>
       </c>
       <c r="D944">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E944" t="s">
         <v>30</v>
@@ -20145,7 +20145,7 @@
         <v>29</v>
       </c>
       <c r="D945">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E945" t="s">
         <v>30</v>
@@ -20179,7 +20179,7 @@
         <v>29</v>
       </c>
       <c r="D947">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E947" t="s">
         <v>30</v>
@@ -20196,7 +20196,7 @@
         <v>29</v>
       </c>
       <c r="D948">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E948" t="s">
         <v>30</v>
@@ -20213,7 +20213,7 @@
         <v>29</v>
       </c>
       <c r="D949">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E949" t="s">
         <v>30</v>
@@ -20230,7 +20230,7 @@
         <v>29</v>
       </c>
       <c r="D950">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E950" t="s">
         <v>30</v>
@@ -20247,7 +20247,7 @@
         <v>29</v>
       </c>
       <c r="D951">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E951" t="s">
         <v>30</v>
@@ -20264,7 +20264,7 @@
         <v>29</v>
       </c>
       <c r="D952">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E952" t="s">
         <v>30</v>
@@ -20281,7 +20281,7 @@
         <v>29</v>
       </c>
       <c r="D953">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E953" t="s">
         <v>30</v>
@@ -20298,7 +20298,7 @@
         <v>29</v>
       </c>
       <c r="D954">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E954" t="s">
         <v>30</v>
@@ -20315,7 +20315,7 @@
         <v>29</v>
       </c>
       <c r="D955">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E955" t="s">
         <v>30</v>
@@ -20332,7 +20332,7 @@
         <v>29</v>
       </c>
       <c r="D956">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E956" t="s">
         <v>30</v>
@@ -20349,7 +20349,7 @@
         <v>29</v>
       </c>
       <c r="D957">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E957" t="s">
         <v>30</v>
@@ -20366,7 +20366,7 @@
         <v>29</v>
       </c>
       <c r="D958">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E958" t="s">
         <v>30</v>
@@ -20383,7 +20383,7 @@
         <v>29</v>
       </c>
       <c r="D959">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E959" t="s">
         <v>30</v>
@@ -20400,7 +20400,7 @@
         <v>29</v>
       </c>
       <c r="D960">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E960" t="s">
         <v>30</v>
@@ -20417,7 +20417,7 @@
         <v>29</v>
       </c>
       <c r="D961">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E961" t="s">
         <v>30</v>
@@ -20434,7 +20434,7 @@
         <v>29</v>
       </c>
       <c r="D962">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E962" t="s">
         <v>30</v>
@@ -20451,7 +20451,7 @@
         <v>29</v>
       </c>
       <c r="D963">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E963" t="s">
         <v>30</v>
@@ -20468,7 +20468,7 @@
         <v>29</v>
       </c>
       <c r="D964">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E964" t="s">
         <v>30</v>
@@ -20485,7 +20485,7 @@
         <v>29</v>
       </c>
       <c r="D965">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E965" t="s">
         <v>30</v>
@@ -20502,7 +20502,7 @@
         <v>29</v>
       </c>
       <c r="D966">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E966" t="s">
         <v>30</v>
@@ -20519,7 +20519,7 @@
         <v>29</v>
       </c>
       <c r="D967">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E967" t="s">
         <v>30</v>
@@ -20536,7 +20536,7 @@
         <v>29</v>
       </c>
       <c r="D968">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E968" t="s">
         <v>30</v>
@@ -20553,7 +20553,7 @@
         <v>29</v>
       </c>
       <c r="D969">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E969" t="s">
         <v>30</v>
@@ -20570,7 +20570,7 @@
         <v>29</v>
       </c>
       <c r="D970">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E970" t="s">
         <v>30</v>
@@ -20604,7 +20604,7 @@
         <v>29</v>
       </c>
       <c r="D972">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E972" t="s">
         <v>30</v>
@@ -20621,7 +20621,7 @@
         <v>29</v>
       </c>
       <c r="D973">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E973" t="s">
         <v>30</v>
@@ -20638,7 +20638,7 @@
         <v>29</v>
       </c>
       <c r="D974">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E974" t="s">
         <v>30</v>
@@ -20655,7 +20655,7 @@
         <v>29</v>
       </c>
       <c r="D975">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E975" t="s">
         <v>30</v>
@@ -20672,7 +20672,7 @@
         <v>29</v>
       </c>
       <c r="D976">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E976" t="s">
         <v>30</v>
@@ -20689,7 +20689,7 @@
         <v>29</v>
       </c>
       <c r="D977">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E977" t="s">
         <v>30</v>
@@ -20706,7 +20706,7 @@
         <v>29</v>
       </c>
       <c r="D978">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E978" t="s">
         <v>30</v>
@@ -20723,7 +20723,7 @@
         <v>29</v>
       </c>
       <c r="D979">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E979" t="s">
         <v>30</v>
@@ -20740,7 +20740,7 @@
         <v>29</v>
       </c>
       <c r="D980">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E980" t="s">
         <v>30</v>
@@ -20757,7 +20757,7 @@
         <v>29</v>
       </c>
       <c r="D981">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E981" t="s">
         <v>30</v>
@@ -20774,7 +20774,7 @@
         <v>29</v>
       </c>
       <c r="D982">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E982" t="s">
         <v>30</v>
@@ -20791,7 +20791,7 @@
         <v>29</v>
       </c>
       <c r="D983">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E983" t="s">
         <v>30</v>
@@ -20808,7 +20808,7 @@
         <v>29</v>
       </c>
       <c r="D984">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E984" t="s">
         <v>30</v>
@@ -20825,7 +20825,7 @@
         <v>29</v>
       </c>
       <c r="D985">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E985" t="s">
         <v>30</v>
@@ -20842,7 +20842,7 @@
         <v>29</v>
       </c>
       <c r="D986">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E986" t="s">
         <v>30</v>
@@ -20859,7 +20859,7 @@
         <v>29</v>
       </c>
       <c r="D987">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E987" t="s">
         <v>30</v>
@@ -20876,7 +20876,7 @@
         <v>29</v>
       </c>
       <c r="D988">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E988" t="s">
         <v>30</v>
@@ -20893,7 +20893,7 @@
         <v>29</v>
       </c>
       <c r="D989">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E989" t="s">
         <v>30</v>
@@ -20910,7 +20910,7 @@
         <v>29</v>
       </c>
       <c r="D990">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E990" t="s">
         <v>30</v>
@@ -20927,7 +20927,7 @@
         <v>29</v>
       </c>
       <c r="D991">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E991" t="s">
         <v>30</v>
@@ -20944,7 +20944,7 @@
         <v>29</v>
       </c>
       <c r="D992">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E992" t="s">
         <v>30</v>
@@ -20961,7 +20961,7 @@
         <v>29</v>
       </c>
       <c r="D993">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E993" t="s">
         <v>30</v>
@@ -20978,7 +20978,7 @@
         <v>29</v>
       </c>
       <c r="D994">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E994" t="s">
         <v>30</v>
@@ -20995,7 +20995,7 @@
         <v>29</v>
       </c>
       <c r="D995">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E995" t="s">
         <v>30</v>
@@ -21012,7 +21012,7 @@
         <v>29</v>
       </c>
       <c r="D996">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E996" t="s">
         <v>30</v>
@@ -21046,7 +21046,7 @@
         <v>29</v>
       </c>
       <c r="D998">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E998" t="s">
         <v>30</v>
@@ -21063,7 +21063,7 @@
         <v>29</v>
       </c>
       <c r="D999">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E999" t="s">
         <v>30</v>
@@ -21080,7 +21080,7 @@
         <v>29</v>
       </c>
       <c r="D1000">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1000" t="s">
         <v>30</v>
@@ -21097,7 +21097,7 @@
         <v>29</v>
       </c>
       <c r="D1001">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1001" t="s">
         <v>30</v>
@@ -21114,7 +21114,7 @@
         <v>29</v>
       </c>
       <c r="D1002">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1002" t="s">
         <v>30</v>
@@ -21131,7 +21131,7 @@
         <v>29</v>
       </c>
       <c r="D1003">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E1003" t="s">
         <v>30</v>
@@ -21148,7 +21148,7 @@
         <v>29</v>
       </c>
       <c r="D1004">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E1004" t="s">
         <v>30</v>
@@ -21165,7 +21165,7 @@
         <v>29</v>
       </c>
       <c r="D1005">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E1005" t="s">
         <v>30</v>
@@ -21182,7 +21182,7 @@
         <v>29</v>
       </c>
       <c r="D1006">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1006" t="s">
         <v>30</v>
@@ -21199,7 +21199,7 @@
         <v>29</v>
       </c>
       <c r="D1007">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1007" t="s">
         <v>30</v>
@@ -21233,7 +21233,7 @@
         <v>29</v>
       </c>
       <c r="D1009">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1009" t="s">
         <v>30</v>
@@ -21250,7 +21250,7 @@
         <v>29</v>
       </c>
       <c r="D1010">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1010" t="s">
         <v>30</v>
@@ -21267,7 +21267,7 @@
         <v>29</v>
       </c>
       <c r="D1011">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1011" t="s">
         <v>30</v>
@@ -21284,7 +21284,7 @@
         <v>29</v>
       </c>
       <c r="D1012">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E1012" t="s">
         <v>30</v>
@@ -21301,7 +21301,7 @@
         <v>29</v>
       </c>
       <c r="D1013">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1013" t="s">
         <v>30</v>
@@ -21318,7 +21318,7 @@
         <v>29</v>
       </c>
       <c r="D1014">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E1014" t="s">
         <v>30</v>
@@ -21335,7 +21335,7 @@
         <v>29</v>
       </c>
       <c r="D1015">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1015" t="s">
         <v>30</v>
@@ -21352,7 +21352,7 @@
         <v>29</v>
       </c>
       <c r="D1016">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1016" t="s">
         <v>30</v>
@@ -21369,7 +21369,7 @@
         <v>29</v>
       </c>
       <c r="D1017">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1017" t="s">
         <v>30</v>
@@ -21386,7 +21386,7 @@
         <v>29</v>
       </c>
       <c r="D1018">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E1018" t="s">
         <v>30</v>
@@ -21403,7 +21403,7 @@
         <v>29</v>
       </c>
       <c r="D1019">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1019" t="s">
         <v>30</v>
@@ -21420,7 +21420,7 @@
         <v>29</v>
       </c>
       <c r="D1020">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1020" t="s">
         <v>30</v>
@@ -21437,7 +21437,7 @@
         <v>29</v>
       </c>
       <c r="D1021">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E1021" t="s">
         <v>30</v>
@@ -21454,7 +21454,7 @@
         <v>29</v>
       </c>
       <c r="D1022">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1022" t="s">
         <v>30</v>
@@ -21505,7 +21505,7 @@
         <v>29</v>
       </c>
       <c r="D1025">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1025" t="s">
         <v>30</v>
@@ -21522,7 +21522,7 @@
         <v>29</v>
       </c>
       <c r="D1026">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E1026" t="s">
         <v>30</v>
@@ -21539,7 +21539,7 @@
         <v>29</v>
       </c>
       <c r="D1027">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1027" t="s">
         <v>30</v>
@@ -21556,7 +21556,7 @@
         <v>29</v>
       </c>
       <c r="D1028">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E1028" t="s">
         <v>30</v>
@@ -21573,7 +21573,7 @@
         <v>29</v>
       </c>
       <c r="D1029">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1029" t="s">
         <v>30</v>
@@ -21590,7 +21590,7 @@
         <v>29</v>
       </c>
       <c r="D1030">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1030" t="s">
         <v>30</v>
@@ -21607,7 +21607,7 @@
         <v>29</v>
       </c>
       <c r="D1031">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1031" t="s">
         <v>30</v>
@@ -21624,7 +21624,7 @@
         <v>29</v>
       </c>
       <c r="D1032">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1032" t="s">
         <v>30</v>
@@ -21641,7 +21641,7 @@
         <v>29</v>
       </c>
       <c r="D1033">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E1033" t="s">
         <v>30</v>
@@ -21658,7 +21658,7 @@
         <v>29</v>
       </c>
       <c r="D1034">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1034" t="s">
         <v>30</v>
@@ -21675,7 +21675,7 @@
         <v>29</v>
       </c>
       <c r="D1035">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1035" t="s">
         <v>30</v>
@@ -21692,7 +21692,7 @@
         <v>29</v>
       </c>
       <c r="D1036">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1036" t="s">
         <v>30</v>
@@ -21709,7 +21709,7 @@
         <v>29</v>
       </c>
       <c r="D1037">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1037" t="s">
         <v>30</v>
@@ -21726,7 +21726,7 @@
         <v>29</v>
       </c>
       <c r="D1038">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1038" t="s">
         <v>30</v>
@@ -21743,7 +21743,7 @@
         <v>29</v>
       </c>
       <c r="D1039">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1039" t="s">
         <v>30</v>
@@ -21760,7 +21760,7 @@
         <v>29</v>
       </c>
       <c r="D1040">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E1040" t="s">
         <v>30</v>
@@ -21777,7 +21777,7 @@
         <v>29</v>
       </c>
       <c r="D1041">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E1041" t="s">
         <v>30</v>
@@ -21794,7 +21794,7 @@
         <v>29</v>
       </c>
       <c r="D1042">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1042" t="s">
         <v>30</v>
@@ -21811,7 +21811,7 @@
         <v>29</v>
       </c>
       <c r="D1043">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1043" t="s">
         <v>30</v>
@@ -21828,7 +21828,7 @@
         <v>29</v>
       </c>
       <c r="D1044">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1044" t="s">
         <v>30</v>
@@ -21845,7 +21845,7 @@
         <v>29</v>
       </c>
       <c r="D1045">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1045" t="s">
         <v>30</v>
@@ -21862,7 +21862,7 @@
         <v>29</v>
       </c>
       <c r="D1046">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1046" t="s">
         <v>30</v>
@@ -21879,7 +21879,7 @@
         <v>29</v>
       </c>
       <c r="D1047">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1047" t="s">
         <v>30</v>
@@ -21896,7 +21896,7 @@
         <v>29</v>
       </c>
       <c r="D1048">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1048" t="s">
         <v>30</v>
@@ -21913,7 +21913,7 @@
         <v>29</v>
       </c>
       <c r="D1049">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1049" t="s">
         <v>30</v>
@@ -21930,7 +21930,7 @@
         <v>29</v>
       </c>
       <c r="D1050">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1050" t="s">
         <v>30</v>
@@ -21947,7 +21947,7 @@
         <v>29</v>
       </c>
       <c r="D1051">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1051" t="s">
         <v>30</v>
@@ -21964,7 +21964,7 @@
         <v>29</v>
       </c>
       <c r="D1052">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E1052" t="s">
         <v>30</v>
@@ -21981,7 +21981,7 @@
         <v>29</v>
       </c>
       <c r="D1053">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E1053" t="s">
         <v>30</v>
@@ -21998,7 +21998,7 @@
         <v>29</v>
       </c>
       <c r="D1054">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E1054" t="s">
         <v>30</v>
@@ -22015,7 +22015,7 @@
         <v>29</v>
       </c>
       <c r="D1055">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E1055" t="s">
         <v>30</v>
@@ -22049,7 +22049,7 @@
         <v>29</v>
       </c>
       <c r="D1057">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1057" t="s">
         <v>30</v>
@@ -22066,7 +22066,7 @@
         <v>29</v>
       </c>
       <c r="D1058">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1058" t="s">
         <v>30</v>
@@ -22083,7 +22083,7 @@
         <v>29</v>
       </c>
       <c r="D1059">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1059" t="s">
         <v>30</v>
@@ -22100,7 +22100,7 @@
         <v>29</v>
       </c>
       <c r="D1060">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1060" t="s">
         <v>30</v>
@@ -22117,7 +22117,7 @@
         <v>29</v>
       </c>
       <c r="D1061">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E1061" t="s">
         <v>30</v>
@@ -22134,7 +22134,7 @@
         <v>29</v>
       </c>
       <c r="D1062">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E1062" t="s">
         <v>30</v>
@@ -22185,7 +22185,7 @@
         <v>29</v>
       </c>
       <c r="D1065">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1065" t="s">
         <v>30</v>
@@ -22202,7 +22202,7 @@
         <v>29</v>
       </c>
       <c r="D1066">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1066" t="s">
         <v>30</v>
@@ -22219,7 +22219,7 @@
         <v>29</v>
       </c>
       <c r="D1067">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1067" t="s">
         <v>30</v>
@@ -22236,7 +22236,7 @@
         <v>29</v>
       </c>
       <c r="D1068">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E1068" t="s">
         <v>30</v>
@@ -22253,7 +22253,7 @@
         <v>29</v>
       </c>
       <c r="D1069">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1069" t="s">
         <v>30</v>
@@ -22270,7 +22270,7 @@
         <v>29</v>
       </c>
       <c r="D1070">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1070" t="s">
         <v>30</v>
@@ -22287,7 +22287,7 @@
         <v>29</v>
       </c>
       <c r="D1071">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1071" t="s">
         <v>30</v>
@@ -22304,7 +22304,7 @@
         <v>29</v>
       </c>
       <c r="D1072">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1072" t="s">
         <v>30</v>
@@ -22338,7 +22338,7 @@
         <v>29</v>
       </c>
       <c r="D1074">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1074" t="s">
         <v>30</v>
@@ -22355,7 +22355,7 @@
         <v>29</v>
       </c>
       <c r="D1075">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1075" t="s">
         <v>30</v>
@@ -22372,7 +22372,7 @@
         <v>29</v>
       </c>
       <c r="D1076">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1076" t="s">
         <v>30</v>
@@ -22406,7 +22406,7 @@
         <v>29</v>
       </c>
       <c r="D1078">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1078" t="s">
         <v>30</v>
@@ -22440,7 +22440,7 @@
         <v>29</v>
       </c>
       <c r="D1080">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1080" t="s">
         <v>30</v>
@@ -22457,7 +22457,7 @@
         <v>29</v>
       </c>
       <c r="D1081">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1081" t="s">
         <v>30</v>
@@ -22474,7 +22474,7 @@
         <v>29</v>
       </c>
       <c r="D1082">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E1082" t="s">
         <v>30</v>
@@ -22491,7 +22491,7 @@
         <v>29</v>
       </c>
       <c r="D1083">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E1083" t="s">
         <v>30</v>
@@ -22508,7 +22508,7 @@
         <v>29</v>
       </c>
       <c r="D1084">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E1084" t="s">
         <v>30</v>
@@ -22525,7 +22525,7 @@
         <v>29</v>
       </c>
       <c r="D1085">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E1085" t="s">
         <v>30</v>
@@ -22542,7 +22542,7 @@
         <v>29</v>
       </c>
       <c r="D1086">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1086" t="s">
         <v>30</v>
@@ -22559,7 +22559,7 @@
         <v>29</v>
       </c>
       <c r="D1087">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E1087" t="s">
         <v>30</v>
@@ -22576,7 +22576,7 @@
         <v>29</v>
       </c>
       <c r="D1088">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1088" t="s">
         <v>30</v>
@@ -22593,7 +22593,7 @@
         <v>29</v>
       </c>
       <c r="D1089">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1089" t="s">
         <v>30</v>
@@ -22610,7 +22610,7 @@
         <v>29</v>
       </c>
       <c r="D1090">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1090" t="s">
         <v>30</v>
@@ -22627,7 +22627,7 @@
         <v>29</v>
       </c>
       <c r="D1091">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E1091" t="s">
         <v>30</v>
@@ -22644,7 +22644,7 @@
         <v>29</v>
       </c>
       <c r="D1092">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E1092" t="s">
         <v>30</v>
@@ -22661,7 +22661,7 @@
         <v>29</v>
       </c>
       <c r="D1093">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E1093" t="s">
         <v>30</v>
@@ -22678,7 +22678,7 @@
         <v>29</v>
       </c>
       <c r="D1094">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1094" t="s">
         <v>30</v>
@@ -22695,7 +22695,7 @@
         <v>29</v>
       </c>
       <c r="D1095">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1095" t="s">
         <v>30</v>
@@ -22712,7 +22712,7 @@
         <v>29</v>
       </c>
       <c r="D1096">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1096" t="s">
         <v>30</v>
@@ -22729,7 +22729,7 @@
         <v>29</v>
       </c>
       <c r="D1097">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1097" t="s">
         <v>30</v>
@@ -22746,7 +22746,7 @@
         <v>29</v>
       </c>
       <c r="D1098">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1098" t="s">
         <v>30</v>
@@ -22763,7 +22763,7 @@
         <v>29</v>
       </c>
       <c r="D1099">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1099" t="s">
         <v>30</v>
@@ -22780,7 +22780,7 @@
         <v>29</v>
       </c>
       <c r="D1100">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1100" t="s">
         <v>30</v>
@@ -22797,7 +22797,7 @@
         <v>29</v>
       </c>
       <c r="D1101">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1101" t="s">
         <v>30</v>
@@ -22814,7 +22814,7 @@
         <v>29</v>
       </c>
       <c r="D1102">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E1102" t="s">
         <v>30</v>
@@ -22831,7 +22831,7 @@
         <v>29</v>
       </c>
       <c r="D1103">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1103" t="s">
         <v>30</v>
@@ -22848,7 +22848,7 @@
         <v>29</v>
       </c>
       <c r="D1104">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1104" t="s">
         <v>30</v>
@@ -22865,7 +22865,7 @@
         <v>29</v>
       </c>
       <c r="D1105">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1105" t="s">
         <v>30</v>
@@ -22882,7 +22882,7 @@
         <v>29</v>
       </c>
       <c r="D1106">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1106" t="s">
         <v>30</v>
@@ -22916,7 +22916,7 @@
         <v>29</v>
       </c>
       <c r="D1108">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1108" t="s">
         <v>30</v>
@@ -22933,7 +22933,7 @@
         <v>29</v>
       </c>
       <c r="D1109">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1109" t="s">
         <v>30</v>
@@ -22950,7 +22950,7 @@
         <v>29</v>
       </c>
       <c r="D1110">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1110" t="s">
         <v>30</v>
@@ -22967,7 +22967,7 @@
         <v>29</v>
       </c>
       <c r="D1111">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E1111" t="s">
         <v>30</v>
@@ -22984,7 +22984,7 @@
         <v>29</v>
       </c>
       <c r="D1112">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1112" t="s">
         <v>30</v>

--- a/reports/latest/android-report.xlsx
+++ b/reports/latest/android-report.xlsx
@@ -39,7 +39,7 @@
     <t>Total Duration (s)</t>
   </si>
   <si>
-    <t>0.01</t>
+    <t>0.00</t>
   </si>
   <si>
     <t>Category</t>
@@ -4114,7 +4114,7 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>1055</v>
+        <v>900</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -4131,7 +4131,7 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -4148,7 +4148,7 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -4182,7 +4182,7 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -4199,7 +4199,7 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -4216,7 +4216,7 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -4233,7 +4233,7 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -4250,7 +4250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
@@ -4284,7 +4284,7 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -4301,7 +4301,7 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -4318,7 +4318,7 @@
         <v>29</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4335,7 +4335,7 @@
         <v>29</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -4352,7 +4352,7 @@
         <v>29</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -4369,7 +4369,7 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -4386,7 +4386,7 @@
         <v>29</v>
       </c>
       <c r="D18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -4403,7 +4403,7 @@
         <v>29</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
@@ -4420,7 +4420,7 @@
         <v>29</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
@@ -4437,7 +4437,7 @@
         <v>29</v>
       </c>
       <c r="D21">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
         <v>30</v>
@@ -4454,7 +4454,7 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
         <v>30</v>
@@ -4471,7 +4471,7 @@
         <v>29</v>
       </c>
       <c r="D23">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
         <v>30</v>
@@ -4488,7 +4488,7 @@
         <v>29</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s">
         <v>30</v>
@@ -4505,7 +4505,7 @@
         <v>29</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
         <v>30</v>
@@ -4522,7 +4522,7 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
         <v>30</v>
@@ -4539,7 +4539,7 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s">
         <v>30</v>
@@ -4556,7 +4556,7 @@
         <v>29</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E28" t="s">
         <v>30</v>
@@ -4573,7 +4573,7 @@
         <v>29</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="s">
         <v>30</v>
@@ -4607,7 +4607,7 @@
         <v>29</v>
       </c>
       <c r="D31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E31" t="s">
         <v>30</v>
@@ -4624,7 +4624,7 @@
         <v>29</v>
       </c>
       <c r="D32">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
         <v>30</v>
@@ -4641,7 +4641,7 @@
         <v>29</v>
       </c>
       <c r="D33">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E33" t="s">
         <v>30</v>
@@ -4658,7 +4658,7 @@
         <v>29</v>
       </c>
       <c r="D34">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E34" t="s">
         <v>30</v>
@@ -4675,7 +4675,7 @@
         <v>29</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
         <v>30</v>
@@ -4692,7 +4692,7 @@
         <v>29</v>
       </c>
       <c r="D36">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
         <v>30</v>
@@ -4709,7 +4709,7 @@
         <v>29</v>
       </c>
       <c r="D37">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E37" t="s">
         <v>30</v>
@@ -4726,7 +4726,7 @@
         <v>29</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
         <v>30</v>
@@ -4743,7 +4743,7 @@
         <v>29</v>
       </c>
       <c r="D39">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E39" t="s">
         <v>30</v>
@@ -4760,7 +4760,7 @@
         <v>29</v>
       </c>
       <c r="D40">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E40" t="s">
         <v>30</v>
@@ -4794,7 +4794,7 @@
         <v>29</v>
       </c>
       <c r="D42">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E42" t="s">
         <v>30</v>
@@ -4811,7 +4811,7 @@
         <v>29</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
         <v>30</v>
@@ -4828,7 +4828,7 @@
         <v>29</v>
       </c>
       <c r="D44">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E44" t="s">
         <v>30</v>
@@ -4845,7 +4845,7 @@
         <v>29</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E45" t="s">
         <v>30</v>
@@ -4862,7 +4862,7 @@
         <v>29</v>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E46" t="s">
         <v>30</v>
@@ -4879,7 +4879,7 @@
         <v>29</v>
       </c>
       <c r="D47">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E47" t="s">
         <v>30</v>
@@ -4896,7 +4896,7 @@
         <v>29</v>
       </c>
       <c r="D48">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
         <v>30</v>
@@ -4913,7 +4913,7 @@
         <v>29</v>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E49" t="s">
         <v>30</v>
@@ -4930,7 +4930,7 @@
         <v>29</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E50" t="s">
         <v>30</v>
@@ -4947,7 +4947,7 @@
         <v>29</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
         <v>30</v>
@@ -4964,7 +4964,7 @@
         <v>29</v>
       </c>
       <c r="D52">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
         <v>30</v>
@@ -4981,7 +4981,7 @@
         <v>29</v>
       </c>
       <c r="D53">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>30</v>
@@ -4998,7 +4998,7 @@
         <v>29</v>
       </c>
       <c r="D54">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E54" t="s">
         <v>30</v>
@@ -5015,7 +5015,7 @@
         <v>29</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E55" t="s">
         <v>30</v>
@@ -5049,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="D57">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E57" t="s">
         <v>30</v>
@@ -5066,7 +5066,7 @@
         <v>29</v>
       </c>
       <c r="D58">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E58" t="s">
         <v>30</v>
@@ -5083,7 +5083,7 @@
         <v>29</v>
       </c>
       <c r="D59">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E59" t="s">
         <v>30</v>
@@ -5100,7 +5100,7 @@
         <v>29</v>
       </c>
       <c r="D60">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E60" t="s">
         <v>30</v>
@@ -5117,7 +5117,7 @@
         <v>29</v>
       </c>
       <c r="D61">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E61" t="s">
         <v>30</v>
@@ -5134,7 +5134,7 @@
         <v>29</v>
       </c>
       <c r="D62">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E62" t="s">
         <v>30</v>
@@ -5151,7 +5151,7 @@
         <v>29</v>
       </c>
       <c r="D63">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
         <v>30</v>
@@ -5168,7 +5168,7 @@
         <v>29</v>
       </c>
       <c r="D64">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E64" t="s">
         <v>30</v>
@@ -5185,7 +5185,7 @@
         <v>29</v>
       </c>
       <c r="D65">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E65" t="s">
         <v>30</v>
@@ -5202,7 +5202,7 @@
         <v>29</v>
       </c>
       <c r="D66">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E66" t="s">
         <v>30</v>
@@ -5219,7 +5219,7 @@
         <v>29</v>
       </c>
       <c r="D67">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E67" t="s">
         <v>30</v>
@@ -5253,7 +5253,7 @@
         <v>29</v>
       </c>
       <c r="D69">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
         <v>30</v>
@@ -5287,7 +5287,7 @@
         <v>29</v>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E71" t="s">
         <v>30</v>
@@ -5304,7 +5304,7 @@
         <v>29</v>
       </c>
       <c r="D72">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E72" t="s">
         <v>30</v>
@@ -5321,7 +5321,7 @@
         <v>29</v>
       </c>
       <c r="D73">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E73" t="s">
         <v>30</v>
@@ -5338,7 +5338,7 @@
         <v>29</v>
       </c>
       <c r="D74">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E74" t="s">
         <v>30</v>
@@ -5355,7 +5355,7 @@
         <v>29</v>
       </c>
       <c r="D75">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E75" t="s">
         <v>30</v>
@@ -5372,7 +5372,7 @@
         <v>29</v>
       </c>
       <c r="D76">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E76" t="s">
         <v>30</v>
@@ -5389,7 +5389,7 @@
         <v>29</v>
       </c>
       <c r="D77">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E77" t="s">
         <v>30</v>
@@ -5406,7 +5406,7 @@
         <v>29</v>
       </c>
       <c r="D78">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E78" t="s">
         <v>30</v>
@@ -5423,7 +5423,7 @@
         <v>29</v>
       </c>
       <c r="D79">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E79" t="s">
         <v>30</v>
@@ -5440,7 +5440,7 @@
         <v>29</v>
       </c>
       <c r="D80">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E80" t="s">
         <v>30</v>
@@ -5457,7 +5457,7 @@
         <v>29</v>
       </c>
       <c r="D81">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
         <v>30</v>
@@ -5474,7 +5474,7 @@
         <v>29</v>
       </c>
       <c r="D82">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E82" t="s">
         <v>30</v>
@@ -5491,7 +5491,7 @@
         <v>29</v>
       </c>
       <c r="D83">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E83" t="s">
         <v>30</v>
@@ -5508,7 +5508,7 @@
         <v>29</v>
       </c>
       <c r="D84">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E84" t="s">
         <v>30</v>
@@ -5525,7 +5525,7 @@
         <v>29</v>
       </c>
       <c r="D85">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>30</v>
@@ -5542,7 +5542,7 @@
         <v>29</v>
       </c>
       <c r="D86">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E86" t="s">
         <v>30</v>
@@ -5559,7 +5559,7 @@
         <v>29</v>
       </c>
       <c r="D87">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E87" t="s">
         <v>30</v>
@@ -5576,7 +5576,7 @@
         <v>29</v>
       </c>
       <c r="D88">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
         <v>30</v>
@@ -5593,7 +5593,7 @@
         <v>29</v>
       </c>
       <c r="D89">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E89" t="s">
         <v>30</v>
@@ -5610,7 +5610,7 @@
         <v>29</v>
       </c>
       <c r="D90">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E90" t="s">
         <v>30</v>
@@ -5627,7 +5627,7 @@
         <v>29</v>
       </c>
       <c r="D91">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E91" t="s">
         <v>30</v>
@@ -5644,7 +5644,7 @@
         <v>29</v>
       </c>
       <c r="D92">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
         <v>30</v>
@@ -5661,7 +5661,7 @@
         <v>29</v>
       </c>
       <c r="D93">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E93" t="s">
         <v>30</v>
@@ -5678,7 +5678,7 @@
         <v>29</v>
       </c>
       <c r="D94">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E94" t="s">
         <v>30</v>
@@ -5695,7 +5695,7 @@
         <v>29</v>
       </c>
       <c r="D95">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E95" t="s">
         <v>30</v>
@@ -5712,7 +5712,7 @@
         <v>29</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E96" t="s">
         <v>30</v>
@@ -5729,7 +5729,7 @@
         <v>29</v>
       </c>
       <c r="D97">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E97" t="s">
         <v>30</v>
@@ -5746,7 +5746,7 @@
         <v>29</v>
       </c>
       <c r="D98">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E98" t="s">
         <v>30</v>
@@ -5763,7 +5763,7 @@
         <v>29</v>
       </c>
       <c r="D99">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E99" t="s">
         <v>30</v>
@@ -5780,7 +5780,7 @@
         <v>29</v>
       </c>
       <c r="D100">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E100" t="s">
         <v>30</v>
@@ -5797,7 +5797,7 @@
         <v>29</v>
       </c>
       <c r="D101">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E101" t="s">
         <v>30</v>
@@ -5814,7 +5814,7 @@
         <v>29</v>
       </c>
       <c r="D102">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E102" t="s">
         <v>30</v>
@@ -5848,7 +5848,7 @@
         <v>29</v>
       </c>
       <c r="D104">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E104" t="s">
         <v>30</v>
@@ -5865,7 +5865,7 @@
         <v>29</v>
       </c>
       <c r="D105">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E105" t="s">
         <v>30</v>
@@ -5882,7 +5882,7 @@
         <v>29</v>
       </c>
       <c r="D106">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E106" t="s">
         <v>30</v>
@@ -5899,7 +5899,7 @@
         <v>29</v>
       </c>
       <c r="D107">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E107" t="s">
         <v>30</v>
@@ -5916,7 +5916,7 @@
         <v>29</v>
       </c>
       <c r="D108">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E108" t="s">
         <v>30</v>
@@ -5950,7 +5950,7 @@
         <v>29</v>
       </c>
       <c r="D110">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E110" t="s">
         <v>30</v>
@@ -5967,7 +5967,7 @@
         <v>29</v>
       </c>
       <c r="D111">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E111" t="s">
         <v>30</v>
@@ -5984,7 +5984,7 @@
         <v>29</v>
       </c>
       <c r="D112">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E112" t="s">
         <v>30</v>
@@ -6001,7 +6001,7 @@
         <v>29</v>
       </c>
       <c r="D113">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E113" t="s">
         <v>30</v>
@@ -6018,7 +6018,7 @@
         <v>29</v>
       </c>
       <c r="D114">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E114" t="s">
         <v>30</v>
@@ -6035,7 +6035,7 @@
         <v>29</v>
       </c>
       <c r="D115">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E115" t="s">
         <v>30</v>
@@ -6052,7 +6052,7 @@
         <v>29</v>
       </c>
       <c r="D116">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E116" t="s">
         <v>30</v>
@@ -6069,7 +6069,7 @@
         <v>29</v>
       </c>
       <c r="D117">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E117" t="s">
         <v>30</v>
@@ -6086,7 +6086,7 @@
         <v>29</v>
       </c>
       <c r="D118">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E118" t="s">
         <v>30</v>
@@ -6103,7 +6103,7 @@
         <v>29</v>
       </c>
       <c r="D119">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E119" t="s">
         <v>30</v>
@@ -6120,7 +6120,7 @@
         <v>29</v>
       </c>
       <c r="D120">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E120" t="s">
         <v>30</v>
@@ -6137,7 +6137,7 @@
         <v>29</v>
       </c>
       <c r="D121">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E121" t="s">
         <v>30</v>
@@ -6154,7 +6154,7 @@
         <v>29</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E122" t="s">
         <v>30</v>
@@ -6171,7 +6171,7 @@
         <v>29</v>
       </c>
       <c r="D123">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E123" t="s">
         <v>30</v>
@@ -6188,7 +6188,7 @@
         <v>29</v>
       </c>
       <c r="D124">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E124" t="s">
         <v>30</v>
@@ -6205,7 +6205,7 @@
         <v>29</v>
       </c>
       <c r="D125">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E125" t="s">
         <v>30</v>
@@ -6222,7 +6222,7 @@
         <v>29</v>
       </c>
       <c r="D126">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E126" t="s">
         <v>30</v>
@@ -6239,7 +6239,7 @@
         <v>29</v>
       </c>
       <c r="D127">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E127" t="s">
         <v>30</v>
@@ -6273,7 +6273,7 @@
         <v>29</v>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E129" t="s">
         <v>30</v>
@@ -6290,7 +6290,7 @@
         <v>29</v>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E130" t="s">
         <v>30</v>
@@ -6307,7 +6307,7 @@
         <v>29</v>
       </c>
       <c r="D131">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E131" t="s">
         <v>30</v>
@@ -6324,7 +6324,7 @@
         <v>29</v>
       </c>
       <c r="D132">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E132" t="s">
         <v>30</v>
@@ -6341,7 +6341,7 @@
         <v>29</v>
       </c>
       <c r="D133">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E133" t="s">
         <v>30</v>
@@ -6358,7 +6358,7 @@
         <v>29</v>
       </c>
       <c r="D134">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E134" t="s">
         <v>30</v>
@@ -6375,7 +6375,7 @@
         <v>29</v>
       </c>
       <c r="D135">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E135" t="s">
         <v>30</v>
@@ -6392,7 +6392,7 @@
         <v>29</v>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E136" t="s">
         <v>30</v>
@@ -6409,7 +6409,7 @@
         <v>29</v>
       </c>
       <c r="D137">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E137" t="s">
         <v>30</v>
@@ -6426,7 +6426,7 @@
         <v>29</v>
       </c>
       <c r="D138">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E138" t="s">
         <v>30</v>
@@ -6443,7 +6443,7 @@
         <v>29</v>
       </c>
       <c r="D139">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E139" t="s">
         <v>30</v>
@@ -6460,7 +6460,7 @@
         <v>29</v>
       </c>
       <c r="D140">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E140" t="s">
         <v>30</v>
@@ -6477,7 +6477,7 @@
         <v>29</v>
       </c>
       <c r="D141">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E141" t="s">
         <v>30</v>
@@ -6494,7 +6494,7 @@
         <v>29</v>
       </c>
       <c r="D142">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E142" t="s">
         <v>30</v>
@@ -6511,7 +6511,7 @@
         <v>29</v>
       </c>
       <c r="D143">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E143" t="s">
         <v>30</v>
@@ -6528,7 +6528,7 @@
         <v>29</v>
       </c>
       <c r="D144">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E144" t="s">
         <v>30</v>
@@ -6545,7 +6545,7 @@
         <v>29</v>
       </c>
       <c r="D145">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E145" t="s">
         <v>30</v>
@@ -6562,7 +6562,7 @@
         <v>29</v>
       </c>
       <c r="D146">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E146" t="s">
         <v>30</v>
@@ -6579,7 +6579,7 @@
         <v>29</v>
       </c>
       <c r="D147">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E147" t="s">
         <v>30</v>
@@ -6596,7 +6596,7 @@
         <v>29</v>
       </c>
       <c r="D148">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E148" t="s">
         <v>30</v>
@@ -6613,7 +6613,7 @@
         <v>29</v>
       </c>
       <c r="D149">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E149" t="s">
         <v>30</v>
@@ -6630,7 +6630,7 @@
         <v>29</v>
       </c>
       <c r="D150">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E150" t="s">
         <v>30</v>
@@ -6664,7 +6664,7 @@
         <v>29</v>
       </c>
       <c r="D152">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E152" t="s">
         <v>30</v>
@@ -6681,7 +6681,7 @@
         <v>29</v>
       </c>
       <c r="D153">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E153" t="s">
         <v>30</v>
@@ -6698,7 +6698,7 @@
         <v>29</v>
       </c>
       <c r="D154">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E154" t="s">
         <v>30</v>
@@ -6715,7 +6715,7 @@
         <v>29</v>
       </c>
       <c r="D155">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E155" t="s">
         <v>30</v>
@@ -6732,7 +6732,7 @@
         <v>29</v>
       </c>
       <c r="D156">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E156" t="s">
         <v>30</v>
@@ -6749,7 +6749,7 @@
         <v>29</v>
       </c>
       <c r="D157">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E157" t="s">
         <v>30</v>
@@ -6766,7 +6766,7 @@
         <v>29</v>
       </c>
       <c r="D158">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E158" t="s">
         <v>30</v>
@@ -6783,7 +6783,7 @@
         <v>29</v>
       </c>
       <c r="D159">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E159" t="s">
         <v>30</v>
@@ -6800,7 +6800,7 @@
         <v>29</v>
       </c>
       <c r="D160">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E160" t="s">
         <v>30</v>
@@ -6817,7 +6817,7 @@
         <v>29</v>
       </c>
       <c r="D161">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E161" t="s">
         <v>30</v>
@@ -6834,7 +6834,7 @@
         <v>29</v>
       </c>
       <c r="D162">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E162" t="s">
         <v>30</v>
@@ -6851,7 +6851,7 @@
         <v>29</v>
       </c>
       <c r="D163">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E163" t="s">
         <v>30</v>
@@ -6885,7 +6885,7 @@
         <v>29</v>
       </c>
       <c r="D165">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E165" t="s">
         <v>30</v>
@@ -6902,7 +6902,7 @@
         <v>29</v>
       </c>
       <c r="D166">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E166" t="s">
         <v>30</v>
@@ -6919,7 +6919,7 @@
         <v>29</v>
       </c>
       <c r="D167">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E167" t="s">
         <v>30</v>
@@ -6936,7 +6936,7 @@
         <v>29</v>
       </c>
       <c r="D168">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E168" t="s">
         <v>30</v>
@@ -6953,7 +6953,7 @@
         <v>29</v>
       </c>
       <c r="D169">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E169" t="s">
         <v>30</v>
@@ -6987,7 +6987,7 @@
         <v>29</v>
       </c>
       <c r="D171">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E171" t="s">
         <v>30</v>
@@ -7004,7 +7004,7 @@
         <v>29</v>
       </c>
       <c r="D172">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E172" t="s">
         <v>30</v>
@@ -7021,7 +7021,7 @@
         <v>29</v>
       </c>
       <c r="D173">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E173" t="s">
         <v>30</v>
@@ -7038,7 +7038,7 @@
         <v>29</v>
       </c>
       <c r="D174">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E174" t="s">
         <v>30</v>
@@ -7055,7 +7055,7 @@
         <v>29</v>
       </c>
       <c r="D175">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E175" t="s">
         <v>30</v>
@@ -7072,7 +7072,7 @@
         <v>29</v>
       </c>
       <c r="D176">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E176" t="s">
         <v>30</v>
@@ -7089,7 +7089,7 @@
         <v>29</v>
       </c>
       <c r="D177">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E177" t="s">
         <v>30</v>
@@ -7106,7 +7106,7 @@
         <v>29</v>
       </c>
       <c r="D178">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E178" t="s">
         <v>30</v>
@@ -7123,7 +7123,7 @@
         <v>29</v>
       </c>
       <c r="D179">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E179" t="s">
         <v>30</v>
@@ -7140,7 +7140,7 @@
         <v>29</v>
       </c>
       <c r="D180">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E180" t="s">
         <v>30</v>
@@ -7157,7 +7157,7 @@
         <v>29</v>
       </c>
       <c r="D181">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E181" t="s">
         <v>30</v>
@@ -7174,7 +7174,7 @@
         <v>29</v>
       </c>
       <c r="D182">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E182" t="s">
         <v>30</v>
@@ -7191,7 +7191,7 @@
         <v>29</v>
       </c>
       <c r="D183">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E183" t="s">
         <v>30</v>
@@ -7208,7 +7208,7 @@
         <v>29</v>
       </c>
       <c r="D184">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E184" t="s">
         <v>30</v>
@@ -7225,7 +7225,7 @@
         <v>29</v>
       </c>
       <c r="D185">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E185" t="s">
         <v>30</v>
@@ -7242,7 +7242,7 @@
         <v>29</v>
       </c>
       <c r="D186">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E186" t="s">
         <v>30</v>
@@ -7276,7 +7276,7 @@
         <v>29</v>
       </c>
       <c r="D188">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E188" t="s">
         <v>30</v>
@@ -7293,7 +7293,7 @@
         <v>29</v>
       </c>
       <c r="D189">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E189" t="s">
         <v>30</v>
@@ -7310,7 +7310,7 @@
         <v>29</v>
       </c>
       <c r="D190">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E190" t="s">
         <v>30</v>
@@ -7327,7 +7327,7 @@
         <v>29</v>
       </c>
       <c r="D191">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E191" t="s">
         <v>30</v>
@@ -7344,7 +7344,7 @@
         <v>29</v>
       </c>
       <c r="D192">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E192" t="s">
         <v>30</v>
@@ -7361,7 +7361,7 @@
         <v>29</v>
       </c>
       <c r="D193">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E193" t="s">
         <v>30</v>
@@ -7378,7 +7378,7 @@
         <v>29</v>
       </c>
       <c r="D194">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E194" t="s">
         <v>30</v>
@@ -7395,7 +7395,7 @@
         <v>29</v>
       </c>
       <c r="D195">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E195" t="s">
         <v>30</v>
@@ -7412,7 +7412,7 @@
         <v>29</v>
       </c>
       <c r="D196">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E196" t="s">
         <v>30</v>
@@ -7429,7 +7429,7 @@
         <v>29</v>
       </c>
       <c r="D197">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E197" t="s">
         <v>30</v>
@@ -7446,7 +7446,7 @@
         <v>29</v>
       </c>
       <c r="D198">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E198" t="s">
         <v>30</v>
@@ -7463,7 +7463,7 @@
         <v>29</v>
       </c>
       <c r="D199">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E199" t="s">
         <v>30</v>
@@ -7480,7 +7480,7 @@
         <v>29</v>
       </c>
       <c r="D200">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E200" t="s">
         <v>30</v>
@@ -7497,7 +7497,7 @@
         <v>29</v>
       </c>
       <c r="D201">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E201" t="s">
         <v>30</v>
@@ -7514,7 +7514,7 @@
         <v>29</v>
       </c>
       <c r="D202">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E202" t="s">
         <v>30</v>
@@ -7531,7 +7531,7 @@
         <v>29</v>
       </c>
       <c r="D203">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E203" t="s">
         <v>30</v>
@@ -7548,7 +7548,7 @@
         <v>29</v>
       </c>
       <c r="D204">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E204" t="s">
         <v>30</v>
@@ -7565,7 +7565,7 @@
         <v>29</v>
       </c>
       <c r="D205">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E205" t="s">
         <v>30</v>
@@ -7582,7 +7582,7 @@
         <v>29</v>
       </c>
       <c r="D206">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E206" t="s">
         <v>30</v>
@@ -7599,7 +7599,7 @@
         <v>29</v>
       </c>
       <c r="D207">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E207" t="s">
         <v>30</v>
@@ -7616,7 +7616,7 @@
         <v>29</v>
       </c>
       <c r="D208">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E208" t="s">
         <v>30</v>
@@ -7633,7 +7633,7 @@
         <v>29</v>
       </c>
       <c r="D209">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E209" t="s">
         <v>30</v>
@@ -7650,7 +7650,7 @@
         <v>29</v>
       </c>
       <c r="D210">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E210" t="s">
         <v>30</v>
@@ -7667,7 +7667,7 @@
         <v>29</v>
       </c>
       <c r="D211">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E211" t="s">
         <v>30</v>
@@ -7684,7 +7684,7 @@
         <v>29</v>
       </c>
       <c r="D212">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E212" t="s">
         <v>30</v>
@@ -7701,7 +7701,7 @@
         <v>29</v>
       </c>
       <c r="D213">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E213" t="s">
         <v>30</v>
@@ -7718,7 +7718,7 @@
         <v>29</v>
       </c>
       <c r="D214">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E214" t="s">
         <v>30</v>
@@ -7735,7 +7735,7 @@
         <v>29</v>
       </c>
       <c r="D215">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E215" t="s">
         <v>30</v>
@@ -7752,7 +7752,7 @@
         <v>29</v>
       </c>
       <c r="D216">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E216" t="s">
         <v>30</v>
@@ -7769,7 +7769,7 @@
         <v>29</v>
       </c>
       <c r="D217">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E217" t="s">
         <v>30</v>
@@ -7786,7 +7786,7 @@
         <v>29</v>
       </c>
       <c r="D218">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E218" t="s">
         <v>30</v>
@@ -7820,7 +7820,7 @@
         <v>29</v>
       </c>
       <c r="D220">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E220" t="s">
         <v>30</v>
@@ -7837,7 +7837,7 @@
         <v>29</v>
       </c>
       <c r="D221">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E221" t="s">
         <v>30</v>
@@ -7854,7 +7854,7 @@
         <v>29</v>
       </c>
       <c r="D222">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E222" t="s">
         <v>30</v>
@@ -7871,7 +7871,7 @@
         <v>29</v>
       </c>
       <c r="D223">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E223" t="s">
         <v>30</v>
@@ -7888,7 +7888,7 @@
         <v>29</v>
       </c>
       <c r="D224">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E224" t="s">
         <v>30</v>
@@ -7905,7 +7905,7 @@
         <v>29</v>
       </c>
       <c r="D225">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E225" t="s">
         <v>30</v>
@@ -7922,7 +7922,7 @@
         <v>29</v>
       </c>
       <c r="D226">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E226" t="s">
         <v>30</v>
@@ -7939,7 +7939,7 @@
         <v>29</v>
       </c>
       <c r="D227">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E227" t="s">
         <v>30</v>
@@ -7956,7 +7956,7 @@
         <v>29</v>
       </c>
       <c r="D228">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E228" t="s">
         <v>30</v>
@@ -7973,7 +7973,7 @@
         <v>29</v>
       </c>
       <c r="D229">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E229" t="s">
         <v>30</v>
@@ -7990,7 +7990,7 @@
         <v>29</v>
       </c>
       <c r="D230">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E230" t="s">
         <v>30</v>
@@ -8007,7 +8007,7 @@
         <v>29</v>
       </c>
       <c r="D231">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E231" t="s">
         <v>30</v>
@@ -8024,7 +8024,7 @@
         <v>29</v>
       </c>
       <c r="D232">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E232" t="s">
         <v>30</v>
@@ -8041,7 +8041,7 @@
         <v>29</v>
       </c>
       <c r="D233">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E233" t="s">
         <v>30</v>
@@ -8075,7 +8075,7 @@
         <v>29</v>
       </c>
       <c r="D235">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E235" t="s">
         <v>30</v>
@@ -8092,7 +8092,7 @@
         <v>29</v>
       </c>
       <c r="D236">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E236" t="s">
         <v>30</v>
@@ -8126,7 +8126,7 @@
         <v>29</v>
       </c>
       <c r="D238">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E238" t="s">
         <v>30</v>
@@ -8143,7 +8143,7 @@
         <v>29</v>
       </c>
       <c r="D239">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E239" t="s">
         <v>30</v>
@@ -8160,7 +8160,7 @@
         <v>29</v>
       </c>
       <c r="D240">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E240" t="s">
         <v>30</v>
@@ -8177,7 +8177,7 @@
         <v>29</v>
       </c>
       <c r="D241">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E241" t="s">
         <v>30</v>
@@ -8211,7 +8211,7 @@
         <v>29</v>
       </c>
       <c r="D243">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E243" t="s">
         <v>30</v>
@@ -8228,7 +8228,7 @@
         <v>29</v>
       </c>
       <c r="D244">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E244" t="s">
         <v>30</v>
@@ -8245,7 +8245,7 @@
         <v>29</v>
       </c>
       <c r="D245">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E245" t="s">
         <v>30</v>
@@ -8262,7 +8262,7 @@
         <v>29</v>
       </c>
       <c r="D246">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E246" t="s">
         <v>30</v>
@@ -8279,7 +8279,7 @@
         <v>29</v>
       </c>
       <c r="D247">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E247" t="s">
         <v>30</v>
@@ -8296,7 +8296,7 @@
         <v>29</v>
       </c>
       <c r="D248">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E248" t="s">
         <v>30</v>
@@ -8313,7 +8313,7 @@
         <v>29</v>
       </c>
       <c r="D249">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E249" t="s">
         <v>30</v>
@@ -8330,7 +8330,7 @@
         <v>29</v>
       </c>
       <c r="D250">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E250" t="s">
         <v>30</v>
@@ -8347,7 +8347,7 @@
         <v>29</v>
       </c>
       <c r="D251">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E251" t="s">
         <v>30</v>
@@ -8364,7 +8364,7 @@
         <v>29</v>
       </c>
       <c r="D252">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E252" t="s">
         <v>30</v>
@@ -8381,7 +8381,7 @@
         <v>29</v>
       </c>
       <c r="D253">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E253" t="s">
         <v>30</v>
@@ -8398,7 +8398,7 @@
         <v>29</v>
       </c>
       <c r="D254">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E254" t="s">
         <v>30</v>
@@ -8415,7 +8415,7 @@
         <v>29</v>
       </c>
       <c r="D255">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E255" t="s">
         <v>30</v>
@@ -8432,7 +8432,7 @@
         <v>29</v>
       </c>
       <c r="D256">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E256" t="s">
         <v>30</v>
@@ -8449,7 +8449,7 @@
         <v>29</v>
       </c>
       <c r="D257">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E257" t="s">
         <v>30</v>
@@ -8466,7 +8466,7 @@
         <v>29</v>
       </c>
       <c r="D258">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E258" t="s">
         <v>30</v>
@@ -8483,7 +8483,7 @@
         <v>29</v>
       </c>
       <c r="D259">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E259" t="s">
         <v>30</v>
@@ -8500,7 +8500,7 @@
         <v>29</v>
       </c>
       <c r="D260">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E260" t="s">
         <v>30</v>
@@ -8517,7 +8517,7 @@
         <v>29</v>
       </c>
       <c r="D261">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E261" t="s">
         <v>30</v>
@@ -8534,7 +8534,7 @@
         <v>29</v>
       </c>
       <c r="D262">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E262" t="s">
         <v>30</v>
@@ -8551,7 +8551,7 @@
         <v>29</v>
       </c>
       <c r="D263">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E263" t="s">
         <v>30</v>
@@ -8568,7 +8568,7 @@
         <v>29</v>
       </c>
       <c r="D264">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E264" t="s">
         <v>30</v>
@@ -8585,7 +8585,7 @@
         <v>29</v>
       </c>
       <c r="D265">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E265" t="s">
         <v>30</v>
@@ -8602,7 +8602,7 @@
         <v>29</v>
       </c>
       <c r="D266">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E266" t="s">
         <v>30</v>
@@ -8619,7 +8619,7 @@
         <v>29</v>
       </c>
       <c r="D267">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E267" t="s">
         <v>30</v>
@@ -8636,7 +8636,7 @@
         <v>29</v>
       </c>
       <c r="D268">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E268" t="s">
         <v>30</v>
@@ -8653,7 +8653,7 @@
         <v>29</v>
       </c>
       <c r="D269">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E269" t="s">
         <v>30</v>
@@ -8670,7 +8670,7 @@
         <v>29</v>
       </c>
       <c r="D270">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E270" t="s">
         <v>30</v>
@@ -8687,7 +8687,7 @@
         <v>29</v>
       </c>
       <c r="D271">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E271" t="s">
         <v>30</v>
@@ -8704,7 +8704,7 @@
         <v>29</v>
       </c>
       <c r="D272">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E272" t="s">
         <v>30</v>
@@ -8721,7 +8721,7 @@
         <v>29</v>
       </c>
       <c r="D273">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E273" t="s">
         <v>30</v>
@@ -8738,7 +8738,7 @@
         <v>29</v>
       </c>
       <c r="D274">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E274" t="s">
         <v>30</v>
@@ -8755,7 +8755,7 @@
         <v>29</v>
       </c>
       <c r="D275">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E275" t="s">
         <v>30</v>
@@ -8772,7 +8772,7 @@
         <v>29</v>
       </c>
       <c r="D276">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E276" t="s">
         <v>30</v>
@@ -8789,7 +8789,7 @@
         <v>29</v>
       </c>
       <c r="D277">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E277" t="s">
         <v>30</v>
@@ -8823,7 +8823,7 @@
         <v>29</v>
       </c>
       <c r="D279">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E279" t="s">
         <v>30</v>
@@ -8840,7 +8840,7 @@
         <v>29</v>
       </c>
       <c r="D280">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E280" t="s">
         <v>30</v>
@@ -8857,7 +8857,7 @@
         <v>29</v>
       </c>
       <c r="D281">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E281" t="s">
         <v>30</v>
@@ -8874,7 +8874,7 @@
         <v>29</v>
       </c>
       <c r="D282">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E282" t="s">
         <v>30</v>
@@ -8891,7 +8891,7 @@
         <v>29</v>
       </c>
       <c r="D283">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E283" t="s">
         <v>30</v>
@@ -8908,7 +8908,7 @@
         <v>29</v>
       </c>
       <c r="D284">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E284" t="s">
         <v>30</v>
@@ -8925,7 +8925,7 @@
         <v>29</v>
       </c>
       <c r="D285">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E285" t="s">
         <v>30</v>
@@ -8942,7 +8942,7 @@
         <v>29</v>
       </c>
       <c r="D286">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E286" t="s">
         <v>30</v>
@@ -8959,7 +8959,7 @@
         <v>29</v>
       </c>
       <c r="D287">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E287" t="s">
         <v>30</v>
@@ -8976,7 +8976,7 @@
         <v>29</v>
       </c>
       <c r="D288">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E288" t="s">
         <v>30</v>
@@ -8993,7 +8993,7 @@
         <v>29</v>
       </c>
       <c r="D289">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E289" t="s">
         <v>30</v>
@@ -9010,7 +9010,7 @@
         <v>29</v>
       </c>
       <c r="D290">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E290" t="s">
         <v>30</v>
@@ -9027,7 +9027,7 @@
         <v>29</v>
       </c>
       <c r="D291">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E291" t="s">
         <v>30</v>
@@ -9044,7 +9044,7 @@
         <v>29</v>
       </c>
       <c r="D292">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E292" t="s">
         <v>30</v>
@@ -9061,7 +9061,7 @@
         <v>29</v>
       </c>
       <c r="D293">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E293" t="s">
         <v>30</v>
@@ -9078,7 +9078,7 @@
         <v>29</v>
       </c>
       <c r="D294">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E294" t="s">
         <v>30</v>
@@ -9095,7 +9095,7 @@
         <v>29</v>
       </c>
       <c r="D295">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E295" t="s">
         <v>30</v>
@@ -9112,7 +9112,7 @@
         <v>29</v>
       </c>
       <c r="D296">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E296" t="s">
         <v>30</v>
@@ -9146,7 +9146,7 @@
         <v>29</v>
       </c>
       <c r="D298">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E298" t="s">
         <v>30</v>
@@ -9163,7 +9163,7 @@
         <v>29</v>
       </c>
       <c r="D299">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E299" t="s">
         <v>30</v>
@@ -9180,7 +9180,7 @@
         <v>29</v>
       </c>
       <c r="D300">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E300" t="s">
         <v>30</v>
@@ -9197,7 +9197,7 @@
         <v>29</v>
       </c>
       <c r="D301">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E301" t="s">
         <v>30</v>
@@ -9214,7 +9214,7 @@
         <v>29</v>
       </c>
       <c r="D302">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E302" t="s">
         <v>30</v>
@@ -9231,7 +9231,7 @@
         <v>29</v>
       </c>
       <c r="D303">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E303" t="s">
         <v>30</v>
@@ -9248,7 +9248,7 @@
         <v>29</v>
       </c>
       <c r="D304">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E304" t="s">
         <v>30</v>
@@ -9265,7 +9265,7 @@
         <v>29</v>
       </c>
       <c r="D305">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E305" t="s">
         <v>30</v>
@@ -9282,7 +9282,7 @@
         <v>29</v>
       </c>
       <c r="D306">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E306" t="s">
         <v>30</v>
@@ -9299,7 +9299,7 @@
         <v>29</v>
       </c>
       <c r="D307">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E307" t="s">
         <v>30</v>
@@ -9316,7 +9316,7 @@
         <v>29</v>
       </c>
       <c r="D308">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E308" t="s">
         <v>30</v>
@@ -9333,7 +9333,7 @@
         <v>29</v>
       </c>
       <c r="D309">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E309" t="s">
         <v>30</v>
@@ -9350,7 +9350,7 @@
         <v>29</v>
       </c>
       <c r="D310">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E310" t="s">
         <v>30</v>
@@ -9367,7 +9367,7 @@
         <v>29</v>
       </c>
       <c r="D311">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E311" t="s">
         <v>30</v>
@@ -9401,7 +9401,7 @@
         <v>29</v>
       </c>
       <c r="D313">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E313" t="s">
         <v>30</v>
@@ -9418,7 +9418,7 @@
         <v>29</v>
       </c>
       <c r="D314">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E314" t="s">
         <v>30</v>
@@ -9435,7 +9435,7 @@
         <v>29</v>
       </c>
       <c r="D315">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E315" t="s">
         <v>30</v>
@@ -9452,7 +9452,7 @@
         <v>29</v>
       </c>
       <c r="D316">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E316" t="s">
         <v>30</v>
@@ -9469,7 +9469,7 @@
         <v>29</v>
       </c>
       <c r="D317">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E317" t="s">
         <v>30</v>
@@ -9503,7 +9503,7 @@
         <v>29</v>
       </c>
       <c r="D319">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E319" t="s">
         <v>30</v>
@@ -9520,7 +9520,7 @@
         <v>29</v>
       </c>
       <c r="D320">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E320" t="s">
         <v>30</v>
@@ -9537,7 +9537,7 @@
         <v>29</v>
       </c>
       <c r="D321">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E321" t="s">
         <v>30</v>
@@ -9554,7 +9554,7 @@
         <v>29</v>
       </c>
       <c r="D322">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E322" t="s">
         <v>30</v>
@@ -9571,7 +9571,7 @@
         <v>29</v>
       </c>
       <c r="D323">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E323" t="s">
         <v>30</v>
@@ -9588,7 +9588,7 @@
         <v>29</v>
       </c>
       <c r="D324">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E324" t="s">
         <v>30</v>
@@ -9605,7 +9605,7 @@
         <v>29</v>
       </c>
       <c r="D325">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E325" t="s">
         <v>30</v>
@@ -9622,7 +9622,7 @@
         <v>29</v>
       </c>
       <c r="D326">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E326" t="s">
         <v>30</v>
@@ -9639,7 +9639,7 @@
         <v>29</v>
       </c>
       <c r="D327">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E327" t="s">
         <v>30</v>
@@ -9656,7 +9656,7 @@
         <v>29</v>
       </c>
       <c r="D328">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E328" t="s">
         <v>30</v>
@@ -9673,7 +9673,7 @@
         <v>29</v>
       </c>
       <c r="D329">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E329" t="s">
         <v>30</v>
@@ -9690,7 +9690,7 @@
         <v>29</v>
       </c>
       <c r="D330">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E330" t="s">
         <v>30</v>
@@ -9707,7 +9707,7 @@
         <v>29</v>
       </c>
       <c r="D331">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E331" t="s">
         <v>30</v>
@@ -9724,7 +9724,7 @@
         <v>29</v>
       </c>
       <c r="D332">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E332" t="s">
         <v>30</v>
@@ -9741,7 +9741,7 @@
         <v>29</v>
       </c>
       <c r="D333">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E333" t="s">
         <v>30</v>
@@ -9758,7 +9758,7 @@
         <v>29</v>
       </c>
       <c r="D334">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E334" t="s">
         <v>30</v>
@@ -9775,7 +9775,7 @@
         <v>29</v>
       </c>
       <c r="D335">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E335" t="s">
         <v>30</v>
@@ -9792,7 +9792,7 @@
         <v>29</v>
       </c>
       <c r="D336">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E336" t="s">
         <v>30</v>
@@ -9809,7 +9809,7 @@
         <v>29</v>
       </c>
       <c r="D337">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E337" t="s">
         <v>30</v>
@@ -9826,7 +9826,7 @@
         <v>29</v>
       </c>
       <c r="D338">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E338" t="s">
         <v>30</v>
@@ -9843,7 +9843,7 @@
         <v>29</v>
       </c>
       <c r="D339">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E339" t="s">
         <v>30</v>
@@ -9877,7 +9877,7 @@
         <v>29</v>
       </c>
       <c r="D341">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E341" t="s">
         <v>30</v>
@@ -9894,7 +9894,7 @@
         <v>29</v>
       </c>
       <c r="D342">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E342" t="s">
         <v>30</v>
@@ -9911,7 +9911,7 @@
         <v>29</v>
       </c>
       <c r="D343">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E343" t="s">
         <v>30</v>
@@ -9928,7 +9928,7 @@
         <v>29</v>
       </c>
       <c r="D344">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E344" t="s">
         <v>30</v>
@@ -9945,7 +9945,7 @@
         <v>29</v>
       </c>
       <c r="D345">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E345" t="s">
         <v>30</v>
@@ -9962,7 +9962,7 @@
         <v>29</v>
       </c>
       <c r="D346">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E346" t="s">
         <v>30</v>
@@ -9979,7 +9979,7 @@
         <v>29</v>
       </c>
       <c r="D347">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E347" t="s">
         <v>30</v>
@@ -9996,7 +9996,7 @@
         <v>29</v>
       </c>
       <c r="D348">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E348" t="s">
         <v>30</v>
@@ -10013,7 +10013,7 @@
         <v>29</v>
       </c>
       <c r="D349">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E349" t="s">
         <v>30</v>
@@ -10030,7 +10030,7 @@
         <v>29</v>
       </c>
       <c r="D350">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E350" t="s">
         <v>30</v>
@@ -10047,7 +10047,7 @@
         <v>29</v>
       </c>
       <c r="D351">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E351" t="s">
         <v>30</v>
@@ -10064,7 +10064,7 @@
         <v>29</v>
       </c>
       <c r="D352">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E352" t="s">
         <v>30</v>
@@ -10081,7 +10081,7 @@
         <v>29</v>
       </c>
       <c r="D353">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E353" t="s">
         <v>30</v>
@@ -10098,7 +10098,7 @@
         <v>29</v>
       </c>
       <c r="D354">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E354" t="s">
         <v>30</v>
@@ -10115,7 +10115,7 @@
         <v>29</v>
       </c>
       <c r="D355">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E355" t="s">
         <v>30</v>
@@ -10132,7 +10132,7 @@
         <v>29</v>
       </c>
       <c r="D356">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E356" t="s">
         <v>30</v>
@@ -10149,7 +10149,7 @@
         <v>29</v>
       </c>
       <c r="D357">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E357" t="s">
         <v>30</v>
@@ -10166,7 +10166,7 @@
         <v>29</v>
       </c>
       <c r="D358">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E358" t="s">
         <v>30</v>
@@ -10200,7 +10200,7 @@
         <v>29</v>
       </c>
       <c r="D360">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E360" t="s">
         <v>30</v>
@@ -10217,7 +10217,7 @@
         <v>29</v>
       </c>
       <c r="D361">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E361" t="s">
         <v>30</v>
@@ -10251,7 +10251,7 @@
         <v>29</v>
       </c>
       <c r="D363">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E363" t="s">
         <v>30</v>
@@ -10268,7 +10268,7 @@
         <v>29</v>
       </c>
       <c r="D364">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E364" t="s">
         <v>30</v>
@@ -10285,7 +10285,7 @@
         <v>29</v>
       </c>
       <c r="D365">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E365" t="s">
         <v>30</v>
@@ -10302,7 +10302,7 @@
         <v>29</v>
       </c>
       <c r="D366">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E366" t="s">
         <v>30</v>
@@ -10319,7 +10319,7 @@
         <v>29</v>
       </c>
       <c r="D367">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E367" t="s">
         <v>30</v>
@@ -10336,7 +10336,7 @@
         <v>29</v>
       </c>
       <c r="D368">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E368" t="s">
         <v>30</v>
@@ -10353,7 +10353,7 @@
         <v>29</v>
       </c>
       <c r="D369">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E369" t="s">
         <v>30</v>
@@ -10370,7 +10370,7 @@
         <v>29</v>
       </c>
       <c r="D370">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E370" t="s">
         <v>30</v>
@@ -10387,7 +10387,7 @@
         <v>29</v>
       </c>
       <c r="D371">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E371" t="s">
         <v>30</v>
@@ -10404,7 +10404,7 @@
         <v>29</v>
       </c>
       <c r="D372">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E372" t="s">
         <v>30</v>
@@ -10421,7 +10421,7 @@
         <v>29</v>
       </c>
       <c r="D373">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E373" t="s">
         <v>30</v>
@@ -10438,7 +10438,7 @@
         <v>29</v>
       </c>
       <c r="D374">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E374" t="s">
         <v>30</v>
@@ -10455,7 +10455,7 @@
         <v>29</v>
       </c>
       <c r="D375">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E375" t="s">
         <v>30</v>
@@ -10472,7 +10472,7 @@
         <v>29</v>
       </c>
       <c r="D376">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E376" t="s">
         <v>30</v>
@@ -10489,7 +10489,7 @@
         <v>29</v>
       </c>
       <c r="D377">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E377" t="s">
         <v>30</v>
@@ -10506,7 +10506,7 @@
         <v>29</v>
       </c>
       <c r="D378">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E378" t="s">
         <v>30</v>
@@ -10540,7 +10540,7 @@
         <v>29</v>
       </c>
       <c r="D380">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E380" t="s">
         <v>30</v>
@@ -10557,7 +10557,7 @@
         <v>29</v>
       </c>
       <c r="D381">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E381" t="s">
         <v>30</v>
@@ -10574,7 +10574,7 @@
         <v>29</v>
       </c>
       <c r="D382">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E382" t="s">
         <v>30</v>
@@ -10591,7 +10591,7 @@
         <v>29</v>
       </c>
       <c r="D383">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E383" t="s">
         <v>30</v>
@@ -10608,7 +10608,7 @@
         <v>29</v>
       </c>
       <c r="D384">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E384" t="s">
         <v>30</v>
@@ -10625,7 +10625,7 @@
         <v>29</v>
       </c>
       <c r="D385">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E385" t="s">
         <v>30</v>
@@ -10642,7 +10642,7 @@
         <v>29</v>
       </c>
       <c r="D386">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E386" t="s">
         <v>30</v>
@@ -10659,7 +10659,7 @@
         <v>29</v>
       </c>
       <c r="D387">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E387" t="s">
         <v>30</v>
@@ -10676,7 +10676,7 @@
         <v>29</v>
       </c>
       <c r="D388">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E388" t="s">
         <v>30</v>
@@ -10693,7 +10693,7 @@
         <v>29</v>
       </c>
       <c r="D389">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E389" t="s">
         <v>30</v>
@@ -10710,7 +10710,7 @@
         <v>29</v>
       </c>
       <c r="D390">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E390" t="s">
         <v>30</v>
@@ -10727,7 +10727,7 @@
         <v>29</v>
       </c>
       <c r="D391">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E391" t="s">
         <v>30</v>
@@ -10744,7 +10744,7 @@
         <v>29</v>
       </c>
       <c r="D392">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E392" t="s">
         <v>30</v>
@@ -10761,7 +10761,7 @@
         <v>29</v>
       </c>
       <c r="D393">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E393" t="s">
         <v>30</v>
@@ -10778,7 +10778,7 @@
         <v>29</v>
       </c>
       <c r="D394">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E394" t="s">
         <v>30</v>
@@ -10795,7 +10795,7 @@
         <v>29</v>
       </c>
       <c r="D395">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E395" t="s">
         <v>30</v>
@@ -10812,7 +10812,7 @@
         <v>29</v>
       </c>
       <c r="D396">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E396" t="s">
         <v>30</v>
@@ -10829,7 +10829,7 @@
         <v>29</v>
       </c>
       <c r="D397">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E397" t="s">
         <v>30</v>
@@ -10846,7 +10846,7 @@
         <v>29</v>
       </c>
       <c r="D398">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E398" t="s">
         <v>30</v>
@@ -10863,7 +10863,7 @@
         <v>29</v>
       </c>
       <c r="D399">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E399" t="s">
         <v>30</v>
@@ -10880,7 +10880,7 @@
         <v>29</v>
       </c>
       <c r="D400">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E400" t="s">
         <v>30</v>
@@ -10897,7 +10897,7 @@
         <v>29</v>
       </c>
       <c r="D401">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E401" t="s">
         <v>30</v>
@@ -10914,7 +10914,7 @@
         <v>29</v>
       </c>
       <c r="D402">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E402" t="s">
         <v>30</v>
@@ -10931,7 +10931,7 @@
         <v>29</v>
       </c>
       <c r="D403">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E403" t="s">
         <v>30</v>
@@ -10948,7 +10948,7 @@
         <v>29</v>
       </c>
       <c r="D404">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E404" t="s">
         <v>30</v>
@@ -10965,7 +10965,7 @@
         <v>29</v>
       </c>
       <c r="D405">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E405" t="s">
         <v>30</v>
@@ -10982,7 +10982,7 @@
         <v>29</v>
       </c>
       <c r="D406">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E406" t="s">
         <v>30</v>
@@ -10999,7 +10999,7 @@
         <v>29</v>
       </c>
       <c r="D407">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E407" t="s">
         <v>30</v>
@@ -11016,7 +11016,7 @@
         <v>29</v>
       </c>
       <c r="D408">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E408" t="s">
         <v>30</v>
@@ -11033,7 +11033,7 @@
         <v>29</v>
       </c>
       <c r="D409">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E409" t="s">
         <v>30</v>
@@ -11050,7 +11050,7 @@
         <v>29</v>
       </c>
       <c r="D410">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E410" t="s">
         <v>30</v>
@@ -11067,7 +11067,7 @@
         <v>29</v>
       </c>
       <c r="D411">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E411" t="s">
         <v>30</v>
@@ -11084,7 +11084,7 @@
         <v>29</v>
       </c>
       <c r="D412">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E412" t="s">
         <v>30</v>
@@ -11101,7 +11101,7 @@
         <v>29</v>
       </c>
       <c r="D413">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E413" t="s">
         <v>30</v>
@@ -11118,7 +11118,7 @@
         <v>29</v>
       </c>
       <c r="D414">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E414" t="s">
         <v>30</v>
@@ -11135,7 +11135,7 @@
         <v>29</v>
       </c>
       <c r="D415">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E415" t="s">
         <v>30</v>
@@ -11152,7 +11152,7 @@
         <v>29</v>
       </c>
       <c r="D416">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E416" t="s">
         <v>30</v>
@@ -11169,7 +11169,7 @@
         <v>29</v>
       </c>
       <c r="D417">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E417" t="s">
         <v>30</v>
@@ -11186,7 +11186,7 @@
         <v>29</v>
       </c>
       <c r="D418">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E418" t="s">
         <v>30</v>
@@ -11203,7 +11203,7 @@
         <v>29</v>
       </c>
       <c r="D419">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E419" t="s">
         <v>30</v>
@@ -11220,7 +11220,7 @@
         <v>29</v>
       </c>
       <c r="D420">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E420" t="s">
         <v>30</v>
@@ -11237,7 +11237,7 @@
         <v>29</v>
       </c>
       <c r="D421">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E421" t="s">
         <v>30</v>
@@ -11254,7 +11254,7 @@
         <v>29</v>
       </c>
       <c r="D422">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E422" t="s">
         <v>30</v>
@@ -11271,7 +11271,7 @@
         <v>29</v>
       </c>
       <c r="D423">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E423" t="s">
         <v>30</v>
@@ -11288,7 +11288,7 @@
         <v>29</v>
       </c>
       <c r="D424">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E424" t="s">
         <v>30</v>
@@ -11305,7 +11305,7 @@
         <v>29</v>
       </c>
       <c r="D425">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E425" t="s">
         <v>30</v>
@@ -11322,7 +11322,7 @@
         <v>29</v>
       </c>
       <c r="D426">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E426" t="s">
         <v>30</v>
@@ -11339,7 +11339,7 @@
         <v>29</v>
       </c>
       <c r="D427">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E427" t="s">
         <v>30</v>
@@ -11356,7 +11356,7 @@
         <v>29</v>
       </c>
       <c r="D428">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E428" t="s">
         <v>30</v>
@@ -11373,7 +11373,7 @@
         <v>29</v>
       </c>
       <c r="D429">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E429" t="s">
         <v>30</v>
@@ -11390,7 +11390,7 @@
         <v>29</v>
       </c>
       <c r="D430">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E430" t="s">
         <v>30</v>
@@ -11407,7 +11407,7 @@
         <v>29</v>
       </c>
       <c r="D431">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E431" t="s">
         <v>30</v>
@@ -11424,7 +11424,7 @@
         <v>29</v>
       </c>
       <c r="D432">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E432" t="s">
         <v>30</v>
@@ -11441,7 +11441,7 @@
         <v>29</v>
       </c>
       <c r="D433">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E433" t="s">
         <v>30</v>
@@ -11458,7 +11458,7 @@
         <v>29</v>
       </c>
       <c r="D434">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E434" t="s">
         <v>30</v>
@@ -11475,7 +11475,7 @@
         <v>29</v>
       </c>
       <c r="D435">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E435" t="s">
         <v>30</v>
@@ -11492,7 +11492,7 @@
         <v>29</v>
       </c>
       <c r="D436">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E436" t="s">
         <v>30</v>
@@ -11526,7 +11526,7 @@
         <v>29</v>
       </c>
       <c r="D438">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E438" t="s">
         <v>30</v>
@@ -11543,7 +11543,7 @@
         <v>29</v>
       </c>
       <c r="D439">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E439" t="s">
         <v>30</v>
@@ -11577,7 +11577,7 @@
         <v>29</v>
       </c>
       <c r="D441">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E441" t="s">
         <v>30</v>
@@ -11594,7 +11594,7 @@
         <v>29</v>
       </c>
       <c r="D442">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E442" t="s">
         <v>30</v>
@@ -11611,7 +11611,7 @@
         <v>29</v>
       </c>
       <c r="D443">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E443" t="s">
         <v>30</v>
@@ -11628,7 +11628,7 @@
         <v>29</v>
       </c>
       <c r="D444">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E444" t="s">
         <v>30</v>
@@ -11645,7 +11645,7 @@
         <v>29</v>
       </c>
       <c r="D445">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E445" t="s">
         <v>30</v>
@@ -11662,7 +11662,7 @@
         <v>29</v>
       </c>
       <c r="D446">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E446" t="s">
         <v>30</v>
@@ -11679,7 +11679,7 @@
         <v>29</v>
       </c>
       <c r="D447">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E447" t="s">
         <v>30</v>
@@ -11713,7 +11713,7 @@
         <v>29</v>
       </c>
       <c r="D449">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E449" t="s">
         <v>30</v>
@@ -11730,7 +11730,7 @@
         <v>29</v>
       </c>
       <c r="D450">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E450" t="s">
         <v>30</v>
@@ -11747,7 +11747,7 @@
         <v>29</v>
       </c>
       <c r="D451">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E451" t="s">
         <v>30</v>
@@ -11764,7 +11764,7 @@
         <v>29</v>
       </c>
       <c r="D452">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E452" t="s">
         <v>30</v>
@@ -11781,7 +11781,7 @@
         <v>29</v>
       </c>
       <c r="D453">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E453" t="s">
         <v>30</v>
@@ -11798,7 +11798,7 @@
         <v>29</v>
       </c>
       <c r="D454">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E454" t="s">
         <v>30</v>
@@ -11815,7 +11815,7 @@
         <v>29</v>
       </c>
       <c r="D455">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E455" t="s">
         <v>30</v>
@@ -11832,7 +11832,7 @@
         <v>29</v>
       </c>
       <c r="D456">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E456" t="s">
         <v>30</v>
@@ -11849,7 +11849,7 @@
         <v>29</v>
       </c>
       <c r="D457">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E457" t="s">
         <v>30</v>
@@ -11866,7 +11866,7 @@
         <v>29</v>
       </c>
       <c r="D458">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E458" t="s">
         <v>30</v>
@@ -11883,7 +11883,7 @@
         <v>29</v>
       </c>
       <c r="D459">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E459" t="s">
         <v>30</v>
@@ -11917,7 +11917,7 @@
         <v>29</v>
       </c>
       <c r="D461">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E461" t="s">
         <v>30</v>
@@ -11934,7 +11934,7 @@
         <v>29</v>
       </c>
       <c r="D462">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E462" t="s">
         <v>30</v>
@@ -11951,7 +11951,7 @@
         <v>29</v>
       </c>
       <c r="D463">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E463" t="s">
         <v>30</v>
@@ -11968,7 +11968,7 @@
         <v>29</v>
       </c>
       <c r="D464">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E464" t="s">
         <v>30</v>
@@ -11985,7 +11985,7 @@
         <v>29</v>
       </c>
       <c r="D465">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E465" t="s">
         <v>30</v>
@@ -12002,7 +12002,7 @@
         <v>29</v>
       </c>
       <c r="D466">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E466" t="s">
         <v>30</v>
@@ -12019,7 +12019,7 @@
         <v>29</v>
       </c>
       <c r="D467">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E467" t="s">
         <v>30</v>
@@ -12036,7 +12036,7 @@
         <v>29</v>
       </c>
       <c r="D468">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E468" t="s">
         <v>30</v>
@@ -12053,7 +12053,7 @@
         <v>29</v>
       </c>
       <c r="D469">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E469" t="s">
         <v>30</v>
@@ -12070,7 +12070,7 @@
         <v>29</v>
       </c>
       <c r="D470">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E470" t="s">
         <v>30</v>
@@ -12104,7 +12104,7 @@
         <v>29</v>
       </c>
       <c r="D472">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E472" t="s">
         <v>30</v>
@@ -12121,7 +12121,7 @@
         <v>29</v>
       </c>
       <c r="D473">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E473" t="s">
         <v>30</v>
@@ -12138,7 +12138,7 @@
         <v>29</v>
       </c>
       <c r="D474">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E474" t="s">
         <v>30</v>
@@ -12155,7 +12155,7 @@
         <v>29</v>
       </c>
       <c r="D475">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E475" t="s">
         <v>30</v>
@@ -12172,7 +12172,7 @@
         <v>29</v>
       </c>
       <c r="D476">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E476" t="s">
         <v>30</v>
@@ -12189,7 +12189,7 @@
         <v>29</v>
       </c>
       <c r="D477">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E477" t="s">
         <v>30</v>
@@ -12206,7 +12206,7 @@
         <v>29</v>
       </c>
       <c r="D478">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E478" t="s">
         <v>30</v>
@@ -12223,7 +12223,7 @@
         <v>29</v>
       </c>
       <c r="D479">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E479" t="s">
         <v>30</v>
@@ -12240,7 +12240,7 @@
         <v>29</v>
       </c>
       <c r="D480">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E480" t="s">
         <v>30</v>
@@ -12257,7 +12257,7 @@
         <v>29</v>
       </c>
       <c r="D481">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E481" t="s">
         <v>30</v>
@@ -12274,7 +12274,7 @@
         <v>29</v>
       </c>
       <c r="D482">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E482" t="s">
         <v>30</v>
@@ -12291,7 +12291,7 @@
         <v>29</v>
       </c>
       <c r="D483">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E483" t="s">
         <v>30</v>
@@ -12308,7 +12308,7 @@
         <v>29</v>
       </c>
       <c r="D484">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E484" t="s">
         <v>30</v>
@@ -12325,7 +12325,7 @@
         <v>29</v>
       </c>
       <c r="D485">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E485" t="s">
         <v>30</v>
@@ -12342,7 +12342,7 @@
         <v>29</v>
       </c>
       <c r="D486">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E486" t="s">
         <v>30</v>
@@ -12359,7 +12359,7 @@
         <v>29</v>
       </c>
       <c r="D487">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E487" t="s">
         <v>30</v>
@@ -12376,7 +12376,7 @@
         <v>29</v>
       </c>
       <c r="D488">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E488" t="s">
         <v>30</v>
@@ -12393,7 +12393,7 @@
         <v>29</v>
       </c>
       <c r="D489">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E489" t="s">
         <v>30</v>
@@ -12410,7 +12410,7 @@
         <v>29</v>
       </c>
       <c r="D490">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E490" t="s">
         <v>30</v>
@@ -12427,7 +12427,7 @@
         <v>29</v>
       </c>
       <c r="D491">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E491" t="s">
         <v>30</v>
@@ -12444,7 +12444,7 @@
         <v>29</v>
       </c>
       <c r="D492">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E492" t="s">
         <v>30</v>
@@ -12461,7 +12461,7 @@
         <v>29</v>
       </c>
       <c r="D493">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E493" t="s">
         <v>30</v>
@@ -12478,7 +12478,7 @@
         <v>29</v>
       </c>
       <c r="D494">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E494" t="s">
         <v>30</v>
@@ -12512,7 +12512,7 @@
         <v>29</v>
       </c>
       <c r="D496">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E496" t="s">
         <v>30</v>
@@ -12546,7 +12546,7 @@
         <v>29</v>
       </c>
       <c r="D498">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E498" t="s">
         <v>30</v>
@@ -12563,7 +12563,7 @@
         <v>29</v>
       </c>
       <c r="D499">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E499" t="s">
         <v>30</v>
@@ -12597,7 +12597,7 @@
         <v>29</v>
       </c>
       <c r="D501">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E501" t="s">
         <v>30</v>
@@ -12614,7 +12614,7 @@
         <v>29</v>
       </c>
       <c r="D502">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E502" t="s">
         <v>30</v>
@@ -12631,7 +12631,7 @@
         <v>29</v>
       </c>
       <c r="D503">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E503" t="s">
         <v>30</v>
@@ -12648,7 +12648,7 @@
         <v>29</v>
       </c>
       <c r="D504">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E504" t="s">
         <v>30</v>
@@ -12665,7 +12665,7 @@
         <v>29</v>
       </c>
       <c r="D505">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E505" t="s">
         <v>30</v>
@@ -12682,7 +12682,7 @@
         <v>29</v>
       </c>
       <c r="D506">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E506" t="s">
         <v>30</v>
@@ -12699,7 +12699,7 @@
         <v>29</v>
       </c>
       <c r="D507">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E507" t="s">
         <v>30</v>
@@ -12716,7 +12716,7 @@
         <v>29</v>
       </c>
       <c r="D508">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E508" t="s">
         <v>30</v>
@@ -12733,7 +12733,7 @@
         <v>29</v>
       </c>
       <c r="D509">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E509" t="s">
         <v>30</v>
@@ -12750,7 +12750,7 @@
         <v>29</v>
       </c>
       <c r="D510">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E510" t="s">
         <v>30</v>
@@ -12767,7 +12767,7 @@
         <v>29</v>
       </c>
       <c r="D511">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E511" t="s">
         <v>30</v>
@@ -12784,7 +12784,7 @@
         <v>29</v>
       </c>
       <c r="D512">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E512" t="s">
         <v>30</v>
@@ -12801,7 +12801,7 @@
         <v>29</v>
       </c>
       <c r="D513">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E513" t="s">
         <v>30</v>
@@ -12818,7 +12818,7 @@
         <v>29</v>
       </c>
       <c r="D514">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E514" t="s">
         <v>30</v>
@@ -12835,7 +12835,7 @@
         <v>29</v>
       </c>
       <c r="D515">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E515" t="s">
         <v>30</v>
@@ -12852,7 +12852,7 @@
         <v>29</v>
       </c>
       <c r="D516">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E516" t="s">
         <v>30</v>
@@ -12869,7 +12869,7 @@
         <v>29</v>
       </c>
       <c r="D517">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E517" t="s">
         <v>30</v>
@@ -12886,7 +12886,7 @@
         <v>29</v>
       </c>
       <c r="D518">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E518" t="s">
         <v>30</v>
@@ -12903,7 +12903,7 @@
         <v>29</v>
       </c>
       <c r="D519">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E519" t="s">
         <v>30</v>
@@ -12920,7 +12920,7 @@
         <v>29</v>
       </c>
       <c r="D520">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E520" t="s">
         <v>30</v>
@@ -12937,7 +12937,7 @@
         <v>29</v>
       </c>
       <c r="D521">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E521" t="s">
         <v>30</v>
@@ -12954,7 +12954,7 @@
         <v>29</v>
       </c>
       <c r="D522">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E522" t="s">
         <v>30</v>
@@ -12971,7 +12971,7 @@
         <v>29</v>
       </c>
       <c r="D523">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E523" t="s">
         <v>30</v>
@@ -12988,7 +12988,7 @@
         <v>29</v>
       </c>
       <c r="D524">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E524" t="s">
         <v>30</v>
@@ -13005,7 +13005,7 @@
         <v>29</v>
       </c>
       <c r="D525">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E525" t="s">
         <v>30</v>
@@ -13039,7 +13039,7 @@
         <v>29</v>
       </c>
       <c r="D527">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E527" t="s">
         <v>30</v>
@@ -13073,7 +13073,7 @@
         <v>29</v>
       </c>
       <c r="D529">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E529" t="s">
         <v>30</v>
@@ -13107,7 +13107,7 @@
         <v>29</v>
       </c>
       <c r="D531">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E531" t="s">
         <v>30</v>
@@ -13124,7 +13124,7 @@
         <v>29</v>
       </c>
       <c r="D532">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E532" t="s">
         <v>30</v>
@@ -13141,7 +13141,7 @@
         <v>29</v>
       </c>
       <c r="D533">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E533" t="s">
         <v>30</v>
@@ -13158,7 +13158,7 @@
         <v>29</v>
       </c>
       <c r="D534">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E534" t="s">
         <v>30</v>
@@ -13175,7 +13175,7 @@
         <v>29</v>
       </c>
       <c r="D535">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E535" t="s">
         <v>30</v>
@@ -13192,7 +13192,7 @@
         <v>29</v>
       </c>
       <c r="D536">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E536" t="s">
         <v>30</v>
@@ -13209,7 +13209,7 @@
         <v>29</v>
       </c>
       <c r="D537">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E537" t="s">
         <v>30</v>
@@ -13226,7 +13226,7 @@
         <v>29</v>
       </c>
       <c r="D538">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E538" t="s">
         <v>30</v>
@@ -13243,7 +13243,7 @@
         <v>29</v>
       </c>
       <c r="D539">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E539" t="s">
         <v>30</v>
@@ -13260,7 +13260,7 @@
         <v>29</v>
       </c>
       <c r="D540">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E540" t="s">
         <v>30</v>
@@ -13277,7 +13277,7 @@
         <v>29</v>
       </c>
       <c r="D541">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E541" t="s">
         <v>30</v>
@@ -13294,7 +13294,7 @@
         <v>29</v>
       </c>
       <c r="D542">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E542" t="s">
         <v>30</v>
@@ -13311,7 +13311,7 @@
         <v>29</v>
       </c>
       <c r="D543">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E543" t="s">
         <v>30</v>
@@ -13328,7 +13328,7 @@
         <v>29</v>
       </c>
       <c r="D544">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E544" t="s">
         <v>30</v>
@@ -13345,7 +13345,7 @@
         <v>29</v>
       </c>
       <c r="D545">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E545" t="s">
         <v>30</v>
@@ -13362,7 +13362,7 @@
         <v>29</v>
       </c>
       <c r="D546">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E546" t="s">
         <v>30</v>
@@ -13379,7 +13379,7 @@
         <v>29</v>
       </c>
       <c r="D547">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E547" t="s">
         <v>30</v>
@@ -13396,7 +13396,7 @@
         <v>29</v>
       </c>
       <c r="D548">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E548" t="s">
         <v>30</v>
@@ -13413,7 +13413,7 @@
         <v>29</v>
       </c>
       <c r="D549">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E549" t="s">
         <v>30</v>
@@ -13430,7 +13430,7 @@
         <v>29</v>
       </c>
       <c r="D550">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E550" t="s">
         <v>30</v>
@@ -13447,7 +13447,7 @@
         <v>29</v>
       </c>
       <c r="D551">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E551" t="s">
         <v>30</v>
@@ -13464,7 +13464,7 @@
         <v>29</v>
       </c>
       <c r="D552">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E552" t="s">
         <v>30</v>
@@ -13481,7 +13481,7 @@
         <v>29</v>
       </c>
       <c r="D553">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E553" t="s">
         <v>30</v>
@@ -13498,7 +13498,7 @@
         <v>29</v>
       </c>
       <c r="D554">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E554" t="s">
         <v>30</v>
@@ -13515,7 +13515,7 @@
         <v>29</v>
       </c>
       <c r="D555">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E555" t="s">
         <v>30</v>
@@ -13532,7 +13532,7 @@
         <v>29</v>
       </c>
       <c r="D556">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E556" t="s">
         <v>30</v>
@@ -13566,7 +13566,7 @@
         <v>29</v>
       </c>
       <c r="D558">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E558" t="s">
         <v>30</v>
@@ -13583,7 +13583,7 @@
         <v>29</v>
       </c>
       <c r="D559">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E559" t="s">
         <v>30</v>
@@ -13600,7 +13600,7 @@
         <v>29</v>
       </c>
       <c r="D560">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E560" t="s">
         <v>30</v>
@@ -13617,7 +13617,7 @@
         <v>29</v>
       </c>
       <c r="D561">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E561" t="s">
         <v>30</v>
@@ -13634,7 +13634,7 @@
         <v>29</v>
       </c>
       <c r="D562">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E562" t="s">
         <v>30</v>
@@ -13651,7 +13651,7 @@
         <v>29</v>
       </c>
       <c r="D563">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E563" t="s">
         <v>30</v>
@@ -13668,7 +13668,7 @@
         <v>29</v>
       </c>
       <c r="D564">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E564" t="s">
         <v>30</v>
@@ -13685,7 +13685,7 @@
         <v>29</v>
       </c>
       <c r="D565">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E565" t="s">
         <v>30</v>
@@ -13702,7 +13702,7 @@
         <v>29</v>
       </c>
       <c r="D566">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E566" t="s">
         <v>30</v>
@@ -13719,7 +13719,7 @@
         <v>29</v>
       </c>
       <c r="D567">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E567" t="s">
         <v>30</v>
@@ -13753,7 +13753,7 @@
         <v>29</v>
       </c>
       <c r="D569">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E569" t="s">
         <v>30</v>
@@ -13770,7 +13770,7 @@
         <v>29</v>
       </c>
       <c r="D570">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E570" t="s">
         <v>30</v>
@@ -13787,7 +13787,7 @@
         <v>29</v>
       </c>
       <c r="D571">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E571" t="s">
         <v>30</v>
@@ -13804,7 +13804,7 @@
         <v>29</v>
       </c>
       <c r="D572">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E572" t="s">
         <v>30</v>
@@ -13821,7 +13821,7 @@
         <v>29</v>
       </c>
       <c r="D573">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E573" t="s">
         <v>30</v>
@@ -13838,7 +13838,7 @@
         <v>29</v>
       </c>
       <c r="D574">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E574" t="s">
         <v>30</v>
@@ -13855,7 +13855,7 @@
         <v>29</v>
       </c>
       <c r="D575">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E575" t="s">
         <v>30</v>
@@ -13889,7 +13889,7 @@
         <v>29</v>
       </c>
       <c r="D577">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E577" t="s">
         <v>30</v>
@@ -13906,7 +13906,7 @@
         <v>29</v>
       </c>
       <c r="D578">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E578" t="s">
         <v>30</v>
@@ -13923,7 +13923,7 @@
         <v>29</v>
       </c>
       <c r="D579">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E579" t="s">
         <v>30</v>
@@ -13957,7 +13957,7 @@
         <v>29</v>
       </c>
       <c r="D581">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E581" t="s">
         <v>30</v>
@@ -13974,7 +13974,7 @@
         <v>29</v>
       </c>
       <c r="D582">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E582" t="s">
         <v>30</v>
@@ -13991,7 +13991,7 @@
         <v>29</v>
       </c>
       <c r="D583">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E583" t="s">
         <v>30</v>
@@ -14008,7 +14008,7 @@
         <v>29</v>
       </c>
       <c r="D584">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E584" t="s">
         <v>30</v>
@@ -14025,7 +14025,7 @@
         <v>29</v>
       </c>
       <c r="D585">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E585" t="s">
         <v>30</v>
@@ -14042,7 +14042,7 @@
         <v>29</v>
       </c>
       <c r="D586">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E586" t="s">
         <v>30</v>
@@ -14059,7 +14059,7 @@
         <v>29</v>
       </c>
       <c r="D587">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E587" t="s">
         <v>30</v>
@@ -14076,7 +14076,7 @@
         <v>29</v>
       </c>
       <c r="D588">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E588" t="s">
         <v>30</v>
@@ -14093,7 +14093,7 @@
         <v>29</v>
       </c>
       <c r="D589">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E589" t="s">
         <v>30</v>
@@ -14110,7 +14110,7 @@
         <v>29</v>
       </c>
       <c r="D590">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E590" t="s">
         <v>30</v>
@@ -14127,7 +14127,7 @@
         <v>29</v>
       </c>
       <c r="D591">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E591" t="s">
         <v>30</v>
@@ -14144,7 +14144,7 @@
         <v>29</v>
       </c>
       <c r="D592">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E592" t="s">
         <v>30</v>
@@ -14161,7 +14161,7 @@
         <v>29</v>
       </c>
       <c r="D593">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E593" t="s">
         <v>30</v>
@@ -14178,7 +14178,7 @@
         <v>29</v>
       </c>
       <c r="D594">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E594" t="s">
         <v>30</v>
@@ -14195,7 +14195,7 @@
         <v>29</v>
       </c>
       <c r="D595">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E595" t="s">
         <v>30</v>
@@ -14212,7 +14212,7 @@
         <v>29</v>
       </c>
       <c r="D596">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E596" t="s">
         <v>30</v>
@@ -14229,7 +14229,7 @@
         <v>29</v>
       </c>
       <c r="D597">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E597" t="s">
         <v>30</v>
@@ -14246,7 +14246,7 @@
         <v>29</v>
       </c>
       <c r="D598">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E598" t="s">
         <v>30</v>
@@ -14263,7 +14263,7 @@
         <v>29</v>
       </c>
       <c r="D599">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E599" t="s">
         <v>30</v>
@@ -14280,7 +14280,7 @@
         <v>29</v>
       </c>
       <c r="D600">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E600" t="s">
         <v>30</v>
@@ -14297,7 +14297,7 @@
         <v>29</v>
       </c>
       <c r="D601">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E601" t="s">
         <v>30</v>
@@ -14314,7 +14314,7 @@
         <v>29</v>
       </c>
       <c r="D602">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E602" t="s">
         <v>30</v>
@@ -14331,7 +14331,7 @@
         <v>29</v>
       </c>
       <c r="D603">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E603" t="s">
         <v>30</v>
@@ -14348,7 +14348,7 @@
         <v>29</v>
       </c>
       <c r="D604">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E604" t="s">
         <v>30</v>
@@ -14365,7 +14365,7 @@
         <v>29</v>
       </c>
       <c r="D605">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E605" t="s">
         <v>30</v>
@@ -14382,7 +14382,7 @@
         <v>29</v>
       </c>
       <c r="D606">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E606" t="s">
         <v>30</v>
@@ -14399,7 +14399,7 @@
         <v>29</v>
       </c>
       <c r="D607">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E607" t="s">
         <v>30</v>
@@ -14416,7 +14416,7 @@
         <v>29</v>
       </c>
       <c r="D608">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E608" t="s">
         <v>30</v>
@@ -14450,7 +14450,7 @@
         <v>29</v>
       </c>
       <c r="D610">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E610" t="s">
         <v>30</v>
@@ -14467,7 +14467,7 @@
         <v>29</v>
       </c>
       <c r="D611">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E611" t="s">
         <v>30</v>
@@ -14484,7 +14484,7 @@
         <v>29</v>
       </c>
       <c r="D612">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E612" t="s">
         <v>30</v>
@@ -14501,7 +14501,7 @@
         <v>29</v>
       </c>
       <c r="D613">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E613" t="s">
         <v>30</v>
@@ -14518,7 +14518,7 @@
         <v>29</v>
       </c>
       <c r="D614">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E614" t="s">
         <v>30</v>
@@ -14552,7 +14552,7 @@
         <v>29</v>
       </c>
       <c r="D616">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E616" t="s">
         <v>30</v>
@@ -14569,7 +14569,7 @@
         <v>29</v>
       </c>
       <c r="D617">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E617" t="s">
         <v>30</v>
@@ -14586,7 +14586,7 @@
         <v>29</v>
       </c>
       <c r="D618">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E618" t="s">
         <v>30</v>
@@ -14603,7 +14603,7 @@
         <v>29</v>
       </c>
       <c r="D619">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E619" t="s">
         <v>30</v>
@@ -14620,7 +14620,7 @@
         <v>29</v>
       </c>
       <c r="D620">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E620" t="s">
         <v>30</v>
@@ -14654,7 +14654,7 @@
         <v>29</v>
       </c>
       <c r="D622">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E622" t="s">
         <v>30</v>
@@ -14671,7 +14671,7 @@
         <v>29</v>
       </c>
       <c r="D623">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E623" t="s">
         <v>30</v>
@@ -14688,7 +14688,7 @@
         <v>29</v>
       </c>
       <c r="D624">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E624" t="s">
         <v>30</v>
@@ -14705,7 +14705,7 @@
         <v>29</v>
       </c>
       <c r="D625">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E625" t="s">
         <v>30</v>
@@ -14739,7 +14739,7 @@
         <v>29</v>
       </c>
       <c r="D627">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E627" t="s">
         <v>30</v>
@@ -14756,7 +14756,7 @@
         <v>29</v>
       </c>
       <c r="D628">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E628" t="s">
         <v>30</v>
@@ -14773,7 +14773,7 @@
         <v>29</v>
       </c>
       <c r="D629">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E629" t="s">
         <v>30</v>
@@ -14807,7 +14807,7 @@
         <v>29</v>
       </c>
       <c r="D631">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E631" t="s">
         <v>30</v>
@@ -14824,7 +14824,7 @@
         <v>29</v>
       </c>
       <c r="D632">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E632" t="s">
         <v>30</v>
@@ -14858,7 +14858,7 @@
         <v>29</v>
       </c>
       <c r="D634">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E634" t="s">
         <v>30</v>
@@ -14875,7 +14875,7 @@
         <v>29</v>
       </c>
       <c r="D635">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E635" t="s">
         <v>30</v>
@@ -14892,7 +14892,7 @@
         <v>29</v>
       </c>
       <c r="D636">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E636" t="s">
         <v>30</v>
@@ -14909,7 +14909,7 @@
         <v>29</v>
       </c>
       <c r="D637">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E637" t="s">
         <v>30</v>
@@ -14926,7 +14926,7 @@
         <v>29</v>
       </c>
       <c r="D638">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E638" t="s">
         <v>30</v>
@@ -14943,7 +14943,7 @@
         <v>29</v>
       </c>
       <c r="D639">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E639" t="s">
         <v>30</v>
@@ -14960,7 +14960,7 @@
         <v>29</v>
       </c>
       <c r="D640">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E640" t="s">
         <v>30</v>
@@ -14977,7 +14977,7 @@
         <v>29</v>
       </c>
       <c r="D641">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E641" t="s">
         <v>30</v>
@@ -14994,7 +14994,7 @@
         <v>29</v>
       </c>
       <c r="D642">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E642" t="s">
         <v>30</v>
@@ -15011,7 +15011,7 @@
         <v>29</v>
       </c>
       <c r="D643">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E643" t="s">
         <v>30</v>
@@ -15028,7 +15028,7 @@
         <v>29</v>
       </c>
       <c r="D644">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E644" t="s">
         <v>30</v>
@@ -15062,7 +15062,7 @@
         <v>29</v>
       </c>
       <c r="D646">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E646" t="s">
         <v>30</v>
@@ -15096,7 +15096,7 @@
         <v>29</v>
       </c>
       <c r="D648">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E648" t="s">
         <v>30</v>
@@ -15113,7 +15113,7 @@
         <v>29</v>
       </c>
       <c r="D649">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E649" t="s">
         <v>30</v>
@@ -15130,7 +15130,7 @@
         <v>29</v>
       </c>
       <c r="D650">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E650" t="s">
         <v>30</v>
@@ -15147,7 +15147,7 @@
         <v>29</v>
       </c>
       <c r="D651">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E651" t="s">
         <v>30</v>
@@ -15164,7 +15164,7 @@
         <v>29</v>
       </c>
       <c r="D652">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E652" t="s">
         <v>30</v>
@@ -15198,7 +15198,7 @@
         <v>29</v>
       </c>
       <c r="D654">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E654" t="s">
         <v>30</v>
@@ -15215,7 +15215,7 @@
         <v>29</v>
       </c>
       <c r="D655">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E655" t="s">
         <v>30</v>
@@ -15249,7 +15249,7 @@
         <v>29</v>
       </c>
       <c r="D657">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E657" t="s">
         <v>30</v>
@@ -15266,7 +15266,7 @@
         <v>29</v>
       </c>
       <c r="D658">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E658" t="s">
         <v>30</v>
@@ -15283,7 +15283,7 @@
         <v>29</v>
       </c>
       <c r="D659">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E659" t="s">
         <v>30</v>
@@ -15300,7 +15300,7 @@
         <v>29</v>
       </c>
       <c r="D660">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E660" t="s">
         <v>30</v>
@@ -15334,7 +15334,7 @@
         <v>29</v>
       </c>
       <c r="D662">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E662" t="s">
         <v>30</v>
@@ -15351,7 +15351,7 @@
         <v>29</v>
       </c>
       <c r="D663">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E663" t="s">
         <v>30</v>
@@ -15368,7 +15368,7 @@
         <v>29</v>
       </c>
       <c r="D664">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E664" t="s">
         <v>30</v>
@@ -15385,7 +15385,7 @@
         <v>29</v>
       </c>
       <c r="D665">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E665" t="s">
         <v>30</v>
@@ -15402,7 +15402,7 @@
         <v>29</v>
       </c>
       <c r="D666">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E666" t="s">
         <v>30</v>
@@ -15419,7 +15419,7 @@
         <v>29</v>
       </c>
       <c r="D667">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E667" t="s">
         <v>30</v>
@@ -15436,7 +15436,7 @@
         <v>29</v>
       </c>
       <c r="D668">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E668" t="s">
         <v>30</v>
@@ -15453,7 +15453,7 @@
         <v>29</v>
       </c>
       <c r="D669">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E669" t="s">
         <v>30</v>
@@ -15470,7 +15470,7 @@
         <v>29</v>
       </c>
       <c r="D670">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E670" t="s">
         <v>30</v>
@@ -15487,7 +15487,7 @@
         <v>29</v>
       </c>
       <c r="D671">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E671" t="s">
         <v>30</v>
@@ -15504,7 +15504,7 @@
         <v>29</v>
       </c>
       <c r="D672">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E672" t="s">
         <v>30</v>
@@ -15538,7 +15538,7 @@
         <v>29</v>
       </c>
       <c r="D674">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E674" t="s">
         <v>30</v>
@@ -15555,7 +15555,7 @@
         <v>29</v>
       </c>
       <c r="D675">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E675" t="s">
         <v>30</v>
@@ -15572,7 +15572,7 @@
         <v>29</v>
       </c>
       <c r="D676">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E676" t="s">
         <v>30</v>
@@ -15589,7 +15589,7 @@
         <v>29</v>
       </c>
       <c r="D677">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E677" t="s">
         <v>30</v>
@@ -15606,7 +15606,7 @@
         <v>29</v>
       </c>
       <c r="D678">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E678" t="s">
         <v>30</v>
@@ -15623,7 +15623,7 @@
         <v>29</v>
       </c>
       <c r="D679">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E679" t="s">
         <v>30</v>
@@ -15640,7 +15640,7 @@
         <v>29</v>
       </c>
       <c r="D680">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E680" t="s">
         <v>30</v>
@@ -15657,7 +15657,7 @@
         <v>29</v>
       </c>
       <c r="D681">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E681" t="s">
         <v>30</v>
@@ -15674,7 +15674,7 @@
         <v>29</v>
       </c>
       <c r="D682">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E682" t="s">
         <v>30</v>
@@ -15708,7 +15708,7 @@
         <v>29</v>
       </c>
       <c r="D684">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E684" t="s">
         <v>30</v>
@@ -15725,7 +15725,7 @@
         <v>29</v>
       </c>
       <c r="D685">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E685" t="s">
         <v>30</v>
@@ -15742,7 +15742,7 @@
         <v>29</v>
       </c>
       <c r="D686">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E686" t="s">
         <v>30</v>
@@ -15759,7 +15759,7 @@
         <v>29</v>
       </c>
       <c r="D687">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E687" t="s">
         <v>30</v>
@@ -15793,7 +15793,7 @@
         <v>29</v>
       </c>
       <c r="D689">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E689" t="s">
         <v>30</v>
@@ -15810,7 +15810,7 @@
         <v>29</v>
       </c>
       <c r="D690">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E690" t="s">
         <v>30</v>
@@ -15844,7 +15844,7 @@
         <v>29</v>
       </c>
       <c r="D692">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E692" t="s">
         <v>30</v>
@@ -15861,7 +15861,7 @@
         <v>29</v>
       </c>
       <c r="D693">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E693" t="s">
         <v>30</v>
@@ -15878,7 +15878,7 @@
         <v>29</v>
       </c>
       <c r="D694">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E694" t="s">
         <v>30</v>
@@ -15895,7 +15895,7 @@
         <v>29</v>
       </c>
       <c r="D695">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E695" t="s">
         <v>30</v>
@@ -15912,7 +15912,7 @@
         <v>29</v>
       </c>
       <c r="D696">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E696" t="s">
         <v>30</v>
@@ -15929,7 +15929,7 @@
         <v>29</v>
       </c>
       <c r="D697">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E697" t="s">
         <v>30</v>
@@ -15946,7 +15946,7 @@
         <v>29</v>
       </c>
       <c r="D698">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E698" t="s">
         <v>30</v>
@@ -15963,7 +15963,7 @@
         <v>29</v>
       </c>
       <c r="D699">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E699" t="s">
         <v>30</v>
@@ -15980,7 +15980,7 @@
         <v>29</v>
       </c>
       <c r="D700">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E700" t="s">
         <v>30</v>
@@ -15997,7 +15997,7 @@
         <v>29</v>
       </c>
       <c r="D701">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E701" t="s">
         <v>30</v>
@@ -16014,7 +16014,7 @@
         <v>29</v>
       </c>
       <c r="D702">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E702" t="s">
         <v>30</v>
@@ -16048,7 +16048,7 @@
         <v>29</v>
       </c>
       <c r="D704">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E704" t="s">
         <v>30</v>
@@ -16065,7 +16065,7 @@
         <v>29</v>
       </c>
       <c r="D705">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E705" t="s">
         <v>30</v>
@@ -16082,7 +16082,7 @@
         <v>29</v>
       </c>
       <c r="D706">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E706" t="s">
         <v>30</v>
@@ -16099,7 +16099,7 @@
         <v>29</v>
       </c>
       <c r="D707">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E707" t="s">
         <v>30</v>
@@ -16116,7 +16116,7 @@
         <v>29</v>
       </c>
       <c r="D708">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E708" t="s">
         <v>30</v>
@@ -16133,7 +16133,7 @@
         <v>29</v>
       </c>
       <c r="D709">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E709" t="s">
         <v>30</v>
@@ -16150,7 +16150,7 @@
         <v>29</v>
       </c>
       <c r="D710">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E710" t="s">
         <v>30</v>
@@ -16167,7 +16167,7 @@
         <v>29</v>
       </c>
       <c r="D711">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E711" t="s">
         <v>30</v>
@@ -16184,7 +16184,7 @@
         <v>29</v>
       </c>
       <c r="D712">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E712" t="s">
         <v>30</v>
@@ -16201,7 +16201,7 @@
         <v>29</v>
       </c>
       <c r="D713">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E713" t="s">
         <v>30</v>
@@ -16218,7 +16218,7 @@
         <v>29</v>
       </c>
       <c r="D714">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E714" t="s">
         <v>30</v>
@@ -16235,7 +16235,7 @@
         <v>29</v>
       </c>
       <c r="D715">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E715" t="s">
         <v>30</v>
@@ -16252,7 +16252,7 @@
         <v>29</v>
       </c>
       <c r="D716">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E716" t="s">
         <v>30</v>
@@ -16269,7 +16269,7 @@
         <v>29</v>
       </c>
       <c r="D717">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E717" t="s">
         <v>30</v>
@@ -16286,7 +16286,7 @@
         <v>29</v>
       </c>
       <c r="D718">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E718" t="s">
         <v>30</v>
@@ -16303,7 +16303,7 @@
         <v>29</v>
       </c>
       <c r="D719">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E719" t="s">
         <v>30</v>
@@ -16320,7 +16320,7 @@
         <v>29</v>
       </c>
       <c r="D720">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E720" t="s">
         <v>30</v>
@@ -16337,7 +16337,7 @@
         <v>29</v>
       </c>
       <c r="D721">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E721" t="s">
         <v>30</v>
@@ -16354,7 +16354,7 @@
         <v>29</v>
       </c>
       <c r="D722">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E722" t="s">
         <v>30</v>
@@ -16371,7 +16371,7 @@
         <v>29</v>
       </c>
       <c r="D723">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E723" t="s">
         <v>30</v>
@@ -16388,7 +16388,7 @@
         <v>29</v>
       </c>
       <c r="D724">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E724" t="s">
         <v>30</v>
@@ -16405,7 +16405,7 @@
         <v>29</v>
       </c>
       <c r="D725">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E725" t="s">
         <v>30</v>
@@ -16422,7 +16422,7 @@
         <v>29</v>
       </c>
       <c r="D726">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E726" t="s">
         <v>30</v>
@@ -16456,7 +16456,7 @@
         <v>29</v>
       </c>
       <c r="D728">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E728" t="s">
         <v>30</v>
@@ -16473,7 +16473,7 @@
         <v>29</v>
       </c>
       <c r="D729">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E729" t="s">
         <v>30</v>
@@ -16490,7 +16490,7 @@
         <v>29</v>
       </c>
       <c r="D730">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E730" t="s">
         <v>30</v>
@@ -16507,7 +16507,7 @@
         <v>29</v>
       </c>
       <c r="D731">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E731" t="s">
         <v>30</v>
@@ -16524,7 +16524,7 @@
         <v>29</v>
       </c>
       <c r="D732">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E732" t="s">
         <v>30</v>
@@ -16541,7 +16541,7 @@
         <v>29</v>
       </c>
       <c r="D733">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E733" t="s">
         <v>30</v>
@@ -16558,7 +16558,7 @@
         <v>29</v>
       </c>
       <c r="D734">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E734" t="s">
         <v>30</v>
@@ -16575,7 +16575,7 @@
         <v>29</v>
       </c>
       <c r="D735">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E735" t="s">
         <v>30</v>
@@ -16592,7 +16592,7 @@
         <v>29</v>
       </c>
       <c r="D736">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E736" t="s">
         <v>30</v>
@@ -16609,7 +16609,7 @@
         <v>29</v>
       </c>
       <c r="D737">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E737" t="s">
         <v>30</v>
@@ -16626,7 +16626,7 @@
         <v>29</v>
       </c>
       <c r="D738">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E738" t="s">
         <v>30</v>
@@ -16643,7 +16643,7 @@
         <v>29</v>
       </c>
       <c r="D739">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E739" t="s">
         <v>30</v>
@@ -16660,7 +16660,7 @@
         <v>29</v>
       </c>
       <c r="D740">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E740" t="s">
         <v>30</v>
@@ -16677,7 +16677,7 @@
         <v>29</v>
       </c>
       <c r="D741">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E741" t="s">
         <v>30</v>
@@ -16694,7 +16694,7 @@
         <v>29</v>
       </c>
       <c r="D742">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E742" t="s">
         <v>30</v>
@@ -16711,7 +16711,7 @@
         <v>29</v>
       </c>
       <c r="D743">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E743" t="s">
         <v>30</v>
@@ -16728,7 +16728,7 @@
         <v>29</v>
       </c>
       <c r="D744">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E744" t="s">
         <v>30</v>
@@ -16745,7 +16745,7 @@
         <v>29</v>
       </c>
       <c r="D745">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E745" t="s">
         <v>30</v>
@@ -16762,7 +16762,7 @@
         <v>29</v>
       </c>
       <c r="D746">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E746" t="s">
         <v>30</v>
@@ -16779,7 +16779,7 @@
         <v>29</v>
       </c>
       <c r="D747">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E747" t="s">
         <v>30</v>
@@ -16796,7 +16796,7 @@
         <v>29</v>
       </c>
       <c r="D748">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E748" t="s">
         <v>30</v>
@@ -16813,7 +16813,7 @@
         <v>29</v>
       </c>
       <c r="D749">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E749" t="s">
         <v>30</v>
@@ -16830,7 +16830,7 @@
         <v>29</v>
       </c>
       <c r="D750">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E750" t="s">
         <v>30</v>
@@ -16847,7 +16847,7 @@
         <v>29</v>
       </c>
       <c r="D751">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E751" t="s">
         <v>30</v>
@@ -16864,7 +16864,7 @@
         <v>29</v>
       </c>
       <c r="D752">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E752" t="s">
         <v>30</v>
@@ -16881,7 +16881,7 @@
         <v>29</v>
       </c>
       <c r="D753">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E753" t="s">
         <v>30</v>
@@ -16898,7 +16898,7 @@
         <v>29</v>
       </c>
       <c r="D754">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E754" t="s">
         <v>30</v>
@@ -16915,7 +16915,7 @@
         <v>29</v>
       </c>
       <c r="D755">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E755" t="s">
         <v>30</v>
@@ -16932,7 +16932,7 @@
         <v>29</v>
       </c>
       <c r="D756">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E756" t="s">
         <v>30</v>
@@ -16949,7 +16949,7 @@
         <v>29</v>
       </c>
       <c r="D757">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E757" t="s">
         <v>30</v>
@@ -16966,7 +16966,7 @@
         <v>29</v>
       </c>
       <c r="D758">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E758" t="s">
         <v>30</v>
@@ -16983,7 +16983,7 @@
         <v>29</v>
       </c>
       <c r="D759">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E759" t="s">
         <v>30</v>
@@ -17000,7 +17000,7 @@
         <v>29</v>
       </c>
       <c r="D760">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E760" t="s">
         <v>30</v>
@@ -17017,7 +17017,7 @@
         <v>29</v>
       </c>
       <c r="D761">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E761" t="s">
         <v>30</v>
@@ -17051,7 +17051,7 @@
         <v>29</v>
       </c>
       <c r="D763">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E763" t="s">
         <v>30</v>
@@ -17068,7 +17068,7 @@
         <v>29</v>
       </c>
       <c r="D764">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E764" t="s">
         <v>30</v>
@@ -17085,7 +17085,7 @@
         <v>29</v>
       </c>
       <c r="D765">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E765" t="s">
         <v>30</v>
@@ -17102,7 +17102,7 @@
         <v>29</v>
       </c>
       <c r="D766">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E766" t="s">
         <v>30</v>
@@ -17119,7 +17119,7 @@
         <v>29</v>
       </c>
       <c r="D767">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E767" t="s">
         <v>30</v>
@@ -17136,7 +17136,7 @@
         <v>29</v>
       </c>
       <c r="D768">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E768" t="s">
         <v>30</v>
@@ -17170,7 +17170,7 @@
         <v>29</v>
       </c>
       <c r="D770">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E770" t="s">
         <v>30</v>
@@ -17187,7 +17187,7 @@
         <v>29</v>
       </c>
       <c r="D771">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E771" t="s">
         <v>30</v>
@@ -17204,7 +17204,7 @@
         <v>29</v>
       </c>
       <c r="D772">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E772" t="s">
         <v>30</v>
@@ -17221,7 +17221,7 @@
         <v>29</v>
       </c>
       <c r="D773">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E773" t="s">
         <v>30</v>
@@ -17238,7 +17238,7 @@
         <v>29</v>
       </c>
       <c r="D774">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E774" t="s">
         <v>30</v>
@@ -17255,7 +17255,7 @@
         <v>29</v>
       </c>
       <c r="D775">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E775" t="s">
         <v>30</v>
@@ -17272,7 +17272,7 @@
         <v>29</v>
       </c>
       <c r="D776">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E776" t="s">
         <v>30</v>
@@ -17289,7 +17289,7 @@
         <v>29</v>
       </c>
       <c r="D777">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E777" t="s">
         <v>30</v>
@@ -17306,7 +17306,7 @@
         <v>29</v>
       </c>
       <c r="D778">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E778" t="s">
         <v>30</v>
@@ -17323,7 +17323,7 @@
         <v>29</v>
       </c>
       <c r="D779">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E779" t="s">
         <v>30</v>
@@ -17340,7 +17340,7 @@
         <v>29</v>
       </c>
       <c r="D780">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E780" t="s">
         <v>30</v>
@@ -17357,7 +17357,7 @@
         <v>29</v>
       </c>
       <c r="D781">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E781" t="s">
         <v>30</v>
@@ -17374,7 +17374,7 @@
         <v>29</v>
       </c>
       <c r="D782">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E782" t="s">
         <v>30</v>
@@ -17391,7 +17391,7 @@
         <v>29</v>
       </c>
       <c r="D783">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E783" t="s">
         <v>30</v>
@@ -17408,7 +17408,7 @@
         <v>29</v>
       </c>
       <c r="D784">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E784" t="s">
         <v>30</v>
@@ -17425,7 +17425,7 @@
         <v>29</v>
       </c>
       <c r="D785">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E785" t="s">
         <v>30</v>
@@ -17442,7 +17442,7 @@
         <v>29</v>
       </c>
       <c r="D786">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E786" t="s">
         <v>30</v>
@@ -17459,7 +17459,7 @@
         <v>29</v>
       </c>
       <c r="D787">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E787" t="s">
         <v>30</v>
@@ -17476,7 +17476,7 @@
         <v>29</v>
       </c>
       <c r="D788">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E788" t="s">
         <v>30</v>
@@ -17493,7 +17493,7 @@
         <v>29</v>
       </c>
       <c r="D789">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E789" t="s">
         <v>30</v>
@@ -17510,7 +17510,7 @@
         <v>29</v>
       </c>
       <c r="D790">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E790" t="s">
         <v>30</v>
@@ -17527,7 +17527,7 @@
         <v>29</v>
       </c>
       <c r="D791">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E791" t="s">
         <v>30</v>
@@ -17544,7 +17544,7 @@
         <v>29</v>
       </c>
       <c r="D792">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E792" t="s">
         <v>30</v>
@@ -17561,7 +17561,7 @@
         <v>29</v>
       </c>
       <c r="D793">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E793" t="s">
         <v>30</v>
@@ -17578,7 +17578,7 @@
         <v>29</v>
       </c>
       <c r="D794">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E794" t="s">
         <v>30</v>
@@ -17595,7 +17595,7 @@
         <v>29</v>
       </c>
       <c r="D795">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E795" t="s">
         <v>30</v>
@@ -17612,7 +17612,7 @@
         <v>29</v>
       </c>
       <c r="D796">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E796" t="s">
         <v>30</v>
@@ -17629,7 +17629,7 @@
         <v>29</v>
       </c>
       <c r="D797">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E797" t="s">
         <v>30</v>
@@ -17646,7 +17646,7 @@
         <v>29</v>
       </c>
       <c r="D798">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E798" t="s">
         <v>30</v>
@@ -17663,7 +17663,7 @@
         <v>29</v>
       </c>
       <c r="D799">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E799" t="s">
         <v>30</v>
@@ -17680,7 +17680,7 @@
         <v>29</v>
       </c>
       <c r="D800">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E800" t="s">
         <v>30</v>
@@ -17697,7 +17697,7 @@
         <v>29</v>
       </c>
       <c r="D801">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E801" t="s">
         <v>30</v>
@@ -17714,7 +17714,7 @@
         <v>29</v>
       </c>
       <c r="D802">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E802" t="s">
         <v>30</v>
@@ -17731,7 +17731,7 @@
         <v>29</v>
       </c>
       <c r="D803">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E803" t="s">
         <v>30</v>
@@ -17748,7 +17748,7 @@
         <v>29</v>
       </c>
       <c r="D804">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E804" t="s">
         <v>30</v>
@@ -17765,7 +17765,7 @@
         <v>29</v>
       </c>
       <c r="D805">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E805" t="s">
         <v>30</v>
@@ -17782,7 +17782,7 @@
         <v>29</v>
       </c>
       <c r="D806">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E806" t="s">
         <v>30</v>
@@ -17799,7 +17799,7 @@
         <v>29</v>
       </c>
       <c r="D807">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E807" t="s">
         <v>30</v>
@@ -17816,7 +17816,7 @@
         <v>29</v>
       </c>
       <c r="D808">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E808" t="s">
         <v>30</v>
@@ -17833,7 +17833,7 @@
         <v>29</v>
       </c>
       <c r="D809">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E809" t="s">
         <v>30</v>
@@ -17850,7 +17850,7 @@
         <v>29</v>
       </c>
       <c r="D810">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E810" t="s">
         <v>30</v>
@@ -17867,7 +17867,7 @@
         <v>29</v>
       </c>
       <c r="D811">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E811" t="s">
         <v>30</v>
@@ -17884,7 +17884,7 @@
         <v>29</v>
       </c>
       <c r="D812">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E812" t="s">
         <v>30</v>
@@ -17901,7 +17901,7 @@
         <v>29</v>
       </c>
       <c r="D813">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E813" t="s">
         <v>30</v>
@@ -17935,7 +17935,7 @@
         <v>29</v>
       </c>
       <c r="D815">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E815" t="s">
         <v>30</v>
@@ -17952,7 +17952,7 @@
         <v>29</v>
       </c>
       <c r="D816">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E816" t="s">
         <v>30</v>
@@ -17969,7 +17969,7 @@
         <v>29</v>
       </c>
       <c r="D817">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E817" t="s">
         <v>30</v>
@@ -17986,7 +17986,7 @@
         <v>29</v>
       </c>
       <c r="D818">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E818" t="s">
         <v>30</v>
@@ -18003,7 +18003,7 @@
         <v>29</v>
       </c>
       <c r="D819">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E819" t="s">
         <v>30</v>
@@ -18020,7 +18020,7 @@
         <v>29</v>
       </c>
       <c r="D820">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E820" t="s">
         <v>30</v>
@@ -18037,7 +18037,7 @@
         <v>29</v>
       </c>
       <c r="D821">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E821" t="s">
         <v>30</v>
@@ -18054,7 +18054,7 @@
         <v>29</v>
       </c>
       <c r="D822">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E822" t="s">
         <v>30</v>
@@ -18071,7 +18071,7 @@
         <v>29</v>
       </c>
       <c r="D823">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E823" t="s">
         <v>30</v>
@@ -18088,7 +18088,7 @@
         <v>29</v>
       </c>
       <c r="D824">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E824" t="s">
         <v>30</v>
@@ -18105,7 +18105,7 @@
         <v>29</v>
       </c>
       <c r="D825">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E825" t="s">
         <v>30</v>
@@ -18122,7 +18122,7 @@
         <v>29</v>
       </c>
       <c r="D826">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E826" t="s">
         <v>30</v>
@@ -18139,7 +18139,7 @@
         <v>29</v>
       </c>
       <c r="D827">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E827" t="s">
         <v>30</v>
@@ -18156,7 +18156,7 @@
         <v>29</v>
       </c>
       <c r="D828">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E828" t="s">
         <v>30</v>
@@ -18173,7 +18173,7 @@
         <v>29</v>
       </c>
       <c r="D829">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E829" t="s">
         <v>30</v>
@@ -18190,7 +18190,7 @@
         <v>29</v>
       </c>
       <c r="D830">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E830" t="s">
         <v>30</v>
@@ -18207,7 +18207,7 @@
         <v>29</v>
       </c>
       <c r="D831">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E831" t="s">
         <v>30</v>
@@ -18241,7 +18241,7 @@
         <v>29</v>
       </c>
       <c r="D833">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E833" t="s">
         <v>30</v>
@@ -18258,7 +18258,7 @@
         <v>29</v>
       </c>
       <c r="D834">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E834" t="s">
         <v>30</v>
@@ -18292,7 +18292,7 @@
         <v>29</v>
       </c>
       <c r="D836">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E836" t="s">
         <v>30</v>
@@ -18309,7 +18309,7 @@
         <v>29</v>
       </c>
       <c r="D837">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E837" t="s">
         <v>30</v>
@@ -18326,7 +18326,7 @@
         <v>29</v>
       </c>
       <c r="D838">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E838" t="s">
         <v>30</v>
@@ -18343,7 +18343,7 @@
         <v>29</v>
       </c>
       <c r="D839">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E839" t="s">
         <v>30</v>
@@ -18360,7 +18360,7 @@
         <v>29</v>
       </c>
       <c r="D840">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E840" t="s">
         <v>30</v>
@@ -18377,7 +18377,7 @@
         <v>29</v>
       </c>
       <c r="D841">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E841" t="s">
         <v>30</v>
@@ -18394,7 +18394,7 @@
         <v>29</v>
       </c>
       <c r="D842">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E842" t="s">
         <v>30</v>
@@ -18411,7 +18411,7 @@
         <v>29</v>
       </c>
       <c r="D843">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E843" t="s">
         <v>30</v>
@@ -18428,7 +18428,7 @@
         <v>29</v>
       </c>
       <c r="D844">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E844" t="s">
         <v>30</v>
@@ -18445,7 +18445,7 @@
         <v>29</v>
       </c>
       <c r="D845">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E845" t="s">
         <v>30</v>
@@ -18462,7 +18462,7 @@
         <v>29</v>
       </c>
       <c r="D846">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E846" t="s">
         <v>30</v>
@@ -18479,7 +18479,7 @@
         <v>29</v>
       </c>
       <c r="D847">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E847" t="s">
         <v>30</v>
@@ -18496,7 +18496,7 @@
         <v>29</v>
       </c>
       <c r="D848">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E848" t="s">
         <v>30</v>
@@ -18513,7 +18513,7 @@
         <v>29</v>
       </c>
       <c r="D849">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E849" t="s">
         <v>30</v>
@@ -18530,7 +18530,7 @@
         <v>29</v>
       </c>
       <c r="D850">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E850" t="s">
         <v>30</v>
@@ -18547,7 +18547,7 @@
         <v>29</v>
       </c>
       <c r="D851">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E851" t="s">
         <v>30</v>
@@ -18564,7 +18564,7 @@
         <v>29</v>
       </c>
       <c r="D852">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E852" t="s">
         <v>30</v>
@@ -18581,7 +18581,7 @@
         <v>29</v>
       </c>
       <c r="D853">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E853" t="s">
         <v>30</v>
@@ -18598,7 +18598,7 @@
         <v>29</v>
       </c>
       <c r="D854">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E854" t="s">
         <v>30</v>
@@ -18615,7 +18615,7 @@
         <v>29</v>
       </c>
       <c r="D855">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E855" t="s">
         <v>30</v>
@@ -18632,7 +18632,7 @@
         <v>29</v>
       </c>
       <c r="D856">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E856" t="s">
         <v>30</v>
@@ -18649,7 +18649,7 @@
         <v>29</v>
       </c>
       <c r="D857">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E857" t="s">
         <v>30</v>
@@ -18666,7 +18666,7 @@
         <v>29</v>
       </c>
       <c r="D858">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E858" t="s">
         <v>30</v>
@@ -18683,7 +18683,7 @@
         <v>29</v>
       </c>
       <c r="D859">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E859" t="s">
         <v>30</v>
@@ -18717,7 +18717,7 @@
         <v>29</v>
       </c>
       <c r="D861">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E861" t="s">
         <v>30</v>
@@ -18734,7 +18734,7 @@
         <v>29</v>
       </c>
       <c r="D862">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E862" t="s">
         <v>30</v>
@@ -18751,7 +18751,7 @@
         <v>29</v>
       </c>
       <c r="D863">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E863" t="s">
         <v>30</v>
@@ -18768,7 +18768,7 @@
         <v>29</v>
       </c>
       <c r="D864">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E864" t="s">
         <v>30</v>
@@ -18785,7 +18785,7 @@
         <v>29</v>
       </c>
       <c r="D865">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E865" t="s">
         <v>30</v>
@@ -18802,7 +18802,7 @@
         <v>29</v>
       </c>
       <c r="D866">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E866" t="s">
         <v>30</v>
@@ -18819,7 +18819,7 @@
         <v>29</v>
       </c>
       <c r="D867">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E867" t="s">
         <v>30</v>
@@ -18836,7 +18836,7 @@
         <v>29</v>
       </c>
       <c r="D868">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E868" t="s">
         <v>30</v>
@@ -18853,7 +18853,7 @@
         <v>29</v>
       </c>
       <c r="D869">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E869" t="s">
         <v>30</v>
@@ -18870,7 +18870,7 @@
         <v>29</v>
       </c>
       <c r="D870">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E870" t="s">
         <v>30</v>
@@ -18887,7 +18887,7 @@
         <v>29</v>
       </c>
       <c r="D871">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E871" t="s">
         <v>30</v>
@@ -18904,7 +18904,7 @@
         <v>29</v>
       </c>
       <c r="D872">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E872" t="s">
         <v>30</v>
@@ -18938,7 +18938,7 @@
         <v>29</v>
       </c>
       <c r="D874">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E874" t="s">
         <v>30</v>
@@ -18955,7 +18955,7 @@
         <v>29</v>
       </c>
       <c r="D875">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E875" t="s">
         <v>30</v>
@@ -18972,7 +18972,7 @@
         <v>29</v>
       </c>
       <c r="D876">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E876" t="s">
         <v>30</v>
@@ -18989,7 +18989,7 @@
         <v>29</v>
       </c>
       <c r="D877">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E877" t="s">
         <v>30</v>
@@ -19006,7 +19006,7 @@
         <v>29</v>
       </c>
       <c r="D878">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E878" t="s">
         <v>30</v>
@@ -19023,7 +19023,7 @@
         <v>29</v>
       </c>
       <c r="D879">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E879" t="s">
         <v>30</v>
@@ -19040,7 +19040,7 @@
         <v>29</v>
       </c>
       <c r="D880">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E880" t="s">
         <v>30</v>
@@ -19057,7 +19057,7 @@
         <v>29</v>
       </c>
       <c r="D881">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E881" t="s">
         <v>30</v>
@@ -19091,7 +19091,7 @@
         <v>29</v>
       </c>
       <c r="D883">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E883" t="s">
         <v>30</v>
@@ -19108,7 +19108,7 @@
         <v>29</v>
       </c>
       <c r="D884">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E884" t="s">
         <v>30</v>
@@ -19125,7 +19125,7 @@
         <v>29</v>
       </c>
       <c r="D885">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E885" t="s">
         <v>30</v>
@@ -19142,7 +19142,7 @@
         <v>29</v>
       </c>
       <c r="D886">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E886" t="s">
         <v>30</v>
@@ -19159,7 +19159,7 @@
         <v>29</v>
       </c>
       <c r="D887">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E887" t="s">
         <v>30</v>
@@ -19176,7 +19176,7 @@
         <v>29</v>
       </c>
       <c r="D888">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E888" t="s">
         <v>30</v>
@@ -19193,7 +19193,7 @@
         <v>29</v>
       </c>
       <c r="D889">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E889" t="s">
         <v>30</v>
@@ -19210,7 +19210,7 @@
         <v>29</v>
       </c>
       <c r="D890">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E890" t="s">
         <v>30</v>
@@ -19227,7 +19227,7 @@
         <v>29</v>
       </c>
       <c r="D891">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E891" t="s">
         <v>30</v>
@@ -19244,7 +19244,7 @@
         <v>29</v>
       </c>
       <c r="D892">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E892" t="s">
         <v>30</v>
@@ -19261,7 +19261,7 @@
         <v>29</v>
       </c>
       <c r="D893">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E893" t="s">
         <v>30</v>
@@ -19278,7 +19278,7 @@
         <v>29</v>
       </c>
       <c r="D894">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E894" t="s">
         <v>30</v>
@@ -19295,7 +19295,7 @@
         <v>29</v>
       </c>
       <c r="D895">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E895" t="s">
         <v>30</v>
@@ -19312,7 +19312,7 @@
         <v>29</v>
       </c>
       <c r="D896">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E896" t="s">
         <v>30</v>
@@ -19329,7 +19329,7 @@
         <v>29</v>
       </c>
       <c r="D897">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E897" t="s">
         <v>30</v>
@@ -19346,7 +19346,7 @@
         <v>29</v>
       </c>
       <c r="D898">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E898" t="s">
         <v>30</v>
@@ -19363,7 +19363,7 @@
         <v>29</v>
       </c>
       <c r="D899">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E899" t="s">
         <v>30</v>
@@ -19380,7 +19380,7 @@
         <v>29</v>
       </c>
       <c r="D900">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E900" t="s">
         <v>30</v>
@@ -19397,7 +19397,7 @@
         <v>29</v>
       </c>
       <c r="D901">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E901" t="s">
         <v>30</v>
@@ -19414,7 +19414,7 @@
         <v>29</v>
       </c>
       <c r="D902">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E902" t="s">
         <v>30</v>
@@ -19431,7 +19431,7 @@
         <v>29</v>
       </c>
       <c r="D903">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E903" t="s">
         <v>30</v>
@@ -19448,7 +19448,7 @@
         <v>29</v>
       </c>
       <c r="D904">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E904" t="s">
         <v>30</v>
@@ -19465,7 +19465,7 @@
         <v>29</v>
       </c>
       <c r="D905">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E905" t="s">
         <v>30</v>
@@ -19482,7 +19482,7 @@
         <v>29</v>
       </c>
       <c r="D906">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E906" t="s">
         <v>30</v>
@@ -19499,7 +19499,7 @@
         <v>29</v>
       </c>
       <c r="D907">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E907" t="s">
         <v>30</v>
@@ -19516,7 +19516,7 @@
         <v>29</v>
       </c>
       <c r="D908">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E908" t="s">
         <v>30</v>
@@ -19533,7 +19533,7 @@
         <v>29</v>
       </c>
       <c r="D909">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E909" t="s">
         <v>30</v>
@@ -19550,7 +19550,7 @@
         <v>29</v>
       </c>
       <c r="D910">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E910" t="s">
         <v>30</v>
@@ -19567,7 +19567,7 @@
         <v>29</v>
       </c>
       <c r="D911">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E911" t="s">
         <v>30</v>
@@ -19584,7 +19584,7 @@
         <v>29</v>
       </c>
       <c r="D912">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E912" t="s">
         <v>30</v>
@@ -19601,7 +19601,7 @@
         <v>29</v>
       </c>
       <c r="D913">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E913" t="s">
         <v>30</v>
@@ -19618,7 +19618,7 @@
         <v>29</v>
       </c>
       <c r="D914">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E914" t="s">
         <v>30</v>
@@ -19635,7 +19635,7 @@
         <v>29</v>
       </c>
       <c r="D915">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E915" t="s">
         <v>30</v>
@@ -19652,7 +19652,7 @@
         <v>29</v>
       </c>
       <c r="D916">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E916" t="s">
         <v>30</v>
@@ -19669,7 +19669,7 @@
         <v>29</v>
       </c>
       <c r="D917">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E917" t="s">
         <v>30</v>
@@ -19686,7 +19686,7 @@
         <v>29</v>
       </c>
       <c r="D918">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E918" t="s">
         <v>30</v>
@@ -19703,7 +19703,7 @@
         <v>29</v>
       </c>
       <c r="D919">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E919" t="s">
         <v>30</v>
@@ -19720,7 +19720,7 @@
         <v>29</v>
       </c>
       <c r="D920">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E920" t="s">
         <v>30</v>
@@ -19737,7 +19737,7 @@
         <v>29</v>
       </c>
       <c r="D921">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E921" t="s">
         <v>30</v>
@@ -19754,7 +19754,7 @@
         <v>29</v>
       </c>
       <c r="D922">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E922" t="s">
         <v>30</v>
@@ -19771,7 +19771,7 @@
         <v>29</v>
       </c>
       <c r="D923">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E923" t="s">
         <v>30</v>
@@ -19788,7 +19788,7 @@
         <v>29</v>
       </c>
       <c r="D924">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E924" t="s">
         <v>30</v>
@@ -19805,7 +19805,7 @@
         <v>29</v>
       </c>
       <c r="D925">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E925" t="s">
         <v>30</v>
@@ -19822,7 +19822,7 @@
         <v>29</v>
       </c>
       <c r="D926">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E926" t="s">
         <v>30</v>
@@ -19839,7 +19839,7 @@
         <v>29</v>
       </c>
       <c r="D927">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E927" t="s">
         <v>30</v>
@@ -19856,7 +19856,7 @@
         <v>29</v>
       </c>
       <c r="D928">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E928" t="s">
         <v>30</v>
@@ -19873,7 +19873,7 @@
         <v>29</v>
       </c>
       <c r="D929">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E929" t="s">
         <v>30</v>
@@ -19890,7 +19890,7 @@
         <v>29</v>
       </c>
       <c r="D930">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E930" t="s">
         <v>30</v>
@@ -19907,7 +19907,7 @@
         <v>29</v>
       </c>
       <c r="D931">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E931" t="s">
         <v>30</v>
@@ -19924,7 +19924,7 @@
         <v>29</v>
       </c>
       <c r="D932">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E932" t="s">
         <v>30</v>
@@ -19941,7 +19941,7 @@
         <v>29</v>
       </c>
       <c r="D933">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E933" t="s">
         <v>30</v>
@@ -19958,7 +19958,7 @@
         <v>29</v>
       </c>
       <c r="D934">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E934" t="s">
         <v>30</v>
@@ -19975,7 +19975,7 @@
         <v>29</v>
       </c>
       <c r="D935">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E935" t="s">
         <v>30</v>
@@ -19992,7 +19992,7 @@
         <v>29</v>
       </c>
       <c r="D936">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E936" t="s">
         <v>30</v>
@@ -20009,7 +20009,7 @@
         <v>29</v>
       </c>
       <c r="D937">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E937" t="s">
         <v>30</v>
@@ -20026,7 +20026,7 @@
         <v>29</v>
       </c>
       <c r="D938">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E938" t="s">
         <v>30</v>
@@ -20043,7 +20043,7 @@
         <v>29</v>
       </c>
       <c r="D939">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E939" t="s">
         <v>30</v>
@@ -20060,7 +20060,7 @@
         <v>29</v>
       </c>
       <c r="D940">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E940" t="s">
         <v>30</v>
@@ -20077,7 +20077,7 @@
         <v>29</v>
       </c>
       <c r="D941">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E941" t="s">
         <v>30</v>
@@ -20094,7 +20094,7 @@
         <v>29</v>
       </c>
       <c r="D942">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E942" t="s">
         <v>30</v>
@@ -20111,7 +20111,7 @@
         <v>29</v>
       </c>
       <c r="D943">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E943" t="s">
         <v>30</v>
@@ -20128,7 +20128,7 @@
         <v>29</v>
       </c>
       <c r="D944">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E944" t="s">
         <v>30</v>
@@ -20145,7 +20145,7 @@
         <v>29</v>
       </c>
       <c r="D945">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E945" t="s">
         <v>30</v>
@@ -20162,7 +20162,7 @@
         <v>29</v>
       </c>
       <c r="D946">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E946" t="s">
         <v>30</v>
@@ -20179,7 +20179,7 @@
         <v>29</v>
       </c>
       <c r="D947">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E947" t="s">
         <v>30</v>
@@ -20196,7 +20196,7 @@
         <v>29</v>
       </c>
       <c r="D948">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E948" t="s">
         <v>30</v>
@@ -20213,7 +20213,7 @@
         <v>29</v>
       </c>
       <c r="D949">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E949" t="s">
         <v>30</v>
@@ -20247,7 +20247,7 @@
         <v>29</v>
       </c>
       <c r="D951">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E951" t="s">
         <v>30</v>
@@ -20264,7 +20264,7 @@
         <v>29</v>
       </c>
       <c r="D952">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E952" t="s">
         <v>30</v>
@@ -20281,7 +20281,7 @@
         <v>29</v>
       </c>
       <c r="D953">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E953" t="s">
         <v>30</v>
@@ -20298,7 +20298,7 @@
         <v>29</v>
       </c>
       <c r="D954">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E954" t="s">
         <v>30</v>
@@ -20315,7 +20315,7 @@
         <v>29</v>
       </c>
       <c r="D955">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E955" t="s">
         <v>30</v>
@@ -20332,7 +20332,7 @@
         <v>29</v>
       </c>
       <c r="D956">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E956" t="s">
         <v>30</v>
@@ -20349,7 +20349,7 @@
         <v>29</v>
       </c>
       <c r="D957">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E957" t="s">
         <v>30</v>
@@ -20366,7 +20366,7 @@
         <v>29</v>
       </c>
       <c r="D958">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E958" t="s">
         <v>30</v>
@@ -20383,7 +20383,7 @@
         <v>29</v>
       </c>
       <c r="D959">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E959" t="s">
         <v>30</v>
@@ -20400,7 +20400,7 @@
         <v>29</v>
       </c>
       <c r="D960">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E960" t="s">
         <v>30</v>
@@ -20417,7 +20417,7 @@
         <v>29</v>
       </c>
       <c r="D961">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E961" t="s">
         <v>30</v>
@@ -20434,7 +20434,7 @@
         <v>29</v>
       </c>
       <c r="D962">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E962" t="s">
         <v>30</v>
@@ -20451,7 +20451,7 @@
         <v>29</v>
       </c>
       <c r="D963">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E963" t="s">
         <v>30</v>
@@ -20468,7 +20468,7 @@
         <v>29</v>
       </c>
       <c r="D964">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E964" t="s">
         <v>30</v>
@@ -20485,7 +20485,7 @@
         <v>29</v>
       </c>
       <c r="D965">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E965" t="s">
         <v>30</v>
@@ -20502,7 +20502,7 @@
         <v>29</v>
       </c>
       <c r="D966">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E966" t="s">
         <v>30</v>
@@ -20519,7 +20519,7 @@
         <v>29</v>
       </c>
       <c r="D967">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E967" t="s">
         <v>30</v>
@@ -20536,7 +20536,7 @@
         <v>29</v>
       </c>
       <c r="D968">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E968" t="s">
         <v>30</v>
@@ -20553,7 +20553,7 @@
         <v>29</v>
       </c>
       <c r="D969">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E969" t="s">
         <v>30</v>
@@ -20570,7 +20570,7 @@
         <v>29</v>
       </c>
       <c r="D970">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E970" t="s">
         <v>30</v>
@@ -20587,7 +20587,7 @@
         <v>29</v>
       </c>
       <c r="D971">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E971" t="s">
         <v>30</v>
@@ -20604,7 +20604,7 @@
         <v>29</v>
       </c>
       <c r="D972">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E972" t="s">
         <v>30</v>
@@ -20621,7 +20621,7 @@
         <v>29</v>
       </c>
       <c r="D973">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E973" t="s">
         <v>30</v>
@@ -20638,7 +20638,7 @@
         <v>29</v>
       </c>
       <c r="D974">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E974" t="s">
         <v>30</v>
@@ -20655,7 +20655,7 @@
         <v>29</v>
       </c>
       <c r="D975">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E975" t="s">
         <v>30</v>
@@ -20672,7 +20672,7 @@
         <v>29</v>
       </c>
       <c r="D976">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E976" t="s">
         <v>30</v>
@@ -20689,7 +20689,7 @@
         <v>29</v>
       </c>
       <c r="D977">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E977" t="s">
         <v>30</v>
@@ -20706,7 +20706,7 @@
         <v>29</v>
       </c>
       <c r="D978">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E978" t="s">
         <v>30</v>
@@ -20723,7 +20723,7 @@
         <v>29</v>
       </c>
       <c r="D979">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E979" t="s">
         <v>30</v>
@@ -20740,7 +20740,7 @@
         <v>29</v>
       </c>
       <c r="D980">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E980" t="s">
         <v>30</v>
@@ -20757,7 +20757,7 @@
         <v>29</v>
       </c>
       <c r="D981">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E981" t="s">
         <v>30</v>
@@ -20774,7 +20774,7 @@
         <v>29</v>
       </c>
       <c r="D982">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E982" t="s">
         <v>30</v>
@@ -20808,7 +20808,7 @@
         <v>29</v>
       </c>
       <c r="D984">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E984" t="s">
         <v>30</v>
@@ -20842,7 +20842,7 @@
         <v>29</v>
       </c>
       <c r="D986">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E986" t="s">
         <v>30</v>
@@ -20859,7 +20859,7 @@
         <v>29</v>
       </c>
       <c r="D987">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E987" t="s">
         <v>30</v>
@@ -20876,7 +20876,7 @@
         <v>29</v>
       </c>
       <c r="D988">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E988" t="s">
         <v>30</v>
@@ -20893,7 +20893,7 @@
         <v>29</v>
       </c>
       <c r="D989">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E989" t="s">
         <v>30</v>
@@ -20910,7 +20910,7 @@
         <v>29</v>
       </c>
       <c r="D990">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E990" t="s">
         <v>30</v>
@@ -20927,7 +20927,7 @@
         <v>29</v>
       </c>
       <c r="D991">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E991" t="s">
         <v>30</v>
@@ -20944,7 +20944,7 @@
         <v>29</v>
       </c>
       <c r="D992">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E992" t="s">
         <v>30</v>
@@ -20961,7 +20961,7 @@
         <v>29</v>
       </c>
       <c r="D993">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E993" t="s">
         <v>30</v>
@@ -20978,7 +20978,7 @@
         <v>29</v>
       </c>
       <c r="D994">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E994" t="s">
         <v>30</v>
@@ -20995,7 +20995,7 @@
         <v>29</v>
       </c>
       <c r="D995">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E995" t="s">
         <v>30</v>
@@ -21012,7 +21012,7 @@
         <v>29</v>
       </c>
       <c r="D996">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E996" t="s">
         <v>30</v>
@@ -21029,7 +21029,7 @@
         <v>29</v>
       </c>
       <c r="D997">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E997" t="s">
         <v>30</v>
@@ -21046,7 +21046,7 @@
         <v>29</v>
       </c>
       <c r="D998">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E998" t="s">
         <v>30</v>
@@ -21063,7 +21063,7 @@
         <v>29</v>
       </c>
       <c r="D999">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E999" t="s">
         <v>30</v>
@@ -21080,7 +21080,7 @@
         <v>29</v>
       </c>
       <c r="D1000">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1000" t="s">
         <v>30</v>
@@ -21114,7 +21114,7 @@
         <v>29</v>
       </c>
       <c r="D1002">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E1002" t="s">
         <v>30</v>
@@ -21131,7 +21131,7 @@
         <v>29</v>
       </c>
       <c r="D1003">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1003" t="s">
         <v>30</v>
@@ -21148,7 +21148,7 @@
         <v>29</v>
       </c>
       <c r="D1004">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1004" t="s">
         <v>30</v>
@@ -21165,7 +21165,7 @@
         <v>29</v>
       </c>
       <c r="D1005">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1005" t="s">
         <v>30</v>
@@ -21182,7 +21182,7 @@
         <v>29</v>
       </c>
       <c r="D1006">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1006" t="s">
         <v>30</v>
@@ -21199,7 +21199,7 @@
         <v>29</v>
       </c>
       <c r="D1007">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E1007" t="s">
         <v>30</v>
@@ -21216,7 +21216,7 @@
         <v>29</v>
       </c>
       <c r="D1008">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1008" t="s">
         <v>30</v>
@@ -21233,7 +21233,7 @@
         <v>29</v>
       </c>
       <c r="D1009">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1009" t="s">
         <v>30</v>
@@ -21250,7 +21250,7 @@
         <v>29</v>
       </c>
       <c r="D1010">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1010" t="s">
         <v>30</v>
@@ -21267,7 +21267,7 @@
         <v>29</v>
       </c>
       <c r="D1011">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E1011" t="s">
         <v>30</v>
@@ -21284,7 +21284,7 @@
         <v>29</v>
       </c>
       <c r="D1012">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E1012" t="s">
         <v>30</v>
@@ -21318,7 +21318,7 @@
         <v>29</v>
       </c>
       <c r="D1014">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E1014" t="s">
         <v>30</v>
@@ -21352,7 +21352,7 @@
         <v>29</v>
       </c>
       <c r="D1016">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1016" t="s">
         <v>30</v>
@@ -21369,7 +21369,7 @@
         <v>29</v>
       </c>
       <c r="D1017">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E1017" t="s">
         <v>30</v>
@@ -21386,7 +21386,7 @@
         <v>29</v>
       </c>
       <c r="D1018">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E1018" t="s">
         <v>30</v>
@@ -21403,7 +21403,7 @@
         <v>29</v>
       </c>
       <c r="D1019">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E1019" t="s">
         <v>30</v>
@@ -21420,7 +21420,7 @@
         <v>29</v>
       </c>
       <c r="D1020">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1020" t="s">
         <v>30</v>
@@ -21437,7 +21437,7 @@
         <v>29</v>
       </c>
       <c r="D1021">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E1021" t="s">
         <v>30</v>
@@ -21454,7 +21454,7 @@
         <v>29</v>
       </c>
       <c r="D1022">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E1022" t="s">
         <v>30</v>
@@ -21505,7 +21505,7 @@
         <v>29</v>
       </c>
       <c r="D1025">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1025" t="s">
         <v>30</v>
@@ -21522,7 +21522,7 @@
         <v>29</v>
       </c>
       <c r="D1026">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1026" t="s">
         <v>30</v>
@@ -21539,7 +21539,7 @@
         <v>29</v>
       </c>
       <c r="D1027">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1027" t="s">
         <v>30</v>
@@ -21556,7 +21556,7 @@
         <v>29</v>
       </c>
       <c r="D1028">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1028" t="s">
         <v>30</v>
@@ -21573,7 +21573,7 @@
         <v>29</v>
       </c>
       <c r="D1029">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1029" t="s">
         <v>30</v>
@@ -21590,7 +21590,7 @@
         <v>29</v>
       </c>
       <c r="D1030">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1030" t="s">
         <v>30</v>
@@ -21607,7 +21607,7 @@
         <v>29</v>
       </c>
       <c r="D1031">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1031" t="s">
         <v>30</v>
@@ -21624,7 +21624,7 @@
         <v>29</v>
       </c>
       <c r="D1032">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E1032" t="s">
         <v>30</v>
@@ -21641,7 +21641,7 @@
         <v>29</v>
       </c>
       <c r="D1033">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1033" t="s">
         <v>30</v>
@@ -21658,7 +21658,7 @@
         <v>29</v>
       </c>
       <c r="D1034">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1034" t="s">
         <v>30</v>
@@ -21675,7 +21675,7 @@
         <v>29</v>
       </c>
       <c r="D1035">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E1035" t="s">
         <v>30</v>
@@ -21692,7 +21692,7 @@
         <v>29</v>
       </c>
       <c r="D1036">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1036" t="s">
         <v>30</v>
@@ -21709,7 +21709,7 @@
         <v>29</v>
       </c>
       <c r="D1037">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1037" t="s">
         <v>30</v>
@@ -21726,7 +21726,7 @@
         <v>29</v>
       </c>
       <c r="D1038">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1038" t="s">
         <v>30</v>
@@ -21743,7 +21743,7 @@
         <v>29</v>
       </c>
       <c r="D1039">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1039" t="s">
         <v>30</v>
@@ -21760,7 +21760,7 @@
         <v>29</v>
       </c>
       <c r="D1040">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1040" t="s">
         <v>30</v>
@@ -21777,7 +21777,7 @@
         <v>29</v>
       </c>
       <c r="D1041">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E1041" t="s">
         <v>30</v>
@@ -21794,7 +21794,7 @@
         <v>29</v>
       </c>
       <c r="D1042">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1042" t="s">
         <v>30</v>
@@ -21811,7 +21811,7 @@
         <v>29</v>
       </c>
       <c r="D1043">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1043" t="s">
         <v>30</v>
@@ -21828,7 +21828,7 @@
         <v>29</v>
       </c>
       <c r="D1044">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E1044" t="s">
         <v>30</v>
@@ -21845,7 +21845,7 @@
         <v>29</v>
       </c>
       <c r="D1045">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1045" t="s">
         <v>30</v>
@@ -21862,7 +21862,7 @@
         <v>29</v>
       </c>
       <c r="D1046">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1046" t="s">
         <v>30</v>
@@ -21879,7 +21879,7 @@
         <v>29</v>
       </c>
       <c r="D1047">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1047" t="s">
         <v>30</v>
@@ -21896,7 +21896,7 @@
         <v>29</v>
       </c>
       <c r="D1048">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1048" t="s">
         <v>30</v>
@@ -21913,7 +21913,7 @@
         <v>29</v>
       </c>
       <c r="D1049">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1049" t="s">
         <v>30</v>
@@ -21930,7 +21930,7 @@
         <v>29</v>
       </c>
       <c r="D1050">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1050" t="s">
         <v>30</v>
@@ -21947,7 +21947,7 @@
         <v>29</v>
       </c>
       <c r="D1051">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1051" t="s">
         <v>30</v>
@@ -21964,7 +21964,7 @@
         <v>29</v>
       </c>
       <c r="D1052">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1052" t="s">
         <v>30</v>
@@ -21981,7 +21981,7 @@
         <v>29</v>
       </c>
       <c r="D1053">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E1053" t="s">
         <v>30</v>
@@ -22015,7 +22015,7 @@
         <v>29</v>
       </c>
       <c r="D1055">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E1055" t="s">
         <v>30</v>
@@ -22032,7 +22032,7 @@
         <v>29</v>
       </c>
       <c r="D1056">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E1056" t="s">
         <v>30</v>
@@ -22049,7 +22049,7 @@
         <v>29</v>
       </c>
       <c r="D1057">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1057" t="s">
         <v>30</v>
@@ -22066,7 +22066,7 @@
         <v>29</v>
       </c>
       <c r="D1058">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E1058" t="s">
         <v>30</v>
@@ -22100,7 +22100,7 @@
         <v>29</v>
       </c>
       <c r="D1060">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1060" t="s">
         <v>30</v>
@@ -22117,7 +22117,7 @@
         <v>29</v>
       </c>
       <c r="D1061">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1061" t="s">
         <v>30</v>
@@ -22134,7 +22134,7 @@
         <v>29</v>
       </c>
       <c r="D1062">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1062" t="s">
         <v>30</v>
@@ -22151,7 +22151,7 @@
         <v>29</v>
       </c>
       <c r="D1063">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E1063" t="s">
         <v>30</v>
@@ -22168,7 +22168,7 @@
         <v>29</v>
       </c>
       <c r="D1064">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E1064" t="s">
         <v>30</v>
@@ -22185,7 +22185,7 @@
         <v>29</v>
       </c>
       <c r="D1065">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1065" t="s">
         <v>30</v>
@@ -22202,7 +22202,7 @@
         <v>29</v>
       </c>
       <c r="D1066">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1066" t="s">
         <v>30</v>
@@ -22219,7 +22219,7 @@
         <v>29</v>
       </c>
       <c r="D1067">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1067" t="s">
         <v>30</v>
@@ -22236,7 +22236,7 @@
         <v>29</v>
       </c>
       <c r="D1068">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1068" t="s">
         <v>30</v>
@@ -22253,7 +22253,7 @@
         <v>29</v>
       </c>
       <c r="D1069">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1069" t="s">
         <v>30</v>
@@ -22270,7 +22270,7 @@
         <v>29</v>
       </c>
       <c r="D1070">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1070" t="s">
         <v>30</v>
@@ -22287,7 +22287,7 @@
         <v>29</v>
       </c>
       <c r="D1071">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1071" t="s">
         <v>30</v>
@@ -22304,7 +22304,7 @@
         <v>29</v>
       </c>
       <c r="D1072">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1072" t="s">
         <v>30</v>
@@ -22321,7 +22321,7 @@
         <v>29</v>
       </c>
       <c r="D1073">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1073" t="s">
         <v>30</v>
@@ -22338,7 +22338,7 @@
         <v>29</v>
       </c>
       <c r="D1074">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1074" t="s">
         <v>30</v>
@@ -22355,7 +22355,7 @@
         <v>29</v>
       </c>
       <c r="D1075">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E1075" t="s">
         <v>30</v>
@@ -22372,7 +22372,7 @@
         <v>29</v>
       </c>
       <c r="D1076">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E1076" t="s">
         <v>30</v>
@@ -22389,7 +22389,7 @@
         <v>29</v>
       </c>
       <c r="D1077">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1077" t="s">
         <v>30</v>
@@ -22406,7 +22406,7 @@
         <v>29</v>
       </c>
       <c r="D1078">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1078" t="s">
         <v>30</v>
@@ -22423,7 +22423,7 @@
         <v>29</v>
       </c>
       <c r="D1079">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E1079" t="s">
         <v>30</v>
@@ -22440,7 +22440,7 @@
         <v>29</v>
       </c>
       <c r="D1080">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E1080" t="s">
         <v>30</v>
@@ -22457,7 +22457,7 @@
         <v>29</v>
       </c>
       <c r="D1081">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E1081" t="s">
         <v>30</v>
@@ -22474,7 +22474,7 @@
         <v>29</v>
       </c>
       <c r="D1082">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E1082" t="s">
         <v>30</v>
@@ -22491,7 +22491,7 @@
         <v>29</v>
       </c>
       <c r="D1083">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1083" t="s">
         <v>30</v>
@@ -22525,7 +22525,7 @@
         <v>29</v>
       </c>
       <c r="D1085">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E1085" t="s">
         <v>30</v>
@@ -22542,7 +22542,7 @@
         <v>29</v>
       </c>
       <c r="D1086">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1086" t="s">
         <v>30</v>
@@ -22559,7 +22559,7 @@
         <v>29</v>
       </c>
       <c r="D1087">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1087" t="s">
         <v>30</v>
@@ -22576,7 +22576,7 @@
         <v>29</v>
       </c>
       <c r="D1088">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E1088" t="s">
         <v>30</v>
@@ -22593,7 +22593,7 @@
         <v>29</v>
       </c>
       <c r="D1089">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1089" t="s">
         <v>30</v>
@@ -22610,7 +22610,7 @@
         <v>29</v>
       </c>
       <c r="D1090">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1090" t="s">
         <v>30</v>
@@ -22627,7 +22627,7 @@
         <v>29</v>
       </c>
       <c r="D1091">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E1091" t="s">
         <v>30</v>
@@ -22644,7 +22644,7 @@
         <v>29</v>
       </c>
       <c r="D1092">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1092" t="s">
         <v>30</v>
@@ -22661,7 +22661,7 @@
         <v>29</v>
       </c>
       <c r="D1093">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E1093" t="s">
         <v>30</v>
@@ -22678,7 +22678,7 @@
         <v>29</v>
       </c>
       <c r="D1094">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E1094" t="s">
         <v>30</v>
@@ -22695,7 +22695,7 @@
         <v>29</v>
       </c>
       <c r="D1095">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1095" t="s">
         <v>30</v>
@@ -22712,7 +22712,7 @@
         <v>29</v>
       </c>
       <c r="D1096">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1096" t="s">
         <v>30</v>
@@ -22729,7 +22729,7 @@
         <v>29</v>
       </c>
       <c r="D1097">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1097" t="s">
         <v>30</v>
@@ -22746,7 +22746,7 @@
         <v>29</v>
       </c>
       <c r="D1098">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E1098" t="s">
         <v>30</v>
@@ -22763,7 +22763,7 @@
         <v>29</v>
       </c>
       <c r="D1099">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E1099" t="s">
         <v>30</v>
@@ -22780,7 +22780,7 @@
         <v>29</v>
       </c>
       <c r="D1100">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E1100" t="s">
         <v>30</v>
@@ -22797,7 +22797,7 @@
         <v>29</v>
       </c>
       <c r="D1101">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1101" t="s">
         <v>30</v>
@@ -22814,7 +22814,7 @@
         <v>29</v>
       </c>
       <c r="D1102">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1102" t="s">
         <v>30</v>
@@ -22831,7 +22831,7 @@
         <v>29</v>
       </c>
       <c r="D1103">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E1103" t="s">
         <v>30</v>
@@ -22848,7 +22848,7 @@
         <v>29</v>
       </c>
       <c r="D1104">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1104" t="s">
         <v>30</v>
@@ -22865,7 +22865,7 @@
         <v>29</v>
       </c>
       <c r="D1105">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E1105" t="s">
         <v>30</v>
@@ -22882,7 +22882,7 @@
         <v>29</v>
       </c>
       <c r="D1106">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1106" t="s">
         <v>30</v>
@@ -22899,7 +22899,7 @@
         <v>29</v>
       </c>
       <c r="D1107">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1107" t="s">
         <v>30</v>
@@ -22916,7 +22916,7 @@
         <v>29</v>
       </c>
       <c r="D1108">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1108" t="s">
         <v>30</v>
@@ -22933,7 +22933,7 @@
         <v>29</v>
       </c>
       <c r="D1109">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1109" t="s">
         <v>30</v>
@@ -22950,7 +22950,7 @@
         <v>29</v>
       </c>
       <c r="D1110">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1110" t="s">
         <v>30</v>
@@ -22967,7 +22967,7 @@
         <v>29</v>
       </c>
       <c r="D1111">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E1111" t="s">
         <v>30</v>
@@ -22984,7 +22984,7 @@
         <v>29</v>
       </c>
       <c r="D1112">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1112" t="s">
         <v>30</v>

--- a/reports/latest/android-report.xlsx
+++ b/reports/latest/android-report.xlsx
@@ -4114,7 +4114,7 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>900</v>
+        <v>1006</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -4131,7 +4131,7 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -4148,7 +4148,7 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -4165,7 +4165,7 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -4182,7 +4182,7 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -4199,7 +4199,7 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -4216,7 +4216,7 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -4233,7 +4233,7 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -4250,7 +4250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
@@ -4267,7 +4267,7 @@
         <v>29</v>
       </c>
       <c r="D11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -4284,7 +4284,7 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -4301,7 +4301,7 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -4318,7 +4318,7 @@
         <v>29</v>
       </c>
       <c r="D14">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4335,7 +4335,7 @@
         <v>29</v>
       </c>
       <c r="D15">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -4352,7 +4352,7 @@
         <v>29</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -4369,7 +4369,7 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -4386,7 +4386,7 @@
         <v>29</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -4403,7 +4403,7 @@
         <v>29</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
@@ -4420,7 +4420,7 @@
         <v>29</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
@@ -4437,7 +4437,7 @@
         <v>29</v>
       </c>
       <c r="D21">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
         <v>30</v>
@@ -4454,7 +4454,7 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
         <v>30</v>
@@ -4471,7 +4471,7 @@
         <v>29</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
         <v>30</v>
@@ -4488,7 +4488,7 @@
         <v>29</v>
       </c>
       <c r="D24">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
         <v>30</v>
@@ -4505,7 +4505,7 @@
         <v>29</v>
       </c>
       <c r="D25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s">
         <v>30</v>
@@ -4522,7 +4522,7 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s">
         <v>30</v>
@@ -4539,7 +4539,7 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
         <v>30</v>
@@ -4556,7 +4556,7 @@
         <v>29</v>
       </c>
       <c r="D28">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
         <v>30</v>
@@ -4573,7 +4573,7 @@
         <v>29</v>
       </c>
       <c r="D29">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
         <v>30</v>
@@ -4590,7 +4590,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E30" t="s">
         <v>30</v>
@@ -4607,7 +4607,7 @@
         <v>29</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
         <v>30</v>
@@ -4624,7 +4624,7 @@
         <v>29</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E32" t="s">
         <v>30</v>
@@ -4641,7 +4641,7 @@
         <v>29</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E33" t="s">
         <v>30</v>
@@ -4658,7 +4658,7 @@
         <v>29</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
         <v>30</v>
@@ -4675,7 +4675,7 @@
         <v>29</v>
       </c>
       <c r="D35">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E35" t="s">
         <v>30</v>
@@ -4692,7 +4692,7 @@
         <v>29</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E36" t="s">
         <v>30</v>
@@ -4709,7 +4709,7 @@
         <v>29</v>
       </c>
       <c r="D37">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E37" t="s">
         <v>30</v>
@@ -4726,7 +4726,7 @@
         <v>29</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E38" t="s">
         <v>30</v>
@@ -4743,7 +4743,7 @@
         <v>29</v>
       </c>
       <c r="D39">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E39" t="s">
         <v>30</v>
@@ -4760,7 +4760,7 @@
         <v>29</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E40" t="s">
         <v>30</v>
@@ -4777,7 +4777,7 @@
         <v>29</v>
       </c>
       <c r="D41">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E41" t="s">
         <v>30</v>
@@ -4794,7 +4794,7 @@
         <v>29</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E42" t="s">
         <v>30</v>
@@ -4811,7 +4811,7 @@
         <v>29</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E43" t="s">
         <v>30</v>
@@ -4828,7 +4828,7 @@
         <v>29</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E44" t="s">
         <v>30</v>
@@ -4845,7 +4845,7 @@
         <v>29</v>
       </c>
       <c r="D45">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
         <v>30</v>
@@ -4862,7 +4862,7 @@
         <v>29</v>
       </c>
       <c r="D46">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
         <v>30</v>
@@ -4879,7 +4879,7 @@
         <v>29</v>
       </c>
       <c r="D47">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
         <v>30</v>
@@ -4896,7 +4896,7 @@
         <v>29</v>
       </c>
       <c r="D48">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E48" t="s">
         <v>30</v>
@@ -4913,7 +4913,7 @@
         <v>29</v>
       </c>
       <c r="D49">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
         <v>30</v>
@@ -4930,7 +4930,7 @@
         <v>29</v>
       </c>
       <c r="D50">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E50" t="s">
         <v>30</v>
@@ -4947,7 +4947,7 @@
         <v>29</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
         <v>30</v>
@@ -4964,7 +4964,7 @@
         <v>29</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
         <v>30</v>
@@ -4981,7 +4981,7 @@
         <v>29</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E53" t="s">
         <v>30</v>
@@ -4998,7 +4998,7 @@
         <v>29</v>
       </c>
       <c r="D54">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E54" t="s">
         <v>30</v>
@@ -5015,7 +5015,7 @@
         <v>29</v>
       </c>
       <c r="D55">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
         <v>30</v>
@@ -5032,7 +5032,7 @@
         <v>29</v>
       </c>
       <c r="D56">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E56" t="s">
         <v>30</v>
@@ -5049,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="D57">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
         <v>30</v>
@@ -5083,7 +5083,7 @@
         <v>29</v>
       </c>
       <c r="D59">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E59" t="s">
         <v>30</v>
@@ -5100,7 +5100,7 @@
         <v>29</v>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E60" t="s">
         <v>30</v>
@@ -5117,7 +5117,7 @@
         <v>29</v>
       </c>
       <c r="D61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E61" t="s">
         <v>30</v>
@@ -5134,7 +5134,7 @@
         <v>29</v>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E62" t="s">
         <v>30</v>
@@ -5151,7 +5151,7 @@
         <v>29</v>
       </c>
       <c r="D63">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E63" t="s">
         <v>30</v>
@@ -5168,7 +5168,7 @@
         <v>29</v>
       </c>
       <c r="D64">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E64" t="s">
         <v>30</v>
@@ -5185,7 +5185,7 @@
         <v>29</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E65" t="s">
         <v>30</v>
@@ -5202,7 +5202,7 @@
         <v>29</v>
       </c>
       <c r="D66">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
         <v>30</v>
@@ -5219,7 +5219,7 @@
         <v>29</v>
       </c>
       <c r="D67">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E67" t="s">
         <v>30</v>
@@ -5236,7 +5236,7 @@
         <v>29</v>
       </c>
       <c r="D68">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
         <v>30</v>
@@ -5253,7 +5253,7 @@
         <v>29</v>
       </c>
       <c r="D69">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E69" t="s">
         <v>30</v>
@@ -5287,7 +5287,7 @@
         <v>29</v>
       </c>
       <c r="D71">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E71" t="s">
         <v>30</v>
@@ -5304,7 +5304,7 @@
         <v>29</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E72" t="s">
         <v>30</v>
@@ -5321,7 +5321,7 @@
         <v>29</v>
       </c>
       <c r="D73">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E73" t="s">
         <v>30</v>
@@ -5338,7 +5338,7 @@
         <v>29</v>
       </c>
       <c r="D74">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E74" t="s">
         <v>30</v>
@@ -5355,7 +5355,7 @@
         <v>29</v>
       </c>
       <c r="D75">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E75" t="s">
         <v>30</v>
@@ -5372,7 +5372,7 @@
         <v>29</v>
       </c>
       <c r="D76">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E76" t="s">
         <v>30</v>
@@ -5389,7 +5389,7 @@
         <v>29</v>
       </c>
       <c r="D77">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E77" t="s">
         <v>30</v>
@@ -5406,7 +5406,7 @@
         <v>29</v>
       </c>
       <c r="D78">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
         <v>30</v>
@@ -5423,7 +5423,7 @@
         <v>29</v>
       </c>
       <c r="D79">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E79" t="s">
         <v>30</v>
@@ -5440,7 +5440,7 @@
         <v>29</v>
       </c>
       <c r="D80">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
         <v>30</v>
@@ -5457,7 +5457,7 @@
         <v>29</v>
       </c>
       <c r="D81">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E81" t="s">
         <v>30</v>
@@ -5474,7 +5474,7 @@
         <v>29</v>
       </c>
       <c r="D82">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E82" t="s">
         <v>30</v>
@@ -5491,7 +5491,7 @@
         <v>29</v>
       </c>
       <c r="D83">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E83" t="s">
         <v>30</v>
@@ -5508,7 +5508,7 @@
         <v>29</v>
       </c>
       <c r="D84">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E84" t="s">
         <v>30</v>
@@ -5525,7 +5525,7 @@
         <v>29</v>
       </c>
       <c r="D85">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E85" t="s">
         <v>30</v>
@@ -5542,7 +5542,7 @@
         <v>29</v>
       </c>
       <c r="D86">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E86" t="s">
         <v>30</v>
@@ -5559,7 +5559,7 @@
         <v>29</v>
       </c>
       <c r="D87">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E87" t="s">
         <v>30</v>
@@ -5593,7 +5593,7 @@
         <v>29</v>
       </c>
       <c r="D89">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E89" t="s">
         <v>30</v>
@@ -5610,7 +5610,7 @@
         <v>29</v>
       </c>
       <c r="D90">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E90" t="s">
         <v>30</v>
@@ -5627,7 +5627,7 @@
         <v>29</v>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E91" t="s">
         <v>30</v>
@@ -5644,7 +5644,7 @@
         <v>29</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E92" t="s">
         <v>30</v>
@@ -5661,7 +5661,7 @@
         <v>29</v>
       </c>
       <c r="D93">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E93" t="s">
         <v>30</v>
@@ -5678,7 +5678,7 @@
         <v>29</v>
       </c>
       <c r="D94">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E94" t="s">
         <v>30</v>
@@ -5695,7 +5695,7 @@
         <v>29</v>
       </c>
       <c r="D95">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E95" t="s">
         <v>30</v>
@@ -5712,7 +5712,7 @@
         <v>29</v>
       </c>
       <c r="D96">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
         <v>30</v>
@@ -5729,7 +5729,7 @@
         <v>29</v>
       </c>
       <c r="D97">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E97" t="s">
         <v>30</v>
@@ -5746,7 +5746,7 @@
         <v>29</v>
       </c>
       <c r="D98">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E98" t="s">
         <v>30</v>
@@ -5763,7 +5763,7 @@
         <v>29</v>
       </c>
       <c r="D99">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E99" t="s">
         <v>30</v>
@@ -5780,7 +5780,7 @@
         <v>29</v>
       </c>
       <c r="D100">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E100" t="s">
         <v>30</v>
@@ -5797,7 +5797,7 @@
         <v>29</v>
       </c>
       <c r="D101">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E101" t="s">
         <v>30</v>
@@ -5814,7 +5814,7 @@
         <v>29</v>
       </c>
       <c r="D102">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E102" t="s">
         <v>30</v>
@@ -5831,7 +5831,7 @@
         <v>29</v>
       </c>
       <c r="D103">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E103" t="s">
         <v>30</v>
@@ -5848,7 +5848,7 @@
         <v>29</v>
       </c>
       <c r="D104">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E104" t="s">
         <v>30</v>
@@ -5865,7 +5865,7 @@
         <v>29</v>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E105" t="s">
         <v>30</v>
@@ -5882,7 +5882,7 @@
         <v>29</v>
       </c>
       <c r="D106">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E106" t="s">
         <v>30</v>
@@ -5899,7 +5899,7 @@
         <v>29</v>
       </c>
       <c r="D107">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E107" t="s">
         <v>30</v>
@@ -5916,7 +5916,7 @@
         <v>29</v>
       </c>
       <c r="D108">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
         <v>30</v>
@@ -5933,7 +5933,7 @@
         <v>29</v>
       </c>
       <c r="D109">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E109" t="s">
         <v>30</v>
@@ -5950,7 +5950,7 @@
         <v>29</v>
       </c>
       <c r="D110">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E110" t="s">
         <v>30</v>
@@ -5967,7 +5967,7 @@
         <v>29</v>
       </c>
       <c r="D111">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
         <v>30</v>
@@ -5984,7 +5984,7 @@
         <v>29</v>
       </c>
       <c r="D112">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E112" t="s">
         <v>30</v>
@@ -6001,7 +6001,7 @@
         <v>29</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E113" t="s">
         <v>30</v>
@@ -6018,7 +6018,7 @@
         <v>29</v>
       </c>
       <c r="D114">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E114" t="s">
         <v>30</v>
@@ -6035,7 +6035,7 @@
         <v>29</v>
       </c>
       <c r="D115">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E115" t="s">
         <v>30</v>
@@ -6052,7 +6052,7 @@
         <v>29</v>
       </c>
       <c r="D116">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E116" t="s">
         <v>30</v>
@@ -6086,7 +6086,7 @@
         <v>29</v>
       </c>
       <c r="D118">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E118" t="s">
         <v>30</v>
@@ -6103,7 +6103,7 @@
         <v>29</v>
       </c>
       <c r="D119">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E119" t="s">
         <v>30</v>
@@ -6120,7 +6120,7 @@
         <v>29</v>
       </c>
       <c r="D120">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E120" t="s">
         <v>30</v>
@@ -6137,7 +6137,7 @@
         <v>29</v>
       </c>
       <c r="D121">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E121" t="s">
         <v>30</v>
@@ -6154,7 +6154,7 @@
         <v>29</v>
       </c>
       <c r="D122">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E122" t="s">
         <v>30</v>
@@ -6171,7 +6171,7 @@
         <v>29</v>
       </c>
       <c r="D123">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E123" t="s">
         <v>30</v>
@@ -6205,7 +6205,7 @@
         <v>29</v>
       </c>
       <c r="D125">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E125" t="s">
         <v>30</v>
@@ -6222,7 +6222,7 @@
         <v>29</v>
       </c>
       <c r="D126">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E126" t="s">
         <v>30</v>
@@ -6239,7 +6239,7 @@
         <v>29</v>
       </c>
       <c r="D127">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E127" t="s">
         <v>30</v>
@@ -6256,7 +6256,7 @@
         <v>29</v>
       </c>
       <c r="D128">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E128" t="s">
         <v>30</v>
@@ -6273,7 +6273,7 @@
         <v>29</v>
       </c>
       <c r="D129">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E129" t="s">
         <v>30</v>
@@ -6290,7 +6290,7 @@
         <v>29</v>
       </c>
       <c r="D130">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E130" t="s">
         <v>30</v>
@@ -6307,7 +6307,7 @@
         <v>29</v>
       </c>
       <c r="D131">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E131" t="s">
         <v>30</v>
@@ -6324,7 +6324,7 @@
         <v>29</v>
       </c>
       <c r="D132">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E132" t="s">
         <v>30</v>
@@ -6341,7 +6341,7 @@
         <v>29</v>
       </c>
       <c r="D133">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E133" t="s">
         <v>30</v>
@@ -6358,7 +6358,7 @@
         <v>29</v>
       </c>
       <c r="D134">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E134" t="s">
         <v>30</v>
@@ -6375,7 +6375,7 @@
         <v>29</v>
       </c>
       <c r="D135">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E135" t="s">
         <v>30</v>
@@ -6409,7 +6409,7 @@
         <v>29</v>
       </c>
       <c r="D137">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E137" t="s">
         <v>30</v>
@@ -6443,7 +6443,7 @@
         <v>29</v>
       </c>
       <c r="D139">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E139" t="s">
         <v>30</v>
@@ -6477,7 +6477,7 @@
         <v>29</v>
       </c>
       <c r="D141">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E141" t="s">
         <v>30</v>
@@ -6494,7 +6494,7 @@
         <v>29</v>
       </c>
       <c r="D142">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E142" t="s">
         <v>30</v>
@@ -6511,7 +6511,7 @@
         <v>29</v>
       </c>
       <c r="D143">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E143" t="s">
         <v>30</v>
@@ -6528,7 +6528,7 @@
         <v>29</v>
       </c>
       <c r="D144">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E144" t="s">
         <v>30</v>
@@ -6545,7 +6545,7 @@
         <v>29</v>
       </c>
       <c r="D145">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E145" t="s">
         <v>30</v>
@@ -6562,7 +6562,7 @@
         <v>29</v>
       </c>
       <c r="D146">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E146" t="s">
         <v>30</v>
@@ -6579,7 +6579,7 @@
         <v>29</v>
       </c>
       <c r="D147">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E147" t="s">
         <v>30</v>
@@ -6613,7 +6613,7 @@
         <v>29</v>
       </c>
       <c r="D149">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E149" t="s">
         <v>30</v>
@@ -6630,7 +6630,7 @@
         <v>29</v>
       </c>
       <c r="D150">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E150" t="s">
         <v>30</v>
@@ -6681,7 +6681,7 @@
         <v>29</v>
       </c>
       <c r="D153">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E153" t="s">
         <v>30</v>
@@ -6698,7 +6698,7 @@
         <v>29</v>
       </c>
       <c r="D154">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E154" t="s">
         <v>30</v>
@@ -6715,7 +6715,7 @@
         <v>29</v>
       </c>
       <c r="D155">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E155" t="s">
         <v>30</v>
@@ -6732,7 +6732,7 @@
         <v>29</v>
       </c>
       <c r="D156">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E156" t="s">
         <v>30</v>
@@ -6749,7 +6749,7 @@
         <v>29</v>
       </c>
       <c r="D157">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E157" t="s">
         <v>30</v>
@@ -6766,7 +6766,7 @@
         <v>29</v>
       </c>
       <c r="D158">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E158" t="s">
         <v>30</v>
@@ -6783,7 +6783,7 @@
         <v>29</v>
       </c>
       <c r="D159">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E159" t="s">
         <v>30</v>
@@ -6800,7 +6800,7 @@
         <v>29</v>
       </c>
       <c r="D160">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E160" t="s">
         <v>30</v>
@@ -6834,7 +6834,7 @@
         <v>29</v>
       </c>
       <c r="D162">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E162" t="s">
         <v>30</v>
@@ -6851,7 +6851,7 @@
         <v>29</v>
       </c>
       <c r="D163">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E163" t="s">
         <v>30</v>
@@ -6868,7 +6868,7 @@
         <v>29</v>
       </c>
       <c r="D164">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E164" t="s">
         <v>30</v>
@@ -6885,7 +6885,7 @@
         <v>29</v>
       </c>
       <c r="D165">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E165" t="s">
         <v>30</v>
@@ -6902,7 +6902,7 @@
         <v>29</v>
       </c>
       <c r="D166">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E166" t="s">
         <v>30</v>
@@ -6919,7 +6919,7 @@
         <v>29</v>
       </c>
       <c r="D167">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E167" t="s">
         <v>30</v>
@@ -6936,7 +6936,7 @@
         <v>29</v>
       </c>
       <c r="D168">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E168" t="s">
         <v>30</v>
@@ -6953,7 +6953,7 @@
         <v>29</v>
       </c>
       <c r="D169">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E169" t="s">
         <v>30</v>
@@ -6970,7 +6970,7 @@
         <v>29</v>
       </c>
       <c r="D170">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E170" t="s">
         <v>30</v>
@@ -6987,7 +6987,7 @@
         <v>29</v>
       </c>
       <c r="D171">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E171" t="s">
         <v>30</v>
@@ -7004,7 +7004,7 @@
         <v>29</v>
       </c>
       <c r="D172">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
         <v>30</v>
@@ -7021,7 +7021,7 @@
         <v>29</v>
       </c>
       <c r="D173">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E173" t="s">
         <v>30</v>
@@ -7038,7 +7038,7 @@
         <v>29</v>
       </c>
       <c r="D174">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E174" t="s">
         <v>30</v>
@@ -7055,7 +7055,7 @@
         <v>29</v>
       </c>
       <c r="D175">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E175" t="s">
         <v>30</v>
@@ -7072,7 +7072,7 @@
         <v>29</v>
       </c>
       <c r="D176">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E176" t="s">
         <v>30</v>
@@ -7089,7 +7089,7 @@
         <v>29</v>
       </c>
       <c r="D177">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E177" t="s">
         <v>30</v>
@@ -7106,7 +7106,7 @@
         <v>29</v>
       </c>
       <c r="D178">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E178" t="s">
         <v>30</v>
@@ -7123,7 +7123,7 @@
         <v>29</v>
       </c>
       <c r="D179">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E179" t="s">
         <v>30</v>
@@ -7140,7 +7140,7 @@
         <v>29</v>
       </c>
       <c r="D180">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E180" t="s">
         <v>30</v>
@@ -7157,7 +7157,7 @@
         <v>29</v>
       </c>
       <c r="D181">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E181" t="s">
         <v>30</v>
@@ -7174,7 +7174,7 @@
         <v>29</v>
       </c>
       <c r="D182">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E182" t="s">
         <v>30</v>
@@ -7191,7 +7191,7 @@
         <v>29</v>
       </c>
       <c r="D183">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E183" t="s">
         <v>30</v>
@@ -7208,7 +7208,7 @@
         <v>29</v>
       </c>
       <c r="D184">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E184" t="s">
         <v>30</v>
@@ -7225,7 +7225,7 @@
         <v>29</v>
       </c>
       <c r="D185">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E185" t="s">
         <v>30</v>
@@ -7242,7 +7242,7 @@
         <v>29</v>
       </c>
       <c r="D186">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E186" t="s">
         <v>30</v>
@@ -7259,7 +7259,7 @@
         <v>29</v>
       </c>
       <c r="D187">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E187" t="s">
         <v>30</v>
@@ -7276,7 +7276,7 @@
         <v>29</v>
       </c>
       <c r="D188">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E188" t="s">
         <v>30</v>
@@ -7293,7 +7293,7 @@
         <v>29</v>
       </c>
       <c r="D189">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E189" t="s">
         <v>30</v>
@@ -7310,7 +7310,7 @@
         <v>29</v>
       </c>
       <c r="D190">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E190" t="s">
         <v>30</v>
@@ -7327,7 +7327,7 @@
         <v>29</v>
       </c>
       <c r="D191">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E191" t="s">
         <v>30</v>
@@ -7344,7 +7344,7 @@
         <v>29</v>
       </c>
       <c r="D192">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E192" t="s">
         <v>30</v>
@@ -7361,7 +7361,7 @@
         <v>29</v>
       </c>
       <c r="D193">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E193" t="s">
         <v>30</v>
@@ -7378,7 +7378,7 @@
         <v>29</v>
       </c>
       <c r="D194">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E194" t="s">
         <v>30</v>
@@ -7395,7 +7395,7 @@
         <v>29</v>
       </c>
       <c r="D195">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E195" t="s">
         <v>30</v>
@@ -7412,7 +7412,7 @@
         <v>29</v>
       </c>
       <c r="D196">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E196" t="s">
         <v>30</v>
@@ -7429,7 +7429,7 @@
         <v>29</v>
       </c>
       <c r="D197">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E197" t="s">
         <v>30</v>
@@ -7446,7 +7446,7 @@
         <v>29</v>
       </c>
       <c r="D198">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E198" t="s">
         <v>30</v>
@@ -7463,7 +7463,7 @@
         <v>29</v>
       </c>
       <c r="D199">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E199" t="s">
         <v>30</v>
@@ -7480,7 +7480,7 @@
         <v>29</v>
       </c>
       <c r="D200">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E200" t="s">
         <v>30</v>
@@ -7497,7 +7497,7 @@
         <v>29</v>
       </c>
       <c r="D201">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E201" t="s">
         <v>30</v>
@@ -7514,7 +7514,7 @@
         <v>29</v>
       </c>
       <c r="D202">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E202" t="s">
         <v>30</v>
@@ -7531,7 +7531,7 @@
         <v>29</v>
       </c>
       <c r="D203">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E203" t="s">
         <v>30</v>
@@ -7548,7 +7548,7 @@
         <v>29</v>
       </c>
       <c r="D204">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E204" t="s">
         <v>30</v>
@@ -7565,7 +7565,7 @@
         <v>29</v>
       </c>
       <c r="D205">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E205" t="s">
         <v>30</v>
@@ -7582,7 +7582,7 @@
         <v>29</v>
       </c>
       <c r="D206">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E206" t="s">
         <v>30</v>
@@ -7599,7 +7599,7 @@
         <v>29</v>
       </c>
       <c r="D207">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E207" t="s">
         <v>30</v>
@@ -7616,7 +7616,7 @@
         <v>29</v>
       </c>
       <c r="D208">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E208" t="s">
         <v>30</v>
@@ -7633,7 +7633,7 @@
         <v>29</v>
       </c>
       <c r="D209">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E209" t="s">
         <v>30</v>
@@ -7650,7 +7650,7 @@
         <v>29</v>
       </c>
       <c r="D210">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E210" t="s">
         <v>30</v>
@@ -7667,7 +7667,7 @@
         <v>29</v>
       </c>
       <c r="D211">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E211" t="s">
         <v>30</v>
@@ -7684,7 +7684,7 @@
         <v>29</v>
       </c>
       <c r="D212">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E212" t="s">
         <v>30</v>
@@ -7701,7 +7701,7 @@
         <v>29</v>
       </c>
       <c r="D213">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E213" t="s">
         <v>30</v>
@@ -7718,7 +7718,7 @@
         <v>29</v>
       </c>
       <c r="D214">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E214" t="s">
         <v>30</v>
@@ -7735,7 +7735,7 @@
         <v>29</v>
       </c>
       <c r="D215">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E215" t="s">
         <v>30</v>
@@ -7752,7 +7752,7 @@
         <v>29</v>
       </c>
       <c r="D216">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E216" t="s">
         <v>30</v>
@@ -7769,7 +7769,7 @@
         <v>29</v>
       </c>
       <c r="D217">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E217" t="s">
         <v>30</v>
@@ -7786,7 +7786,7 @@
         <v>29</v>
       </c>
       <c r="D218">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E218" t="s">
         <v>30</v>
@@ -7803,7 +7803,7 @@
         <v>29</v>
       </c>
       <c r="D219">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E219" t="s">
         <v>30</v>
@@ -7837,7 +7837,7 @@
         <v>29</v>
       </c>
       <c r="D221">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E221" t="s">
         <v>30</v>
@@ -7854,7 +7854,7 @@
         <v>29</v>
       </c>
       <c r="D222">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E222" t="s">
         <v>30</v>
@@ -7871,7 +7871,7 @@
         <v>29</v>
       </c>
       <c r="D223">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E223" t="s">
         <v>30</v>
@@ -7888,7 +7888,7 @@
         <v>29</v>
       </c>
       <c r="D224">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E224" t="s">
         <v>30</v>
@@ -7905,7 +7905,7 @@
         <v>29</v>
       </c>
       <c r="D225">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E225" t="s">
         <v>30</v>
@@ -7922,7 +7922,7 @@
         <v>29</v>
       </c>
       <c r="D226">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E226" t="s">
         <v>30</v>
@@ -7939,7 +7939,7 @@
         <v>29</v>
       </c>
       <c r="D227">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E227" t="s">
         <v>30</v>
@@ -7973,7 +7973,7 @@
         <v>29</v>
       </c>
       <c r="D229">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E229" t="s">
         <v>30</v>
@@ -7990,7 +7990,7 @@
         <v>29</v>
       </c>
       <c r="D230">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E230" t="s">
         <v>30</v>
@@ -8007,7 +8007,7 @@
         <v>29</v>
       </c>
       <c r="D231">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E231" t="s">
         <v>30</v>
@@ -8024,7 +8024,7 @@
         <v>29</v>
       </c>
       <c r="D232">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E232" t="s">
         <v>30</v>
@@ -8041,7 +8041,7 @@
         <v>29</v>
       </c>
       <c r="D233">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E233" t="s">
         <v>30</v>
@@ -8058,7 +8058,7 @@
         <v>29</v>
       </c>
       <c r="D234">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E234" t="s">
         <v>30</v>
@@ -8075,7 +8075,7 @@
         <v>29</v>
       </c>
       <c r="D235">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E235" t="s">
         <v>30</v>
@@ -8092,7 +8092,7 @@
         <v>29</v>
       </c>
       <c r="D236">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E236" t="s">
         <v>30</v>
@@ -8109,7 +8109,7 @@
         <v>29</v>
       </c>
       <c r="D237">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E237" t="s">
         <v>30</v>
@@ -8126,7 +8126,7 @@
         <v>29</v>
       </c>
       <c r="D238">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E238" t="s">
         <v>30</v>
@@ -8143,7 +8143,7 @@
         <v>29</v>
       </c>
       <c r="D239">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E239" t="s">
         <v>30</v>
@@ -8160,7 +8160,7 @@
         <v>29</v>
       </c>
       <c r="D240">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E240" t="s">
         <v>30</v>
@@ -8177,7 +8177,7 @@
         <v>29</v>
       </c>
       <c r="D241">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E241" t="s">
         <v>30</v>
@@ -8194,7 +8194,7 @@
         <v>29</v>
       </c>
       <c r="D242">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E242" t="s">
         <v>30</v>
@@ -8211,7 +8211,7 @@
         <v>29</v>
       </c>
       <c r="D243">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E243" t="s">
         <v>30</v>
@@ -8228,7 +8228,7 @@
         <v>29</v>
       </c>
       <c r="D244">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E244" t="s">
         <v>30</v>
@@ -8245,7 +8245,7 @@
         <v>29</v>
       </c>
       <c r="D245">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E245" t="s">
         <v>30</v>
@@ -8262,7 +8262,7 @@
         <v>29</v>
       </c>
       <c r="D246">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E246" t="s">
         <v>30</v>
@@ -8296,7 +8296,7 @@
         <v>29</v>
       </c>
       <c r="D248">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E248" t="s">
         <v>30</v>
@@ -8313,7 +8313,7 @@
         <v>29</v>
       </c>
       <c r="D249">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E249" t="s">
         <v>30</v>
@@ -8330,7 +8330,7 @@
         <v>29</v>
       </c>
       <c r="D250">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E250" t="s">
         <v>30</v>
@@ -8347,7 +8347,7 @@
         <v>29</v>
       </c>
       <c r="D251">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E251" t="s">
         <v>30</v>
@@ -8364,7 +8364,7 @@
         <v>29</v>
       </c>
       <c r="D252">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E252" t="s">
         <v>30</v>
@@ -8381,7 +8381,7 @@
         <v>29</v>
       </c>
       <c r="D253">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E253" t="s">
         <v>30</v>
@@ -8398,7 +8398,7 @@
         <v>29</v>
       </c>
       <c r="D254">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E254" t="s">
         <v>30</v>
@@ -8415,7 +8415,7 @@
         <v>29</v>
       </c>
       <c r="D255">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E255" t="s">
         <v>30</v>
@@ -8432,7 +8432,7 @@
         <v>29</v>
       </c>
       <c r="D256">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E256" t="s">
         <v>30</v>
@@ -8449,7 +8449,7 @@
         <v>29</v>
       </c>
       <c r="D257">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E257" t="s">
         <v>30</v>
@@ -8466,7 +8466,7 @@
         <v>29</v>
       </c>
       <c r="D258">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E258" t="s">
         <v>30</v>
@@ -8483,7 +8483,7 @@
         <v>29</v>
       </c>
       <c r="D259">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E259" t="s">
         <v>30</v>
@@ -8500,7 +8500,7 @@
         <v>29</v>
       </c>
       <c r="D260">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E260" t="s">
         <v>30</v>
@@ -8517,7 +8517,7 @@
         <v>29</v>
       </c>
       <c r="D261">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E261" t="s">
         <v>30</v>
@@ -8534,7 +8534,7 @@
         <v>29</v>
       </c>
       <c r="D262">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E262" t="s">
         <v>30</v>
@@ -8551,7 +8551,7 @@
         <v>29</v>
       </c>
       <c r="D263">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E263" t="s">
         <v>30</v>
@@ -8568,7 +8568,7 @@
         <v>29</v>
       </c>
       <c r="D264">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E264" t="s">
         <v>30</v>
@@ -8585,7 +8585,7 @@
         <v>29</v>
       </c>
       <c r="D265">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E265" t="s">
         <v>30</v>
@@ -8619,7 +8619,7 @@
         <v>29</v>
       </c>
       <c r="D267">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E267" t="s">
         <v>30</v>
@@ -8636,7 +8636,7 @@
         <v>29</v>
       </c>
       <c r="D268">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E268" t="s">
         <v>30</v>
@@ -8653,7 +8653,7 @@
         <v>29</v>
       </c>
       <c r="D269">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E269" t="s">
         <v>30</v>
@@ -8670,7 +8670,7 @@
         <v>29</v>
       </c>
       <c r="D270">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E270" t="s">
         <v>30</v>
@@ -8704,7 +8704,7 @@
         <v>29</v>
       </c>
       <c r="D272">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E272" t="s">
         <v>30</v>
@@ -8721,7 +8721,7 @@
         <v>29</v>
       </c>
       <c r="D273">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E273" t="s">
         <v>30</v>
@@ -8738,7 +8738,7 @@
         <v>29</v>
       </c>
       <c r="D274">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E274" t="s">
         <v>30</v>
@@ -8755,7 +8755,7 @@
         <v>29</v>
       </c>
       <c r="D275">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E275" t="s">
         <v>30</v>
@@ -8789,7 +8789,7 @@
         <v>29</v>
       </c>
       <c r="D277">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E277" t="s">
         <v>30</v>
@@ -8806,7 +8806,7 @@
         <v>29</v>
       </c>
       <c r="D278">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E278" t="s">
         <v>30</v>
@@ -8823,7 +8823,7 @@
         <v>29</v>
       </c>
       <c r="D279">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E279" t="s">
         <v>30</v>
@@ -8840,7 +8840,7 @@
         <v>29</v>
       </c>
       <c r="D280">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E280" t="s">
         <v>30</v>
@@ -8874,7 +8874,7 @@
         <v>29</v>
       </c>
       <c r="D282">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E282" t="s">
         <v>30</v>
@@ -8891,7 +8891,7 @@
         <v>29</v>
       </c>
       <c r="D283">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E283" t="s">
         <v>30</v>
@@ -8908,7 +8908,7 @@
         <v>29</v>
       </c>
       <c r="D284">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E284" t="s">
         <v>30</v>
@@ -8925,7 +8925,7 @@
         <v>29</v>
       </c>
       <c r="D285">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E285" t="s">
         <v>30</v>
@@ -8942,7 +8942,7 @@
         <v>29</v>
       </c>
       <c r="D286">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E286" t="s">
         <v>30</v>
@@ -8959,7 +8959,7 @@
         <v>29</v>
       </c>
       <c r="D287">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E287" t="s">
         <v>30</v>
@@ -8976,7 +8976,7 @@
         <v>29</v>
       </c>
       <c r="D288">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E288" t="s">
         <v>30</v>
@@ -8993,7 +8993,7 @@
         <v>29</v>
       </c>
       <c r="D289">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E289" t="s">
         <v>30</v>
@@ -9010,7 +9010,7 @@
         <v>29</v>
       </c>
       <c r="D290">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E290" t="s">
         <v>30</v>
@@ -9027,7 +9027,7 @@
         <v>29</v>
       </c>
       <c r="D291">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E291" t="s">
         <v>30</v>
@@ -9044,7 +9044,7 @@
         <v>29</v>
       </c>
       <c r="D292">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E292" t="s">
         <v>30</v>
@@ -9061,7 +9061,7 @@
         <v>29</v>
       </c>
       <c r="D293">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E293" t="s">
         <v>30</v>
@@ -9078,7 +9078,7 @@
         <v>29</v>
       </c>
       <c r="D294">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E294" t="s">
         <v>30</v>
@@ -9095,7 +9095,7 @@
         <v>29</v>
       </c>
       <c r="D295">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E295" t="s">
         <v>30</v>
@@ -9112,7 +9112,7 @@
         <v>29</v>
       </c>
       <c r="D296">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E296" t="s">
         <v>30</v>
@@ -9129,7 +9129,7 @@
         <v>29</v>
       </c>
       <c r="D297">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E297" t="s">
         <v>30</v>
@@ -9146,7 +9146,7 @@
         <v>29</v>
       </c>
       <c r="D298">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E298" t="s">
         <v>30</v>
@@ -9163,7 +9163,7 @@
         <v>29</v>
       </c>
       <c r="D299">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E299" t="s">
         <v>30</v>
@@ -9180,7 +9180,7 @@
         <v>29</v>
       </c>
       <c r="D300">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E300" t="s">
         <v>30</v>
@@ -9197,7 +9197,7 @@
         <v>29</v>
       </c>
       <c r="D301">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E301" t="s">
         <v>30</v>
@@ -9214,7 +9214,7 @@
         <v>29</v>
       </c>
       <c r="D302">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E302" t="s">
         <v>30</v>
@@ -9231,7 +9231,7 @@
         <v>29</v>
       </c>
       <c r="D303">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E303" t="s">
         <v>30</v>
@@ -9248,7 +9248,7 @@
         <v>29</v>
       </c>
       <c r="D304">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E304" t="s">
         <v>30</v>
@@ -9265,7 +9265,7 @@
         <v>29</v>
       </c>
       <c r="D305">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E305" t="s">
         <v>30</v>
@@ -9282,7 +9282,7 @@
         <v>29</v>
       </c>
       <c r="D306">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E306" t="s">
         <v>30</v>
@@ -9299,7 +9299,7 @@
         <v>29</v>
       </c>
       <c r="D307">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E307" t="s">
         <v>30</v>
@@ -9316,7 +9316,7 @@
         <v>29</v>
       </c>
       <c r="D308">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E308" t="s">
         <v>30</v>
@@ -9333,7 +9333,7 @@
         <v>29</v>
       </c>
       <c r="D309">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E309" t="s">
         <v>30</v>
@@ -9350,7 +9350,7 @@
         <v>29</v>
       </c>
       <c r="D310">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E310" t="s">
         <v>30</v>
@@ -9367,7 +9367,7 @@
         <v>29</v>
       </c>
       <c r="D311">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E311" t="s">
         <v>30</v>
@@ -9384,7 +9384,7 @@
         <v>29</v>
       </c>
       <c r="D312">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E312" t="s">
         <v>30</v>
@@ -9401,7 +9401,7 @@
         <v>29</v>
       </c>
       <c r="D313">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E313" t="s">
         <v>30</v>
@@ -9418,7 +9418,7 @@
         <v>29</v>
       </c>
       <c r="D314">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E314" t="s">
         <v>30</v>
@@ -9435,7 +9435,7 @@
         <v>29</v>
       </c>
       <c r="D315">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E315" t="s">
         <v>30</v>
@@ -9452,7 +9452,7 @@
         <v>29</v>
       </c>
       <c r="D316">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E316" t="s">
         <v>30</v>
@@ -9469,7 +9469,7 @@
         <v>29</v>
       </c>
       <c r="D317">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E317" t="s">
         <v>30</v>
@@ -9486,7 +9486,7 @@
         <v>29</v>
       </c>
       <c r="D318">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E318" t="s">
         <v>30</v>
@@ -9503,7 +9503,7 @@
         <v>29</v>
       </c>
       <c r="D319">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E319" t="s">
         <v>30</v>
@@ -9520,7 +9520,7 @@
         <v>29</v>
       </c>
       <c r="D320">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E320" t="s">
         <v>30</v>
@@ -9537,7 +9537,7 @@
         <v>29</v>
       </c>
       <c r="D321">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E321" t="s">
         <v>30</v>
@@ -9554,7 +9554,7 @@
         <v>29</v>
       </c>
       <c r="D322">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E322" t="s">
         <v>30</v>
@@ -9571,7 +9571,7 @@
         <v>29</v>
       </c>
       <c r="D323">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E323" t="s">
         <v>30</v>
@@ -9588,7 +9588,7 @@
         <v>29</v>
       </c>
       <c r="D324">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E324" t="s">
         <v>30</v>
@@ -9605,7 +9605,7 @@
         <v>29</v>
       </c>
       <c r="D325">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E325" t="s">
         <v>30</v>
@@ -9622,7 +9622,7 @@
         <v>29</v>
       </c>
       <c r="D326">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E326" t="s">
         <v>30</v>
@@ -9639,7 +9639,7 @@
         <v>29</v>
       </c>
       <c r="D327">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E327" t="s">
         <v>30</v>
@@ -9656,7 +9656,7 @@
         <v>29</v>
       </c>
       <c r="D328">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E328" t="s">
         <v>30</v>
@@ -9673,7 +9673,7 @@
         <v>29</v>
       </c>
       <c r="D329">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E329" t="s">
         <v>30</v>
@@ -9690,7 +9690,7 @@
         <v>29</v>
       </c>
       <c r="D330">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E330" t="s">
         <v>30</v>
@@ -9707,7 +9707,7 @@
         <v>29</v>
       </c>
       <c r="D331">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E331" t="s">
         <v>30</v>
@@ -9724,7 +9724,7 @@
         <v>29</v>
       </c>
       <c r="D332">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E332" t="s">
         <v>30</v>
@@ -9741,7 +9741,7 @@
         <v>29</v>
       </c>
       <c r="D333">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E333" t="s">
         <v>30</v>
@@ -9758,7 +9758,7 @@
         <v>29</v>
       </c>
       <c r="D334">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E334" t="s">
         <v>30</v>
@@ -9775,7 +9775,7 @@
         <v>29</v>
       </c>
       <c r="D335">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E335" t="s">
         <v>30</v>
@@ -9792,7 +9792,7 @@
         <v>29</v>
       </c>
       <c r="D336">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E336" t="s">
         <v>30</v>
@@ -9809,7 +9809,7 @@
         <v>29</v>
       </c>
       <c r="D337">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E337" t="s">
         <v>30</v>
@@ -9826,7 +9826,7 @@
         <v>29</v>
       </c>
       <c r="D338">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E338" t="s">
         <v>30</v>
@@ -9843,7 +9843,7 @@
         <v>29</v>
       </c>
       <c r="D339">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E339" t="s">
         <v>30</v>
@@ -9877,7 +9877,7 @@
         <v>29</v>
       </c>
       <c r="D341">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E341" t="s">
         <v>30</v>
@@ -9894,7 +9894,7 @@
         <v>29</v>
       </c>
       <c r="D342">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E342" t="s">
         <v>30</v>
@@ -9911,7 +9911,7 @@
         <v>29</v>
       </c>
       <c r="D343">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E343" t="s">
         <v>30</v>
@@ -9928,7 +9928,7 @@
         <v>29</v>
       </c>
       <c r="D344">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E344" t="s">
         <v>30</v>
@@ -9945,7 +9945,7 @@
         <v>29</v>
       </c>
       <c r="D345">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E345" t="s">
         <v>30</v>
@@ -9962,7 +9962,7 @@
         <v>29</v>
       </c>
       <c r="D346">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E346" t="s">
         <v>30</v>
@@ -9979,7 +9979,7 @@
         <v>29</v>
       </c>
       <c r="D347">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E347" t="s">
         <v>30</v>
@@ -9996,7 +9996,7 @@
         <v>29</v>
       </c>
       <c r="D348">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E348" t="s">
         <v>30</v>
@@ -10013,7 +10013,7 @@
         <v>29</v>
       </c>
       <c r="D349">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E349" t="s">
         <v>30</v>
@@ -10030,7 +10030,7 @@
         <v>29</v>
       </c>
       <c r="D350">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E350" t="s">
         <v>30</v>
@@ -10064,7 +10064,7 @@
         <v>29</v>
       </c>
       <c r="D352">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E352" t="s">
         <v>30</v>
@@ -10081,7 +10081,7 @@
         <v>29</v>
       </c>
       <c r="D353">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E353" t="s">
         <v>30</v>
@@ -10098,7 +10098,7 @@
         <v>29</v>
       </c>
       <c r="D354">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E354" t="s">
         <v>30</v>
@@ -10115,7 +10115,7 @@
         <v>29</v>
       </c>
       <c r="D355">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E355" t="s">
         <v>30</v>
@@ -10132,7 +10132,7 @@
         <v>29</v>
       </c>
       <c r="D356">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E356" t="s">
         <v>30</v>
@@ -10149,7 +10149,7 @@
         <v>29</v>
       </c>
       <c r="D357">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E357" t="s">
         <v>30</v>
@@ -10166,7 +10166,7 @@
         <v>29</v>
       </c>
       <c r="D358">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E358" t="s">
         <v>30</v>
@@ -10183,7 +10183,7 @@
         <v>29</v>
       </c>
       <c r="D359">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E359" t="s">
         <v>30</v>
@@ -10200,7 +10200,7 @@
         <v>29</v>
       </c>
       <c r="D360">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E360" t="s">
         <v>30</v>
@@ -10217,7 +10217,7 @@
         <v>29</v>
       </c>
       <c r="D361">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E361" t="s">
         <v>30</v>
@@ -10234,7 +10234,7 @@
         <v>29</v>
       </c>
       <c r="D362">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E362" t="s">
         <v>30</v>
@@ -10251,7 +10251,7 @@
         <v>29</v>
       </c>
       <c r="D363">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E363" t="s">
         <v>30</v>
@@ -10268,7 +10268,7 @@
         <v>29</v>
       </c>
       <c r="D364">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E364" t="s">
         <v>30</v>
@@ -10285,7 +10285,7 @@
         <v>29</v>
       </c>
       <c r="D365">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E365" t="s">
         <v>30</v>
@@ -10302,7 +10302,7 @@
         <v>29</v>
       </c>
       <c r="D366">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E366" t="s">
         <v>30</v>
@@ -10319,7 +10319,7 @@
         <v>29</v>
       </c>
       <c r="D367">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E367" t="s">
         <v>30</v>
@@ -10336,7 +10336,7 @@
         <v>29</v>
       </c>
       <c r="D368">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E368" t="s">
         <v>30</v>
@@ -10353,7 +10353,7 @@
         <v>29</v>
       </c>
       <c r="D369">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E369" t="s">
         <v>30</v>
@@ -10370,7 +10370,7 @@
         <v>29</v>
       </c>
       <c r="D370">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E370" t="s">
         <v>30</v>
@@ -10387,7 +10387,7 @@
         <v>29</v>
       </c>
       <c r="D371">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E371" t="s">
         <v>30</v>
@@ -10404,7 +10404,7 @@
         <v>29</v>
       </c>
       <c r="D372">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E372" t="s">
         <v>30</v>
@@ -10421,7 +10421,7 @@
         <v>29</v>
       </c>
       <c r="D373">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E373" t="s">
         <v>30</v>
@@ -10438,7 +10438,7 @@
         <v>29</v>
       </c>
       <c r="D374">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E374" t="s">
         <v>30</v>
@@ -10455,7 +10455,7 @@
         <v>29</v>
       </c>
       <c r="D375">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E375" t="s">
         <v>30</v>
@@ -10472,7 +10472,7 @@
         <v>29</v>
       </c>
       <c r="D376">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E376" t="s">
         <v>30</v>
@@ -10489,7 +10489,7 @@
         <v>29</v>
       </c>
       <c r="D377">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E377" t="s">
         <v>30</v>
@@ -10506,7 +10506,7 @@
         <v>29</v>
       </c>
       <c r="D378">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E378" t="s">
         <v>30</v>
@@ -10523,7 +10523,7 @@
         <v>29</v>
       </c>
       <c r="D379">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E379" t="s">
         <v>30</v>
@@ -10540,7 +10540,7 @@
         <v>29</v>
       </c>
       <c r="D380">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E380" t="s">
         <v>30</v>
@@ -10557,7 +10557,7 @@
         <v>29</v>
       </c>
       <c r="D381">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E381" t="s">
         <v>30</v>
@@ -10574,7 +10574,7 @@
         <v>29</v>
       </c>
       <c r="D382">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E382" t="s">
         <v>30</v>
@@ -10591,7 +10591,7 @@
         <v>29</v>
       </c>
       <c r="D383">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E383" t="s">
         <v>30</v>
@@ -10608,7 +10608,7 @@
         <v>29</v>
       </c>
       <c r="D384">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E384" t="s">
         <v>30</v>
@@ -10625,7 +10625,7 @@
         <v>29</v>
       </c>
       <c r="D385">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E385" t="s">
         <v>30</v>
@@ -10642,7 +10642,7 @@
         <v>29</v>
       </c>
       <c r="D386">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E386" t="s">
         <v>30</v>
@@ -10676,7 +10676,7 @@
         <v>29</v>
       </c>
       <c r="D388">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E388" t="s">
         <v>30</v>
@@ -10693,7 +10693,7 @@
         <v>29</v>
       </c>
       <c r="D389">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E389" t="s">
         <v>30</v>
@@ -10710,7 +10710,7 @@
         <v>29</v>
       </c>
       <c r="D390">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E390" t="s">
         <v>30</v>
@@ -10727,7 +10727,7 @@
         <v>29</v>
       </c>
       <c r="D391">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E391" t="s">
         <v>30</v>
@@ -10744,7 +10744,7 @@
         <v>29</v>
       </c>
       <c r="D392">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E392" t="s">
         <v>30</v>
@@ -10761,7 +10761,7 @@
         <v>29</v>
       </c>
       <c r="D393">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E393" t="s">
         <v>30</v>
@@ -10778,7 +10778,7 @@
         <v>29</v>
       </c>
       <c r="D394">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E394" t="s">
         <v>30</v>
@@ -10795,7 +10795,7 @@
         <v>29</v>
       </c>
       <c r="D395">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E395" t="s">
         <v>30</v>
@@ -10812,7 +10812,7 @@
         <v>29</v>
       </c>
       <c r="D396">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E396" t="s">
         <v>30</v>
@@ -10829,7 +10829,7 @@
         <v>29</v>
       </c>
       <c r="D397">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E397" t="s">
         <v>30</v>
@@ -10846,7 +10846,7 @@
         <v>29</v>
       </c>
       <c r="D398">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E398" t="s">
         <v>30</v>
@@ -10880,7 +10880,7 @@
         <v>29</v>
       </c>
       <c r="D400">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E400" t="s">
         <v>30</v>
@@ -10897,7 +10897,7 @@
         <v>29</v>
       </c>
       <c r="D401">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" t="s">
         <v>30</v>
@@ -10931,7 +10931,7 @@
         <v>29</v>
       </c>
       <c r="D403">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E403" t="s">
         <v>30</v>
@@ -10948,7 +10948,7 @@
         <v>29</v>
       </c>
       <c r="D404">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E404" t="s">
         <v>30</v>
@@ -10965,7 +10965,7 @@
         <v>29</v>
       </c>
       <c r="D405">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E405" t="s">
         <v>30</v>
@@ -10982,7 +10982,7 @@
         <v>29</v>
       </c>
       <c r="D406">
-        <v>14</v>
+        <v>434</v>
       </c>
       <c r="E406" t="s">
         <v>30</v>
@@ -10999,7 +10999,7 @@
         <v>29</v>
       </c>
       <c r="D407">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E407" t="s">
         <v>30</v>
@@ -11016,7 +11016,7 @@
         <v>29</v>
       </c>
       <c r="D408">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E408" t="s">
         <v>30</v>
@@ -11033,7 +11033,7 @@
         <v>29</v>
       </c>
       <c r="D409">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E409" t="s">
         <v>30</v>
@@ -11050,7 +11050,7 @@
         <v>29</v>
       </c>
       <c r="D410">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E410" t="s">
         <v>30</v>
@@ -11067,7 +11067,7 @@
         <v>29</v>
       </c>
       <c r="D411">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E411" t="s">
         <v>30</v>
@@ -11084,7 +11084,7 @@
         <v>29</v>
       </c>
       <c r="D412">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E412" t="s">
         <v>30</v>
@@ -11101,7 +11101,7 @@
         <v>29</v>
       </c>
       <c r="D413">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E413" t="s">
         <v>30</v>
@@ -11118,7 +11118,7 @@
         <v>29</v>
       </c>
       <c r="D414">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E414" t="s">
         <v>30</v>
@@ -11135,7 +11135,7 @@
         <v>29</v>
       </c>
       <c r="D415">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E415" t="s">
         <v>30</v>
@@ -11152,7 +11152,7 @@
         <v>29</v>
       </c>
       <c r="D416">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E416" t="s">
         <v>30</v>
@@ -11169,7 +11169,7 @@
         <v>29</v>
       </c>
       <c r="D417">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E417" t="s">
         <v>30</v>
@@ -11186,7 +11186,7 @@
         <v>29</v>
       </c>
       <c r="D418">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E418" t="s">
         <v>30</v>
@@ -11203,7 +11203,7 @@
         <v>29</v>
       </c>
       <c r="D419">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E419" t="s">
         <v>30</v>
@@ -11220,7 +11220,7 @@
         <v>29</v>
       </c>
       <c r="D420">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E420" t="s">
         <v>30</v>
@@ -11237,7 +11237,7 @@
         <v>29</v>
       </c>
       <c r="D421">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E421" t="s">
         <v>30</v>
@@ -11254,7 +11254,7 @@
         <v>29</v>
       </c>
       <c r="D422">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E422" t="s">
         <v>30</v>
@@ -11271,7 +11271,7 @@
         <v>29</v>
       </c>
       <c r="D423">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E423" t="s">
         <v>30</v>
@@ -11288,7 +11288,7 @@
         <v>29</v>
       </c>
       <c r="D424">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E424" t="s">
         <v>30</v>
@@ -11305,7 +11305,7 @@
         <v>29</v>
       </c>
       <c r="D425">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E425" t="s">
         <v>30</v>
@@ -11339,7 +11339,7 @@
         <v>29</v>
       </c>
       <c r="D427">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E427" t="s">
         <v>30</v>
@@ -11356,7 +11356,7 @@
         <v>29</v>
       </c>
       <c r="D428">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E428" t="s">
         <v>30</v>
@@ -11373,7 +11373,7 @@
         <v>29</v>
       </c>
       <c r="D429">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E429" t="s">
         <v>30</v>
@@ -11390,7 +11390,7 @@
         <v>29</v>
       </c>
       <c r="D430">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E430" t="s">
         <v>30</v>
@@ -11407,7 +11407,7 @@
         <v>29</v>
       </c>
       <c r="D431">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E431" t="s">
         <v>30</v>
@@ -11424,7 +11424,7 @@
         <v>29</v>
       </c>
       <c r="D432">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E432" t="s">
         <v>30</v>
@@ -11441,7 +11441,7 @@
         <v>29</v>
       </c>
       <c r="D433">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E433" t="s">
         <v>30</v>
@@ -11475,7 +11475,7 @@
         <v>29</v>
       </c>
       <c r="D435">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E435" t="s">
         <v>30</v>
@@ -11492,7 +11492,7 @@
         <v>29</v>
       </c>
       <c r="D436">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E436" t="s">
         <v>30</v>
@@ -11509,7 +11509,7 @@
         <v>29</v>
       </c>
       <c r="D437">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E437" t="s">
         <v>30</v>
@@ -11526,7 +11526,7 @@
         <v>29</v>
       </c>
       <c r="D438">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E438" t="s">
         <v>30</v>
@@ -11543,7 +11543,7 @@
         <v>29</v>
       </c>
       <c r="D439">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E439" t="s">
         <v>30</v>
@@ -11560,7 +11560,7 @@
         <v>29</v>
       </c>
       <c r="D440">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E440" t="s">
         <v>30</v>
@@ -11577,7 +11577,7 @@
         <v>29</v>
       </c>
       <c r="D441">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E441" t="s">
         <v>30</v>
@@ -11594,7 +11594,7 @@
         <v>29</v>
       </c>
       <c r="D442">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E442" t="s">
         <v>30</v>
@@ -11611,7 +11611,7 @@
         <v>29</v>
       </c>
       <c r="D443">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E443" t="s">
         <v>30</v>
@@ -11628,7 +11628,7 @@
         <v>29</v>
       </c>
       <c r="D444">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E444" t="s">
         <v>30</v>
@@ -11645,7 +11645,7 @@
         <v>29</v>
       </c>
       <c r="D445">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E445" t="s">
         <v>30</v>
@@ -11662,7 +11662,7 @@
         <v>29</v>
       </c>
       <c r="D446">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E446" t="s">
         <v>30</v>
@@ -11679,7 +11679,7 @@
         <v>29</v>
       </c>
       <c r="D447">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E447" t="s">
         <v>30</v>
@@ -11696,7 +11696,7 @@
         <v>29</v>
       </c>
       <c r="D448">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E448" t="s">
         <v>30</v>
@@ -11713,7 +11713,7 @@
         <v>29</v>
       </c>
       <c r="D449">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E449" t="s">
         <v>30</v>
@@ -11730,7 +11730,7 @@
         <v>29</v>
       </c>
       <c r="D450">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E450" t="s">
         <v>30</v>
@@ -11747,7 +11747,7 @@
         <v>29</v>
       </c>
       <c r="D451">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E451" t="s">
         <v>30</v>
@@ -11764,7 +11764,7 @@
         <v>29</v>
       </c>
       <c r="D452">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E452" t="s">
         <v>30</v>
@@ -11781,7 +11781,7 @@
         <v>29</v>
       </c>
       <c r="D453">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E453" t="s">
         <v>30</v>
@@ -11798,7 +11798,7 @@
         <v>29</v>
       </c>
       <c r="D454">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E454" t="s">
         <v>30</v>
@@ -11815,7 +11815,7 @@
         <v>29</v>
       </c>
       <c r="D455">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E455" t="s">
         <v>30</v>
@@ -11832,7 +11832,7 @@
         <v>29</v>
       </c>
       <c r="D456">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E456" t="s">
         <v>30</v>
@@ -11849,7 +11849,7 @@
         <v>29</v>
       </c>
       <c r="D457">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E457" t="s">
         <v>30</v>
@@ -11866,7 +11866,7 @@
         <v>29</v>
       </c>
       <c r="D458">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E458" t="s">
         <v>30</v>
@@ -11883,7 +11883,7 @@
         <v>29</v>
       </c>
       <c r="D459">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E459" t="s">
         <v>30</v>
@@ -11900,7 +11900,7 @@
         <v>29</v>
       </c>
       <c r="D460">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E460" t="s">
         <v>30</v>
@@ -11917,7 +11917,7 @@
         <v>29</v>
       </c>
       <c r="D461">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E461" t="s">
         <v>30</v>
@@ -11934,7 +11934,7 @@
         <v>29</v>
       </c>
       <c r="D462">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E462" t="s">
         <v>30</v>
@@ -11951,7 +11951,7 @@
         <v>29</v>
       </c>
       <c r="D463">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E463" t="s">
         <v>30</v>
@@ -11968,7 +11968,7 @@
         <v>29</v>
       </c>
       <c r="D464">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E464" t="s">
         <v>30</v>
@@ -11985,7 +11985,7 @@
         <v>29</v>
       </c>
       <c r="D465">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E465" t="s">
         <v>30</v>
@@ -12002,7 +12002,7 @@
         <v>29</v>
       </c>
       <c r="D466">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E466" t="s">
         <v>30</v>
@@ -12019,7 +12019,7 @@
         <v>29</v>
       </c>
       <c r="D467">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E467" t="s">
         <v>30</v>
@@ -12036,7 +12036,7 @@
         <v>29</v>
       </c>
       <c r="D468">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E468" t="s">
         <v>30</v>
@@ -12053,7 +12053,7 @@
         <v>29</v>
       </c>
       <c r="D469">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E469" t="s">
         <v>30</v>
@@ -12070,7 +12070,7 @@
         <v>29</v>
       </c>
       <c r="D470">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E470" t="s">
         <v>30</v>
@@ -12087,7 +12087,7 @@
         <v>29</v>
       </c>
       <c r="D471">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E471" t="s">
         <v>30</v>
@@ -12104,7 +12104,7 @@
         <v>29</v>
       </c>
       <c r="D472">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E472" t="s">
         <v>30</v>
@@ -12121,7 +12121,7 @@
         <v>29</v>
       </c>
       <c r="D473">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E473" t="s">
         <v>30</v>
@@ -12155,7 +12155,7 @@
         <v>29</v>
       </c>
       <c r="D475">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E475" t="s">
         <v>30</v>
@@ -12172,7 +12172,7 @@
         <v>29</v>
       </c>
       <c r="D476">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E476" t="s">
         <v>30</v>
@@ -12189,7 +12189,7 @@
         <v>29</v>
       </c>
       <c r="D477">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E477" t="s">
         <v>30</v>
@@ -12206,7 +12206,7 @@
         <v>29</v>
       </c>
       <c r="D478">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E478" t="s">
         <v>30</v>
@@ -12223,7 +12223,7 @@
         <v>29</v>
       </c>
       <c r="D479">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E479" t="s">
         <v>30</v>
@@ -12240,7 +12240,7 @@
         <v>29</v>
       </c>
       <c r="D480">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E480" t="s">
         <v>30</v>
@@ -12257,7 +12257,7 @@
         <v>29</v>
       </c>
       <c r="D481">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E481" t="s">
         <v>30</v>
@@ -12274,7 +12274,7 @@
         <v>29</v>
       </c>
       <c r="D482">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E482" t="s">
         <v>30</v>
@@ -12291,7 +12291,7 @@
         <v>29</v>
       </c>
       <c r="D483">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E483" t="s">
         <v>30</v>
@@ -12308,7 +12308,7 @@
         <v>29</v>
       </c>
       <c r="D484">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E484" t="s">
         <v>30</v>
@@ -12325,7 +12325,7 @@
         <v>29</v>
       </c>
       <c r="D485">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E485" t="s">
         <v>30</v>
@@ -12342,7 +12342,7 @@
         <v>29</v>
       </c>
       <c r="D486">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E486" t="s">
         <v>30</v>
@@ -12359,7 +12359,7 @@
         <v>29</v>
       </c>
       <c r="D487">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E487" t="s">
         <v>30</v>
@@ -12376,7 +12376,7 @@
         <v>29</v>
       </c>
       <c r="D488">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E488" t="s">
         <v>30</v>
@@ -12393,7 +12393,7 @@
         <v>29</v>
       </c>
       <c r="D489">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E489" t="s">
         <v>30</v>
@@ -12410,7 +12410,7 @@
         <v>29</v>
       </c>
       <c r="D490">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E490" t="s">
         <v>30</v>
@@ -12427,7 +12427,7 @@
         <v>29</v>
       </c>
       <c r="D491">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E491" t="s">
         <v>30</v>
@@ -12444,7 +12444,7 @@
         <v>29</v>
       </c>
       <c r="D492">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E492" t="s">
         <v>30</v>
@@ -12461,7 +12461,7 @@
         <v>29</v>
       </c>
       <c r="D493">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E493" t="s">
         <v>30</v>
@@ -12478,7 +12478,7 @@
         <v>29</v>
       </c>
       <c r="D494">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E494" t="s">
         <v>30</v>
@@ -12495,7 +12495,7 @@
         <v>29</v>
       </c>
       <c r="D495">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E495" t="s">
         <v>30</v>
@@ -12512,7 +12512,7 @@
         <v>29</v>
       </c>
       <c r="D496">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E496" t="s">
         <v>30</v>
@@ -12529,7 +12529,7 @@
         <v>29</v>
       </c>
       <c r="D497">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E497" t="s">
         <v>30</v>
@@ -12546,7 +12546,7 @@
         <v>29</v>
       </c>
       <c r="D498">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E498" t="s">
         <v>30</v>
@@ -12563,7 +12563,7 @@
         <v>29</v>
       </c>
       <c r="D499">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E499" t="s">
         <v>30</v>
@@ -12580,7 +12580,7 @@
         <v>29</v>
       </c>
       <c r="D500">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E500" t="s">
         <v>30</v>
@@ -12597,7 +12597,7 @@
         <v>29</v>
       </c>
       <c r="D501">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E501" t="s">
         <v>30</v>
@@ -12614,7 +12614,7 @@
         <v>29</v>
       </c>
       <c r="D502">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E502" t="s">
         <v>30</v>
@@ -12631,7 +12631,7 @@
         <v>29</v>
       </c>
       <c r="D503">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E503" t="s">
         <v>30</v>
@@ -12648,7 +12648,7 @@
         <v>29</v>
       </c>
       <c r="D504">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E504" t="s">
         <v>30</v>
@@ -12665,7 +12665,7 @@
         <v>29</v>
       </c>
       <c r="D505">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E505" t="s">
         <v>30</v>
@@ -12682,7 +12682,7 @@
         <v>29</v>
       </c>
       <c r="D506">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E506" t="s">
         <v>30</v>
@@ -12699,7 +12699,7 @@
         <v>29</v>
       </c>
       <c r="D507">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E507" t="s">
         <v>30</v>
@@ -12716,7 +12716,7 @@
         <v>29</v>
       </c>
       <c r="D508">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E508" t="s">
         <v>30</v>
@@ -12733,7 +12733,7 @@
         <v>29</v>
       </c>
       <c r="D509">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E509" t="s">
         <v>30</v>
@@ -12750,7 +12750,7 @@
         <v>29</v>
       </c>
       <c r="D510">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E510" t="s">
         <v>30</v>
@@ -12767,7 +12767,7 @@
         <v>29</v>
       </c>
       <c r="D511">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E511" t="s">
         <v>30</v>
@@ -12784,7 +12784,7 @@
         <v>29</v>
       </c>
       <c r="D512">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E512" t="s">
         <v>30</v>
@@ -12801,7 +12801,7 @@
         <v>29</v>
       </c>
       <c r="D513">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E513" t="s">
         <v>30</v>
@@ -12818,7 +12818,7 @@
         <v>29</v>
       </c>
       <c r="D514">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E514" t="s">
         <v>30</v>
@@ -12835,7 +12835,7 @@
         <v>29</v>
       </c>
       <c r="D515">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E515" t="s">
         <v>30</v>
@@ -12852,7 +12852,7 @@
         <v>29</v>
       </c>
       <c r="D516">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E516" t="s">
         <v>30</v>
@@ -12869,7 +12869,7 @@
         <v>29</v>
       </c>
       <c r="D517">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E517" t="s">
         <v>30</v>
@@ -12886,7 +12886,7 @@
         <v>29</v>
       </c>
       <c r="D518">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E518" t="s">
         <v>30</v>
@@ -12903,7 +12903,7 @@
         <v>29</v>
       </c>
       <c r="D519">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E519" t="s">
         <v>30</v>
@@ -12920,7 +12920,7 @@
         <v>29</v>
       </c>
       <c r="D520">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E520" t="s">
         <v>30</v>
@@ -12937,7 +12937,7 @@
         <v>29</v>
       </c>
       <c r="D521">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E521" t="s">
         <v>30</v>
@@ -12954,7 +12954,7 @@
         <v>29</v>
       </c>
       <c r="D522">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E522" t="s">
         <v>30</v>
@@ -12971,7 +12971,7 @@
         <v>29</v>
       </c>
       <c r="D523">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E523" t="s">
         <v>30</v>
@@ -12988,7 +12988,7 @@
         <v>29</v>
       </c>
       <c r="D524">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E524" t="s">
         <v>30</v>
@@ -13005,7 +13005,7 @@
         <v>29</v>
       </c>
       <c r="D525">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E525" t="s">
         <v>30</v>
@@ -13022,7 +13022,7 @@
         <v>29</v>
       </c>
       <c r="D526">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E526" t="s">
         <v>30</v>
@@ -13039,7 +13039,7 @@
         <v>29</v>
       </c>
       <c r="D527">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E527" t="s">
         <v>30</v>
@@ -13056,7 +13056,7 @@
         <v>29</v>
       </c>
       <c r="D528">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E528" t="s">
         <v>30</v>
@@ -13073,7 +13073,7 @@
         <v>29</v>
       </c>
       <c r="D529">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E529" t="s">
         <v>30</v>
@@ -13090,7 +13090,7 @@
         <v>29</v>
       </c>
       <c r="D530">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E530" t="s">
         <v>30</v>
@@ -13107,7 +13107,7 @@
         <v>29</v>
       </c>
       <c r="D531">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E531" t="s">
         <v>30</v>
@@ -13124,7 +13124,7 @@
         <v>29</v>
       </c>
       <c r="D532">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E532" t="s">
         <v>30</v>
@@ -13141,7 +13141,7 @@
         <v>29</v>
       </c>
       <c r="D533">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E533" t="s">
         <v>30</v>
@@ -13158,7 +13158,7 @@
         <v>29</v>
       </c>
       <c r="D534">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E534" t="s">
         <v>30</v>
@@ -13175,7 +13175,7 @@
         <v>29</v>
       </c>
       <c r="D535">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E535" t="s">
         <v>30</v>
@@ -13192,7 +13192,7 @@
         <v>29</v>
       </c>
       <c r="D536">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E536" t="s">
         <v>30</v>
@@ -13209,7 +13209,7 @@
         <v>29</v>
       </c>
       <c r="D537">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E537" t="s">
         <v>30</v>
@@ -13226,7 +13226,7 @@
         <v>29</v>
       </c>
       <c r="D538">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E538" t="s">
         <v>30</v>
@@ -13260,7 +13260,7 @@
         <v>29</v>
       </c>
       <c r="D540">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E540" t="s">
         <v>30</v>
@@ -13277,7 +13277,7 @@
         <v>29</v>
       </c>
       <c r="D541">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E541" t="s">
         <v>30</v>
@@ -13294,7 +13294,7 @@
         <v>29</v>
       </c>
       <c r="D542">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E542" t="s">
         <v>30</v>
@@ -13311,7 +13311,7 @@
         <v>29</v>
       </c>
       <c r="D543">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E543" t="s">
         <v>30</v>
@@ -13328,7 +13328,7 @@
         <v>29</v>
       </c>
       <c r="D544">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E544" t="s">
         <v>30</v>
@@ -13345,7 +13345,7 @@
         <v>29</v>
       </c>
       <c r="D545">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E545" t="s">
         <v>30</v>
@@ -13362,7 +13362,7 @@
         <v>29</v>
       </c>
       <c r="D546">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E546" t="s">
         <v>30</v>
@@ -13379,7 +13379,7 @@
         <v>29</v>
       </c>
       <c r="D547">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E547" t="s">
         <v>30</v>
@@ -13396,7 +13396,7 @@
         <v>29</v>
       </c>
       <c r="D548">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E548" t="s">
         <v>30</v>
@@ -13413,7 +13413,7 @@
         <v>29</v>
       </c>
       <c r="D549">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E549" t="s">
         <v>30</v>
@@ -13430,7 +13430,7 @@
         <v>29</v>
       </c>
       <c r="D550">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E550" t="s">
         <v>30</v>
@@ -13447,7 +13447,7 @@
         <v>29</v>
       </c>
       <c r="D551">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E551" t="s">
         <v>30</v>
@@ -13464,7 +13464,7 @@
         <v>29</v>
       </c>
       <c r="D552">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E552" t="s">
         <v>30</v>
@@ -13481,7 +13481,7 @@
         <v>29</v>
       </c>
       <c r="D553">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E553" t="s">
         <v>30</v>
@@ -13498,7 +13498,7 @@
         <v>29</v>
       </c>
       <c r="D554">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E554" t="s">
         <v>30</v>
@@ -13515,7 +13515,7 @@
         <v>29</v>
       </c>
       <c r="D555">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E555" t="s">
         <v>30</v>
@@ -13532,7 +13532,7 @@
         <v>29</v>
       </c>
       <c r="D556">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E556" t="s">
         <v>30</v>
@@ -13549,7 +13549,7 @@
         <v>29</v>
       </c>
       <c r="D557">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E557" t="s">
         <v>30</v>
@@ -13566,7 +13566,7 @@
         <v>29</v>
       </c>
       <c r="D558">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E558" t="s">
         <v>30</v>
@@ -13583,7 +13583,7 @@
         <v>29</v>
       </c>
       <c r="D559">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E559" t="s">
         <v>30</v>
@@ -13600,7 +13600,7 @@
         <v>29</v>
       </c>
       <c r="D560">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E560" t="s">
         <v>30</v>
@@ -13634,7 +13634,7 @@
         <v>29</v>
       </c>
       <c r="D562">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E562" t="s">
         <v>30</v>
@@ -13651,7 +13651,7 @@
         <v>29</v>
       </c>
       <c r="D563">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E563" t="s">
         <v>30</v>
@@ -13668,7 +13668,7 @@
         <v>29</v>
       </c>
       <c r="D564">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E564" t="s">
         <v>30</v>
@@ -13702,7 +13702,7 @@
         <v>29</v>
       </c>
       <c r="D566">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E566" t="s">
         <v>30</v>
@@ -13719,7 +13719,7 @@
         <v>29</v>
       </c>
       <c r="D567">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E567" t="s">
         <v>30</v>
@@ -13736,7 +13736,7 @@
         <v>29</v>
       </c>
       <c r="D568">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E568" t="s">
         <v>30</v>
@@ -13753,7 +13753,7 @@
         <v>29</v>
       </c>
       <c r="D569">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E569" t="s">
         <v>30</v>
@@ -13770,7 +13770,7 @@
         <v>29</v>
       </c>
       <c r="D570">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E570" t="s">
         <v>30</v>
@@ -13787,7 +13787,7 @@
         <v>29</v>
       </c>
       <c r="D571">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E571" t="s">
         <v>30</v>
@@ -13804,7 +13804,7 @@
         <v>29</v>
       </c>
       <c r="D572">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E572" t="s">
         <v>30</v>
@@ -13821,7 +13821,7 @@
         <v>29</v>
       </c>
       <c r="D573">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E573" t="s">
         <v>30</v>
@@ -13838,7 +13838,7 @@
         <v>29</v>
       </c>
       <c r="D574">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E574" t="s">
         <v>30</v>
@@ -13855,7 +13855,7 @@
         <v>29</v>
       </c>
       <c r="D575">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E575" t="s">
         <v>30</v>
@@ -13872,7 +13872,7 @@
         <v>29</v>
       </c>
       <c r="D576">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E576" t="s">
         <v>30</v>
@@ -13889,7 +13889,7 @@
         <v>29</v>
       </c>
       <c r="D577">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E577" t="s">
         <v>30</v>
@@ -13906,7 +13906,7 @@
         <v>29</v>
       </c>
       <c r="D578">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E578" t="s">
         <v>30</v>
@@ -13923,7 +13923,7 @@
         <v>29</v>
       </c>
       <c r="D579">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E579" t="s">
         <v>30</v>
@@ -13940,7 +13940,7 @@
         <v>29</v>
       </c>
       <c r="D580">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E580" t="s">
         <v>30</v>
@@ -13957,7 +13957,7 @@
         <v>29</v>
       </c>
       <c r="D581">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E581" t="s">
         <v>30</v>
@@ -13974,7 +13974,7 @@
         <v>29</v>
       </c>
       <c r="D582">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E582" t="s">
         <v>30</v>
@@ -13991,7 +13991,7 @@
         <v>29</v>
       </c>
       <c r="D583">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E583" t="s">
         <v>30</v>
@@ -14008,7 +14008,7 @@
         <v>29</v>
       </c>
       <c r="D584">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E584" t="s">
         <v>30</v>
@@ -14025,7 +14025,7 @@
         <v>29</v>
       </c>
       <c r="D585">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E585" t="s">
         <v>30</v>
@@ -14042,7 +14042,7 @@
         <v>29</v>
       </c>
       <c r="D586">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E586" t="s">
         <v>30</v>
@@ -14059,7 +14059,7 @@
         <v>29</v>
       </c>
       <c r="D587">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E587" t="s">
         <v>30</v>
@@ -14076,7 +14076,7 @@
         <v>29</v>
       </c>
       <c r="D588">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E588" t="s">
         <v>30</v>
@@ -14093,7 +14093,7 @@
         <v>29</v>
       </c>
       <c r="D589">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E589" t="s">
         <v>30</v>
@@ -14110,7 +14110,7 @@
         <v>29</v>
       </c>
       <c r="D590">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E590" t="s">
         <v>30</v>
@@ -14127,7 +14127,7 @@
         <v>29</v>
       </c>
       <c r="D591">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E591" t="s">
         <v>30</v>
@@ -14144,7 +14144,7 @@
         <v>29</v>
       </c>
       <c r="D592">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E592" t="s">
         <v>30</v>
@@ -14161,7 +14161,7 @@
         <v>29</v>
       </c>
       <c r="D593">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E593" t="s">
         <v>30</v>
@@ -14178,7 +14178,7 @@
         <v>29</v>
       </c>
       <c r="D594">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E594" t="s">
         <v>30</v>
@@ -14195,7 +14195,7 @@
         <v>29</v>
       </c>
       <c r="D595">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E595" t="s">
         <v>30</v>
@@ -14212,7 +14212,7 @@
         <v>29</v>
       </c>
       <c r="D596">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E596" t="s">
         <v>30</v>
@@ -14229,7 +14229,7 @@
         <v>29</v>
       </c>
       <c r="D597">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E597" t="s">
         <v>30</v>
@@ -14246,7 +14246,7 @@
         <v>29</v>
       </c>
       <c r="D598">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E598" t="s">
         <v>30</v>
@@ -14263,7 +14263,7 @@
         <v>29</v>
       </c>
       <c r="D599">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E599" t="s">
         <v>30</v>
@@ -14280,7 +14280,7 @@
         <v>29</v>
       </c>
       <c r="D600">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E600" t="s">
         <v>30</v>
@@ -14297,7 +14297,7 @@
         <v>29</v>
       </c>
       <c r="D601">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E601" t="s">
         <v>30</v>
@@ -14314,7 +14314,7 @@
         <v>29</v>
       </c>
       <c r="D602">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E602" t="s">
         <v>30</v>
@@ -14348,7 +14348,7 @@
         <v>29</v>
       </c>
       <c r="D604">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E604" t="s">
         <v>30</v>
@@ -14365,7 +14365,7 @@
         <v>29</v>
       </c>
       <c r="D605">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E605" t="s">
         <v>30</v>
@@ -14382,7 +14382,7 @@
         <v>29</v>
       </c>
       <c r="D606">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E606" t="s">
         <v>30</v>
@@ -14416,7 +14416,7 @@
         <v>29</v>
       </c>
       <c r="D608">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E608" t="s">
         <v>30</v>
@@ -14433,7 +14433,7 @@
         <v>29</v>
       </c>
       <c r="D609">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E609" t="s">
         <v>30</v>
@@ -14450,7 +14450,7 @@
         <v>29</v>
       </c>
       <c r="D610">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E610" t="s">
         <v>30</v>
@@ -14467,7 +14467,7 @@
         <v>29</v>
       </c>
       <c r="D611">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E611" t="s">
         <v>30</v>
@@ -14484,7 +14484,7 @@
         <v>29</v>
       </c>
       <c r="D612">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E612" t="s">
         <v>30</v>
@@ -14501,7 +14501,7 @@
         <v>29</v>
       </c>
       <c r="D613">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E613" t="s">
         <v>30</v>
@@ -14518,7 +14518,7 @@
         <v>29</v>
       </c>
       <c r="D614">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E614" t="s">
         <v>30</v>
@@ -14535,7 +14535,7 @@
         <v>29</v>
       </c>
       <c r="D615">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E615" t="s">
         <v>30</v>
@@ -14552,7 +14552,7 @@
         <v>29</v>
       </c>
       <c r="D616">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E616" t="s">
         <v>30</v>
@@ -14569,7 +14569,7 @@
         <v>29</v>
       </c>
       <c r="D617">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E617" t="s">
         <v>30</v>
@@ -14586,7 +14586,7 @@
         <v>29</v>
       </c>
       <c r="D618">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E618" t="s">
         <v>30</v>
@@ -14603,7 +14603,7 @@
         <v>29</v>
       </c>
       <c r="D619">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E619" t="s">
         <v>30</v>
@@ -14620,7 +14620,7 @@
         <v>29</v>
       </c>
       <c r="D620">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E620" t="s">
         <v>30</v>
@@ -14637,7 +14637,7 @@
         <v>29</v>
       </c>
       <c r="D621">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E621" t="s">
         <v>30</v>
@@ -14654,7 +14654,7 @@
         <v>29</v>
       </c>
       <c r="D622">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E622" t="s">
         <v>30</v>
@@ -14671,7 +14671,7 @@
         <v>29</v>
       </c>
       <c r="D623">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E623" t="s">
         <v>30</v>
@@ -14688,7 +14688,7 @@
         <v>29</v>
       </c>
       <c r="D624">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E624" t="s">
         <v>30</v>
@@ -14705,7 +14705,7 @@
         <v>29</v>
       </c>
       <c r="D625">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E625" t="s">
         <v>30</v>
@@ -14722,7 +14722,7 @@
         <v>29</v>
       </c>
       <c r="D626">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E626" t="s">
         <v>30</v>
@@ -14756,7 +14756,7 @@
         <v>29</v>
       </c>
       <c r="D628">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E628" t="s">
         <v>30</v>
@@ -14773,7 +14773,7 @@
         <v>29</v>
       </c>
       <c r="D629">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E629" t="s">
         <v>30</v>
@@ -14790,7 +14790,7 @@
         <v>29</v>
       </c>
       <c r="D630">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E630" t="s">
         <v>30</v>
@@ -14807,7 +14807,7 @@
         <v>29</v>
       </c>
       <c r="D631">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E631" t="s">
         <v>30</v>
@@ -14824,7 +14824,7 @@
         <v>29</v>
       </c>
       <c r="D632">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E632" t="s">
         <v>30</v>
@@ -14841,7 +14841,7 @@
         <v>29</v>
       </c>
       <c r="D633">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E633" t="s">
         <v>30</v>
@@ -14858,7 +14858,7 @@
         <v>29</v>
       </c>
       <c r="D634">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E634" t="s">
         <v>30</v>
@@ -14875,7 +14875,7 @@
         <v>29</v>
       </c>
       <c r="D635">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E635" t="s">
         <v>30</v>
@@ -14892,7 +14892,7 @@
         <v>29</v>
       </c>
       <c r="D636">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E636" t="s">
         <v>30</v>
@@ -14909,7 +14909,7 @@
         <v>29</v>
       </c>
       <c r="D637">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E637" t="s">
         <v>30</v>
@@ -14926,7 +14926,7 @@
         <v>29</v>
       </c>
       <c r="D638">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E638" t="s">
         <v>30</v>
@@ -14943,7 +14943,7 @@
         <v>29</v>
       </c>
       <c r="D639">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E639" t="s">
         <v>30</v>
@@ -14960,7 +14960,7 @@
         <v>29</v>
       </c>
       <c r="D640">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E640" t="s">
         <v>30</v>
@@ -14977,7 +14977,7 @@
         <v>29</v>
       </c>
       <c r="D641">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E641" t="s">
         <v>30</v>
@@ -15011,7 +15011,7 @@
         <v>29</v>
       </c>
       <c r="D643">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E643" t="s">
         <v>30</v>
@@ -15028,7 +15028,7 @@
         <v>29</v>
       </c>
       <c r="D644">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E644" t="s">
         <v>30</v>
@@ -15045,7 +15045,7 @@
         <v>29</v>
       </c>
       <c r="D645">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E645" t="s">
         <v>30</v>
@@ -15062,7 +15062,7 @@
         <v>29</v>
       </c>
       <c r="D646">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E646" t="s">
         <v>30</v>
@@ -15079,7 +15079,7 @@
         <v>29</v>
       </c>
       <c r="D647">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E647" t="s">
         <v>30</v>
@@ -15096,7 +15096,7 @@
         <v>29</v>
       </c>
       <c r="D648">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E648" t="s">
         <v>30</v>
@@ -15113,7 +15113,7 @@
         <v>29</v>
       </c>
       <c r="D649">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E649" t="s">
         <v>30</v>
@@ -15130,7 +15130,7 @@
         <v>29</v>
       </c>
       <c r="D650">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E650" t="s">
         <v>30</v>
@@ -15147,7 +15147,7 @@
         <v>29</v>
       </c>
       <c r="D651">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E651" t="s">
         <v>30</v>
@@ -15164,7 +15164,7 @@
         <v>29</v>
       </c>
       <c r="D652">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E652" t="s">
         <v>30</v>
@@ -15181,7 +15181,7 @@
         <v>29</v>
       </c>
       <c r="D653">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E653" t="s">
         <v>30</v>
@@ -15198,7 +15198,7 @@
         <v>29</v>
       </c>
       <c r="D654">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E654" t="s">
         <v>30</v>
@@ -15215,7 +15215,7 @@
         <v>29</v>
       </c>
       <c r="D655">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E655" t="s">
         <v>30</v>
@@ -15232,7 +15232,7 @@
         <v>29</v>
       </c>
       <c r="D656">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E656" t="s">
         <v>30</v>
@@ -15249,7 +15249,7 @@
         <v>29</v>
       </c>
       <c r="D657">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E657" t="s">
         <v>30</v>
@@ -15266,7 +15266,7 @@
         <v>29</v>
       </c>
       <c r="D658">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E658" t="s">
         <v>30</v>
@@ -15283,7 +15283,7 @@
         <v>29</v>
       </c>
       <c r="D659">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E659" t="s">
         <v>30</v>
@@ -15300,7 +15300,7 @@
         <v>29</v>
       </c>
       <c r="D660">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E660" t="s">
         <v>30</v>
@@ -15317,7 +15317,7 @@
         <v>29</v>
       </c>
       <c r="D661">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E661" t="s">
         <v>30</v>
@@ -15334,7 +15334,7 @@
         <v>29</v>
       </c>
       <c r="D662">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E662" t="s">
         <v>30</v>
@@ -15351,7 +15351,7 @@
         <v>29</v>
       </c>
       <c r="D663">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E663" t="s">
         <v>30</v>
@@ -15368,7 +15368,7 @@
         <v>29</v>
       </c>
       <c r="D664">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E664" t="s">
         <v>30</v>
@@ -15385,7 +15385,7 @@
         <v>29</v>
       </c>
       <c r="D665">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E665" t="s">
         <v>30</v>
@@ -15402,7 +15402,7 @@
         <v>29</v>
       </c>
       <c r="D666">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E666" t="s">
         <v>30</v>
@@ -15419,7 +15419,7 @@
         <v>29</v>
       </c>
       <c r="D667">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E667" t="s">
         <v>30</v>
@@ -15436,7 +15436,7 @@
         <v>29</v>
       </c>
       <c r="D668">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E668" t="s">
         <v>30</v>
@@ -15453,7 +15453,7 @@
         <v>29</v>
       </c>
       <c r="D669">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E669" t="s">
         <v>30</v>
@@ -15487,7 +15487,7 @@
         <v>29</v>
       </c>
       <c r="D671">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E671" t="s">
         <v>30</v>
@@ -15504,7 +15504,7 @@
         <v>29</v>
       </c>
       <c r="D672">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E672" t="s">
         <v>30</v>
@@ -15521,7 +15521,7 @@
         <v>29</v>
       </c>
       <c r="D673">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E673" t="s">
         <v>30</v>
@@ -15538,7 +15538,7 @@
         <v>29</v>
       </c>
       <c r="D674">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E674" t="s">
         <v>30</v>
@@ -15555,7 +15555,7 @@
         <v>29</v>
       </c>
       <c r="D675">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E675" t="s">
         <v>30</v>
@@ -15572,7 +15572,7 @@
         <v>29</v>
       </c>
       <c r="D676">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E676" t="s">
         <v>30</v>
@@ -15589,7 +15589,7 @@
         <v>29</v>
       </c>
       <c r="D677">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E677" t="s">
         <v>30</v>
@@ -15606,7 +15606,7 @@
         <v>29</v>
       </c>
       <c r="D678">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E678" t="s">
         <v>30</v>
@@ -15623,7 +15623,7 @@
         <v>29</v>
       </c>
       <c r="D679">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E679" t="s">
         <v>30</v>
@@ -15640,7 +15640,7 @@
         <v>29</v>
       </c>
       <c r="D680">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E680" t="s">
         <v>30</v>
@@ -15657,7 +15657,7 @@
         <v>29</v>
       </c>
       <c r="D681">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E681" t="s">
         <v>30</v>
@@ -15674,7 +15674,7 @@
         <v>29</v>
       </c>
       <c r="D682">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E682" t="s">
         <v>30</v>
@@ -15691,7 +15691,7 @@
         <v>29</v>
       </c>
       <c r="D683">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E683" t="s">
         <v>30</v>
@@ -15725,7 +15725,7 @@
         <v>29</v>
       </c>
       <c r="D685">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E685" t="s">
         <v>30</v>
@@ -15742,7 +15742,7 @@
         <v>29</v>
       </c>
       <c r="D686">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E686" t="s">
         <v>30</v>
@@ -15759,7 +15759,7 @@
         <v>29</v>
       </c>
       <c r="D687">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E687" t="s">
         <v>30</v>
@@ -15776,7 +15776,7 @@
         <v>29</v>
       </c>
       <c r="D688">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E688" t="s">
         <v>30</v>
@@ -15793,7 +15793,7 @@
         <v>29</v>
       </c>
       <c r="D689">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E689" t="s">
         <v>30</v>
@@ -15810,7 +15810,7 @@
         <v>29</v>
       </c>
       <c r="D690">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E690" t="s">
         <v>30</v>
@@ -15827,7 +15827,7 @@
         <v>29</v>
       </c>
       <c r="D691">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E691" t="s">
         <v>30</v>
@@ -15844,7 +15844,7 @@
         <v>29</v>
       </c>
       <c r="D692">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E692" t="s">
         <v>30</v>
@@ -15861,7 +15861,7 @@
         <v>29</v>
       </c>
       <c r="D693">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E693" t="s">
         <v>30</v>
@@ -15878,7 +15878,7 @@
         <v>29</v>
       </c>
       <c r="D694">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E694" t="s">
         <v>30</v>
@@ -15895,7 +15895,7 @@
         <v>29</v>
       </c>
       <c r="D695">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E695" t="s">
         <v>30</v>
@@ -15912,7 +15912,7 @@
         <v>29</v>
       </c>
       <c r="D696">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E696" t="s">
         <v>30</v>
@@ -15929,7 +15929,7 @@
         <v>29</v>
       </c>
       <c r="D697">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E697" t="s">
         <v>30</v>
@@ -15963,7 +15963,7 @@
         <v>29</v>
       </c>
       <c r="D699">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E699" t="s">
         <v>30</v>
@@ -15980,7 +15980,7 @@
         <v>29</v>
       </c>
       <c r="D700">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E700" t="s">
         <v>30</v>
@@ -15997,7 +15997,7 @@
         <v>29</v>
       </c>
       <c r="D701">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E701" t="s">
         <v>30</v>
@@ -16014,7 +16014,7 @@
         <v>29</v>
       </c>
       <c r="D702">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E702" t="s">
         <v>30</v>
@@ -16031,7 +16031,7 @@
         <v>29</v>
       </c>
       <c r="D703">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E703" t="s">
         <v>30</v>
@@ -16048,7 +16048,7 @@
         <v>29</v>
       </c>
       <c r="D704">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E704" t="s">
         <v>30</v>
@@ -16065,7 +16065,7 @@
         <v>29</v>
       </c>
       <c r="D705">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E705" t="s">
         <v>30</v>
@@ -16082,7 +16082,7 @@
         <v>29</v>
       </c>
       <c r="D706">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E706" t="s">
         <v>30</v>
@@ -16099,7 +16099,7 @@
         <v>29</v>
       </c>
       <c r="D707">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E707" t="s">
         <v>30</v>
@@ -16116,7 +16116,7 @@
         <v>29</v>
       </c>
       <c r="D708">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E708" t="s">
         <v>30</v>
@@ -16133,7 +16133,7 @@
         <v>29</v>
       </c>
       <c r="D709">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E709" t="s">
         <v>30</v>
@@ -16150,7 +16150,7 @@
         <v>29</v>
       </c>
       <c r="D710">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E710" t="s">
         <v>30</v>
@@ -16167,7 +16167,7 @@
         <v>29</v>
       </c>
       <c r="D711">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E711" t="s">
         <v>30</v>
@@ -16184,7 +16184,7 @@
         <v>29</v>
       </c>
       <c r="D712">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E712" t="s">
         <v>30</v>
@@ -16201,7 +16201,7 @@
         <v>29</v>
       </c>
       <c r="D713">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E713" t="s">
         <v>30</v>
@@ -16218,7 +16218,7 @@
         <v>29</v>
       </c>
       <c r="D714">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E714" t="s">
         <v>30</v>
@@ -16235,7 +16235,7 @@
         <v>29</v>
       </c>
       <c r="D715">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E715" t="s">
         <v>30</v>
@@ -16252,7 +16252,7 @@
         <v>29</v>
       </c>
       <c r="D716">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E716" t="s">
         <v>30</v>
@@ -16286,7 +16286,7 @@
         <v>29</v>
       </c>
       <c r="D718">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E718" t="s">
         <v>30</v>
@@ -16303,7 +16303,7 @@
         <v>29</v>
       </c>
       <c r="D719">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E719" t="s">
         <v>30</v>
@@ -16320,7 +16320,7 @@
         <v>29</v>
       </c>
       <c r="D720">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E720" t="s">
         <v>30</v>
@@ -16337,7 +16337,7 @@
         <v>29</v>
       </c>
       <c r="D721">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E721" t="s">
         <v>30</v>
@@ -16354,7 +16354,7 @@
         <v>29</v>
       </c>
       <c r="D722">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E722" t="s">
         <v>30</v>
@@ -16371,7 +16371,7 @@
         <v>29</v>
       </c>
       <c r="D723">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E723" t="s">
         <v>30</v>
@@ -16388,7 +16388,7 @@
         <v>29</v>
       </c>
       <c r="D724">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E724" t="s">
         <v>30</v>
@@ -16405,7 +16405,7 @@
         <v>29</v>
       </c>
       <c r="D725">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E725" t="s">
         <v>30</v>
@@ -16422,7 +16422,7 @@
         <v>29</v>
       </c>
       <c r="D726">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E726" t="s">
         <v>30</v>
@@ -16439,7 +16439,7 @@
         <v>29</v>
       </c>
       <c r="D727">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E727" t="s">
         <v>30</v>
@@ -16456,7 +16456,7 @@
         <v>29</v>
       </c>
       <c r="D728">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E728" t="s">
         <v>30</v>
@@ -16473,7 +16473,7 @@
         <v>29</v>
       </c>
       <c r="D729">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E729" t="s">
         <v>30</v>
@@ -16490,7 +16490,7 @@
         <v>29</v>
       </c>
       <c r="D730">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E730" t="s">
         <v>30</v>
@@ -16507,7 +16507,7 @@
         <v>29</v>
       </c>
       <c r="D731">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E731" t="s">
         <v>30</v>
@@ -16524,7 +16524,7 @@
         <v>29</v>
       </c>
       <c r="D732">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E732" t="s">
         <v>30</v>
@@ -16541,7 +16541,7 @@
         <v>29</v>
       </c>
       <c r="D733">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E733" t="s">
         <v>30</v>
@@ -16558,7 +16558,7 @@
         <v>29</v>
       </c>
       <c r="D734">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E734" t="s">
         <v>30</v>
@@ -16575,7 +16575,7 @@
         <v>29</v>
       </c>
       <c r="D735">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E735" t="s">
         <v>30</v>
@@ -16592,7 +16592,7 @@
         <v>29</v>
       </c>
       <c r="D736">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E736" t="s">
         <v>30</v>
@@ -16609,7 +16609,7 @@
         <v>29</v>
       </c>
       <c r="D737">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E737" t="s">
         <v>30</v>
@@ -16626,7 +16626,7 @@
         <v>29</v>
       </c>
       <c r="D738">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E738" t="s">
         <v>30</v>
@@ -16643,7 +16643,7 @@
         <v>29</v>
       </c>
       <c r="D739">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E739" t="s">
         <v>30</v>
@@ -16660,7 +16660,7 @@
         <v>29</v>
       </c>
       <c r="D740">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E740" t="s">
         <v>30</v>
@@ -16677,7 +16677,7 @@
         <v>29</v>
       </c>
       <c r="D741">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E741" t="s">
         <v>30</v>
@@ -16694,7 +16694,7 @@
         <v>29</v>
       </c>
       <c r="D742">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E742" t="s">
         <v>30</v>
@@ -16711,7 +16711,7 @@
         <v>29</v>
       </c>
       <c r="D743">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E743" t="s">
         <v>30</v>
@@ -16728,7 +16728,7 @@
         <v>29</v>
       </c>
       <c r="D744">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E744" t="s">
         <v>30</v>
@@ -16762,7 +16762,7 @@
         <v>29</v>
       </c>
       <c r="D746">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E746" t="s">
         <v>30</v>
@@ -16779,7 +16779,7 @@
         <v>29</v>
       </c>
       <c r="D747">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E747" t="s">
         <v>30</v>
@@ -16796,7 +16796,7 @@
         <v>29</v>
       </c>
       <c r="D748">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E748" t="s">
         <v>30</v>
@@ -16813,7 +16813,7 @@
         <v>29</v>
       </c>
       <c r="D749">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E749" t="s">
         <v>30</v>
@@ -16830,7 +16830,7 @@
         <v>29</v>
       </c>
       <c r="D750">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E750" t="s">
         <v>30</v>
@@ -16847,7 +16847,7 @@
         <v>29</v>
       </c>
       <c r="D751">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E751" t="s">
         <v>30</v>
@@ -16864,7 +16864,7 @@
         <v>29</v>
       </c>
       <c r="D752">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E752" t="s">
         <v>30</v>
@@ -16881,7 +16881,7 @@
         <v>29</v>
       </c>
       <c r="D753">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E753" t="s">
         <v>30</v>
@@ -16898,7 +16898,7 @@
         <v>29</v>
       </c>
       <c r="D754">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E754" t="s">
         <v>30</v>
@@ -16915,7 +16915,7 @@
         <v>29</v>
       </c>
       <c r="D755">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E755" t="s">
         <v>30</v>
@@ -16949,7 +16949,7 @@
         <v>29</v>
       </c>
       <c r="D757">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E757" t="s">
         <v>30</v>
@@ -16966,7 +16966,7 @@
         <v>29</v>
       </c>
       <c r="D758">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E758" t="s">
         <v>30</v>
@@ -16983,7 +16983,7 @@
         <v>29</v>
       </c>
       <c r="D759">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E759" t="s">
         <v>30</v>
@@ -17017,7 +17017,7 @@
         <v>29</v>
       </c>
       <c r="D761">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E761" t="s">
         <v>30</v>
@@ -17034,7 +17034,7 @@
         <v>29</v>
       </c>
       <c r="D762">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E762" t="s">
         <v>30</v>
@@ -17051,7 +17051,7 @@
         <v>29</v>
       </c>
       <c r="D763">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E763" t="s">
         <v>30</v>
@@ -17068,7 +17068,7 @@
         <v>29</v>
       </c>
       <c r="D764">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E764" t="s">
         <v>30</v>
@@ -17085,7 +17085,7 @@
         <v>29</v>
       </c>
       <c r="D765">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E765" t="s">
         <v>30</v>
@@ -17102,7 +17102,7 @@
         <v>29</v>
       </c>
       <c r="D766">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E766" t="s">
         <v>30</v>
@@ -17119,7 +17119,7 @@
         <v>29</v>
       </c>
       <c r="D767">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E767" t="s">
         <v>30</v>
@@ -17136,7 +17136,7 @@
         <v>29</v>
       </c>
       <c r="D768">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E768" t="s">
         <v>30</v>
@@ -17170,7 +17170,7 @@
         <v>29</v>
       </c>
       <c r="D770">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E770" t="s">
         <v>30</v>
@@ -17187,7 +17187,7 @@
         <v>29</v>
       </c>
       <c r="D771">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E771" t="s">
         <v>30</v>
@@ -17204,7 +17204,7 @@
         <v>29</v>
       </c>
       <c r="D772">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E772" t="s">
         <v>30</v>
@@ -17238,7 +17238,7 @@
         <v>29</v>
       </c>
       <c r="D774">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E774" t="s">
         <v>30</v>
@@ -17255,7 +17255,7 @@
         <v>29</v>
       </c>
       <c r="D775">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E775" t="s">
         <v>30</v>
@@ -17272,7 +17272,7 @@
         <v>29</v>
       </c>
       <c r="D776">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E776" t="s">
         <v>30</v>
@@ -17289,7 +17289,7 @@
         <v>29</v>
       </c>
       <c r="D777">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E777" t="s">
         <v>30</v>
@@ -17306,7 +17306,7 @@
         <v>29</v>
       </c>
       <c r="D778">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E778" t="s">
         <v>30</v>
@@ -17323,7 +17323,7 @@
         <v>29</v>
       </c>
       <c r="D779">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E779" t="s">
         <v>30</v>
@@ -17340,7 +17340,7 @@
         <v>29</v>
       </c>
       <c r="D780">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E780" t="s">
         <v>30</v>
@@ -17357,7 +17357,7 @@
         <v>29</v>
       </c>
       <c r="D781">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E781" t="s">
         <v>30</v>
@@ -17374,7 +17374,7 @@
         <v>29</v>
       </c>
       <c r="D782">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E782" t="s">
         <v>30</v>
@@ -17391,7 +17391,7 @@
         <v>29</v>
       </c>
       <c r="D783">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E783" t="s">
         <v>30</v>
@@ -17408,7 +17408,7 @@
         <v>29</v>
       </c>
       <c r="D784">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E784" t="s">
         <v>30</v>
@@ -17425,7 +17425,7 @@
         <v>29</v>
       </c>
       <c r="D785">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E785" t="s">
         <v>30</v>
@@ -17442,7 +17442,7 @@
         <v>29</v>
       </c>
       <c r="D786">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E786" t="s">
         <v>30</v>
@@ -17459,7 +17459,7 @@
         <v>29</v>
       </c>
       <c r="D787">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E787" t="s">
         <v>30</v>
@@ -17476,7 +17476,7 @@
         <v>29</v>
       </c>
       <c r="D788">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E788" t="s">
         <v>30</v>
@@ -17493,7 +17493,7 @@
         <v>29</v>
       </c>
       <c r="D789">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E789" t="s">
         <v>30</v>
@@ -17510,7 +17510,7 @@
         <v>29</v>
       </c>
       <c r="D790">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E790" t="s">
         <v>30</v>
@@ -17527,7 +17527,7 @@
         <v>29</v>
       </c>
       <c r="D791">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E791" t="s">
         <v>30</v>
@@ -17544,7 +17544,7 @@
         <v>29</v>
       </c>
       <c r="D792">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E792" t="s">
         <v>30</v>
@@ -17561,7 +17561,7 @@
         <v>29</v>
       </c>
       <c r="D793">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E793" t="s">
         <v>30</v>
@@ -17578,7 +17578,7 @@
         <v>29</v>
       </c>
       <c r="D794">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E794" t="s">
         <v>30</v>
@@ -17595,7 +17595,7 @@
         <v>29</v>
       </c>
       <c r="D795">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E795" t="s">
         <v>30</v>
@@ -17612,7 +17612,7 @@
         <v>29</v>
       </c>
       <c r="D796">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E796" t="s">
         <v>30</v>
@@ -17629,7 +17629,7 @@
         <v>29</v>
       </c>
       <c r="D797">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E797" t="s">
         <v>30</v>
@@ -17646,7 +17646,7 @@
         <v>29</v>
       </c>
       <c r="D798">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E798" t="s">
         <v>30</v>
@@ -17680,7 +17680,7 @@
         <v>29</v>
       </c>
       <c r="D800">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E800" t="s">
         <v>30</v>
@@ -17697,7 +17697,7 @@
         <v>29</v>
       </c>
       <c r="D801">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E801" t="s">
         <v>30</v>
@@ -17731,7 +17731,7 @@
         <v>29</v>
       </c>
       <c r="D803">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E803" t="s">
         <v>30</v>
@@ -17748,7 +17748,7 @@
         <v>29</v>
       </c>
       <c r="D804">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E804" t="s">
         <v>30</v>
@@ -17765,7 +17765,7 @@
         <v>29</v>
       </c>
       <c r="D805">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E805" t="s">
         <v>30</v>
@@ -17782,7 +17782,7 @@
         <v>29</v>
       </c>
       <c r="D806">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E806" t="s">
         <v>30</v>
@@ -17799,7 +17799,7 @@
         <v>29</v>
       </c>
       <c r="D807">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E807" t="s">
         <v>30</v>
@@ -17816,7 +17816,7 @@
         <v>29</v>
       </c>
       <c r="D808">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E808" t="s">
         <v>30</v>
@@ -17833,7 +17833,7 @@
         <v>29</v>
       </c>
       <c r="D809">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E809" t="s">
         <v>30</v>
@@ -17850,7 +17850,7 @@
         <v>29</v>
       </c>
       <c r="D810">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E810" t="s">
         <v>30</v>
@@ -17867,7 +17867,7 @@
         <v>29</v>
       </c>
       <c r="D811">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E811" t="s">
         <v>30</v>
@@ -17884,7 +17884,7 @@
         <v>29</v>
       </c>
       <c r="D812">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E812" t="s">
         <v>30</v>
@@ -17901,7 +17901,7 @@
         <v>29</v>
       </c>
       <c r="D813">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E813" t="s">
         <v>30</v>
@@ -17918,7 +17918,7 @@
         <v>29</v>
       </c>
       <c r="D814">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E814" t="s">
         <v>30</v>
@@ -17952,7 +17952,7 @@
         <v>29</v>
       </c>
       <c r="D816">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E816" t="s">
         <v>30</v>
@@ -17969,7 +17969,7 @@
         <v>29</v>
       </c>
       <c r="D817">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E817" t="s">
         <v>30</v>
@@ -17986,7 +17986,7 @@
         <v>29</v>
       </c>
       <c r="D818">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E818" t="s">
         <v>30</v>
@@ -18003,7 +18003,7 @@
         <v>29</v>
       </c>
       <c r="D819">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E819" t="s">
         <v>30</v>
@@ -18020,7 +18020,7 @@
         <v>29</v>
       </c>
       <c r="D820">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E820" t="s">
         <v>30</v>
@@ -18037,7 +18037,7 @@
         <v>29</v>
       </c>
       <c r="D821">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E821" t="s">
         <v>30</v>
@@ -18054,7 +18054,7 @@
         <v>29</v>
       </c>
       <c r="D822">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E822" t="s">
         <v>30</v>
@@ -18071,7 +18071,7 @@
         <v>29</v>
       </c>
       <c r="D823">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E823" t="s">
         <v>30</v>
@@ -18088,7 +18088,7 @@
         <v>29</v>
       </c>
       <c r="D824">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E824" t="s">
         <v>30</v>
@@ -18105,7 +18105,7 @@
         <v>29</v>
       </c>
       <c r="D825">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E825" t="s">
         <v>30</v>
@@ -18122,7 +18122,7 @@
         <v>29</v>
       </c>
       <c r="D826">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E826" t="s">
         <v>30</v>
@@ -18139,7 +18139,7 @@
         <v>29</v>
       </c>
       <c r="D827">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E827" t="s">
         <v>30</v>
@@ -18156,7 +18156,7 @@
         <v>29</v>
       </c>
       <c r="D828">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E828" t="s">
         <v>30</v>
@@ -18173,7 +18173,7 @@
         <v>29</v>
       </c>
       <c r="D829">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E829" t="s">
         <v>30</v>
@@ -18190,7 +18190,7 @@
         <v>29</v>
       </c>
       <c r="D830">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E830" t="s">
         <v>30</v>
@@ -18207,7 +18207,7 @@
         <v>29</v>
       </c>
       <c r="D831">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E831" t="s">
         <v>30</v>
@@ -18224,7 +18224,7 @@
         <v>29</v>
       </c>
       <c r="D832">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E832" t="s">
         <v>30</v>
@@ -18241,7 +18241,7 @@
         <v>29</v>
       </c>
       <c r="D833">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E833" t="s">
         <v>30</v>
@@ -18258,7 +18258,7 @@
         <v>29</v>
       </c>
       <c r="D834">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E834" t="s">
         <v>30</v>
@@ -18275,7 +18275,7 @@
         <v>29</v>
       </c>
       <c r="D835">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E835" t="s">
         <v>30</v>
@@ -18292,7 +18292,7 @@
         <v>29</v>
       </c>
       <c r="D836">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E836" t="s">
         <v>30</v>
@@ -18309,7 +18309,7 @@
         <v>29</v>
       </c>
       <c r="D837">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E837" t="s">
         <v>30</v>
@@ -18326,7 +18326,7 @@
         <v>29</v>
       </c>
       <c r="D838">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E838" t="s">
         <v>30</v>
@@ -18343,7 +18343,7 @@
         <v>29</v>
       </c>
       <c r="D839">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E839" t="s">
         <v>30</v>
@@ -18360,7 +18360,7 @@
         <v>29</v>
       </c>
       <c r="D840">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E840" t="s">
         <v>30</v>
@@ -18377,7 +18377,7 @@
         <v>29</v>
       </c>
       <c r="D841">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E841" t="s">
         <v>30</v>
@@ -18394,7 +18394,7 @@
         <v>29</v>
       </c>
       <c r="D842">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E842" t="s">
         <v>30</v>
@@ -18411,7 +18411,7 @@
         <v>29</v>
       </c>
       <c r="D843">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E843" t="s">
         <v>30</v>
@@ -18428,7 +18428,7 @@
         <v>29</v>
       </c>
       <c r="D844">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E844" t="s">
         <v>30</v>
@@ -18445,7 +18445,7 @@
         <v>29</v>
       </c>
       <c r="D845">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E845" t="s">
         <v>30</v>
@@ -18479,7 +18479,7 @@
         <v>29</v>
       </c>
       <c r="D847">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E847" t="s">
         <v>30</v>
@@ -18496,7 +18496,7 @@
         <v>29</v>
       </c>
       <c r="D848">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E848" t="s">
         <v>30</v>
@@ -18513,7 +18513,7 @@
         <v>29</v>
       </c>
       <c r="D849">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E849" t="s">
         <v>30</v>
@@ -18530,7 +18530,7 @@
         <v>29</v>
       </c>
       <c r="D850">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E850" t="s">
         <v>30</v>
@@ -18547,7 +18547,7 @@
         <v>29</v>
       </c>
       <c r="D851">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E851" t="s">
         <v>30</v>
@@ -18564,7 +18564,7 @@
         <v>29</v>
       </c>
       <c r="D852">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E852" t="s">
         <v>30</v>
@@ -18581,7 +18581,7 @@
         <v>29</v>
       </c>
       <c r="D853">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E853" t="s">
         <v>30</v>
@@ -18598,7 +18598,7 @@
         <v>29</v>
       </c>
       <c r="D854">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E854" t="s">
         <v>30</v>
@@ -18615,7 +18615,7 @@
         <v>29</v>
       </c>
       <c r="D855">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E855" t="s">
         <v>30</v>
@@ -18632,7 +18632,7 @@
         <v>29</v>
       </c>
       <c r="D856">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E856" t="s">
         <v>30</v>
@@ -18649,7 +18649,7 @@
         <v>29</v>
       </c>
       <c r="D857">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E857" t="s">
         <v>30</v>
@@ -18666,7 +18666,7 @@
         <v>29</v>
       </c>
       <c r="D858">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E858" t="s">
         <v>30</v>
@@ -18700,7 +18700,7 @@
         <v>29</v>
       </c>
       <c r="D860">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E860" t="s">
         <v>30</v>
@@ -18717,7 +18717,7 @@
         <v>29</v>
       </c>
       <c r="D861">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E861" t="s">
         <v>30</v>
@@ -18734,7 +18734,7 @@
         <v>29</v>
       </c>
       <c r="D862">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E862" t="s">
         <v>30</v>
@@ -18751,7 +18751,7 @@
         <v>29</v>
       </c>
       <c r="D863">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E863" t="s">
         <v>30</v>
@@ -18768,7 +18768,7 @@
         <v>29</v>
       </c>
       <c r="D864">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E864" t="s">
         <v>30</v>
@@ -18785,7 +18785,7 @@
         <v>29</v>
       </c>
       <c r="D865">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E865" t="s">
         <v>30</v>
@@ -18802,7 +18802,7 @@
         <v>29</v>
       </c>
       <c r="D866">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E866" t="s">
         <v>30</v>
@@ -18819,7 +18819,7 @@
         <v>29</v>
       </c>
       <c r="D867">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E867" t="s">
         <v>30</v>
@@ -18836,7 +18836,7 @@
         <v>29</v>
       </c>
       <c r="D868">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E868" t="s">
         <v>30</v>
@@ -18853,7 +18853,7 @@
         <v>29</v>
       </c>
       <c r="D869">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E869" t="s">
         <v>30</v>
@@ -18870,7 +18870,7 @@
         <v>29</v>
       </c>
       <c r="D870">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E870" t="s">
         <v>30</v>
@@ -18887,7 +18887,7 @@
         <v>29</v>
       </c>
       <c r="D871">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E871" t="s">
         <v>30</v>
@@ -18904,7 +18904,7 @@
         <v>29</v>
       </c>
       <c r="D872">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E872" t="s">
         <v>30</v>
@@ -18921,7 +18921,7 @@
         <v>29</v>
       </c>
       <c r="D873">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E873" t="s">
         <v>30</v>
@@ -18938,7 +18938,7 @@
         <v>29</v>
       </c>
       <c r="D874">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E874" t="s">
         <v>30</v>
@@ -18955,7 +18955,7 @@
         <v>29</v>
       </c>
       <c r="D875">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E875" t="s">
         <v>30</v>
@@ -18972,7 +18972,7 @@
         <v>29</v>
       </c>
       <c r="D876">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E876" t="s">
         <v>30</v>
@@ -18989,7 +18989,7 @@
         <v>29</v>
       </c>
       <c r="D877">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E877" t="s">
         <v>30</v>
@@ -19006,7 +19006,7 @@
         <v>29</v>
       </c>
       <c r="D878">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E878" t="s">
         <v>30</v>
@@ -19023,7 +19023,7 @@
         <v>29</v>
       </c>
       <c r="D879">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E879" t="s">
         <v>30</v>
@@ -19040,7 +19040,7 @@
         <v>29</v>
       </c>
       <c r="D880">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E880" t="s">
         <v>30</v>
@@ -19057,7 +19057,7 @@
         <v>29</v>
       </c>
       <c r="D881">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E881" t="s">
         <v>30</v>
@@ -19074,7 +19074,7 @@
         <v>29</v>
       </c>
       <c r="D882">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E882" t="s">
         <v>30</v>
@@ -19091,7 +19091,7 @@
         <v>29</v>
       </c>
       <c r="D883">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E883" t="s">
         <v>30</v>
@@ -19108,7 +19108,7 @@
         <v>29</v>
       </c>
       <c r="D884">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E884" t="s">
         <v>30</v>
@@ -19125,7 +19125,7 @@
         <v>29</v>
       </c>
       <c r="D885">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E885" t="s">
         <v>30</v>
@@ -19142,7 +19142,7 @@
         <v>29</v>
       </c>
       <c r="D886">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E886" t="s">
         <v>30</v>
@@ -19159,7 +19159,7 @@
         <v>29</v>
       </c>
       <c r="D887">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E887" t="s">
         <v>30</v>
@@ -19176,7 +19176,7 @@
         <v>29</v>
       </c>
       <c r="D888">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E888" t="s">
         <v>30</v>
@@ -19193,7 +19193,7 @@
         <v>29</v>
       </c>
       <c r="D889">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E889" t="s">
         <v>30</v>
@@ -19210,7 +19210,7 @@
         <v>29</v>
       </c>
       <c r="D890">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E890" t="s">
         <v>30</v>
@@ -19227,7 +19227,7 @@
         <v>29</v>
       </c>
       <c r="D891">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E891" t="s">
         <v>30</v>
@@ -19244,7 +19244,7 @@
         <v>29</v>
       </c>
       <c r="D892">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E892" t="s">
         <v>30</v>
@@ -19261,7 +19261,7 @@
         <v>29</v>
       </c>
       <c r="D893">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E893" t="s">
         <v>30</v>
@@ -19278,7 +19278,7 @@
         <v>29</v>
       </c>
       <c r="D894">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E894" t="s">
         <v>30</v>
@@ -19295,7 +19295,7 @@
         <v>29</v>
       </c>
       <c r="D895">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E895" t="s">
         <v>30</v>
@@ -19329,7 +19329,7 @@
         <v>29</v>
       </c>
       <c r="D897">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E897" t="s">
         <v>30</v>
@@ -19346,7 +19346,7 @@
         <v>29</v>
       </c>
       <c r="D898">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E898" t="s">
         <v>30</v>
@@ -19363,7 +19363,7 @@
         <v>29</v>
       </c>
       <c r="D899">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E899" t="s">
         <v>30</v>
@@ -19380,7 +19380,7 @@
         <v>29</v>
       </c>
       <c r="D900">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E900" t="s">
         <v>30</v>
@@ -19397,7 +19397,7 @@
         <v>29</v>
       </c>
       <c r="D901">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E901" t="s">
         <v>30</v>
@@ -19414,7 +19414,7 @@
         <v>29</v>
       </c>
       <c r="D902">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E902" t="s">
         <v>30</v>
@@ -19431,7 +19431,7 @@
         <v>29</v>
       </c>
       <c r="D903">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E903" t="s">
         <v>30</v>
@@ -19448,7 +19448,7 @@
         <v>29</v>
       </c>
       <c r="D904">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E904" t="s">
         <v>30</v>
@@ -19465,7 +19465,7 @@
         <v>29</v>
       </c>
       <c r="D905">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E905" t="s">
         <v>30</v>
@@ -19482,7 +19482,7 @@
         <v>29</v>
       </c>
       <c r="D906">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E906" t="s">
         <v>30</v>
@@ -19499,7 +19499,7 @@
         <v>29</v>
       </c>
       <c r="D907">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E907" t="s">
         <v>30</v>
@@ -19516,7 +19516,7 @@
         <v>29</v>
       </c>
       <c r="D908">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E908" t="s">
         <v>30</v>
@@ -19533,7 +19533,7 @@
         <v>29</v>
       </c>
       <c r="D909">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E909" t="s">
         <v>30</v>
@@ -19550,7 +19550,7 @@
         <v>29</v>
       </c>
       <c r="D910">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E910" t="s">
         <v>30</v>
@@ -19567,7 +19567,7 @@
         <v>29</v>
       </c>
       <c r="D911">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E911" t="s">
         <v>30</v>
@@ -19584,7 +19584,7 @@
         <v>29</v>
       </c>
       <c r="D912">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E912" t="s">
         <v>30</v>
@@ -19601,7 +19601,7 @@
         <v>29</v>
       </c>
       <c r="D913">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E913" t="s">
         <v>30</v>
@@ -19618,7 +19618,7 @@
         <v>29</v>
       </c>
       <c r="D914">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E914" t="s">
         <v>30</v>
@@ -19635,7 +19635,7 @@
         <v>29</v>
       </c>
       <c r="D915">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E915" t="s">
         <v>30</v>
@@ -19652,7 +19652,7 @@
         <v>29</v>
       </c>
       <c r="D916">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E916" t="s">
         <v>30</v>
@@ -19686,7 +19686,7 @@
         <v>29</v>
       </c>
       <c r="D918">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E918" t="s">
         <v>30</v>
@@ -19703,7 +19703,7 @@
         <v>29</v>
       </c>
       <c r="D919">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E919" t="s">
         <v>30</v>
@@ -19720,7 +19720,7 @@
         <v>29</v>
       </c>
       <c r="D920">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E920" t="s">
         <v>30</v>
@@ -19737,7 +19737,7 @@
         <v>29</v>
       </c>
       <c r="D921">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E921" t="s">
         <v>30</v>
@@ -19754,7 +19754,7 @@
         <v>29</v>
       </c>
       <c r="D922">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E922" t="s">
         <v>30</v>
@@ -19771,7 +19771,7 @@
         <v>29</v>
       </c>
       <c r="D923">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E923" t="s">
         <v>30</v>
@@ -19805,7 +19805,7 @@
         <v>29</v>
       </c>
       <c r="D925">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E925" t="s">
         <v>30</v>
@@ -19822,7 +19822,7 @@
         <v>29</v>
       </c>
       <c r="D926">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E926" t="s">
         <v>30</v>
@@ -19839,7 +19839,7 @@
         <v>29</v>
       </c>
       <c r="D927">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E927" t="s">
         <v>30</v>
@@ -19856,7 +19856,7 @@
         <v>29</v>
       </c>
       <c r="D928">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E928" t="s">
         <v>30</v>
@@ -19873,7 +19873,7 @@
         <v>29</v>
       </c>
       <c r="D929">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E929" t="s">
         <v>30</v>
@@ -19890,7 +19890,7 @@
         <v>29</v>
       </c>
       <c r="D930">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E930" t="s">
         <v>30</v>
@@ -19907,7 +19907,7 @@
         <v>29</v>
       </c>
       <c r="D931">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E931" t="s">
         <v>30</v>
@@ -19924,7 +19924,7 @@
         <v>29</v>
       </c>
       <c r="D932">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E932" t="s">
         <v>30</v>
@@ -19941,7 +19941,7 @@
         <v>29</v>
       </c>
       <c r="D933">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E933" t="s">
         <v>30</v>
@@ -19958,7 +19958,7 @@
         <v>29</v>
       </c>
       <c r="D934">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E934" t="s">
         <v>30</v>
@@ -19975,7 +19975,7 @@
         <v>29</v>
       </c>
       <c r="D935">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E935" t="s">
         <v>30</v>
@@ -19992,7 +19992,7 @@
         <v>29</v>
       </c>
       <c r="D936">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E936" t="s">
         <v>30</v>
@@ -20009,7 +20009,7 @@
         <v>29</v>
       </c>
       <c r="D937">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E937" t="s">
         <v>30</v>
@@ -20026,7 +20026,7 @@
         <v>29</v>
       </c>
       <c r="D938">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E938" t="s">
         <v>30</v>
@@ -20043,7 +20043,7 @@
         <v>29</v>
       </c>
       <c r="D939">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E939" t="s">
         <v>30</v>
@@ -20060,7 +20060,7 @@
         <v>29</v>
       </c>
       <c r="D940">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E940" t="s">
         <v>30</v>
@@ -20077,7 +20077,7 @@
         <v>29</v>
       </c>
       <c r="D941">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E941" t="s">
         <v>30</v>
@@ -20094,7 +20094,7 @@
         <v>29</v>
       </c>
       <c r="D942">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E942" t="s">
         <v>30</v>
@@ -20111,7 +20111,7 @@
         <v>29</v>
       </c>
       <c r="D943">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E943" t="s">
         <v>30</v>
@@ -20128,7 +20128,7 @@
         <v>29</v>
       </c>
       <c r="D944">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E944" t="s">
         <v>30</v>
@@ -20145,7 +20145,7 @@
         <v>29</v>
       </c>
       <c r="D945">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E945" t="s">
         <v>30</v>
@@ -20162,7 +20162,7 @@
         <v>29</v>
       </c>
       <c r="D946">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E946" t="s">
         <v>30</v>
@@ -20179,7 +20179,7 @@
         <v>29</v>
       </c>
       <c r="D947">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E947" t="s">
         <v>30</v>
@@ -20196,7 +20196,7 @@
         <v>29</v>
       </c>
       <c r="D948">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E948" t="s">
         <v>30</v>
@@ -20230,7 +20230,7 @@
         <v>29</v>
       </c>
       <c r="D950">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E950" t="s">
         <v>30</v>
@@ -20247,7 +20247,7 @@
         <v>29</v>
       </c>
       <c r="D951">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E951" t="s">
         <v>30</v>
@@ -20264,7 +20264,7 @@
         <v>29</v>
       </c>
       <c r="D952">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E952" t="s">
         <v>30</v>
@@ -20281,7 +20281,7 @@
         <v>29</v>
       </c>
       <c r="D953">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E953" t="s">
         <v>30</v>
@@ -20298,7 +20298,7 @@
         <v>29</v>
       </c>
       <c r="D954">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E954" t="s">
         <v>30</v>
@@ -20315,7 +20315,7 @@
         <v>29</v>
       </c>
       <c r="D955">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E955" t="s">
         <v>30</v>
@@ -20332,7 +20332,7 @@
         <v>29</v>
       </c>
       <c r="D956">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E956" t="s">
         <v>30</v>
@@ -20349,7 +20349,7 @@
         <v>29</v>
       </c>
       <c r="D957">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E957" t="s">
         <v>30</v>
@@ -20366,7 +20366,7 @@
         <v>29</v>
       </c>
       <c r="D958">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E958" t="s">
         <v>30</v>
@@ -20383,7 +20383,7 @@
         <v>29</v>
       </c>
       <c r="D959">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E959" t="s">
         <v>30</v>
@@ -20400,7 +20400,7 @@
         <v>29</v>
       </c>
       <c r="D960">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E960" t="s">
         <v>30</v>
@@ -20417,7 +20417,7 @@
         <v>29</v>
       </c>
       <c r="D961">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E961" t="s">
         <v>30</v>
@@ -20434,7 +20434,7 @@
         <v>29</v>
       </c>
       <c r="D962">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E962" t="s">
         <v>30</v>
@@ -20451,7 +20451,7 @@
         <v>29</v>
       </c>
       <c r="D963">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E963" t="s">
         <v>30</v>
@@ -20468,7 +20468,7 @@
         <v>29</v>
       </c>
       <c r="D964">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E964" t="s">
         <v>30</v>
@@ -20485,7 +20485,7 @@
         <v>29</v>
       </c>
       <c r="D965">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E965" t="s">
         <v>30</v>
@@ -20502,7 +20502,7 @@
         <v>29</v>
       </c>
       <c r="D966">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E966" t="s">
         <v>30</v>
@@ -20519,7 +20519,7 @@
         <v>29</v>
       </c>
       <c r="D967">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E967" t="s">
         <v>30</v>
@@ -20536,7 +20536,7 @@
         <v>29</v>
       </c>
       <c r="D968">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E968" t="s">
         <v>30</v>
@@ -20553,7 +20553,7 @@
         <v>29</v>
       </c>
       <c r="D969">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E969" t="s">
         <v>30</v>
@@ -20570,7 +20570,7 @@
         <v>29</v>
       </c>
       <c r="D970">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E970" t="s">
         <v>30</v>
@@ -20587,7 +20587,7 @@
         <v>29</v>
       </c>
       <c r="D971">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E971" t="s">
         <v>30</v>
@@ -20604,7 +20604,7 @@
         <v>29</v>
       </c>
       <c r="D972">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E972" t="s">
         <v>30</v>
@@ -20621,7 +20621,7 @@
         <v>29</v>
       </c>
       <c r="D973">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E973" t="s">
         <v>30</v>
@@ -20638,7 +20638,7 @@
         <v>29</v>
       </c>
       <c r="D974">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E974" t="s">
         <v>30</v>
@@ -20655,7 +20655,7 @@
         <v>29</v>
       </c>
       <c r="D975">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E975" t="s">
         <v>30</v>
@@ -20672,7 +20672,7 @@
         <v>29</v>
       </c>
       <c r="D976">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E976" t="s">
         <v>30</v>
@@ -20689,7 +20689,7 @@
         <v>29</v>
       </c>
       <c r="D977">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E977" t="s">
         <v>30</v>
@@ -20706,7 +20706,7 @@
         <v>29</v>
       </c>
       <c r="D978">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E978" t="s">
         <v>30</v>
@@ -20723,7 +20723,7 @@
         <v>29</v>
       </c>
       <c r="D979">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E979" t="s">
         <v>30</v>
@@ -20740,7 +20740,7 @@
         <v>29</v>
       </c>
       <c r="D980">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E980" t="s">
         <v>30</v>
@@ -20757,7 +20757,7 @@
         <v>29</v>
       </c>
       <c r="D981">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E981" t="s">
         <v>30</v>
@@ -20774,7 +20774,7 @@
         <v>29</v>
       </c>
       <c r="D982">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E982" t="s">
         <v>30</v>
@@ -20791,7 +20791,7 @@
         <v>29</v>
       </c>
       <c r="D983">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E983" t="s">
         <v>30</v>
@@ -20808,7 +20808,7 @@
         <v>29</v>
       </c>
       <c r="D984">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E984" t="s">
         <v>30</v>
@@ -20825,7 +20825,7 @@
         <v>29</v>
       </c>
       <c r="D985">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E985" t="s">
         <v>30</v>
@@ -20842,7 +20842,7 @@
         <v>29</v>
       </c>
       <c r="D986">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E986" t="s">
         <v>30</v>
@@ -20859,7 +20859,7 @@
         <v>29</v>
       </c>
       <c r="D987">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E987" t="s">
         <v>30</v>
@@ -20876,7 +20876,7 @@
         <v>29</v>
       </c>
       <c r="D988">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E988" t="s">
         <v>30</v>
@@ -20893,7 +20893,7 @@
         <v>29</v>
       </c>
       <c r="D989">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E989" t="s">
         <v>30</v>
@@ -20910,7 +20910,7 @@
         <v>29</v>
       </c>
       <c r="D990">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E990" t="s">
         <v>30</v>
@@ -20927,7 +20927,7 @@
         <v>29</v>
       </c>
       <c r="D991">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E991" t="s">
         <v>30</v>
@@ -20944,7 +20944,7 @@
         <v>29</v>
       </c>
       <c r="D992">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E992" t="s">
         <v>30</v>
@@ -20961,7 +20961,7 @@
         <v>29</v>
       </c>
       <c r="D993">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E993" t="s">
         <v>30</v>
@@ -20978,7 +20978,7 @@
         <v>29</v>
       </c>
       <c r="D994">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E994" t="s">
         <v>30</v>
@@ -20995,7 +20995,7 @@
         <v>29</v>
       </c>
       <c r="D995">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E995" t="s">
         <v>30</v>
@@ -21012,7 +21012,7 @@
         <v>29</v>
       </c>
       <c r="D996">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E996" t="s">
         <v>30</v>
@@ -21029,7 +21029,7 @@
         <v>29</v>
       </c>
       <c r="D997">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E997" t="s">
         <v>30</v>
@@ -21046,7 +21046,7 @@
         <v>29</v>
       </c>
       <c r="D998">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E998" t="s">
         <v>30</v>
@@ -21063,7 +21063,7 @@
         <v>29</v>
       </c>
       <c r="D999">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E999" t="s">
         <v>30</v>
@@ -21080,7 +21080,7 @@
         <v>29</v>
       </c>
       <c r="D1000">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1000" t="s">
         <v>30</v>
@@ -21097,7 +21097,7 @@
         <v>29</v>
       </c>
       <c r="D1001">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E1001" t="s">
         <v>30</v>
@@ -21114,7 +21114,7 @@
         <v>29</v>
       </c>
       <c r="D1002">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E1002" t="s">
         <v>30</v>
@@ -21131,7 +21131,7 @@
         <v>29</v>
       </c>
       <c r="D1003">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1003" t="s">
         <v>30</v>
@@ -21148,7 +21148,7 @@
         <v>29</v>
       </c>
       <c r="D1004">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E1004" t="s">
         <v>30</v>
@@ -21165,7 +21165,7 @@
         <v>29</v>
       </c>
       <c r="D1005">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1005" t="s">
         <v>30</v>
@@ -21182,7 +21182,7 @@
         <v>29</v>
       </c>
       <c r="D1006">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1006" t="s">
         <v>30</v>
@@ -21199,7 +21199,7 @@
         <v>29</v>
       </c>
       <c r="D1007">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E1007" t="s">
         <v>30</v>
@@ -21216,7 +21216,7 @@
         <v>29</v>
       </c>
       <c r="D1008">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1008" t="s">
         <v>30</v>
@@ -21233,7 +21233,7 @@
         <v>29</v>
       </c>
       <c r="D1009">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1009" t="s">
         <v>30</v>
@@ -21250,7 +21250,7 @@
         <v>29</v>
       </c>
       <c r="D1010">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1010" t="s">
         <v>30</v>
@@ -21267,7 +21267,7 @@
         <v>29</v>
       </c>
       <c r="D1011">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E1011" t="s">
         <v>30</v>
@@ -21284,7 +21284,7 @@
         <v>29</v>
       </c>
       <c r="D1012">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1012" t="s">
         <v>30</v>
@@ -21301,7 +21301,7 @@
         <v>29</v>
       </c>
       <c r="D1013">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1013" t="s">
         <v>30</v>
@@ -21318,7 +21318,7 @@
         <v>29</v>
       </c>
       <c r="D1014">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E1014" t="s">
         <v>30</v>
@@ -21335,7 +21335,7 @@
         <v>29</v>
       </c>
       <c r="D1015">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1015" t="s">
         <v>30</v>
@@ -21352,7 +21352,7 @@
         <v>29</v>
       </c>
       <c r="D1016">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1016" t="s">
         <v>30</v>
@@ -21369,7 +21369,7 @@
         <v>29</v>
       </c>
       <c r="D1017">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1017" t="s">
         <v>30</v>
@@ -21403,7 +21403,7 @@
         <v>29</v>
       </c>
       <c r="D1019">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1019" t="s">
         <v>30</v>
@@ -21420,7 +21420,7 @@
         <v>29</v>
       </c>
       <c r="D1020">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E1020" t="s">
         <v>30</v>
@@ -21437,7 +21437,7 @@
         <v>29</v>
       </c>
       <c r="D1021">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1021" t="s">
         <v>30</v>
@@ -21454,7 +21454,7 @@
         <v>29</v>
       </c>
       <c r="D1022">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E1022" t="s">
         <v>30</v>
@@ -21471,7 +21471,7 @@
         <v>29</v>
       </c>
       <c r="D1023">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E1023" t="s">
         <v>30</v>
@@ -21488,7 +21488,7 @@
         <v>29</v>
       </c>
       <c r="D1024">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E1024" t="s">
         <v>30</v>
@@ -21505,7 +21505,7 @@
         <v>29</v>
       </c>
       <c r="D1025">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1025" t="s">
         <v>30</v>
@@ -21522,7 +21522,7 @@
         <v>29</v>
       </c>
       <c r="D1026">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1026" t="s">
         <v>30</v>
@@ -21539,7 +21539,7 @@
         <v>29</v>
       </c>
       <c r="D1027">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1027" t="s">
         <v>30</v>
@@ -21556,7 +21556,7 @@
         <v>29</v>
       </c>
       <c r="D1028">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E1028" t="s">
         <v>30</v>
@@ -21573,7 +21573,7 @@
         <v>29</v>
       </c>
       <c r="D1029">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1029" t="s">
         <v>30</v>
@@ -21590,7 +21590,7 @@
         <v>29</v>
       </c>
       <c r="D1030">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E1030" t="s">
         <v>30</v>
@@ -21607,7 +21607,7 @@
         <v>29</v>
       </c>
       <c r="D1031">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1031" t="s">
         <v>30</v>
@@ -21624,7 +21624,7 @@
         <v>29</v>
       </c>
       <c r="D1032">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E1032" t="s">
         <v>30</v>
@@ -21641,7 +21641,7 @@
         <v>29</v>
       </c>
       <c r="D1033">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1033" t="s">
         <v>30</v>
@@ -21658,7 +21658,7 @@
         <v>29</v>
       </c>
       <c r="D1034">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E1034" t="s">
         <v>30</v>
@@ -21675,7 +21675,7 @@
         <v>29</v>
       </c>
       <c r="D1035">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1035" t="s">
         <v>30</v>
@@ -21692,7 +21692,7 @@
         <v>29</v>
       </c>
       <c r="D1036">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1036" t="s">
         <v>30</v>
@@ -21709,7 +21709,7 @@
         <v>29</v>
       </c>
       <c r="D1037">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1037" t="s">
         <v>30</v>
@@ -21726,7 +21726,7 @@
         <v>29</v>
       </c>
       <c r="D1038">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E1038" t="s">
         <v>30</v>
@@ -21743,7 +21743,7 @@
         <v>29</v>
       </c>
       <c r="D1039">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1039" t="s">
         <v>30</v>
@@ -21760,7 +21760,7 @@
         <v>29</v>
       </c>
       <c r="D1040">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E1040" t="s">
         <v>30</v>
@@ -21777,7 +21777,7 @@
         <v>29</v>
       </c>
       <c r="D1041">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1041" t="s">
         <v>30</v>
@@ -21794,7 +21794,7 @@
         <v>29</v>
       </c>
       <c r="D1042">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1042" t="s">
         <v>30</v>
@@ -21811,7 +21811,7 @@
         <v>29</v>
       </c>
       <c r="D1043">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1043" t="s">
         <v>30</v>
@@ -21828,7 +21828,7 @@
         <v>29</v>
       </c>
       <c r="D1044">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E1044" t="s">
         <v>30</v>
@@ -21845,7 +21845,7 @@
         <v>29</v>
       </c>
       <c r="D1045">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1045" t="s">
         <v>30</v>
@@ -21862,7 +21862,7 @@
         <v>29</v>
       </c>
       <c r="D1046">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E1046" t="s">
         <v>30</v>
@@ -21879,7 +21879,7 @@
         <v>29</v>
       </c>
       <c r="D1047">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1047" t="s">
         <v>30</v>
@@ -21896,7 +21896,7 @@
         <v>29</v>
       </c>
       <c r="D1048">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1048" t="s">
         <v>30</v>
@@ -21913,7 +21913,7 @@
         <v>29</v>
       </c>
       <c r="D1049">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1049" t="s">
         <v>30</v>
@@ -21930,7 +21930,7 @@
         <v>29</v>
       </c>
       <c r="D1050">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1050" t="s">
         <v>30</v>
@@ -21947,7 +21947,7 @@
         <v>29</v>
       </c>
       <c r="D1051">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1051" t="s">
         <v>30</v>
@@ -21964,7 +21964,7 @@
         <v>29</v>
       </c>
       <c r="D1052">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1052" t="s">
         <v>30</v>
@@ -21981,7 +21981,7 @@
         <v>29</v>
       </c>
       <c r="D1053">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1053" t="s">
         <v>30</v>
@@ -21998,7 +21998,7 @@
         <v>29</v>
       </c>
       <c r="D1054">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E1054" t="s">
         <v>30</v>
@@ -22015,7 +22015,7 @@
         <v>29</v>
       </c>
       <c r="D1055">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E1055" t="s">
         <v>30</v>
@@ -22032,7 +22032,7 @@
         <v>29</v>
       </c>
       <c r="D1056">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1056" t="s">
         <v>30</v>
@@ -22049,7 +22049,7 @@
         <v>29</v>
       </c>
       <c r="D1057">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1057" t="s">
         <v>30</v>
@@ -22066,7 +22066,7 @@
         <v>29</v>
       </c>
       <c r="D1058">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1058" t="s">
         <v>30</v>
@@ -22100,7 +22100,7 @@
         <v>29</v>
       </c>
       <c r="D1060">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E1060" t="s">
         <v>30</v>
@@ -22117,7 +22117,7 @@
         <v>29</v>
       </c>
       <c r="D1061">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1061" t="s">
         <v>30</v>
@@ -22134,7 +22134,7 @@
         <v>29</v>
       </c>
       <c r="D1062">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E1062" t="s">
         <v>30</v>
@@ -22151,7 +22151,7 @@
         <v>29</v>
       </c>
       <c r="D1063">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E1063" t="s">
         <v>30</v>
@@ -22168,7 +22168,7 @@
         <v>29</v>
       </c>
       <c r="D1064">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E1064" t="s">
         <v>30</v>
@@ -22185,7 +22185,7 @@
         <v>29</v>
       </c>
       <c r="D1065">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1065" t="s">
         <v>30</v>
@@ -22202,7 +22202,7 @@
         <v>29</v>
       </c>
       <c r="D1066">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1066" t="s">
         <v>30</v>
@@ -22219,7 +22219,7 @@
         <v>29</v>
       </c>
       <c r="D1067">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1067" t="s">
         <v>30</v>
@@ -22236,7 +22236,7 @@
         <v>29</v>
       </c>
       <c r="D1068">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1068" t="s">
         <v>30</v>
@@ -22253,7 +22253,7 @@
         <v>29</v>
       </c>
       <c r="D1069">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E1069" t="s">
         <v>30</v>
@@ -22270,7 +22270,7 @@
         <v>29</v>
       </c>
       <c r="D1070">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E1070" t="s">
         <v>30</v>
@@ -22287,7 +22287,7 @@
         <v>29</v>
       </c>
       <c r="D1071">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1071" t="s">
         <v>30</v>
@@ -22304,7 +22304,7 @@
         <v>29</v>
       </c>
       <c r="D1072">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1072" t="s">
         <v>30</v>
@@ -22321,7 +22321,7 @@
         <v>29</v>
       </c>
       <c r="D1073">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E1073" t="s">
         <v>30</v>
@@ -22355,7 +22355,7 @@
         <v>29</v>
       </c>
       <c r="D1075">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E1075" t="s">
         <v>30</v>
@@ -22372,7 +22372,7 @@
         <v>29</v>
       </c>
       <c r="D1076">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1076" t="s">
         <v>30</v>
@@ -22389,7 +22389,7 @@
         <v>29</v>
       </c>
       <c r="D1077">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1077" t="s">
         <v>30</v>
@@ -22406,7 +22406,7 @@
         <v>29</v>
       </c>
       <c r="D1078">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E1078" t="s">
         <v>30</v>
@@ -22423,7 +22423,7 @@
         <v>29</v>
       </c>
       <c r="D1079">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1079" t="s">
         <v>30</v>
@@ -22440,7 +22440,7 @@
         <v>29</v>
       </c>
       <c r="D1080">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1080" t="s">
         <v>30</v>
@@ -22457,7 +22457,7 @@
         <v>29</v>
       </c>
       <c r="D1081">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1081" t="s">
         <v>30</v>
@@ -22474,7 +22474,7 @@
         <v>29</v>
       </c>
       <c r="D1082">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1082" t="s">
         <v>30</v>
@@ -22491,7 +22491,7 @@
         <v>29</v>
       </c>
       <c r="D1083">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1083" t="s">
         <v>30</v>
@@ -22508,7 +22508,7 @@
         <v>29</v>
       </c>
       <c r="D1084">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1084" t="s">
         <v>30</v>
@@ -22525,7 +22525,7 @@
         <v>29</v>
       </c>
       <c r="D1085">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E1085" t="s">
         <v>30</v>
@@ -22542,7 +22542,7 @@
         <v>29</v>
       </c>
       <c r="D1086">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1086" t="s">
         <v>30</v>
@@ -22559,7 +22559,7 @@
         <v>29</v>
       </c>
       <c r="D1087">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1087" t="s">
         <v>30</v>
@@ -22576,7 +22576,7 @@
         <v>29</v>
       </c>
       <c r="D1088">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E1088" t="s">
         <v>30</v>
@@ -22593,7 +22593,7 @@
         <v>29</v>
       </c>
       <c r="D1089">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1089" t="s">
         <v>30</v>
@@ -22610,7 +22610,7 @@
         <v>29</v>
       </c>
       <c r="D1090">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1090" t="s">
         <v>30</v>
@@ -22627,7 +22627,7 @@
         <v>29</v>
       </c>
       <c r="D1091">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1091" t="s">
         <v>30</v>
@@ -22644,7 +22644,7 @@
         <v>29</v>
       </c>
       <c r="D1092">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E1092" t="s">
         <v>30</v>
@@ -22661,7 +22661,7 @@
         <v>29</v>
       </c>
       <c r="D1093">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E1093" t="s">
         <v>30</v>
@@ -22678,7 +22678,7 @@
         <v>29</v>
       </c>
       <c r="D1094">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1094" t="s">
         <v>30</v>
@@ -22695,7 +22695,7 @@
         <v>29</v>
       </c>
       <c r="D1095">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1095" t="s">
         <v>30</v>
@@ -22712,7 +22712,7 @@
         <v>29</v>
       </c>
       <c r="D1096">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1096" t="s">
         <v>30</v>
@@ -22729,7 +22729,7 @@
         <v>29</v>
       </c>
       <c r="D1097">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1097" t="s">
         <v>30</v>
@@ -22746,7 +22746,7 @@
         <v>29</v>
       </c>
       <c r="D1098">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1098" t="s">
         <v>30</v>
@@ -22763,7 +22763,7 @@
         <v>29</v>
       </c>
       <c r="D1099">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1099" t="s">
         <v>30</v>
@@ -22780,7 +22780,7 @@
         <v>29</v>
       </c>
       <c r="D1100">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E1100" t="s">
         <v>30</v>
@@ -22797,7 +22797,7 @@
         <v>29</v>
       </c>
       <c r="D1101">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1101" t="s">
         <v>30</v>
@@ -22814,7 +22814,7 @@
         <v>29</v>
       </c>
       <c r="D1102">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E1102" t="s">
         <v>30</v>
@@ -22831,7 +22831,7 @@
         <v>29</v>
       </c>
       <c r="D1103">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E1103" t="s">
         <v>30</v>
@@ -22848,7 +22848,7 @@
         <v>29</v>
       </c>
       <c r="D1104">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1104" t="s">
         <v>30</v>
@@ -22865,7 +22865,7 @@
         <v>29</v>
       </c>
       <c r="D1105">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1105" t="s">
         <v>30</v>
@@ -22882,7 +22882,7 @@
         <v>29</v>
       </c>
       <c r="D1106">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1106" t="s">
         <v>30</v>
@@ -22899,7 +22899,7 @@
         <v>29</v>
       </c>
       <c r="D1107">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1107" t="s">
         <v>30</v>
@@ -22916,7 +22916,7 @@
         <v>29</v>
       </c>
       <c r="D1108">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1108" t="s">
         <v>30</v>
@@ -22933,7 +22933,7 @@
         <v>29</v>
       </c>
       <c r="D1109">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1109" t="s">
         <v>30</v>
@@ -22950,7 +22950,7 @@
         <v>29</v>
       </c>
       <c r="D1110">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E1110" t="s">
         <v>30</v>
@@ -22967,7 +22967,7 @@
         <v>29</v>
       </c>
       <c r="D1111">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1111" t="s">
         <v>30</v>
@@ -22984,7 +22984,7 @@
         <v>29</v>
       </c>
       <c r="D1112">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1112" t="s">
         <v>30</v>

--- a/reports/latest/android-report.xlsx
+++ b/reports/latest/android-report.xlsx
@@ -4114,7 +4114,7 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>1006</v>
+        <v>713</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -4131,7 +4131,7 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -4148,7 +4148,7 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -4165,7 +4165,7 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -4182,7 +4182,7 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -4199,7 +4199,7 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
         <v>30</v>
@@ -4216,7 +4216,7 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -4233,7 +4233,7 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -4250,7 +4250,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
@@ -4267,7 +4267,7 @@
         <v>29</v>
       </c>
       <c r="D11">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -4284,7 +4284,7 @@
         <v>29</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
         <v>30</v>
@@ -4301,7 +4301,7 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -4318,7 +4318,7 @@
         <v>29</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -4352,7 +4352,7 @@
         <v>29</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
@@ -4369,7 +4369,7 @@
         <v>29</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
@@ -4386,7 +4386,7 @@
         <v>29</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -4403,7 +4403,7 @@
         <v>29</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
@@ -4420,7 +4420,7 @@
         <v>29</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
         <v>30</v>
@@ -4437,7 +4437,7 @@
         <v>29</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
         <v>30</v>
@@ -4454,7 +4454,7 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
         <v>30</v>
@@ -4471,7 +4471,7 @@
         <v>29</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
         <v>30</v>
@@ -4488,7 +4488,7 @@
         <v>29</v>
       </c>
       <c r="D24">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E24" t="s">
         <v>30</v>
@@ -4505,7 +4505,7 @@
         <v>29</v>
       </c>
       <c r="D25">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
         <v>30</v>
@@ -4522,7 +4522,7 @@
         <v>29</v>
       </c>
       <c r="D26">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E26" t="s">
         <v>30</v>
@@ -4539,7 +4539,7 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
         <v>30</v>
@@ -4556,7 +4556,7 @@
         <v>29</v>
       </c>
       <c r="D28">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
         <v>30</v>
@@ -4573,7 +4573,7 @@
         <v>29</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
         <v>30</v>
@@ -4590,7 +4590,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
         <v>30</v>
@@ -4607,7 +4607,7 @@
         <v>29</v>
       </c>
       <c r="D31">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
         <v>30</v>
@@ -4624,7 +4624,7 @@
         <v>29</v>
       </c>
       <c r="D32">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
         <v>30</v>
@@ -4641,7 +4641,7 @@
         <v>29</v>
       </c>
       <c r="D33">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E33" t="s">
         <v>30</v>
@@ -4658,7 +4658,7 @@
         <v>29</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E34" t="s">
         <v>30</v>
@@ -4675,7 +4675,7 @@
         <v>29</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
         <v>30</v>
@@ -4692,7 +4692,7 @@
         <v>29</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
         <v>30</v>
@@ -4709,7 +4709,7 @@
         <v>29</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E37" t="s">
         <v>30</v>
@@ -4726,7 +4726,7 @@
         <v>29</v>
       </c>
       <c r="D38">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
         <v>30</v>
@@ -4743,7 +4743,7 @@
         <v>29</v>
       </c>
       <c r="D39">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E39" t="s">
         <v>30</v>
@@ -4760,7 +4760,7 @@
         <v>29</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E40" t="s">
         <v>30</v>
@@ -4777,7 +4777,7 @@
         <v>29</v>
       </c>
       <c r="D41">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E41" t="s">
         <v>30</v>
@@ -4794,7 +4794,7 @@
         <v>29</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E42" t="s">
         <v>30</v>
@@ -4811,7 +4811,7 @@
         <v>29</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E43" t="s">
         <v>30</v>
@@ -4828,7 +4828,7 @@
         <v>29</v>
       </c>
       <c r="D44">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E44" t="s">
         <v>30</v>
@@ -4845,7 +4845,7 @@
         <v>29</v>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
         <v>30</v>
@@ -4862,7 +4862,7 @@
         <v>29</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E46" t="s">
         <v>30</v>
@@ -4879,7 +4879,7 @@
         <v>29</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
         <v>30</v>
@@ -4896,7 +4896,7 @@
         <v>29</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E48" t="s">
         <v>30</v>
@@ -4913,7 +4913,7 @@
         <v>29</v>
       </c>
       <c r="D49">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E49" t="s">
         <v>30</v>
@@ -4930,7 +4930,7 @@
         <v>29</v>
       </c>
       <c r="D50">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
         <v>30</v>
@@ -4947,7 +4947,7 @@
         <v>29</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
         <v>30</v>
@@ -4964,7 +4964,7 @@
         <v>29</v>
       </c>
       <c r="D52">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E52" t="s">
         <v>30</v>
@@ -4981,7 +4981,7 @@
         <v>29</v>
       </c>
       <c r="D53">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E53" t="s">
         <v>30</v>
@@ -4998,7 +4998,7 @@
         <v>29</v>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E54" t="s">
         <v>30</v>
@@ -5015,7 +5015,7 @@
         <v>29</v>
       </c>
       <c r="D55">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E55" t="s">
         <v>30</v>
@@ -5032,7 +5032,7 @@
         <v>29</v>
       </c>
       <c r="D56">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E56" t="s">
         <v>30</v>
@@ -5066,7 +5066,7 @@
         <v>29</v>
       </c>
       <c r="D58">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E58" t="s">
         <v>30</v>
@@ -5083,7 +5083,7 @@
         <v>29</v>
       </c>
       <c r="D59">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E59" t="s">
         <v>30</v>
@@ -5100,7 +5100,7 @@
         <v>29</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E60" t="s">
         <v>30</v>
@@ -5117,7 +5117,7 @@
         <v>29</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E61" t="s">
         <v>30</v>
@@ -5134,7 +5134,7 @@
         <v>29</v>
       </c>
       <c r="D62">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E62" t="s">
         <v>30</v>
@@ -5151,7 +5151,7 @@
         <v>29</v>
       </c>
       <c r="D63">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
         <v>30</v>
@@ -5168,7 +5168,7 @@
         <v>29</v>
       </c>
       <c r="D64">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
         <v>30</v>
@@ -5185,7 +5185,7 @@
         <v>29</v>
       </c>
       <c r="D65">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
         <v>30</v>
@@ -5202,7 +5202,7 @@
         <v>29</v>
       </c>
       <c r="D66">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E66" t="s">
         <v>30</v>
@@ -5219,7 +5219,7 @@
         <v>29</v>
       </c>
       <c r="D67">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E67" t="s">
         <v>30</v>
@@ -5236,7 +5236,7 @@
         <v>29</v>
       </c>
       <c r="D68">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E68" t="s">
         <v>30</v>
@@ -5253,7 +5253,7 @@
         <v>29</v>
       </c>
       <c r="D69">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E69" t="s">
         <v>30</v>
@@ -5270,7 +5270,7 @@
         <v>29</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E70" t="s">
         <v>30</v>
@@ -5287,7 +5287,7 @@
         <v>29</v>
       </c>
       <c r="D71">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E71" t="s">
         <v>30</v>
@@ -5304,7 +5304,7 @@
         <v>29</v>
       </c>
       <c r="D72">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E72" t="s">
         <v>30</v>
@@ -5321,7 +5321,7 @@
         <v>29</v>
       </c>
       <c r="D73">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E73" t="s">
         <v>30</v>
@@ -5338,7 +5338,7 @@
         <v>29</v>
       </c>
       <c r="D74">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E74" t="s">
         <v>30</v>
@@ -5355,7 +5355,7 @@
         <v>29</v>
       </c>
       <c r="D75">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E75" t="s">
         <v>30</v>
@@ -5372,7 +5372,7 @@
         <v>29</v>
       </c>
       <c r="D76">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E76" t="s">
         <v>30</v>
@@ -5389,7 +5389,7 @@
         <v>29</v>
       </c>
       <c r="D77">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E77" t="s">
         <v>30</v>
@@ -5406,7 +5406,7 @@
         <v>29</v>
       </c>
       <c r="D78">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>30</v>
@@ -5423,7 +5423,7 @@
         <v>29</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E79" t="s">
         <v>30</v>
@@ -5440,7 +5440,7 @@
         <v>29</v>
       </c>
       <c r="D80">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E80" t="s">
         <v>30</v>
@@ -5457,7 +5457,7 @@
         <v>29</v>
       </c>
       <c r="D81">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E81" t="s">
         <v>30</v>
@@ -5474,7 +5474,7 @@
         <v>29</v>
       </c>
       <c r="D82">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E82" t="s">
         <v>30</v>
@@ -5491,7 +5491,7 @@
         <v>29</v>
       </c>
       <c r="D83">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E83" t="s">
         <v>30</v>
@@ -5508,7 +5508,7 @@
         <v>29</v>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E84" t="s">
         <v>30</v>
@@ -5525,7 +5525,7 @@
         <v>29</v>
       </c>
       <c r="D85">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E85" t="s">
         <v>30</v>
@@ -5542,7 +5542,7 @@
         <v>29</v>
       </c>
       <c r="D86">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E86" t="s">
         <v>30</v>
@@ -5576,7 +5576,7 @@
         <v>29</v>
       </c>
       <c r="D88">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E88" t="s">
         <v>30</v>
@@ -5593,7 +5593,7 @@
         <v>29</v>
       </c>
       <c r="D89">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E89" t="s">
         <v>30</v>
@@ -5610,7 +5610,7 @@
         <v>29</v>
       </c>
       <c r="D90">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E90" t="s">
         <v>30</v>
@@ -5627,7 +5627,7 @@
         <v>29</v>
       </c>
       <c r="D91">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E91" t="s">
         <v>30</v>
@@ -5644,7 +5644,7 @@
         <v>29</v>
       </c>
       <c r="D92">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
         <v>30</v>
@@ -5661,7 +5661,7 @@
         <v>29</v>
       </c>
       <c r="D93">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E93" t="s">
         <v>30</v>
@@ -5678,7 +5678,7 @@
         <v>29</v>
       </c>
       <c r="D94">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E94" t="s">
         <v>30</v>
@@ -5695,7 +5695,7 @@
         <v>29</v>
       </c>
       <c r="D95">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E95" t="s">
         <v>30</v>
@@ -5712,7 +5712,7 @@
         <v>29</v>
       </c>
       <c r="D96">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E96" t="s">
         <v>30</v>
@@ -5729,7 +5729,7 @@
         <v>29</v>
       </c>
       <c r="D97">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E97" t="s">
         <v>30</v>
@@ -5746,7 +5746,7 @@
         <v>29</v>
       </c>
       <c r="D98">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E98" t="s">
         <v>30</v>
@@ -5763,7 +5763,7 @@
         <v>29</v>
       </c>
       <c r="D99">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E99" t="s">
         <v>30</v>
@@ -5780,7 +5780,7 @@
         <v>29</v>
       </c>
       <c r="D100">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E100" t="s">
         <v>30</v>
@@ -5797,7 +5797,7 @@
         <v>29</v>
       </c>
       <c r="D101">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E101" t="s">
         <v>30</v>
@@ -5814,7 +5814,7 @@
         <v>29</v>
       </c>
       <c r="D102">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E102" t="s">
         <v>30</v>
@@ -5831,7 +5831,7 @@
         <v>29</v>
       </c>
       <c r="D103">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E103" t="s">
         <v>30</v>
@@ -5848,7 +5848,7 @@
         <v>29</v>
       </c>
       <c r="D104">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E104" t="s">
         <v>30</v>
@@ -5865,7 +5865,7 @@
         <v>29</v>
       </c>
       <c r="D105">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E105" t="s">
         <v>30</v>
@@ -5882,7 +5882,7 @@
         <v>29</v>
       </c>
       <c r="D106">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E106" t="s">
         <v>30</v>
@@ -5899,7 +5899,7 @@
         <v>29</v>
       </c>
       <c r="D107">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E107" t="s">
         <v>30</v>
@@ -5916,7 +5916,7 @@
         <v>29</v>
       </c>
       <c r="D108">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
         <v>30</v>
@@ -5933,7 +5933,7 @@
         <v>29</v>
       </c>
       <c r="D109">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E109" t="s">
         <v>30</v>
@@ -5950,7 +5950,7 @@
         <v>29</v>
       </c>
       <c r="D110">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E110" t="s">
         <v>30</v>
@@ -5967,7 +5967,7 @@
         <v>29</v>
       </c>
       <c r="D111">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E111" t="s">
         <v>30</v>
@@ -5984,7 +5984,7 @@
         <v>29</v>
       </c>
       <c r="D112">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E112" t="s">
         <v>30</v>
@@ -6001,7 +6001,7 @@
         <v>29</v>
       </c>
       <c r="D113">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E113" t="s">
         <v>30</v>
@@ -6018,7 +6018,7 @@
         <v>29</v>
       </c>
       <c r="D114">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E114" t="s">
         <v>30</v>
@@ -6035,7 +6035,7 @@
         <v>29</v>
       </c>
       <c r="D115">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E115" t="s">
         <v>30</v>
@@ -6069,7 +6069,7 @@
         <v>29</v>
       </c>
       <c r="D117">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E117" t="s">
         <v>30</v>
@@ -6086,7 +6086,7 @@
         <v>29</v>
       </c>
       <c r="D118">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E118" t="s">
         <v>30</v>
@@ -6103,7 +6103,7 @@
         <v>29</v>
       </c>
       <c r="D119">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E119" t="s">
         <v>30</v>
@@ -6120,7 +6120,7 @@
         <v>29</v>
       </c>
       <c r="D120">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E120" t="s">
         <v>30</v>
@@ -6154,7 +6154,7 @@
         <v>29</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E122" t="s">
         <v>30</v>
@@ -6171,7 +6171,7 @@
         <v>29</v>
       </c>
       <c r="D123">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E123" t="s">
         <v>30</v>
@@ -6188,7 +6188,7 @@
         <v>29</v>
       </c>
       <c r="D124">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E124" t="s">
         <v>30</v>
@@ -6222,7 +6222,7 @@
         <v>29</v>
       </c>
       <c r="D126">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E126" t="s">
         <v>30</v>
@@ -6239,7 +6239,7 @@
         <v>29</v>
       </c>
       <c r="D127">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E127" t="s">
         <v>30</v>
@@ -6256,7 +6256,7 @@
         <v>29</v>
       </c>
       <c r="D128">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E128" t="s">
         <v>30</v>
@@ -6273,7 +6273,7 @@
         <v>29</v>
       </c>
       <c r="D129">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E129" t="s">
         <v>30</v>
@@ -6290,7 +6290,7 @@
         <v>29</v>
       </c>
       <c r="D130">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E130" t="s">
         <v>30</v>
@@ -6307,7 +6307,7 @@
         <v>29</v>
       </c>
       <c r="D131">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E131" t="s">
         <v>30</v>
@@ -6324,7 +6324,7 @@
         <v>29</v>
       </c>
       <c r="D132">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E132" t="s">
         <v>30</v>
@@ -6341,7 +6341,7 @@
         <v>29</v>
       </c>
       <c r="D133">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E133" t="s">
         <v>30</v>
@@ -6358,7 +6358,7 @@
         <v>29</v>
       </c>
       <c r="D134">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E134" t="s">
         <v>30</v>
@@ -6375,7 +6375,7 @@
         <v>29</v>
       </c>
       <c r="D135">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E135" t="s">
         <v>30</v>
@@ -6392,7 +6392,7 @@
         <v>29</v>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E136" t="s">
         <v>30</v>
@@ -6409,7 +6409,7 @@
         <v>29</v>
       </c>
       <c r="D137">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E137" t="s">
         <v>30</v>
@@ -6443,7 +6443,7 @@
         <v>29</v>
       </c>
       <c r="D139">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E139" t="s">
         <v>30</v>
@@ -6460,7 +6460,7 @@
         <v>29</v>
       </c>
       <c r="D140">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E140" t="s">
         <v>30</v>
@@ -6477,7 +6477,7 @@
         <v>29</v>
       </c>
       <c r="D141">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E141" t="s">
         <v>30</v>
@@ -6494,7 +6494,7 @@
         <v>29</v>
       </c>
       <c r="D142">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E142" t="s">
         <v>30</v>
@@ -6511,7 +6511,7 @@
         <v>29</v>
       </c>
       <c r="D143">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E143" t="s">
         <v>30</v>
@@ -6528,7 +6528,7 @@
         <v>29</v>
       </c>
       <c r="D144">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E144" t="s">
         <v>30</v>
@@ -6545,7 +6545,7 @@
         <v>29</v>
       </c>
       <c r="D145">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E145" t="s">
         <v>30</v>
@@ -6562,7 +6562,7 @@
         <v>29</v>
       </c>
       <c r="D146">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E146" t="s">
         <v>30</v>
@@ -6579,7 +6579,7 @@
         <v>29</v>
       </c>
       <c r="D147">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E147" t="s">
         <v>30</v>
@@ -6596,7 +6596,7 @@
         <v>29</v>
       </c>
       <c r="D148">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E148" t="s">
         <v>30</v>
@@ -6613,7 +6613,7 @@
         <v>29</v>
       </c>
       <c r="D149">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E149" t="s">
         <v>30</v>
@@ -6630,7 +6630,7 @@
         <v>29</v>
       </c>
       <c r="D150">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E150" t="s">
         <v>30</v>
@@ -6647,7 +6647,7 @@
         <v>29</v>
       </c>
       <c r="D151">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E151" t="s">
         <v>30</v>
@@ -6664,7 +6664,7 @@
         <v>29</v>
       </c>
       <c r="D152">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E152" t="s">
         <v>30</v>
@@ -6681,7 +6681,7 @@
         <v>29</v>
       </c>
       <c r="D153">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E153" t="s">
         <v>30</v>
@@ -6698,7 +6698,7 @@
         <v>29</v>
       </c>
       <c r="D154">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E154" t="s">
         <v>30</v>
@@ -6715,7 +6715,7 @@
         <v>29</v>
       </c>
       <c r="D155">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E155" t="s">
         <v>30</v>
@@ -6732,7 +6732,7 @@
         <v>29</v>
       </c>
       <c r="D156">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E156" t="s">
         <v>30</v>
@@ -6749,7 +6749,7 @@
         <v>29</v>
       </c>
       <c r="D157">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E157" t="s">
         <v>30</v>
@@ -6766,7 +6766,7 @@
         <v>29</v>
       </c>
       <c r="D158">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E158" t="s">
         <v>30</v>
@@ -6783,7 +6783,7 @@
         <v>29</v>
       </c>
       <c r="D159">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s">
         <v>30</v>
@@ -6800,7 +6800,7 @@
         <v>29</v>
       </c>
       <c r="D160">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E160" t="s">
         <v>30</v>
@@ -6817,7 +6817,7 @@
         <v>29</v>
       </c>
       <c r="D161">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E161" t="s">
         <v>30</v>
@@ -6834,7 +6834,7 @@
         <v>29</v>
       </c>
       <c r="D162">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E162" t="s">
         <v>30</v>
@@ -6851,7 +6851,7 @@
         <v>29</v>
       </c>
       <c r="D163">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E163" t="s">
         <v>30</v>
@@ -6868,7 +6868,7 @@
         <v>29</v>
       </c>
       <c r="D164">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E164" t="s">
         <v>30</v>
@@ -6885,7 +6885,7 @@
         <v>29</v>
       </c>
       <c r="D165">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E165" t="s">
         <v>30</v>
@@ -6902,7 +6902,7 @@
         <v>29</v>
       </c>
       <c r="D166">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E166" t="s">
         <v>30</v>
@@ -6919,7 +6919,7 @@
         <v>29</v>
       </c>
       <c r="D167">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E167" t="s">
         <v>30</v>
@@ -6936,7 +6936,7 @@
         <v>29</v>
       </c>
       <c r="D168">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E168" t="s">
         <v>30</v>
@@ -6953,7 +6953,7 @@
         <v>29</v>
       </c>
       <c r="D169">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E169" t="s">
         <v>30</v>
@@ -6970,7 +6970,7 @@
         <v>29</v>
       </c>
       <c r="D170">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E170" t="s">
         <v>30</v>
@@ -6987,7 +6987,7 @@
         <v>29</v>
       </c>
       <c r="D171">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E171" t="s">
         <v>30</v>
@@ -7004,7 +7004,7 @@
         <v>29</v>
       </c>
       <c r="D172">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E172" t="s">
         <v>30</v>
@@ -7021,7 +7021,7 @@
         <v>29</v>
       </c>
       <c r="D173">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E173" t="s">
         <v>30</v>
@@ -7038,7 +7038,7 @@
         <v>29</v>
       </c>
       <c r="D174">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E174" t="s">
         <v>30</v>
@@ -7055,7 +7055,7 @@
         <v>29</v>
       </c>
       <c r="D175">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E175" t="s">
         <v>30</v>
@@ -7072,7 +7072,7 @@
         <v>29</v>
       </c>
       <c r="D176">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E176" t="s">
         <v>30</v>
@@ -7106,7 +7106,7 @@
         <v>29</v>
       </c>
       <c r="D178">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E178" t="s">
         <v>30</v>
@@ -7123,7 +7123,7 @@
         <v>29</v>
       </c>
       <c r="D179">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E179" t="s">
         <v>30</v>
@@ -7140,7 +7140,7 @@
         <v>29</v>
       </c>
       <c r="D180">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E180" t="s">
         <v>30</v>
@@ -7157,7 +7157,7 @@
         <v>29</v>
       </c>
       <c r="D181">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E181" t="s">
         <v>30</v>
@@ -7174,7 +7174,7 @@
         <v>29</v>
       </c>
       <c r="D182">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E182" t="s">
         <v>30</v>
@@ -7191,7 +7191,7 @@
         <v>29</v>
       </c>
       <c r="D183">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E183" t="s">
         <v>30</v>
@@ -7208,7 +7208,7 @@
         <v>29</v>
       </c>
       <c r="D184">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E184" t="s">
         <v>30</v>
@@ -7225,7 +7225,7 @@
         <v>29</v>
       </c>
       <c r="D185">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E185" t="s">
         <v>30</v>
@@ -7242,7 +7242,7 @@
         <v>29</v>
       </c>
       <c r="D186">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E186" t="s">
         <v>30</v>
@@ -7259,7 +7259,7 @@
         <v>29</v>
       </c>
       <c r="D187">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E187" t="s">
         <v>30</v>
@@ -7276,7 +7276,7 @@
         <v>29</v>
       </c>
       <c r="D188">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E188" t="s">
         <v>30</v>
@@ -7293,7 +7293,7 @@
         <v>29</v>
       </c>
       <c r="D189">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E189" t="s">
         <v>30</v>
@@ -7310,7 +7310,7 @@
         <v>29</v>
       </c>
       <c r="D190">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E190" t="s">
         <v>30</v>
@@ -7327,7 +7327,7 @@
         <v>29</v>
       </c>
       <c r="D191">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E191" t="s">
         <v>30</v>
@@ -7344,7 +7344,7 @@
         <v>29</v>
       </c>
       <c r="D192">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E192" t="s">
         <v>30</v>
@@ -7361,7 +7361,7 @@
         <v>29</v>
       </c>
       <c r="D193">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E193" t="s">
         <v>30</v>
@@ -7378,7 +7378,7 @@
         <v>29</v>
       </c>
       <c r="D194">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E194" t="s">
         <v>30</v>
@@ -7395,7 +7395,7 @@
         <v>29</v>
       </c>
       <c r="D195">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E195" t="s">
         <v>30</v>
@@ -7412,7 +7412,7 @@
         <v>29</v>
       </c>
       <c r="D196">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E196" t="s">
         <v>30</v>
@@ -7429,7 +7429,7 @@
         <v>29</v>
       </c>
       <c r="D197">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E197" t="s">
         <v>30</v>
@@ -7446,7 +7446,7 @@
         <v>29</v>
       </c>
       <c r="D198">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E198" t="s">
         <v>30</v>
@@ -7463,7 +7463,7 @@
         <v>29</v>
       </c>
       <c r="D199">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E199" t="s">
         <v>30</v>
@@ -7480,7 +7480,7 @@
         <v>29</v>
       </c>
       <c r="D200">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E200" t="s">
         <v>30</v>
@@ -7497,7 +7497,7 @@
         <v>29</v>
       </c>
       <c r="D201">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E201" t="s">
         <v>30</v>
@@ -7514,7 +7514,7 @@
         <v>29</v>
       </c>
       <c r="D202">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E202" t="s">
         <v>30</v>
@@ -7531,7 +7531,7 @@
         <v>29</v>
       </c>
       <c r="D203">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E203" t="s">
         <v>30</v>
@@ -7548,7 +7548,7 @@
         <v>29</v>
       </c>
       <c r="D204">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E204" t="s">
         <v>30</v>
@@ -7565,7 +7565,7 @@
         <v>29</v>
       </c>
       <c r="D205">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E205" t="s">
         <v>30</v>
@@ -7582,7 +7582,7 @@
         <v>29</v>
       </c>
       <c r="D206">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E206" t="s">
         <v>30</v>
@@ -7599,7 +7599,7 @@
         <v>29</v>
       </c>
       <c r="D207">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E207" t="s">
         <v>30</v>
@@ -7616,7 +7616,7 @@
         <v>29</v>
       </c>
       <c r="D208">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E208" t="s">
         <v>30</v>
@@ -7633,7 +7633,7 @@
         <v>29</v>
       </c>
       <c r="D209">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E209" t="s">
         <v>30</v>
@@ -7650,7 +7650,7 @@
         <v>29</v>
       </c>
       <c r="D210">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E210" t="s">
         <v>30</v>
@@ -7667,7 +7667,7 @@
         <v>29</v>
       </c>
       <c r="D211">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E211" t="s">
         <v>30</v>
@@ -7684,7 +7684,7 @@
         <v>29</v>
       </c>
       <c r="D212">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E212" t="s">
         <v>30</v>
@@ -7701,7 +7701,7 @@
         <v>29</v>
       </c>
       <c r="D213">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E213" t="s">
         <v>30</v>
@@ -7718,7 +7718,7 @@
         <v>29</v>
       </c>
       <c r="D214">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E214" t="s">
         <v>30</v>
@@ -7735,7 +7735,7 @@
         <v>29</v>
       </c>
       <c r="D215">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E215" t="s">
         <v>30</v>
@@ -7752,7 +7752,7 @@
         <v>29</v>
       </c>
       <c r="D216">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E216" t="s">
         <v>30</v>
@@ -7769,7 +7769,7 @@
         <v>29</v>
       </c>
       <c r="D217">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E217" t="s">
         <v>30</v>
@@ -7786,7 +7786,7 @@
         <v>29</v>
       </c>
       <c r="D218">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
         <v>30</v>
@@ -7803,7 +7803,7 @@
         <v>29</v>
       </c>
       <c r="D219">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E219" t="s">
         <v>30</v>
@@ -7820,7 +7820,7 @@
         <v>29</v>
       </c>
       <c r="D220">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E220" t="s">
         <v>30</v>
@@ -7837,7 +7837,7 @@
         <v>29</v>
       </c>
       <c r="D221">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E221" t="s">
         <v>30</v>
@@ -7854,7 +7854,7 @@
         <v>29</v>
       </c>
       <c r="D222">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E222" t="s">
         <v>30</v>
@@ -7871,7 +7871,7 @@
         <v>29</v>
       </c>
       <c r="D223">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E223" t="s">
         <v>30</v>
@@ -7888,7 +7888,7 @@
         <v>29</v>
       </c>
       <c r="D224">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E224" t="s">
         <v>30</v>
@@ -7905,7 +7905,7 @@
         <v>29</v>
       </c>
       <c r="D225">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E225" t="s">
         <v>30</v>
@@ -7922,7 +7922,7 @@
         <v>29</v>
       </c>
       <c r="D226">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E226" t="s">
         <v>30</v>
@@ -7939,7 +7939,7 @@
         <v>29</v>
       </c>
       <c r="D227">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E227" t="s">
         <v>30</v>
@@ -7956,7 +7956,7 @@
         <v>29</v>
       </c>
       <c r="D228">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E228" t="s">
         <v>30</v>
@@ -7990,7 +7990,7 @@
         <v>29</v>
       </c>
       <c r="D230">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E230" t="s">
         <v>30</v>
@@ -8007,7 +8007,7 @@
         <v>29</v>
       </c>
       <c r="D231">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E231" t="s">
         <v>30</v>
@@ -8024,7 +8024,7 @@
         <v>29</v>
       </c>
       <c r="D232">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E232" t="s">
         <v>30</v>
@@ -8041,7 +8041,7 @@
         <v>29</v>
       </c>
       <c r="D233">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E233" t="s">
         <v>30</v>
@@ -8058,7 +8058,7 @@
         <v>29</v>
       </c>
       <c r="D234">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E234" t="s">
         <v>30</v>
@@ -8075,7 +8075,7 @@
         <v>29</v>
       </c>
       <c r="D235">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E235" t="s">
         <v>30</v>
@@ -8092,7 +8092,7 @@
         <v>29</v>
       </c>
       <c r="D236">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E236" t="s">
         <v>30</v>
@@ -8109,7 +8109,7 @@
         <v>29</v>
       </c>
       <c r="D237">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E237" t="s">
         <v>30</v>
@@ -8126,7 +8126,7 @@
         <v>29</v>
       </c>
       <c r="D238">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E238" t="s">
         <v>30</v>
@@ -8143,7 +8143,7 @@
         <v>29</v>
       </c>
       <c r="D239">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E239" t="s">
         <v>30</v>
@@ -8160,7 +8160,7 @@
         <v>29</v>
       </c>
       <c r="D240">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E240" t="s">
         <v>30</v>
@@ -8177,7 +8177,7 @@
         <v>29</v>
       </c>
       <c r="D241">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E241" t="s">
         <v>30</v>
@@ -8194,7 +8194,7 @@
         <v>29</v>
       </c>
       <c r="D242">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E242" t="s">
         <v>30</v>
@@ -8211,7 +8211,7 @@
         <v>29</v>
       </c>
       <c r="D243">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E243" t="s">
         <v>30</v>
@@ -8228,7 +8228,7 @@
         <v>29</v>
       </c>
       <c r="D244">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E244" t="s">
         <v>30</v>
@@ -8245,7 +8245,7 @@
         <v>29</v>
       </c>
       <c r="D245">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E245" t="s">
         <v>30</v>
@@ -8262,7 +8262,7 @@
         <v>29</v>
       </c>
       <c r="D246">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E246" t="s">
         <v>30</v>
@@ -8279,7 +8279,7 @@
         <v>29</v>
       </c>
       <c r="D247">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E247" t="s">
         <v>30</v>
@@ -8296,7 +8296,7 @@
         <v>29</v>
       </c>
       <c r="D248">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E248" t="s">
         <v>30</v>
@@ -8313,7 +8313,7 @@
         <v>29</v>
       </c>
       <c r="D249">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E249" t="s">
         <v>30</v>
@@ -8330,7 +8330,7 @@
         <v>29</v>
       </c>
       <c r="D250">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E250" t="s">
         <v>30</v>
@@ -8347,7 +8347,7 @@
         <v>29</v>
       </c>
       <c r="D251">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E251" t="s">
         <v>30</v>
@@ -8364,7 +8364,7 @@
         <v>29</v>
       </c>
       <c r="D252">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E252" t="s">
         <v>30</v>
@@ -8398,7 +8398,7 @@
         <v>29</v>
       </c>
       <c r="D254">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E254" t="s">
         <v>30</v>
@@ -8415,7 +8415,7 @@
         <v>29</v>
       </c>
       <c r="D255">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E255" t="s">
         <v>30</v>
@@ -8432,7 +8432,7 @@
         <v>29</v>
       </c>
       <c r="D256">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E256" t="s">
         <v>30</v>
@@ -8449,7 +8449,7 @@
         <v>29</v>
       </c>
       <c r="D257">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E257" t="s">
         <v>30</v>
@@ -8466,7 +8466,7 @@
         <v>29</v>
       </c>
       <c r="D258">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E258" t="s">
         <v>30</v>
@@ -8483,7 +8483,7 @@
         <v>29</v>
       </c>
       <c r="D259">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E259" t="s">
         <v>30</v>
@@ -8500,7 +8500,7 @@
         <v>29</v>
       </c>
       <c r="D260">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E260" t="s">
         <v>30</v>
@@ -8517,7 +8517,7 @@
         <v>29</v>
       </c>
       <c r="D261">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E261" t="s">
         <v>30</v>
@@ -8534,7 +8534,7 @@
         <v>29</v>
       </c>
       <c r="D262">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E262" t="s">
         <v>30</v>
@@ -8551,7 +8551,7 @@
         <v>29</v>
       </c>
       <c r="D263">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E263" t="s">
         <v>30</v>
@@ -8568,7 +8568,7 @@
         <v>29</v>
       </c>
       <c r="D264">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E264" t="s">
         <v>30</v>
@@ -8585,7 +8585,7 @@
         <v>29</v>
       </c>
       <c r="D265">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E265" t="s">
         <v>30</v>
@@ -8602,7 +8602,7 @@
         <v>29</v>
       </c>
       <c r="D266">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E266" t="s">
         <v>30</v>
@@ -8619,7 +8619,7 @@
         <v>29</v>
       </c>
       <c r="D267">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E267" t="s">
         <v>30</v>
@@ -8636,7 +8636,7 @@
         <v>29</v>
       </c>
       <c r="D268">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E268" t="s">
         <v>30</v>
@@ -8653,7 +8653,7 @@
         <v>29</v>
       </c>
       <c r="D269">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E269" t="s">
         <v>30</v>
@@ -8670,7 +8670,7 @@
         <v>29</v>
       </c>
       <c r="D270">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E270" t="s">
         <v>30</v>
@@ -8687,7 +8687,7 @@
         <v>29</v>
       </c>
       <c r="D271">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E271" t="s">
         <v>30</v>
@@ -8704,7 +8704,7 @@
         <v>29</v>
       </c>
       <c r="D272">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E272" t="s">
         <v>30</v>
@@ -8721,7 +8721,7 @@
         <v>29</v>
       </c>
       <c r="D273">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E273" t="s">
         <v>30</v>
@@ -8738,7 +8738,7 @@
         <v>29</v>
       </c>
       <c r="D274">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E274" t="s">
         <v>30</v>
@@ -8755,7 +8755,7 @@
         <v>29</v>
       </c>
       <c r="D275">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E275" t="s">
         <v>30</v>
@@ -8772,7 +8772,7 @@
         <v>29</v>
       </c>
       <c r="D276">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E276" t="s">
         <v>30</v>
@@ -8789,7 +8789,7 @@
         <v>29</v>
       </c>
       <c r="D277">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E277" t="s">
         <v>30</v>
@@ -8806,7 +8806,7 @@
         <v>29</v>
       </c>
       <c r="D278">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E278" t="s">
         <v>30</v>
@@ -8823,7 +8823,7 @@
         <v>29</v>
       </c>
       <c r="D279">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E279" t="s">
         <v>30</v>
@@ -8840,7 +8840,7 @@
         <v>29</v>
       </c>
       <c r="D280">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E280" t="s">
         <v>30</v>
@@ -8857,7 +8857,7 @@
         <v>29</v>
       </c>
       <c r="D281">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E281" t="s">
         <v>30</v>
@@ -8874,7 +8874,7 @@
         <v>29</v>
       </c>
       <c r="D282">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E282" t="s">
         <v>30</v>
@@ -8891,7 +8891,7 @@
         <v>29</v>
       </c>
       <c r="D283">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E283" t="s">
         <v>30</v>
@@ -8908,7 +8908,7 @@
         <v>29</v>
       </c>
       <c r="D284">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E284" t="s">
         <v>30</v>
@@ -8925,7 +8925,7 @@
         <v>29</v>
       </c>
       <c r="D285">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E285" t="s">
         <v>30</v>
@@ -8959,7 +8959,7 @@
         <v>29</v>
       </c>
       <c r="D287">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E287" t="s">
         <v>30</v>
@@ -8976,7 +8976,7 @@
         <v>29</v>
       </c>
       <c r="D288">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E288" t="s">
         <v>30</v>
@@ -8993,7 +8993,7 @@
         <v>29</v>
       </c>
       <c r="D289">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E289" t="s">
         <v>30</v>
@@ -9010,7 +9010,7 @@
         <v>29</v>
       </c>
       <c r="D290">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E290" t="s">
         <v>30</v>
@@ -9027,7 +9027,7 @@
         <v>29</v>
       </c>
       <c r="D291">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E291" t="s">
         <v>30</v>
@@ -9044,7 +9044,7 @@
         <v>29</v>
       </c>
       <c r="D292">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E292" t="s">
         <v>30</v>
@@ -9061,7 +9061,7 @@
         <v>29</v>
       </c>
       <c r="D293">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E293" t="s">
         <v>30</v>
@@ -9078,7 +9078,7 @@
         <v>29</v>
       </c>
       <c r="D294">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E294" t="s">
         <v>30</v>
@@ -9095,7 +9095,7 @@
         <v>29</v>
       </c>
       <c r="D295">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E295" t="s">
         <v>30</v>
@@ -9112,7 +9112,7 @@
         <v>29</v>
       </c>
       <c r="D296">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E296" t="s">
         <v>30</v>
@@ -9129,7 +9129,7 @@
         <v>29</v>
       </c>
       <c r="D297">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E297" t="s">
         <v>30</v>
@@ -9146,7 +9146,7 @@
         <v>29</v>
       </c>
       <c r="D298">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E298" t="s">
         <v>30</v>
@@ -9163,7 +9163,7 @@
         <v>29</v>
       </c>
       <c r="D299">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E299" t="s">
         <v>30</v>
@@ -9180,7 +9180,7 @@
         <v>29</v>
       </c>
       <c r="D300">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E300" t="s">
         <v>30</v>
@@ -9197,7 +9197,7 @@
         <v>29</v>
       </c>
       <c r="D301">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E301" t="s">
         <v>30</v>
@@ -9214,7 +9214,7 @@
         <v>29</v>
       </c>
       <c r="D302">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E302" t="s">
         <v>30</v>
@@ -9231,7 +9231,7 @@
         <v>29</v>
       </c>
       <c r="D303">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E303" t="s">
         <v>30</v>
@@ -9248,7 +9248,7 @@
         <v>29</v>
       </c>
       <c r="D304">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E304" t="s">
         <v>30</v>
@@ -9282,7 +9282,7 @@
         <v>29</v>
       </c>
       <c r="D306">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E306" t="s">
         <v>30</v>
@@ -9299,7 +9299,7 @@
         <v>29</v>
       </c>
       <c r="D307">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E307" t="s">
         <v>30</v>
@@ -9316,7 +9316,7 @@
         <v>29</v>
       </c>
       <c r="D308">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E308" t="s">
         <v>30</v>
@@ -9333,7 +9333,7 @@
         <v>29</v>
       </c>
       <c r="D309">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E309" t="s">
         <v>30</v>
@@ -9350,7 +9350,7 @@
         <v>29</v>
       </c>
       <c r="D310">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E310" t="s">
         <v>30</v>
@@ -9367,7 +9367,7 @@
         <v>29</v>
       </c>
       <c r="D311">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E311" t="s">
         <v>30</v>
@@ -9384,7 +9384,7 @@
         <v>29</v>
       </c>
       <c r="D312">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E312" t="s">
         <v>30</v>
@@ -9401,7 +9401,7 @@
         <v>29</v>
       </c>
       <c r="D313">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E313" t="s">
         <v>30</v>
@@ -9418,7 +9418,7 @@
         <v>29</v>
       </c>
       <c r="D314">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E314" t="s">
         <v>30</v>
@@ -9435,7 +9435,7 @@
         <v>29</v>
       </c>
       <c r="D315">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E315" t="s">
         <v>30</v>
@@ -9452,7 +9452,7 @@
         <v>29</v>
       </c>
       <c r="D316">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E316" t="s">
         <v>30</v>
@@ -9486,7 +9486,7 @@
         <v>29</v>
       </c>
       <c r="D318">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E318" t="s">
         <v>30</v>
@@ -9503,7 +9503,7 @@
         <v>29</v>
       </c>
       <c r="D319">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E319" t="s">
         <v>30</v>
@@ -9520,7 +9520,7 @@
         <v>29</v>
       </c>
       <c r="D320">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E320" t="s">
         <v>30</v>
@@ -9537,7 +9537,7 @@
         <v>29</v>
       </c>
       <c r="D321">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E321" t="s">
         <v>30</v>
@@ -9554,7 +9554,7 @@
         <v>29</v>
       </c>
       <c r="D322">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E322" t="s">
         <v>30</v>
@@ -9571,7 +9571,7 @@
         <v>29</v>
       </c>
       <c r="D323">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E323" t="s">
         <v>30</v>
@@ -9588,7 +9588,7 @@
         <v>29</v>
       </c>
       <c r="D324">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E324" t="s">
         <v>30</v>
@@ -9605,7 +9605,7 @@
         <v>29</v>
       </c>
       <c r="D325">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E325" t="s">
         <v>30</v>
@@ -9622,7 +9622,7 @@
         <v>29</v>
       </c>
       <c r="D326">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E326" t="s">
         <v>30</v>
@@ -9639,7 +9639,7 @@
         <v>29</v>
       </c>
       <c r="D327">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E327" t="s">
         <v>30</v>
@@ -9656,7 +9656,7 @@
         <v>29</v>
       </c>
       <c r="D328">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E328" t="s">
         <v>30</v>
@@ -9673,7 +9673,7 @@
         <v>29</v>
       </c>
       <c r="D329">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E329" t="s">
         <v>30</v>
@@ -9690,7 +9690,7 @@
         <v>29</v>
       </c>
       <c r="D330">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E330" t="s">
         <v>30</v>
@@ -9707,7 +9707,7 @@
         <v>29</v>
       </c>
       <c r="D331">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E331" t="s">
         <v>30</v>
@@ -9741,7 +9741,7 @@
         <v>29</v>
       </c>
       <c r="D333">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E333" t="s">
         <v>30</v>
@@ -9758,7 +9758,7 @@
         <v>29</v>
       </c>
       <c r="D334">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E334" t="s">
         <v>30</v>
@@ -9775,7 +9775,7 @@
         <v>29</v>
       </c>
       <c r="D335">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E335" t="s">
         <v>30</v>
@@ -9792,7 +9792,7 @@
         <v>29</v>
       </c>
       <c r="D336">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E336" t="s">
         <v>30</v>
@@ -9809,7 +9809,7 @@
         <v>29</v>
       </c>
       <c r="D337">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E337" t="s">
         <v>30</v>
@@ -9826,7 +9826,7 @@
         <v>29</v>
       </c>
       <c r="D338">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E338" t="s">
         <v>30</v>
@@ -9860,7 +9860,7 @@
         <v>29</v>
       </c>
       <c r="D340">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E340" t="s">
         <v>30</v>
@@ -9877,7 +9877,7 @@
         <v>29</v>
       </c>
       <c r="D341">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E341" t="s">
         <v>30</v>
@@ -9894,7 +9894,7 @@
         <v>29</v>
       </c>
       <c r="D342">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E342" t="s">
         <v>30</v>
@@ -9911,7 +9911,7 @@
         <v>29</v>
       </c>
       <c r="D343">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E343" t="s">
         <v>30</v>
@@ -9928,7 +9928,7 @@
         <v>29</v>
       </c>
       <c r="D344">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E344" t="s">
         <v>30</v>
@@ -9945,7 +9945,7 @@
         <v>29</v>
       </c>
       <c r="D345">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E345" t="s">
         <v>30</v>
@@ -9962,7 +9962,7 @@
         <v>29</v>
       </c>
       <c r="D346">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E346" t="s">
         <v>30</v>
@@ -9996,7 +9996,7 @@
         <v>29</v>
       </c>
       <c r="D348">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E348" t="s">
         <v>30</v>
@@ -10013,7 +10013,7 @@
         <v>29</v>
       </c>
       <c r="D349">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E349" t="s">
         <v>30</v>
@@ -10030,7 +10030,7 @@
         <v>29</v>
       </c>
       <c r="D350">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E350" t="s">
         <v>30</v>
@@ -10047,7 +10047,7 @@
         <v>29</v>
       </c>
       <c r="D351">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E351" t="s">
         <v>30</v>
@@ -10064,7 +10064,7 @@
         <v>29</v>
       </c>
       <c r="D352">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E352" t="s">
         <v>30</v>
@@ -10081,7 +10081,7 @@
         <v>29</v>
       </c>
       <c r="D353">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E353" t="s">
         <v>30</v>
@@ -10098,7 +10098,7 @@
         <v>29</v>
       </c>
       <c r="D354">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E354" t="s">
         <v>30</v>
@@ -10115,7 +10115,7 @@
         <v>29</v>
       </c>
       <c r="D355">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E355" t="s">
         <v>30</v>
@@ -10132,7 +10132,7 @@
         <v>29</v>
       </c>
       <c r="D356">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E356" t="s">
         <v>30</v>
@@ -10149,7 +10149,7 @@
         <v>29</v>
       </c>
       <c r="D357">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E357" t="s">
         <v>30</v>
@@ -10166,7 +10166,7 @@
         <v>29</v>
       </c>
       <c r="D358">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E358" t="s">
         <v>30</v>
@@ -10183,7 +10183,7 @@
         <v>29</v>
       </c>
       <c r="D359">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E359" t="s">
         <v>30</v>
@@ -10200,7 +10200,7 @@
         <v>29</v>
       </c>
       <c r="D360">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E360" t="s">
         <v>30</v>
@@ -10217,7 +10217,7 @@
         <v>29</v>
       </c>
       <c r="D361">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E361" t="s">
         <v>30</v>
@@ -10234,7 +10234,7 @@
         <v>29</v>
       </c>
       <c r="D362">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E362" t="s">
         <v>30</v>
@@ -10251,7 +10251,7 @@
         <v>29</v>
       </c>
       <c r="D363">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E363" t="s">
         <v>30</v>
@@ -10268,7 +10268,7 @@
         <v>29</v>
       </c>
       <c r="D364">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E364" t="s">
         <v>30</v>
@@ -10285,7 +10285,7 @@
         <v>29</v>
       </c>
       <c r="D365">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E365" t="s">
         <v>30</v>
@@ -10302,7 +10302,7 @@
         <v>29</v>
       </c>
       <c r="D366">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E366" t="s">
         <v>30</v>
@@ -10319,7 +10319,7 @@
         <v>29</v>
       </c>
       <c r="D367">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E367" t="s">
         <v>30</v>
@@ -10336,7 +10336,7 @@
         <v>29</v>
       </c>
       <c r="D368">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E368" t="s">
         <v>30</v>
@@ -10370,7 +10370,7 @@
         <v>29</v>
       </c>
       <c r="D370">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E370" t="s">
         <v>30</v>
@@ -10387,7 +10387,7 @@
         <v>29</v>
       </c>
       <c r="D371">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E371" t="s">
         <v>30</v>
@@ -10404,7 +10404,7 @@
         <v>29</v>
       </c>
       <c r="D372">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E372" t="s">
         <v>30</v>
@@ -10421,7 +10421,7 @@
         <v>29</v>
       </c>
       <c r="D373">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E373" t="s">
         <v>30</v>
@@ -10438,7 +10438,7 @@
         <v>29</v>
       </c>
       <c r="D374">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E374" t="s">
         <v>30</v>
@@ -10455,7 +10455,7 @@
         <v>29</v>
       </c>
       <c r="D375">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E375" t="s">
         <v>30</v>
@@ -10506,7 +10506,7 @@
         <v>29</v>
       </c>
       <c r="D378">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E378" t="s">
         <v>30</v>
@@ -10523,7 +10523,7 @@
         <v>29</v>
       </c>
       <c r="D379">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E379" t="s">
         <v>30</v>
@@ -10540,7 +10540,7 @@
         <v>29</v>
       </c>
       <c r="D380">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E380" t="s">
         <v>30</v>
@@ -10557,7 +10557,7 @@
         <v>29</v>
       </c>
       <c r="D381">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E381" t="s">
         <v>30</v>
@@ -10574,7 +10574,7 @@
         <v>29</v>
       </c>
       <c r="D382">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E382" t="s">
         <v>30</v>
@@ -10591,7 +10591,7 @@
         <v>29</v>
       </c>
       <c r="D383">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E383" t="s">
         <v>30</v>
@@ -10608,7 +10608,7 @@
         <v>29</v>
       </c>
       <c r="D384">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E384" t="s">
         <v>30</v>
@@ -10625,7 +10625,7 @@
         <v>29</v>
       </c>
       <c r="D385">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E385" t="s">
         <v>30</v>
@@ -10642,7 +10642,7 @@
         <v>29</v>
       </c>
       <c r="D386">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E386" t="s">
         <v>30</v>
@@ -10659,7 +10659,7 @@
         <v>29</v>
       </c>
       <c r="D387">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E387" t="s">
         <v>30</v>
@@ -10676,7 +10676,7 @@
         <v>29</v>
       </c>
       <c r="D388">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E388" t="s">
         <v>30</v>
@@ -10693,7 +10693,7 @@
         <v>29</v>
       </c>
       <c r="D389">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E389" t="s">
         <v>30</v>
@@ -10710,7 +10710,7 @@
         <v>29</v>
       </c>
       <c r="D390">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E390" t="s">
         <v>30</v>
@@ -10727,7 +10727,7 @@
         <v>29</v>
       </c>
       <c r="D391">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E391" t="s">
         <v>30</v>
@@ -10744,7 +10744,7 @@
         <v>29</v>
       </c>
       <c r="D392">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E392" t="s">
         <v>30</v>
@@ -10761,7 +10761,7 @@
         <v>29</v>
       </c>
       <c r="D393">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E393" t="s">
         <v>30</v>
@@ -10778,7 +10778,7 @@
         <v>29</v>
       </c>
       <c r="D394">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E394" t="s">
         <v>30</v>
@@ -10795,7 +10795,7 @@
         <v>29</v>
       </c>
       <c r="D395">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E395" t="s">
         <v>30</v>
@@ -10812,7 +10812,7 @@
         <v>29</v>
       </c>
       <c r="D396">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E396" t="s">
         <v>30</v>
@@ -10829,7 +10829,7 @@
         <v>29</v>
       </c>
       <c r="D397">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E397" t="s">
         <v>30</v>
@@ -10846,7 +10846,7 @@
         <v>29</v>
       </c>
       <c r="D398">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E398" t="s">
         <v>30</v>
@@ -10863,7 +10863,7 @@
         <v>29</v>
       </c>
       <c r="D399">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E399" t="s">
         <v>30</v>
@@ -10880,7 +10880,7 @@
         <v>29</v>
       </c>
       <c r="D400">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E400" t="s">
         <v>30</v>
@@ -10897,7 +10897,7 @@
         <v>29</v>
       </c>
       <c r="D401">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E401" t="s">
         <v>30</v>
@@ -10914,7 +10914,7 @@
         <v>29</v>
       </c>
       <c r="D402">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E402" t="s">
         <v>30</v>
@@ -10931,7 +10931,7 @@
         <v>29</v>
       </c>
       <c r="D403">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E403" t="s">
         <v>30</v>
@@ -10948,7 +10948,7 @@
         <v>29</v>
       </c>
       <c r="D404">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E404" t="s">
         <v>30</v>
@@ -10965,7 +10965,7 @@
         <v>29</v>
       </c>
       <c r="D405">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E405" t="s">
         <v>30</v>
@@ -10982,7 +10982,7 @@
         <v>29</v>
       </c>
       <c r="D406">
-        <v>434</v>
+        <v>11</v>
       </c>
       <c r="E406" t="s">
         <v>30</v>
@@ -10999,7 +10999,7 @@
         <v>29</v>
       </c>
       <c r="D407">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E407" t="s">
         <v>30</v>
@@ -11016,7 +11016,7 @@
         <v>29</v>
       </c>
       <c r="D408">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E408" t="s">
         <v>30</v>
@@ -11050,7 +11050,7 @@
         <v>29</v>
       </c>
       <c r="D410">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E410" t="s">
         <v>30</v>
@@ -11067,7 +11067,7 @@
         <v>29</v>
       </c>
       <c r="D411">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E411" t="s">
         <v>30</v>
@@ -11101,7 +11101,7 @@
         <v>29</v>
       </c>
       <c r="D413">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E413" t="s">
         <v>30</v>
@@ -11118,7 +11118,7 @@
         <v>29</v>
       </c>
       <c r="D414">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E414" t="s">
         <v>30</v>
@@ -11135,7 +11135,7 @@
         <v>29</v>
       </c>
       <c r="D415">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E415" t="s">
         <v>30</v>
@@ -11152,7 +11152,7 @@
         <v>29</v>
       </c>
       <c r="D416">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E416" t="s">
         <v>30</v>
@@ -11169,7 +11169,7 @@
         <v>29</v>
       </c>
       <c r="D417">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E417" t="s">
         <v>30</v>
@@ -11186,7 +11186,7 @@
         <v>29</v>
       </c>
       <c r="D418">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E418" t="s">
         <v>30</v>
@@ -11203,7 +11203,7 @@
         <v>29</v>
       </c>
       <c r="D419">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E419" t="s">
         <v>30</v>
@@ -11220,7 +11220,7 @@
         <v>29</v>
       </c>
       <c r="D420">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E420" t="s">
         <v>30</v>
@@ -11237,7 +11237,7 @@
         <v>29</v>
       </c>
       <c r="D421">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E421" t="s">
         <v>30</v>
@@ -11271,7 +11271,7 @@
         <v>29</v>
       </c>
       <c r="D423">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E423" t="s">
         <v>30</v>
@@ -11288,7 +11288,7 @@
         <v>29</v>
       </c>
       <c r="D424">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E424" t="s">
         <v>30</v>
@@ -11305,7 +11305,7 @@
         <v>29</v>
       </c>
       <c r="D425">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E425" t="s">
         <v>30</v>
@@ -11339,7 +11339,7 @@
         <v>29</v>
       </c>
       <c r="D427">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E427" t="s">
         <v>30</v>
@@ -11356,7 +11356,7 @@
         <v>29</v>
       </c>
       <c r="D428">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E428" t="s">
         <v>30</v>
@@ -11373,7 +11373,7 @@
         <v>29</v>
       </c>
       <c r="D429">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E429" t="s">
         <v>30</v>
@@ -11390,7 +11390,7 @@
         <v>29</v>
       </c>
       <c r="D430">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E430" t="s">
         <v>30</v>
@@ -11407,7 +11407,7 @@
         <v>29</v>
       </c>
       <c r="D431">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E431" t="s">
         <v>30</v>
@@ -11424,7 +11424,7 @@
         <v>29</v>
       </c>
       <c r="D432">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E432" t="s">
         <v>30</v>
@@ -11441,7 +11441,7 @@
         <v>29</v>
       </c>
       <c r="D433">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E433" t="s">
         <v>30</v>
@@ -11458,7 +11458,7 @@
         <v>29</v>
       </c>
       <c r="D434">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E434" t="s">
         <v>30</v>
@@ -11475,7 +11475,7 @@
         <v>29</v>
       </c>
       <c r="D435">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E435" t="s">
         <v>30</v>
@@ -11492,7 +11492,7 @@
         <v>29</v>
       </c>
       <c r="D436">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E436" t="s">
         <v>30</v>
@@ -11509,7 +11509,7 @@
         <v>29</v>
       </c>
       <c r="D437">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E437" t="s">
         <v>30</v>
@@ -11526,7 +11526,7 @@
         <v>29</v>
       </c>
       <c r="D438">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E438" t="s">
         <v>30</v>
@@ -11543,7 +11543,7 @@
         <v>29</v>
       </c>
       <c r="D439">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E439" t="s">
         <v>30</v>
@@ -11560,7 +11560,7 @@
         <v>29</v>
       </c>
       <c r="D440">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E440" t="s">
         <v>30</v>
@@ -11577,7 +11577,7 @@
         <v>29</v>
       </c>
       <c r="D441">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E441" t="s">
         <v>30</v>
@@ -11594,7 +11594,7 @@
         <v>29</v>
       </c>
       <c r="D442">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E442" t="s">
         <v>30</v>
@@ -11611,7 +11611,7 @@
         <v>29</v>
       </c>
       <c r="D443">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E443" t="s">
         <v>30</v>
@@ -11628,7 +11628,7 @@
         <v>29</v>
       </c>
       <c r="D444">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E444" t="s">
         <v>30</v>
@@ -11645,7 +11645,7 @@
         <v>29</v>
       </c>
       <c r="D445">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E445" t="s">
         <v>30</v>
@@ -11662,7 +11662,7 @@
         <v>29</v>
       </c>
       <c r="D446">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E446" t="s">
         <v>30</v>
@@ -11679,7 +11679,7 @@
         <v>29</v>
       </c>
       <c r="D447">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E447" t="s">
         <v>30</v>
@@ -11696,7 +11696,7 @@
         <v>29</v>
       </c>
       <c r="D448">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E448" t="s">
         <v>30</v>
@@ -11713,7 +11713,7 @@
         <v>29</v>
       </c>
       <c r="D449">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E449" t="s">
         <v>30</v>
@@ -11730,7 +11730,7 @@
         <v>29</v>
       </c>
       <c r="D450">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E450" t="s">
         <v>30</v>
@@ -11747,7 +11747,7 @@
         <v>29</v>
       </c>
       <c r="D451">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E451" t="s">
         <v>30</v>
@@ -11764,7 +11764,7 @@
         <v>29</v>
       </c>
       <c r="D452">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E452" t="s">
         <v>30</v>
@@ -11781,7 +11781,7 @@
         <v>29</v>
       </c>
       <c r="D453">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E453" t="s">
         <v>30</v>
@@ -11798,7 +11798,7 @@
         <v>29</v>
       </c>
       <c r="D454">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E454" t="s">
         <v>30</v>
@@ -11815,7 +11815,7 @@
         <v>29</v>
       </c>
       <c r="D455">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E455" t="s">
         <v>30</v>
@@ -11832,7 +11832,7 @@
         <v>29</v>
       </c>
       <c r="D456">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E456" t="s">
         <v>30</v>
@@ -11849,7 +11849,7 @@
         <v>29</v>
       </c>
       <c r="D457">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E457" t="s">
         <v>30</v>
@@ -11883,7 +11883,7 @@
         <v>29</v>
       </c>
       <c r="D459">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E459" t="s">
         <v>30</v>
@@ -11900,7 +11900,7 @@
         <v>29</v>
       </c>
       <c r="D460">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E460" t="s">
         <v>30</v>
@@ -11934,7 +11934,7 @@
         <v>29</v>
       </c>
       <c r="D462">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E462" t="s">
         <v>30</v>
@@ -11951,7 +11951,7 @@
         <v>29</v>
       </c>
       <c r="D463">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E463" t="s">
         <v>30</v>
@@ -11968,7 +11968,7 @@
         <v>29</v>
       </c>
       <c r="D464">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E464" t="s">
         <v>30</v>
@@ -11985,7 +11985,7 @@
         <v>29</v>
       </c>
       <c r="D465">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E465" t="s">
         <v>30</v>
@@ -12002,7 +12002,7 @@
         <v>29</v>
       </c>
       <c r="D466">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E466" t="s">
         <v>30</v>
@@ -12019,7 +12019,7 @@
         <v>29</v>
       </c>
       <c r="D467">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E467" t="s">
         <v>30</v>
@@ -12036,7 +12036,7 @@
         <v>29</v>
       </c>
       <c r="D468">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E468" t="s">
         <v>30</v>
@@ -12053,7 +12053,7 @@
         <v>29</v>
       </c>
       <c r="D469">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E469" t="s">
         <v>30</v>
@@ -12070,7 +12070,7 @@
         <v>29</v>
       </c>
       <c r="D470">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E470" t="s">
         <v>30</v>
@@ -12087,7 +12087,7 @@
         <v>29</v>
       </c>
       <c r="D471">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E471" t="s">
         <v>30</v>
@@ -12104,7 +12104,7 @@
         <v>29</v>
       </c>
       <c r="D472">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E472" t="s">
         <v>30</v>
@@ -12121,7 +12121,7 @@
         <v>29</v>
       </c>
       <c r="D473">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E473" t="s">
         <v>30</v>
@@ -12138,7 +12138,7 @@
         <v>29</v>
       </c>
       <c r="D474">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E474" t="s">
         <v>30</v>
@@ -12155,7 +12155,7 @@
         <v>29</v>
       </c>
       <c r="D475">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E475" t="s">
         <v>30</v>
@@ -12172,7 +12172,7 @@
         <v>29</v>
       </c>
       <c r="D476">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E476" t="s">
         <v>30</v>
@@ -12189,7 +12189,7 @@
         <v>29</v>
       </c>
       <c r="D477">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E477" t="s">
         <v>30</v>
@@ -12206,7 +12206,7 @@
         <v>29</v>
       </c>
       <c r="D478">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E478" t="s">
         <v>30</v>
@@ -12223,7 +12223,7 @@
         <v>29</v>
       </c>
       <c r="D479">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E479" t="s">
         <v>30</v>
@@ -12240,7 +12240,7 @@
         <v>29</v>
       </c>
       <c r="D480">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E480" t="s">
         <v>30</v>
@@ -12257,7 +12257,7 @@
         <v>29</v>
       </c>
       <c r="D481">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E481" t="s">
         <v>30</v>
@@ -12274,7 +12274,7 @@
         <v>29</v>
       </c>
       <c r="D482">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E482" t="s">
         <v>30</v>
@@ -12291,7 +12291,7 @@
         <v>29</v>
       </c>
       <c r="D483">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E483" t="s">
         <v>30</v>
@@ -12308,7 +12308,7 @@
         <v>29</v>
       </c>
       <c r="D484">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E484" t="s">
         <v>30</v>
@@ -12325,7 +12325,7 @@
         <v>29</v>
       </c>
       <c r="D485">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E485" t="s">
         <v>30</v>
@@ -12342,7 +12342,7 @@
         <v>29</v>
       </c>
       <c r="D486">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E486" t="s">
         <v>30</v>
@@ -12359,7 +12359,7 @@
         <v>29</v>
       </c>
       <c r="D487">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E487" t="s">
         <v>30</v>
@@ -12376,7 +12376,7 @@
         <v>29</v>
       </c>
       <c r="D488">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E488" t="s">
         <v>30</v>
@@ -12393,7 +12393,7 @@
         <v>29</v>
       </c>
       <c r="D489">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E489" t="s">
         <v>30</v>
@@ -12410,7 +12410,7 @@
         <v>29</v>
       </c>
       <c r="D490">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E490" t="s">
         <v>30</v>
@@ -12427,7 +12427,7 @@
         <v>29</v>
       </c>
       <c r="D491">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E491" t="s">
         <v>30</v>
@@ -12444,7 +12444,7 @@
         <v>29</v>
       </c>
       <c r="D492">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E492" t="s">
         <v>30</v>
@@ -12461,7 +12461,7 @@
         <v>29</v>
       </c>
       <c r="D493">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E493" t="s">
         <v>30</v>
@@ -12478,7 +12478,7 @@
         <v>29</v>
       </c>
       <c r="D494">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E494" t="s">
         <v>30</v>
@@ -12495,7 +12495,7 @@
         <v>29</v>
       </c>
       <c r="D495">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E495" t="s">
         <v>30</v>
@@ -12512,7 +12512,7 @@
         <v>29</v>
       </c>
       <c r="D496">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E496" t="s">
         <v>30</v>
@@ -12546,7 +12546,7 @@
         <v>29</v>
       </c>
       <c r="D498">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E498" t="s">
         <v>30</v>
@@ -12580,7 +12580,7 @@
         <v>29</v>
       </c>
       <c r="D500">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E500" t="s">
         <v>30</v>
@@ -12597,7 +12597,7 @@
         <v>29</v>
       </c>
       <c r="D501">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E501" t="s">
         <v>30</v>
@@ -12614,7 +12614,7 @@
         <v>29</v>
       </c>
       <c r="D502">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E502" t="s">
         <v>30</v>
@@ -12631,7 +12631,7 @@
         <v>29</v>
       </c>
       <c r="D503">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E503" t="s">
         <v>30</v>
@@ -12648,7 +12648,7 @@
         <v>29</v>
       </c>
       <c r="D504">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E504" t="s">
         <v>30</v>
@@ -12665,7 +12665,7 @@
         <v>29</v>
       </c>
       <c r="D505">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E505" t="s">
         <v>30</v>
@@ -12682,7 +12682,7 @@
         <v>29</v>
       </c>
       <c r="D506">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E506" t="s">
         <v>30</v>
@@ -12699,7 +12699,7 @@
         <v>29</v>
       </c>
       <c r="D507">
-        <v>9</v>
+        <v>272</v>
       </c>
       <c r="E507" t="s">
         <v>30</v>
@@ -12716,7 +12716,7 @@
         <v>29</v>
       </c>
       <c r="D508">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E508" t="s">
         <v>30</v>
@@ -12733,7 +12733,7 @@
         <v>29</v>
       </c>
       <c r="D509">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E509" t="s">
         <v>30</v>
@@ -12750,7 +12750,7 @@
         <v>29</v>
       </c>
       <c r="D510">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E510" t="s">
         <v>30</v>
@@ -12767,7 +12767,7 @@
         <v>29</v>
       </c>
       <c r="D511">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E511" t="s">
         <v>30</v>
@@ -12784,7 +12784,7 @@
         <v>29</v>
       </c>
       <c r="D512">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E512" t="s">
         <v>30</v>
@@ -12801,7 +12801,7 @@
         <v>29</v>
       </c>
       <c r="D513">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E513" t="s">
         <v>30</v>
@@ -12818,7 +12818,7 @@
         <v>29</v>
       </c>
       <c r="D514">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E514" t="s">
         <v>30</v>
@@ -12835,7 +12835,7 @@
         <v>29</v>
       </c>
       <c r="D515">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E515" t="s">
         <v>30</v>
@@ -12852,7 +12852,7 @@
         <v>29</v>
       </c>
       <c r="D516">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E516" t="s">
         <v>30</v>
@@ -12869,7 +12869,7 @@
         <v>29</v>
       </c>
       <c r="D517">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E517" t="s">
         <v>30</v>
@@ -12886,7 +12886,7 @@
         <v>29</v>
       </c>
       <c r="D518">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E518" t="s">
         <v>30</v>
@@ -12903,7 +12903,7 @@
         <v>29</v>
       </c>
       <c r="D519">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E519" t="s">
         <v>30</v>
@@ -12920,7 +12920,7 @@
         <v>29</v>
       </c>
       <c r="D520">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E520" t="s">
         <v>30</v>
@@ -12937,7 +12937,7 @@
         <v>29</v>
       </c>
       <c r="D521">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E521" t="s">
         <v>30</v>
@@ -12954,7 +12954,7 @@
         <v>29</v>
       </c>
       <c r="D522">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E522" t="s">
         <v>30</v>
@@ -12971,7 +12971,7 @@
         <v>29</v>
       </c>
       <c r="D523">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E523" t="s">
         <v>30</v>
@@ -12988,7 +12988,7 @@
         <v>29</v>
       </c>
       <c r="D524">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E524" t="s">
         <v>30</v>
@@ -13005,7 +13005,7 @@
         <v>29</v>
       </c>
       <c r="D525">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E525" t="s">
         <v>30</v>
@@ -13022,7 +13022,7 @@
         <v>29</v>
       </c>
       <c r="D526">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E526" t="s">
         <v>30</v>
@@ -13039,7 +13039,7 @@
         <v>29</v>
       </c>
       <c r="D527">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E527" t="s">
         <v>30</v>
@@ -13056,7 +13056,7 @@
         <v>29</v>
       </c>
       <c r="D528">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E528" t="s">
         <v>30</v>
@@ -13073,7 +13073,7 @@
         <v>29</v>
       </c>
       <c r="D529">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E529" t="s">
         <v>30</v>
@@ -13090,7 +13090,7 @@
         <v>29</v>
       </c>
       <c r="D530">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E530" t="s">
         <v>30</v>
@@ -13107,7 +13107,7 @@
         <v>29</v>
       </c>
       <c r="D531">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E531" t="s">
         <v>30</v>
@@ -13124,7 +13124,7 @@
         <v>29</v>
       </c>
       <c r="D532">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E532" t="s">
         <v>30</v>
@@ -13141,7 +13141,7 @@
         <v>29</v>
       </c>
       <c r="D533">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E533" t="s">
         <v>30</v>
@@ -13158,7 +13158,7 @@
         <v>29</v>
       </c>
       <c r="D534">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E534" t="s">
         <v>30</v>
@@ -13175,7 +13175,7 @@
         <v>29</v>
       </c>
       <c r="D535">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E535" t="s">
         <v>30</v>
@@ -13192,7 +13192,7 @@
         <v>29</v>
       </c>
       <c r="D536">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E536" t="s">
         <v>30</v>
@@ -13209,7 +13209,7 @@
         <v>29</v>
       </c>
       <c r="D537">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E537" t="s">
         <v>30</v>
@@ -13226,7 +13226,7 @@
         <v>29</v>
       </c>
       <c r="D538">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E538" t="s">
         <v>30</v>
@@ -13243,7 +13243,7 @@
         <v>29</v>
       </c>
       <c r="D539">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E539" t="s">
         <v>30</v>
@@ -13260,7 +13260,7 @@
         <v>29</v>
       </c>
       <c r="D540">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E540" t="s">
         <v>30</v>
@@ -13277,7 +13277,7 @@
         <v>29</v>
       </c>
       <c r="D541">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E541" t="s">
         <v>30</v>
@@ -13294,7 +13294,7 @@
         <v>29</v>
       </c>
       <c r="D542">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E542" t="s">
         <v>30</v>
@@ -13311,7 +13311,7 @@
         <v>29</v>
       </c>
       <c r="D543">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E543" t="s">
         <v>30</v>
@@ -13345,7 +13345,7 @@
         <v>29</v>
       </c>
       <c r="D545">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E545" t="s">
         <v>30</v>
@@ -13362,7 +13362,7 @@
         <v>29</v>
       </c>
       <c r="D546">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E546" t="s">
         <v>30</v>
@@ -13379,7 +13379,7 @@
         <v>29</v>
       </c>
       <c r="D547">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E547" t="s">
         <v>30</v>
@@ -13396,7 +13396,7 @@
         <v>29</v>
       </c>
       <c r="D548">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E548" t="s">
         <v>30</v>
@@ -13413,7 +13413,7 @@
         <v>29</v>
       </c>
       <c r="D549">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E549" t="s">
         <v>30</v>
@@ -13430,7 +13430,7 @@
         <v>29</v>
       </c>
       <c r="D550">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E550" t="s">
         <v>30</v>
@@ -13447,7 +13447,7 @@
         <v>29</v>
       </c>
       <c r="D551">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E551" t="s">
         <v>30</v>
@@ -13481,7 +13481,7 @@
         <v>29</v>
       </c>
       <c r="D553">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E553" t="s">
         <v>30</v>
@@ -13498,7 +13498,7 @@
         <v>29</v>
       </c>
       <c r="D554">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E554" t="s">
         <v>30</v>
@@ -13515,7 +13515,7 @@
         <v>29</v>
       </c>
       <c r="D555">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E555" t="s">
         <v>30</v>
@@ -13532,7 +13532,7 @@
         <v>29</v>
       </c>
       <c r="D556">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E556" t="s">
         <v>30</v>
@@ -13549,7 +13549,7 @@
         <v>29</v>
       </c>
       <c r="D557">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E557" t="s">
         <v>30</v>
@@ -13566,7 +13566,7 @@
         <v>29</v>
       </c>
       <c r="D558">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E558" t="s">
         <v>30</v>
@@ -13583,7 +13583,7 @@
         <v>29</v>
       </c>
       <c r="D559">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E559" t="s">
         <v>30</v>
@@ -13600,7 +13600,7 @@
         <v>29</v>
       </c>
       <c r="D560">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E560" t="s">
         <v>30</v>
@@ -13617,7 +13617,7 @@
         <v>29</v>
       </c>
       <c r="D561">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E561" t="s">
         <v>30</v>
@@ -13634,7 +13634,7 @@
         <v>29</v>
       </c>
       <c r="D562">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E562" t="s">
         <v>30</v>
@@ -13651,7 +13651,7 @@
         <v>29</v>
       </c>
       <c r="D563">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E563" t="s">
         <v>30</v>
@@ -13668,7 +13668,7 @@
         <v>29</v>
       </c>
       <c r="D564">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E564" t="s">
         <v>30</v>
@@ -13685,7 +13685,7 @@
         <v>29</v>
       </c>
       <c r="D565">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E565" t="s">
         <v>30</v>
@@ -13702,7 +13702,7 @@
         <v>29</v>
       </c>
       <c r="D566">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E566" t="s">
         <v>30</v>
@@ -13736,7 +13736,7 @@
         <v>29</v>
       </c>
       <c r="D568">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E568" t="s">
         <v>30</v>
@@ -13753,7 +13753,7 @@
         <v>29</v>
       </c>
       <c r="D569">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E569" t="s">
         <v>30</v>
@@ -13770,7 +13770,7 @@
         <v>29</v>
       </c>
       <c r="D570">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E570" t="s">
         <v>30</v>
@@ -13787,7 +13787,7 @@
         <v>29</v>
       </c>
       <c r="D571">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E571" t="s">
         <v>30</v>
@@ -13821,7 +13821,7 @@
         <v>29</v>
       </c>
       <c r="D573">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E573" t="s">
         <v>30</v>
@@ -13838,7 +13838,7 @@
         <v>29</v>
       </c>
       <c r="D574">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E574" t="s">
         <v>30</v>
@@ -13872,7 +13872,7 @@
         <v>29</v>
       </c>
       <c r="D576">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E576" t="s">
         <v>30</v>
@@ -13906,7 +13906,7 @@
         <v>29</v>
       </c>
       <c r="D578">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E578" t="s">
         <v>30</v>
@@ -13923,7 +13923,7 @@
         <v>29</v>
       </c>
       <c r="D579">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E579" t="s">
         <v>30</v>
@@ -13940,7 +13940,7 @@
         <v>29</v>
       </c>
       <c r="D580">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E580" t="s">
         <v>30</v>
@@ -13957,7 +13957,7 @@
         <v>29</v>
       </c>
       <c r="D581">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E581" t="s">
         <v>30</v>
@@ -13974,7 +13974,7 @@
         <v>29</v>
       </c>
       <c r="D582">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E582" t="s">
         <v>30</v>
@@ -13991,7 +13991,7 @@
         <v>29</v>
       </c>
       <c r="D583">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E583" t="s">
         <v>30</v>
@@ -14008,7 +14008,7 @@
         <v>29</v>
       </c>
       <c r="D584">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E584" t="s">
         <v>30</v>
@@ -14025,7 +14025,7 @@
         <v>29</v>
       </c>
       <c r="D585">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E585" t="s">
         <v>30</v>
@@ -14042,7 +14042,7 @@
         <v>29</v>
       </c>
       <c r="D586">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E586" t="s">
         <v>30</v>
@@ -14059,7 +14059,7 @@
         <v>29</v>
       </c>
       <c r="D587">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E587" t="s">
         <v>30</v>
@@ -14076,7 +14076,7 @@
         <v>29</v>
       </c>
       <c r="D588">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E588" t="s">
         <v>30</v>
@@ -14093,7 +14093,7 @@
         <v>29</v>
       </c>
       <c r="D589">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E589" t="s">
         <v>30</v>
@@ -14127,7 +14127,7 @@
         <v>29</v>
       </c>
       <c r="D591">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E591" t="s">
         <v>30</v>
@@ -14144,7 +14144,7 @@
         <v>29</v>
       </c>
       <c r="D592">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E592" t="s">
         <v>30</v>
@@ -14161,7 +14161,7 @@
         <v>29</v>
       </c>
       <c r="D593">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E593" t="s">
         <v>30</v>
@@ -14178,7 +14178,7 @@
         <v>29</v>
       </c>
       <c r="D594">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E594" t="s">
         <v>30</v>
@@ -14195,7 +14195,7 @@
         <v>29</v>
       </c>
       <c r="D595">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E595" t="s">
         <v>30</v>
@@ -14212,7 +14212,7 @@
         <v>29</v>
       </c>
       <c r="D596">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E596" t="s">
         <v>30</v>
@@ -14229,7 +14229,7 @@
         <v>29</v>
       </c>
       <c r="D597">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E597" t="s">
         <v>30</v>
@@ -14263,7 +14263,7 @@
         <v>29</v>
       </c>
       <c r="D599">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E599" t="s">
         <v>30</v>
@@ -14280,7 +14280,7 @@
         <v>29</v>
       </c>
       <c r="D600">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E600" t="s">
         <v>30</v>
@@ -14297,7 +14297,7 @@
         <v>29</v>
       </c>
       <c r="D601">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E601" t="s">
         <v>30</v>
@@ -14314,7 +14314,7 @@
         <v>29</v>
       </c>
       <c r="D602">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E602" t="s">
         <v>30</v>
@@ -14348,7 +14348,7 @@
         <v>29</v>
       </c>
       <c r="D604">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E604" t="s">
         <v>30</v>
@@ -14365,7 +14365,7 @@
         <v>29</v>
       </c>
       <c r="D605">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E605" t="s">
         <v>30</v>
@@ -14382,7 +14382,7 @@
         <v>29</v>
       </c>
       <c r="D606">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E606" t="s">
         <v>30</v>
@@ -14399,7 +14399,7 @@
         <v>29</v>
       </c>
       <c r="D607">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E607" t="s">
         <v>30</v>
@@ -14416,7 +14416,7 @@
         <v>29</v>
       </c>
       <c r="D608">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E608" t="s">
         <v>30</v>
@@ -14433,7 +14433,7 @@
         <v>29</v>
       </c>
       <c r="D609">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E609" t="s">
         <v>30</v>
@@ -14450,7 +14450,7 @@
         <v>29</v>
       </c>
       <c r="D610">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E610" t="s">
         <v>30</v>
@@ -14467,7 +14467,7 @@
         <v>29</v>
       </c>
       <c r="D611">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E611" t="s">
         <v>30</v>
@@ -14484,7 +14484,7 @@
         <v>29</v>
       </c>
       <c r="D612">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E612" t="s">
         <v>30</v>
@@ -14501,7 +14501,7 @@
         <v>29</v>
       </c>
       <c r="D613">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E613" t="s">
         <v>30</v>
@@ -14518,7 +14518,7 @@
         <v>29</v>
       </c>
       <c r="D614">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E614" t="s">
         <v>30</v>
@@ -14535,7 +14535,7 @@
         <v>29</v>
       </c>
       <c r="D615">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E615" t="s">
         <v>30</v>
@@ -14552,7 +14552,7 @@
         <v>29</v>
       </c>
       <c r="D616">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E616" t="s">
         <v>30</v>
@@ -14569,7 +14569,7 @@
         <v>29</v>
       </c>
       <c r="D617">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E617" t="s">
         <v>30</v>
@@ -14586,7 +14586,7 @@
         <v>29</v>
       </c>
       <c r="D618">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E618" t="s">
         <v>30</v>
@@ -14603,7 +14603,7 @@
         <v>29</v>
       </c>
       <c r="D619">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E619" t="s">
         <v>30</v>
@@ -14637,7 +14637,7 @@
         <v>29</v>
       </c>
       <c r="D621">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E621" t="s">
         <v>30</v>
@@ -14654,7 +14654,7 @@
         <v>29</v>
       </c>
       <c r="D622">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E622" t="s">
         <v>30</v>
@@ -14671,7 +14671,7 @@
         <v>29</v>
       </c>
       <c r="D623">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E623" t="s">
         <v>30</v>
@@ -14688,7 +14688,7 @@
         <v>29</v>
       </c>
       <c r="D624">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E624" t="s">
         <v>30</v>
@@ -14705,7 +14705,7 @@
         <v>29</v>
       </c>
       <c r="D625">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E625" t="s">
         <v>30</v>
@@ -14739,7 +14739,7 @@
         <v>29</v>
       </c>
       <c r="D627">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E627" t="s">
         <v>30</v>
@@ -14756,7 +14756,7 @@
         <v>29</v>
       </c>
       <c r="D628">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E628" t="s">
         <v>30</v>
@@ -14773,7 +14773,7 @@
         <v>29</v>
       </c>
       <c r="D629">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E629" t="s">
         <v>30</v>
@@ -14790,7 +14790,7 @@
         <v>29</v>
       </c>
       <c r="D630">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E630" t="s">
         <v>30</v>
@@ -14807,7 +14807,7 @@
         <v>29</v>
       </c>
       <c r="D631">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E631" t="s">
         <v>30</v>
@@ -14824,7 +14824,7 @@
         <v>29</v>
       </c>
       <c r="D632">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E632" t="s">
         <v>30</v>
@@ -14841,7 +14841,7 @@
         <v>29</v>
       </c>
       <c r="D633">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E633" t="s">
         <v>30</v>
@@ -14858,7 +14858,7 @@
         <v>29</v>
       </c>
       <c r="D634">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E634" t="s">
         <v>30</v>
@@ -14875,7 +14875,7 @@
         <v>29</v>
       </c>
       <c r="D635">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E635" t="s">
         <v>30</v>
@@ -14892,7 +14892,7 @@
         <v>29</v>
       </c>
       <c r="D636">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E636" t="s">
         <v>30</v>
@@ -14909,7 +14909,7 @@
         <v>29</v>
       </c>
       <c r="D637">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E637" t="s">
         <v>30</v>
@@ -14926,7 +14926,7 @@
         <v>29</v>
       </c>
       <c r="D638">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E638" t="s">
         <v>30</v>
@@ -14943,7 +14943,7 @@
         <v>29</v>
       </c>
       <c r="D639">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E639" t="s">
         <v>30</v>
@@ -14960,7 +14960,7 @@
         <v>29</v>
       </c>
       <c r="D640">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E640" t="s">
         <v>30</v>
@@ -14977,7 +14977,7 @@
         <v>29</v>
       </c>
       <c r="D641">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E641" t="s">
         <v>30</v>
@@ -14994,7 +14994,7 @@
         <v>29</v>
       </c>
       <c r="D642">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E642" t="s">
         <v>30</v>
@@ -15011,7 +15011,7 @@
         <v>29</v>
       </c>
       <c r="D643">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E643" t="s">
         <v>30</v>
@@ -15028,7 +15028,7 @@
         <v>29</v>
       </c>
       <c r="D644">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E644" t="s">
         <v>30</v>
@@ -15045,7 +15045,7 @@
         <v>29</v>
       </c>
       <c r="D645">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E645" t="s">
         <v>30</v>
@@ -15079,7 +15079,7 @@
         <v>29</v>
       </c>
       <c r="D647">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E647" t="s">
         <v>30</v>
@@ -15096,7 +15096,7 @@
         <v>29</v>
       </c>
       <c r="D648">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E648" t="s">
         <v>30</v>
@@ -15113,7 +15113,7 @@
         <v>29</v>
       </c>
       <c r="D649">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E649" t="s">
         <v>30</v>
@@ -15130,7 +15130,7 @@
         <v>29</v>
       </c>
       <c r="D650">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E650" t="s">
         <v>30</v>
@@ -15147,7 +15147,7 @@
         <v>29</v>
       </c>
       <c r="D651">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E651" t="s">
         <v>30</v>
@@ -15164,7 +15164,7 @@
         <v>29</v>
       </c>
       <c r="D652">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E652" t="s">
         <v>30</v>
@@ -15181,7 +15181,7 @@
         <v>29</v>
       </c>
       <c r="D653">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E653" t="s">
         <v>30</v>
@@ -15198,7 +15198,7 @@
         <v>29</v>
       </c>
       <c r="D654">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E654" t="s">
         <v>30</v>
@@ -15215,7 +15215,7 @@
         <v>29</v>
       </c>
       <c r="D655">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E655" t="s">
         <v>30</v>
@@ -15232,7 +15232,7 @@
         <v>29</v>
       </c>
       <c r="D656">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E656" t="s">
         <v>30</v>
@@ -15266,7 +15266,7 @@
         <v>29</v>
       </c>
       <c r="D658">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E658" t="s">
         <v>30</v>
@@ -15283,7 +15283,7 @@
         <v>29</v>
       </c>
       <c r="D659">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E659" t="s">
         <v>30</v>
@@ -15300,7 +15300,7 @@
         <v>29</v>
       </c>
       <c r="D660">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E660" t="s">
         <v>30</v>
@@ -15317,7 +15317,7 @@
         <v>29</v>
       </c>
       <c r="D661">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E661" t="s">
         <v>30</v>
@@ -15334,7 +15334,7 @@
         <v>29</v>
       </c>
       <c r="D662">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E662" t="s">
         <v>30</v>
@@ -15351,7 +15351,7 @@
         <v>29</v>
       </c>
       <c r="D663">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E663" t="s">
         <v>30</v>
@@ -15368,7 +15368,7 @@
         <v>29</v>
       </c>
       <c r="D664">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E664" t="s">
         <v>30</v>
@@ -15385,7 +15385,7 @@
         <v>29</v>
       </c>
       <c r="D665">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E665" t="s">
         <v>30</v>
@@ -15402,7 +15402,7 @@
         <v>29</v>
       </c>
       <c r="D666">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E666" t="s">
         <v>30</v>
@@ -15436,7 +15436,7 @@
         <v>29</v>
       </c>
       <c r="D668">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E668" t="s">
         <v>30</v>
@@ -15453,7 +15453,7 @@
         <v>29</v>
       </c>
       <c r="D669">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E669" t="s">
         <v>30</v>
@@ -15470,7 +15470,7 @@
         <v>29</v>
       </c>
       <c r="D670">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E670" t="s">
         <v>30</v>
@@ -15487,7 +15487,7 @@
         <v>29</v>
       </c>
       <c r="D671">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E671" t="s">
         <v>30</v>
@@ -15504,7 +15504,7 @@
         <v>29</v>
       </c>
       <c r="D672">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E672" t="s">
         <v>30</v>
@@ -15521,7 +15521,7 @@
         <v>29</v>
       </c>
       <c r="D673">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E673" t="s">
         <v>30</v>
@@ -15538,7 +15538,7 @@
         <v>29</v>
       </c>
       <c r="D674">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E674" t="s">
         <v>30</v>
@@ -15555,7 +15555,7 @@
         <v>29</v>
       </c>
       <c r="D675">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E675" t="s">
         <v>30</v>
@@ -15572,7 +15572,7 @@
         <v>29</v>
       </c>
       <c r="D676">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E676" t="s">
         <v>30</v>
@@ -15589,7 +15589,7 @@
         <v>29</v>
       </c>
       <c r="D677">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E677" t="s">
         <v>30</v>
@@ -15606,7 +15606,7 @@
         <v>29</v>
       </c>
       <c r="D678">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E678" t="s">
         <v>30</v>
@@ -15623,7 +15623,7 @@
         <v>29</v>
       </c>
       <c r="D679">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E679" t="s">
         <v>30</v>
@@ -15640,7 +15640,7 @@
         <v>29</v>
       </c>
       <c r="D680">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E680" t="s">
         <v>30</v>
@@ -15657,7 +15657,7 @@
         <v>29</v>
       </c>
       <c r="D681">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E681" t="s">
         <v>30</v>
@@ -15674,7 +15674,7 @@
         <v>29</v>
       </c>
       <c r="D682">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E682" t="s">
         <v>30</v>
@@ -15691,7 +15691,7 @@
         <v>29</v>
       </c>
       <c r="D683">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E683" t="s">
         <v>30</v>
@@ -15708,7 +15708,7 @@
         <v>29</v>
       </c>
       <c r="D684">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E684" t="s">
         <v>30</v>
@@ -15725,7 +15725,7 @@
         <v>29</v>
       </c>
       <c r="D685">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E685" t="s">
         <v>30</v>
@@ -15742,7 +15742,7 @@
         <v>29</v>
       </c>
       <c r="D686">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E686" t="s">
         <v>30</v>
@@ -15759,7 +15759,7 @@
         <v>29</v>
       </c>
       <c r="D687">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E687" t="s">
         <v>30</v>
@@ -15776,7 +15776,7 @@
         <v>29</v>
       </c>
       <c r="D688">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E688" t="s">
         <v>30</v>
@@ -15793,7 +15793,7 @@
         <v>29</v>
       </c>
       <c r="D689">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E689" t="s">
         <v>30</v>
@@ -15810,7 +15810,7 @@
         <v>29</v>
       </c>
       <c r="D690">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E690" t="s">
         <v>30</v>
@@ -15827,7 +15827,7 @@
         <v>29</v>
       </c>
       <c r="D691">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E691" t="s">
         <v>30</v>
@@ -15844,7 +15844,7 @@
         <v>29</v>
       </c>
       <c r="D692">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E692" t="s">
         <v>30</v>
@@ -15861,7 +15861,7 @@
         <v>29</v>
       </c>
       <c r="D693">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E693" t="s">
         <v>30</v>
@@ -15878,7 +15878,7 @@
         <v>29</v>
       </c>
       <c r="D694">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E694" t="s">
         <v>30</v>
@@ -15929,7 +15929,7 @@
         <v>29</v>
       </c>
       <c r="D697">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E697" t="s">
         <v>30</v>
@@ -15946,7 +15946,7 @@
         <v>29</v>
       </c>
       <c r="D698">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E698" t="s">
         <v>30</v>
@@ -15963,7 +15963,7 @@
         <v>29</v>
       </c>
       <c r="D699">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E699" t="s">
         <v>30</v>
@@ -15980,7 +15980,7 @@
         <v>29</v>
       </c>
       <c r="D700">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E700" t="s">
         <v>30</v>
@@ -15997,7 +15997,7 @@
         <v>29</v>
       </c>
       <c r="D701">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E701" t="s">
         <v>30</v>
@@ -16014,7 +16014,7 @@
         <v>29</v>
       </c>
       <c r="D702">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E702" t="s">
         <v>30</v>
@@ -16031,7 +16031,7 @@
         <v>29</v>
       </c>
       <c r="D703">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E703" t="s">
         <v>30</v>
@@ -16048,7 +16048,7 @@
         <v>29</v>
       </c>
       <c r="D704">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E704" t="s">
         <v>30</v>
@@ -16065,7 +16065,7 @@
         <v>29</v>
       </c>
       <c r="D705">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E705" t="s">
         <v>30</v>
@@ -16082,7 +16082,7 @@
         <v>29</v>
       </c>
       <c r="D706">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E706" t="s">
         <v>30</v>
@@ -16099,7 +16099,7 @@
         <v>29</v>
       </c>
       <c r="D707">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E707" t="s">
         <v>30</v>
@@ -16116,7 +16116,7 @@
         <v>29</v>
       </c>
       <c r="D708">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E708" t="s">
         <v>30</v>
@@ -16133,7 +16133,7 @@
         <v>29</v>
       </c>
       <c r="D709">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E709" t="s">
         <v>30</v>
@@ -16150,7 +16150,7 @@
         <v>29</v>
       </c>
       <c r="D710">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E710" t="s">
         <v>30</v>
@@ -16167,7 +16167,7 @@
         <v>29</v>
       </c>
       <c r="D711">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E711" t="s">
         <v>30</v>
@@ -16184,7 +16184,7 @@
         <v>29</v>
       </c>
       <c r="D712">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E712" t="s">
         <v>30</v>
@@ -16201,7 +16201,7 @@
         <v>29</v>
       </c>
       <c r="D713">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E713" t="s">
         <v>30</v>
@@ -16218,7 +16218,7 @@
         <v>29</v>
       </c>
       <c r="D714">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E714" t="s">
         <v>30</v>
@@ -16235,7 +16235,7 @@
         <v>29</v>
       </c>
       <c r="D715">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E715" t="s">
         <v>30</v>
@@ -16252,7 +16252,7 @@
         <v>29</v>
       </c>
       <c r="D716">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E716" t="s">
         <v>30</v>
@@ -16269,7 +16269,7 @@
         <v>29</v>
       </c>
       <c r="D717">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E717" t="s">
         <v>30</v>
@@ -16286,7 +16286,7 @@
         <v>29</v>
       </c>
       <c r="D718">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E718" t="s">
         <v>30</v>
@@ -16303,7 +16303,7 @@
         <v>29</v>
       </c>
       <c r="D719">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E719" t="s">
         <v>30</v>
@@ -16320,7 +16320,7 @@
         <v>29</v>
       </c>
       <c r="D720">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E720" t="s">
         <v>30</v>
@@ -16337,7 +16337,7 @@
         <v>29</v>
       </c>
       <c r="D721">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E721" t="s">
         <v>30</v>
@@ -16354,7 +16354,7 @@
         <v>29</v>
       </c>
       <c r="D722">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E722" t="s">
         <v>30</v>
@@ -16371,7 +16371,7 @@
         <v>29</v>
       </c>
       <c r="D723">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E723" t="s">
         <v>30</v>
@@ -16388,7 +16388,7 @@
         <v>29</v>
       </c>
       <c r="D724">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E724" t="s">
         <v>30</v>
@@ -16405,7 +16405,7 @@
         <v>29</v>
       </c>
       <c r="D725">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E725" t="s">
         <v>30</v>
@@ -16422,7 +16422,7 @@
         <v>29</v>
       </c>
       <c r="D726">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E726" t="s">
         <v>30</v>
@@ -16456,7 +16456,7 @@
         <v>29</v>
       </c>
       <c r="D728">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E728" t="s">
         <v>30</v>
@@ -16473,7 +16473,7 @@
         <v>29</v>
       </c>
       <c r="D729">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E729" t="s">
         <v>30</v>
@@ -16490,7 +16490,7 @@
         <v>29</v>
       </c>
       <c r="D730">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E730" t="s">
         <v>30</v>
@@ -16507,7 +16507,7 @@
         <v>29</v>
       </c>
       <c r="D731">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E731" t="s">
         <v>30</v>
@@ -16524,7 +16524,7 @@
         <v>29</v>
       </c>
       <c r="D732">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E732" t="s">
         <v>30</v>
@@ -16541,7 +16541,7 @@
         <v>29</v>
       </c>
       <c r="D733">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E733" t="s">
         <v>30</v>
@@ -16558,7 +16558,7 @@
         <v>29</v>
       </c>
       <c r="D734">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E734" t="s">
         <v>30</v>
@@ -16575,7 +16575,7 @@
         <v>29</v>
       </c>
       <c r="D735">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E735" t="s">
         <v>30</v>
@@ -16592,7 +16592,7 @@
         <v>29</v>
       </c>
       <c r="D736">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E736" t="s">
         <v>30</v>
@@ -16609,7 +16609,7 @@
         <v>29</v>
       </c>
       <c r="D737">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E737" t="s">
         <v>30</v>
@@ -16626,7 +16626,7 @@
         <v>29</v>
       </c>
       <c r="D738">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E738" t="s">
         <v>30</v>
@@ -16643,7 +16643,7 @@
         <v>29</v>
       </c>
       <c r="D739">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E739" t="s">
         <v>30</v>
@@ -16660,7 +16660,7 @@
         <v>29</v>
       </c>
       <c r="D740">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E740" t="s">
         <v>30</v>
@@ -16677,7 +16677,7 @@
         <v>29</v>
       </c>
       <c r="D741">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E741" t="s">
         <v>30</v>
@@ -16694,7 +16694,7 @@
         <v>29</v>
       </c>
       <c r="D742">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E742" t="s">
         <v>30</v>
@@ -16711,7 +16711,7 @@
         <v>29</v>
       </c>
       <c r="D743">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E743" t="s">
         <v>30</v>
@@ -16728,7 +16728,7 @@
         <v>29</v>
       </c>
       <c r="D744">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E744" t="s">
         <v>30</v>
@@ -16745,7 +16745,7 @@
         <v>29</v>
       </c>
       <c r="D745">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E745" t="s">
         <v>30</v>
@@ -16779,7 +16779,7 @@
         <v>29</v>
       </c>
       <c r="D747">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E747" t="s">
         <v>30</v>
@@ -16796,7 +16796,7 @@
         <v>29</v>
       </c>
       <c r="D748">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E748" t="s">
         <v>30</v>
@@ -16813,7 +16813,7 @@
         <v>29</v>
       </c>
       <c r="D749">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E749" t="s">
         <v>30</v>
@@ -16830,7 +16830,7 @@
         <v>29</v>
       </c>
       <c r="D750">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E750" t="s">
         <v>30</v>
@@ -16847,7 +16847,7 @@
         <v>29</v>
       </c>
       <c r="D751">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E751" t="s">
         <v>30</v>
@@ -16864,7 +16864,7 @@
         <v>29</v>
       </c>
       <c r="D752">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E752" t="s">
         <v>30</v>
@@ -16881,7 +16881,7 @@
         <v>29</v>
       </c>
       <c r="D753">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E753" t="s">
         <v>30</v>
@@ -16898,7 +16898,7 @@
         <v>29</v>
       </c>
       <c r="D754">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E754" t="s">
         <v>30</v>
@@ -16932,7 +16932,7 @@
         <v>29</v>
       </c>
       <c r="D756">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E756" t="s">
         <v>30</v>
@@ -16949,7 +16949,7 @@
         <v>29</v>
       </c>
       <c r="D757">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E757" t="s">
         <v>30</v>
@@ -16966,7 +16966,7 @@
         <v>29</v>
       </c>
       <c r="D758">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E758" t="s">
         <v>30</v>
@@ -16983,7 +16983,7 @@
         <v>29</v>
       </c>
       <c r="D759">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E759" t="s">
         <v>30</v>
@@ -17000,7 +17000,7 @@
         <v>29</v>
       </c>
       <c r="D760">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E760" t="s">
         <v>30</v>
@@ -17017,7 +17017,7 @@
         <v>29</v>
       </c>
       <c r="D761">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E761" t="s">
         <v>30</v>
@@ -17034,7 +17034,7 @@
         <v>29</v>
       </c>
       <c r="D762">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E762" t="s">
         <v>30</v>
@@ -17051,7 +17051,7 @@
         <v>29</v>
       </c>
       <c r="D763">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E763" t="s">
         <v>30</v>
@@ -17068,7 +17068,7 @@
         <v>29</v>
       </c>
       <c r="D764">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E764" t="s">
         <v>30</v>
@@ -17085,7 +17085,7 @@
         <v>29</v>
       </c>
       <c r="D765">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E765" t="s">
         <v>30</v>
@@ -17102,7 +17102,7 @@
         <v>29</v>
       </c>
       <c r="D766">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E766" t="s">
         <v>30</v>
@@ -17119,7 +17119,7 @@
         <v>29</v>
       </c>
       <c r="D767">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E767" t="s">
         <v>30</v>
@@ -17136,7 +17136,7 @@
         <v>29</v>
       </c>
       <c r="D768">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E768" t="s">
         <v>30</v>
@@ -17153,7 +17153,7 @@
         <v>29</v>
       </c>
       <c r="D769">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E769" t="s">
         <v>30</v>
@@ -17170,7 +17170,7 @@
         <v>29</v>
       </c>
       <c r="D770">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E770" t="s">
         <v>30</v>
@@ -17187,7 +17187,7 @@
         <v>29</v>
       </c>
       <c r="D771">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E771" t="s">
         <v>30</v>
@@ -17204,7 +17204,7 @@
         <v>29</v>
       </c>
       <c r="D772">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E772" t="s">
         <v>30</v>
@@ -17221,7 +17221,7 @@
         <v>29</v>
       </c>
       <c r="D773">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E773" t="s">
         <v>30</v>
@@ -17238,7 +17238,7 @@
         <v>29</v>
       </c>
       <c r="D774">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E774" t="s">
         <v>30</v>
@@ -17255,7 +17255,7 @@
         <v>29</v>
       </c>
       <c r="D775">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E775" t="s">
         <v>30</v>
@@ -17272,7 +17272,7 @@
         <v>29</v>
       </c>
       <c r="D776">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E776" t="s">
         <v>30</v>
@@ -17306,7 +17306,7 @@
         <v>29</v>
       </c>
       <c r="D778">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E778" t="s">
         <v>30</v>
@@ -17323,7 +17323,7 @@
         <v>29</v>
       </c>
       <c r="D779">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E779" t="s">
         <v>30</v>
@@ -17340,7 +17340,7 @@
         <v>29</v>
       </c>
       <c r="D780">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E780" t="s">
         <v>30</v>
@@ -17357,7 +17357,7 @@
         <v>29</v>
       </c>
       <c r="D781">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E781" t="s">
         <v>30</v>
@@ -17374,7 +17374,7 @@
         <v>29</v>
       </c>
       <c r="D782">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E782" t="s">
         <v>30</v>
@@ -17391,7 +17391,7 @@
         <v>29</v>
       </c>
       <c r="D783">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E783" t="s">
         <v>30</v>
@@ -17408,7 +17408,7 @@
         <v>29</v>
       </c>
       <c r="D784">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E784" t="s">
         <v>30</v>
@@ -17425,7 +17425,7 @@
         <v>29</v>
       </c>
       <c r="D785">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E785" t="s">
         <v>30</v>
@@ -17442,7 +17442,7 @@
         <v>29</v>
       </c>
       <c r="D786">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E786" t="s">
         <v>30</v>
@@ -17459,7 +17459,7 @@
         <v>29</v>
       </c>
       <c r="D787">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E787" t="s">
         <v>30</v>
@@ -17476,7 +17476,7 @@
         <v>29</v>
       </c>
       <c r="D788">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E788" t="s">
         <v>30</v>
@@ -17493,7 +17493,7 @@
         <v>29</v>
       </c>
       <c r="D789">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E789" t="s">
         <v>30</v>
@@ -17510,7 +17510,7 @@
         <v>29</v>
       </c>
       <c r="D790">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E790" t="s">
         <v>30</v>
@@ -17527,7 +17527,7 @@
         <v>29</v>
       </c>
       <c r="D791">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E791" t="s">
         <v>30</v>
@@ -17544,7 +17544,7 @@
         <v>29</v>
       </c>
       <c r="D792">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E792" t="s">
         <v>30</v>
@@ -17561,7 +17561,7 @@
         <v>29</v>
       </c>
       <c r="D793">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E793" t="s">
         <v>30</v>
@@ -17578,7 +17578,7 @@
         <v>29</v>
       </c>
       <c r="D794">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E794" t="s">
         <v>30</v>
@@ -17595,7 +17595,7 @@
         <v>29</v>
       </c>
       <c r="D795">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E795" t="s">
         <v>30</v>
@@ -17612,7 +17612,7 @@
         <v>29</v>
       </c>
       <c r="D796">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E796" t="s">
         <v>30</v>
@@ -17629,7 +17629,7 @@
         <v>29</v>
       </c>
       <c r="D797">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E797" t="s">
         <v>30</v>
@@ -17646,7 +17646,7 @@
         <v>29</v>
       </c>
       <c r="D798">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E798" t="s">
         <v>30</v>
@@ -17663,7 +17663,7 @@
         <v>29</v>
       </c>
       <c r="D799">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E799" t="s">
         <v>30</v>
@@ -17680,7 +17680,7 @@
         <v>29</v>
       </c>
       <c r="D800">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E800" t="s">
         <v>30</v>
@@ -17697,7 +17697,7 @@
         <v>29</v>
       </c>
       <c r="D801">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E801" t="s">
         <v>30</v>
@@ -17714,7 +17714,7 @@
         <v>29</v>
       </c>
       <c r="D802">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E802" t="s">
         <v>30</v>
@@ -17731,7 +17731,7 @@
         <v>29</v>
       </c>
       <c r="D803">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E803" t="s">
         <v>30</v>
@@ -17748,7 +17748,7 @@
         <v>29</v>
       </c>
       <c r="D804">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E804" t="s">
         <v>30</v>
@@ -17765,7 +17765,7 @@
         <v>29</v>
       </c>
       <c r="D805">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E805" t="s">
         <v>30</v>
@@ -17782,7 +17782,7 @@
         <v>29</v>
       </c>
       <c r="D806">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E806" t="s">
         <v>30</v>
@@ -17799,7 +17799,7 @@
         <v>29</v>
       </c>
       <c r="D807">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E807" t="s">
         <v>30</v>
@@ -17816,7 +17816,7 @@
         <v>29</v>
       </c>
       <c r="D808">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E808" t="s">
         <v>30</v>
@@ -17833,7 +17833,7 @@
         <v>29</v>
       </c>
       <c r="D809">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E809" t="s">
         <v>30</v>
@@ -17850,7 +17850,7 @@
         <v>29</v>
       </c>
       <c r="D810">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E810" t="s">
         <v>30</v>
@@ -17867,7 +17867,7 @@
         <v>29</v>
       </c>
       <c r="D811">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E811" t="s">
         <v>30</v>
@@ -17901,7 +17901,7 @@
         <v>29</v>
       </c>
       <c r="D813">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E813" t="s">
         <v>30</v>
@@ -17918,7 +17918,7 @@
         <v>29</v>
       </c>
       <c r="D814">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E814" t="s">
         <v>30</v>
@@ -17935,7 +17935,7 @@
         <v>29</v>
       </c>
       <c r="D815">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E815" t="s">
         <v>30</v>
@@ -17952,7 +17952,7 @@
         <v>29</v>
       </c>
       <c r="D816">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E816" t="s">
         <v>30</v>
@@ -17969,7 +17969,7 @@
         <v>29</v>
       </c>
       <c r="D817">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E817" t="s">
         <v>30</v>
@@ -17986,7 +17986,7 @@
         <v>29</v>
       </c>
       <c r="D818">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E818" t="s">
         <v>30</v>
@@ -18003,7 +18003,7 @@
         <v>29</v>
       </c>
       <c r="D819">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E819" t="s">
         <v>30</v>
@@ -18020,7 +18020,7 @@
         <v>29</v>
       </c>
       <c r="D820">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E820" t="s">
         <v>30</v>
@@ -18037,7 +18037,7 @@
         <v>29</v>
       </c>
       <c r="D821">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E821" t="s">
         <v>30</v>
@@ -18054,7 +18054,7 @@
         <v>29</v>
       </c>
       <c r="D822">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E822" t="s">
         <v>30</v>
@@ -18071,7 +18071,7 @@
         <v>29</v>
       </c>
       <c r="D823">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E823" t="s">
         <v>30</v>
@@ -18088,7 +18088,7 @@
         <v>29</v>
       </c>
       <c r="D824">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E824" t="s">
         <v>30</v>
@@ -18105,7 +18105,7 @@
         <v>29</v>
       </c>
       <c r="D825">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E825" t="s">
         <v>30</v>
@@ -18122,7 +18122,7 @@
         <v>29</v>
       </c>
       <c r="D826">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E826" t="s">
         <v>30</v>
@@ -18139,7 +18139,7 @@
         <v>29</v>
       </c>
       <c r="D827">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E827" t="s">
         <v>30</v>
@@ -18156,7 +18156,7 @@
         <v>29</v>
       </c>
       <c r="D828">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E828" t="s">
         <v>30</v>
@@ -18173,7 +18173,7 @@
         <v>29</v>
       </c>
       <c r="D829">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E829" t="s">
         <v>30</v>
@@ -18190,7 +18190,7 @@
         <v>29</v>
       </c>
       <c r="D830">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E830" t="s">
         <v>30</v>
@@ -18207,7 +18207,7 @@
         <v>29</v>
       </c>
       <c r="D831">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E831" t="s">
         <v>30</v>
@@ -18224,7 +18224,7 @@
         <v>29</v>
       </c>
       <c r="D832">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E832" t="s">
         <v>30</v>
@@ -18241,7 +18241,7 @@
         <v>29</v>
       </c>
       <c r="D833">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E833" t="s">
         <v>30</v>
@@ -18275,7 +18275,7 @@
         <v>29</v>
       </c>
       <c r="D835">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E835" t="s">
         <v>30</v>
@@ -18292,7 +18292,7 @@
         <v>29</v>
       </c>
       <c r="D836">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E836" t="s">
         <v>30</v>
@@ -18309,7 +18309,7 @@
         <v>29</v>
       </c>
       <c r="D837">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E837" t="s">
         <v>30</v>
@@ -18326,7 +18326,7 @@
         <v>29</v>
       </c>
       <c r="D838">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E838" t="s">
         <v>30</v>
@@ -18343,7 +18343,7 @@
         <v>29</v>
       </c>
       <c r="D839">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E839" t="s">
         <v>30</v>
@@ -18360,7 +18360,7 @@
         <v>29</v>
       </c>
       <c r="D840">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E840" t="s">
         <v>30</v>
@@ -18377,7 +18377,7 @@
         <v>29</v>
       </c>
       <c r="D841">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E841" t="s">
         <v>30</v>
@@ -18411,7 +18411,7 @@
         <v>29</v>
       </c>
       <c r="D843">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E843" t="s">
         <v>30</v>
@@ -18428,7 +18428,7 @@
         <v>29</v>
       </c>
       <c r="D844">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E844" t="s">
         <v>30</v>
@@ -18445,7 +18445,7 @@
         <v>29</v>
       </c>
       <c r="D845">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E845" t="s">
         <v>30</v>
@@ -18462,7 +18462,7 @@
         <v>29</v>
       </c>
       <c r="D846">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E846" t="s">
         <v>30</v>
@@ -18479,7 +18479,7 @@
         <v>29</v>
       </c>
       <c r="D847">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E847" t="s">
         <v>30</v>
@@ -18496,7 +18496,7 @@
         <v>29</v>
       </c>
       <c r="D848">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E848" t="s">
         <v>30</v>
@@ -18513,7 +18513,7 @@
         <v>29</v>
       </c>
       <c r="D849">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E849" t="s">
         <v>30</v>
@@ -18530,7 +18530,7 @@
         <v>29</v>
       </c>
       <c r="D850">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E850" t="s">
         <v>30</v>
@@ -18547,7 +18547,7 @@
         <v>29</v>
       </c>
       <c r="D851">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E851" t="s">
         <v>30</v>
@@ -18564,7 +18564,7 @@
         <v>29</v>
       </c>
       <c r="D852">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E852" t="s">
         <v>30</v>
@@ -18581,7 +18581,7 @@
         <v>29</v>
       </c>
       <c r="D853">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E853" t="s">
         <v>30</v>
@@ -18598,7 +18598,7 @@
         <v>29</v>
       </c>
       <c r="D854">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E854" t="s">
         <v>30</v>
@@ -18632,7 +18632,7 @@
         <v>29</v>
       </c>
       <c r="D856">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E856" t="s">
         <v>30</v>
@@ -18649,7 +18649,7 @@
         <v>29</v>
       </c>
       <c r="D857">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E857" t="s">
         <v>30</v>
@@ -18666,7 +18666,7 @@
         <v>29</v>
       </c>
       <c r="D858">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E858" t="s">
         <v>30</v>
@@ -18683,7 +18683,7 @@
         <v>29</v>
       </c>
       <c r="D859">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E859" t="s">
         <v>30</v>
@@ -18700,7 +18700,7 @@
         <v>29</v>
       </c>
       <c r="D860">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E860" t="s">
         <v>30</v>
@@ -18717,7 +18717,7 @@
         <v>29</v>
       </c>
       <c r="D861">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E861" t="s">
         <v>30</v>
@@ -18734,7 +18734,7 @@
         <v>29</v>
       </c>
       <c r="D862">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E862" t="s">
         <v>30</v>
@@ -18751,7 +18751,7 @@
         <v>29</v>
       </c>
       <c r="D863">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E863" t="s">
         <v>30</v>
@@ -18768,7 +18768,7 @@
         <v>29</v>
       </c>
       <c r="D864">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E864" t="s">
         <v>30</v>
@@ -18785,7 +18785,7 @@
         <v>29</v>
       </c>
       <c r="D865">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E865" t="s">
         <v>30</v>
@@ -18802,7 +18802,7 @@
         <v>29</v>
       </c>
       <c r="D866">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E866" t="s">
         <v>30</v>
@@ -18819,7 +18819,7 @@
         <v>29</v>
       </c>
       <c r="D867">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E867" t="s">
         <v>30</v>
@@ -18836,7 +18836,7 @@
         <v>29</v>
       </c>
       <c r="D868">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E868" t="s">
         <v>30</v>
@@ -18853,7 +18853,7 @@
         <v>29</v>
       </c>
       <c r="D869">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E869" t="s">
         <v>30</v>
@@ -18870,7 +18870,7 @@
         <v>29</v>
       </c>
       <c r="D870">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E870" t="s">
         <v>30</v>
@@ -18887,7 +18887,7 @@
         <v>29</v>
       </c>
       <c r="D871">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E871" t="s">
         <v>30</v>
@@ -18904,7 +18904,7 @@
         <v>29</v>
       </c>
       <c r="D872">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E872" t="s">
         <v>30</v>
@@ -18938,7 +18938,7 @@
         <v>29</v>
       </c>
       <c r="D874">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E874" t="s">
         <v>30</v>
@@ -18955,7 +18955,7 @@
         <v>29</v>
       </c>
       <c r="D875">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E875" t="s">
         <v>30</v>
@@ -18989,7 +18989,7 @@
         <v>29</v>
       </c>
       <c r="D877">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E877" t="s">
         <v>30</v>
@@ -19023,7 +19023,7 @@
         <v>29</v>
       </c>
       <c r="D879">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E879" t="s">
         <v>30</v>
@@ -19040,7 +19040,7 @@
         <v>29</v>
       </c>
       <c r="D880">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E880" t="s">
         <v>30</v>
@@ -19057,7 +19057,7 @@
         <v>29</v>
       </c>
       <c r="D881">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E881" t="s">
         <v>30</v>
@@ -19074,7 +19074,7 @@
         <v>29</v>
       </c>
       <c r="D882">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E882" t="s">
         <v>30</v>
@@ -19091,7 +19091,7 @@
         <v>29</v>
       </c>
       <c r="D883">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E883" t="s">
         <v>30</v>
@@ -19108,7 +19108,7 @@
         <v>29</v>
       </c>
       <c r="D884">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E884" t="s">
         <v>30</v>
@@ -19125,7 +19125,7 @@
         <v>29</v>
       </c>
       <c r="D885">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E885" t="s">
         <v>30</v>
@@ -19142,7 +19142,7 @@
         <v>29</v>
       </c>
       <c r="D886">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E886" t="s">
         <v>30</v>
@@ -19159,7 +19159,7 @@
         <v>29</v>
       </c>
       <c r="D887">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E887" t="s">
         <v>30</v>
@@ -19176,7 +19176,7 @@
         <v>29</v>
       </c>
       <c r="D888">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E888" t="s">
         <v>30</v>
@@ -19210,7 +19210,7 @@
         <v>29</v>
       </c>
       <c r="D890">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E890" t="s">
         <v>30</v>
@@ -19227,7 +19227,7 @@
         <v>29</v>
       </c>
       <c r="D891">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E891" t="s">
         <v>30</v>
@@ -19244,7 +19244,7 @@
         <v>29</v>
       </c>
       <c r="D892">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E892" t="s">
         <v>30</v>
@@ -19261,7 +19261,7 @@
         <v>29</v>
       </c>
       <c r="D893">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E893" t="s">
         <v>30</v>
@@ -19278,7 +19278,7 @@
         <v>29</v>
       </c>
       <c r="D894">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E894" t="s">
         <v>30</v>
@@ -19295,7 +19295,7 @@
         <v>29</v>
       </c>
       <c r="D895">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E895" t="s">
         <v>30</v>
@@ -19312,7 +19312,7 @@
         <v>29</v>
       </c>
       <c r="D896">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E896" t="s">
         <v>30</v>
@@ -19329,7 +19329,7 @@
         <v>29</v>
       </c>
       <c r="D897">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E897" t="s">
         <v>30</v>
@@ -19346,7 +19346,7 @@
         <v>29</v>
       </c>
       <c r="D898">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E898" t="s">
         <v>30</v>
@@ -19363,7 +19363,7 @@
         <v>29</v>
       </c>
       <c r="D899">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E899" t="s">
         <v>30</v>
@@ -19380,7 +19380,7 @@
         <v>29</v>
       </c>
       <c r="D900">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E900" t="s">
         <v>30</v>
@@ -19397,7 +19397,7 @@
         <v>29</v>
       </c>
       <c r="D901">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E901" t="s">
         <v>30</v>
@@ -19414,7 +19414,7 @@
         <v>29</v>
       </c>
       <c r="D902">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E902" t="s">
         <v>30</v>
@@ -19431,7 +19431,7 @@
         <v>29</v>
       </c>
       <c r="D903">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E903" t="s">
         <v>30</v>
@@ -19448,7 +19448,7 @@
         <v>29</v>
       </c>
       <c r="D904">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E904" t="s">
         <v>30</v>
@@ -19465,7 +19465,7 @@
         <v>29</v>
       </c>
       <c r="D905">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E905" t="s">
         <v>30</v>
@@ -19482,7 +19482,7 @@
         <v>29</v>
       </c>
       <c r="D906">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E906" t="s">
         <v>30</v>
@@ -19499,7 +19499,7 @@
         <v>29</v>
       </c>
       <c r="D907">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E907" t="s">
         <v>30</v>
@@ -19516,7 +19516,7 @@
         <v>29</v>
       </c>
       <c r="D908">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E908" t="s">
         <v>30</v>
@@ -19533,7 +19533,7 @@
         <v>29</v>
       </c>
       <c r="D909">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E909" t="s">
         <v>30</v>
@@ -19550,7 +19550,7 @@
         <v>29</v>
       </c>
       <c r="D910">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E910" t="s">
         <v>30</v>
@@ -19584,7 +19584,7 @@
         <v>29</v>
       </c>
       <c r="D912">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E912" t="s">
         <v>30</v>
@@ -19601,7 +19601,7 @@
         <v>29</v>
       </c>
       <c r="D913">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E913" t="s">
         <v>30</v>
@@ -19618,7 +19618,7 @@
         <v>29</v>
       </c>
       <c r="D914">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E914" t="s">
         <v>30</v>
@@ -19635,7 +19635,7 @@
         <v>29</v>
       </c>
       <c r="D915">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E915" t="s">
         <v>30</v>
@@ -19652,7 +19652,7 @@
         <v>29</v>
       </c>
       <c r="D916">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E916" t="s">
         <v>30</v>
@@ -19669,7 +19669,7 @@
         <v>29</v>
       </c>
       <c r="D917">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E917" t="s">
         <v>30</v>
@@ -19686,7 +19686,7 @@
         <v>29</v>
       </c>
       <c r="D918">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E918" t="s">
         <v>30</v>
@@ -19703,7 +19703,7 @@
         <v>29</v>
       </c>
       <c r="D919">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E919" t="s">
         <v>30</v>
@@ -19720,7 +19720,7 @@
         <v>29</v>
       </c>
       <c r="D920">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E920" t="s">
         <v>30</v>
@@ -19737,7 +19737,7 @@
         <v>29</v>
       </c>
       <c r="D921">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E921" t="s">
         <v>30</v>
@@ -19754,7 +19754,7 @@
         <v>29</v>
       </c>
       <c r="D922">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E922" t="s">
         <v>30</v>
@@ -19771,7 +19771,7 @@
         <v>29</v>
       </c>
       <c r="D923">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E923" t="s">
         <v>30</v>
@@ -19788,7 +19788,7 @@
         <v>29</v>
       </c>
       <c r="D924">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E924" t="s">
         <v>30</v>
@@ -19805,7 +19805,7 @@
         <v>29</v>
       </c>
       <c r="D925">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E925" t="s">
         <v>30</v>
@@ -19822,7 +19822,7 @@
         <v>29</v>
       </c>
       <c r="D926">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E926" t="s">
         <v>30</v>
@@ -19839,7 +19839,7 @@
         <v>29</v>
       </c>
       <c r="D927">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E927" t="s">
         <v>30</v>
@@ -19856,7 +19856,7 @@
         <v>29</v>
       </c>
       <c r="D928">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E928" t="s">
         <v>30</v>
@@ -19873,7 +19873,7 @@
         <v>29</v>
       </c>
       <c r="D929">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E929" t="s">
         <v>30</v>
@@ -19890,7 +19890,7 @@
         <v>29</v>
       </c>
       <c r="D930">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E930" t="s">
         <v>30</v>
@@ -19907,7 +19907,7 @@
         <v>29</v>
       </c>
       <c r="D931">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E931" t="s">
         <v>30</v>
@@ -19924,7 +19924,7 @@
         <v>29</v>
       </c>
       <c r="D932">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E932" t="s">
         <v>30</v>
@@ -19941,7 +19941,7 @@
         <v>29</v>
       </c>
       <c r="D933">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E933" t="s">
         <v>30</v>
@@ -19958,7 +19958,7 @@
         <v>29</v>
       </c>
       <c r="D934">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E934" t="s">
         <v>30</v>
@@ -19975,7 +19975,7 @@
         <v>29</v>
       </c>
       <c r="D935">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E935" t="s">
         <v>30</v>
@@ -19992,7 +19992,7 @@
         <v>29</v>
       </c>
       <c r="D936">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E936" t="s">
         <v>30</v>
@@ -20009,7 +20009,7 @@
         <v>29</v>
       </c>
       <c r="D937">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E937" t="s">
         <v>30</v>
@@ -20026,7 +20026,7 @@
         <v>29</v>
       </c>
       <c r="D938">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E938" t="s">
         <v>30</v>
@@ -20043,7 +20043,7 @@
         <v>29</v>
       </c>
       <c r="D939">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E939" t="s">
         <v>30</v>
@@ -20060,7 +20060,7 @@
         <v>29</v>
       </c>
       <c r="D940">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E940" t="s">
         <v>30</v>
@@ -20077,7 +20077,7 @@
         <v>29</v>
       </c>
       <c r="D941">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E941" t="s">
         <v>30</v>
@@ -20094,7 +20094,7 @@
         <v>29</v>
       </c>
       <c r="D942">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E942" t="s">
         <v>30</v>
@@ -20111,7 +20111,7 @@
         <v>29</v>
       </c>
       <c r="D943">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E943" t="s">
         <v>30</v>
@@ -20128,7 +20128,7 @@
         <v>29</v>
       </c>
       <c r="D944">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E944" t="s">
         <v>30</v>
@@ -20145,7 +20145,7 @@
         <v>29</v>
       </c>
       <c r="D945">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E945" t="s">
         <v>30</v>
@@ -20162,7 +20162,7 @@
         <v>29</v>
       </c>
       <c r="D946">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E946" t="s">
         <v>30</v>
@@ -20179,7 +20179,7 @@
         <v>29</v>
       </c>
       <c r="D947">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E947" t="s">
         <v>30</v>
@@ -20196,7 +20196,7 @@
         <v>29</v>
       </c>
       <c r="D948">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E948" t="s">
         <v>30</v>
@@ -20230,7 +20230,7 @@
         <v>29</v>
       </c>
       <c r="D950">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E950" t="s">
         <v>30</v>
@@ -20247,7 +20247,7 @@
         <v>29</v>
       </c>
       <c r="D951">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E951" t="s">
         <v>30</v>
@@ -20264,7 +20264,7 @@
         <v>29</v>
       </c>
       <c r="D952">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E952" t="s">
         <v>30</v>
@@ -20281,7 +20281,7 @@
         <v>29</v>
       </c>
       <c r="D953">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E953" t="s">
         <v>30</v>
@@ -20298,7 +20298,7 @@
         <v>29</v>
       </c>
       <c r="D954">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E954" t="s">
         <v>30</v>
@@ -20315,7 +20315,7 @@
         <v>29</v>
       </c>
       <c r="D955">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E955" t="s">
         <v>30</v>
@@ -20332,7 +20332,7 @@
         <v>29</v>
       </c>
       <c r="D956">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E956" t="s">
         <v>30</v>
@@ -20349,7 +20349,7 @@
         <v>29</v>
       </c>
       <c r="D957">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E957" t="s">
         <v>30</v>
@@ -20366,7 +20366,7 @@
         <v>29</v>
       </c>
       <c r="D958">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E958" t="s">
         <v>30</v>
@@ -20383,7 +20383,7 @@
         <v>29</v>
       </c>
       <c r="D959">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E959" t="s">
         <v>30</v>
@@ -20400,7 +20400,7 @@
         <v>29</v>
       </c>
       <c r="D960">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E960" t="s">
         <v>30</v>
@@ -20417,7 +20417,7 @@
         <v>29</v>
       </c>
       <c r="D961">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E961" t="s">
         <v>30</v>
@@ -20434,7 +20434,7 @@
         <v>29</v>
       </c>
       <c r="D962">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E962" t="s">
         <v>30</v>
@@ -20451,7 +20451,7 @@
         <v>29</v>
       </c>
       <c r="D963">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E963" t="s">
         <v>30</v>
@@ -20468,7 +20468,7 @@
         <v>29</v>
       </c>
       <c r="D964">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E964" t="s">
         <v>30</v>
@@ -20485,7 +20485,7 @@
         <v>29</v>
       </c>
       <c r="D965">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E965" t="s">
         <v>30</v>
@@ -20502,7 +20502,7 @@
         <v>29</v>
       </c>
       <c r="D966">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E966" t="s">
         <v>30</v>
@@ -20519,7 +20519,7 @@
         <v>29</v>
       </c>
       <c r="D967">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E967" t="s">
         <v>30</v>
@@ -20536,7 +20536,7 @@
         <v>29</v>
       </c>
       <c r="D968">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E968" t="s">
         <v>30</v>
@@ -20553,7 +20553,7 @@
         <v>29</v>
       </c>
       <c r="D969">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E969" t="s">
         <v>30</v>
@@ -20570,7 +20570,7 @@
         <v>29</v>
       </c>
       <c r="D970">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E970" t="s">
         <v>30</v>
@@ -20587,7 +20587,7 @@
         <v>29</v>
       </c>
       <c r="D971">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E971" t="s">
         <v>30</v>
@@ -20604,7 +20604,7 @@
         <v>29</v>
       </c>
       <c r="D972">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E972" t="s">
         <v>30</v>
@@ -20621,7 +20621,7 @@
         <v>29</v>
       </c>
       <c r="D973">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E973" t="s">
         <v>30</v>
@@ -20638,7 +20638,7 @@
         <v>29</v>
       </c>
       <c r="D974">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E974" t="s">
         <v>30</v>
@@ -20655,7 +20655,7 @@
         <v>29</v>
       </c>
       <c r="D975">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E975" t="s">
         <v>30</v>
@@ -20672,7 +20672,7 @@
         <v>29</v>
       </c>
       <c r="D976">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E976" t="s">
         <v>30</v>
@@ -20689,7 +20689,7 @@
         <v>29</v>
       </c>
       <c r="D977">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E977" t="s">
         <v>30</v>
@@ -20706,7 +20706,7 @@
         <v>29</v>
       </c>
       <c r="D978">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E978" t="s">
         <v>30</v>
@@ -20723,7 +20723,7 @@
         <v>29</v>
       </c>
       <c r="D979">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E979" t="s">
         <v>30</v>
@@ -20740,7 +20740,7 @@
         <v>29</v>
       </c>
       <c r="D980">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E980" t="s">
         <v>30</v>
@@ -20757,7 +20757,7 @@
         <v>29</v>
       </c>
       <c r="D981">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E981" t="s">
         <v>30</v>
@@ -20774,7 +20774,7 @@
         <v>29</v>
       </c>
       <c r="D982">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E982" t="s">
         <v>30</v>
@@ -20791,7 +20791,7 @@
         <v>29</v>
       </c>
       <c r="D983">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E983" t="s">
         <v>30</v>
@@ -20808,7 +20808,7 @@
         <v>29</v>
       </c>
       <c r="D984">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E984" t="s">
         <v>30</v>
@@ -20825,7 +20825,7 @@
         <v>29</v>
       </c>
       <c r="D985">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E985" t="s">
         <v>30</v>
@@ -20842,7 +20842,7 @@
         <v>29</v>
       </c>
       <c r="D986">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E986" t="s">
         <v>30</v>
@@ -20859,7 +20859,7 @@
         <v>29</v>
       </c>
       <c r="D987">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E987" t="s">
         <v>30</v>
@@ -20876,7 +20876,7 @@
         <v>29</v>
       </c>
       <c r="D988">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E988" t="s">
         <v>30</v>
@@ -20893,7 +20893,7 @@
         <v>29</v>
       </c>
       <c r="D989">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E989" t="s">
         <v>30</v>
@@ -20910,7 +20910,7 @@
         <v>29</v>
       </c>
       <c r="D990">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E990" t="s">
         <v>30</v>
@@ -20927,7 +20927,7 @@
         <v>29</v>
       </c>
       <c r="D991">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E991" t="s">
         <v>30</v>
@@ -20944,7 +20944,7 @@
         <v>29</v>
       </c>
       <c r="D992">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E992" t="s">
         <v>30</v>
@@ -20961,7 +20961,7 @@
         <v>29</v>
       </c>
       <c r="D993">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E993" t="s">
         <v>30</v>
@@ -20978,7 +20978,7 @@
         <v>29</v>
       </c>
       <c r="D994">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E994" t="s">
         <v>30</v>
@@ -20995,7 +20995,7 @@
         <v>29</v>
       </c>
       <c r="D995">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E995" t="s">
         <v>30</v>
@@ -21012,7 +21012,7 @@
         <v>29</v>
       </c>
       <c r="D996">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E996" t="s">
         <v>30</v>
@@ -21029,7 +21029,7 @@
         <v>29</v>
       </c>
       <c r="D997">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E997" t="s">
         <v>30</v>
@@ -21046,7 +21046,7 @@
         <v>29</v>
       </c>
       <c r="D998">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E998" t="s">
         <v>30</v>
@@ -21063,7 +21063,7 @@
         <v>29</v>
       </c>
       <c r="D999">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E999" t="s">
         <v>30</v>
@@ -21080,7 +21080,7 @@
         <v>29</v>
       </c>
       <c r="D1000">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1000" t="s">
         <v>30</v>
@@ -21097,7 +21097,7 @@
         <v>29</v>
       </c>
       <c r="D1001">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1001" t="s">
         <v>30</v>
@@ -21131,7 +21131,7 @@
         <v>29</v>
       </c>
       <c r="D1003">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1003" t="s">
         <v>30</v>
@@ -21148,7 +21148,7 @@
         <v>29</v>
       </c>
       <c r="D1004">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1004" t="s">
         <v>30</v>
@@ -21165,7 +21165,7 @@
         <v>29</v>
       </c>
       <c r="D1005">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E1005" t="s">
         <v>30</v>
@@ -21182,7 +21182,7 @@
         <v>29</v>
       </c>
       <c r="D1006">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E1006" t="s">
         <v>30</v>
@@ -21199,7 +21199,7 @@
         <v>29</v>
       </c>
       <c r="D1007">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1007" t="s">
         <v>30</v>
@@ -21216,7 +21216,7 @@
         <v>29</v>
       </c>
       <c r="D1008">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E1008" t="s">
         <v>30</v>
@@ -21233,7 +21233,7 @@
         <v>29</v>
       </c>
       <c r="D1009">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1009" t="s">
         <v>30</v>
@@ -21250,7 +21250,7 @@
         <v>29</v>
       </c>
       <c r="D1010">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1010" t="s">
         <v>30</v>
@@ -21267,7 +21267,7 @@
         <v>29</v>
       </c>
       <c r="D1011">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1011" t="s">
         <v>30</v>
@@ -21284,7 +21284,7 @@
         <v>29</v>
       </c>
       <c r="D1012">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1012" t="s">
         <v>30</v>
@@ -21301,7 +21301,7 @@
         <v>29</v>
       </c>
       <c r="D1013">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1013" t="s">
         <v>30</v>
@@ -21318,7 +21318,7 @@
         <v>29</v>
       </c>
       <c r="D1014">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1014" t="s">
         <v>30</v>
@@ -21335,7 +21335,7 @@
         <v>29</v>
       </c>
       <c r="D1015">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1015" t="s">
         <v>30</v>
@@ -21369,7 +21369,7 @@
         <v>29</v>
       </c>
       <c r="D1017">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1017" t="s">
         <v>30</v>
@@ -21386,7 +21386,7 @@
         <v>29</v>
       </c>
       <c r="D1018">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1018" t="s">
         <v>30</v>
@@ -21403,7 +21403,7 @@
         <v>29</v>
       </c>
       <c r="D1019">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1019" t="s">
         <v>30</v>
@@ -21420,7 +21420,7 @@
         <v>29</v>
       </c>
       <c r="D1020">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1020" t="s">
         <v>30</v>
@@ -21437,7 +21437,7 @@
         <v>29</v>
       </c>
       <c r="D1021">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E1021" t="s">
         <v>30</v>
@@ -21454,7 +21454,7 @@
         <v>29</v>
       </c>
       <c r="D1022">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E1022" t="s">
         <v>30</v>
@@ -21471,7 +21471,7 @@
         <v>29</v>
       </c>
       <c r="D1023">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1023" t="s">
         <v>30</v>
@@ -21488,7 +21488,7 @@
         <v>29</v>
       </c>
       <c r="D1024">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1024" t="s">
         <v>30</v>
@@ -21505,7 +21505,7 @@
         <v>29</v>
       </c>
       <c r="D1025">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1025" t="s">
         <v>30</v>
@@ -21522,7 +21522,7 @@
         <v>29</v>
       </c>
       <c r="D1026">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E1026" t="s">
         <v>30</v>
@@ -21539,7 +21539,7 @@
         <v>29</v>
       </c>
       <c r="D1027">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1027" t="s">
         <v>30</v>
@@ -21556,7 +21556,7 @@
         <v>29</v>
       </c>
       <c r="D1028">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E1028" t="s">
         <v>30</v>
@@ -21573,7 +21573,7 @@
         <v>29</v>
       </c>
       <c r="D1029">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E1029" t="s">
         <v>30</v>
@@ -21590,7 +21590,7 @@
         <v>29</v>
       </c>
       <c r="D1030">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1030" t="s">
         <v>30</v>
@@ -21607,7 +21607,7 @@
         <v>29</v>
       </c>
       <c r="D1031">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E1031" t="s">
         <v>30</v>
@@ -21624,7 +21624,7 @@
         <v>29</v>
       </c>
       <c r="D1032">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E1032" t="s">
         <v>30</v>
@@ -21641,7 +21641,7 @@
         <v>29</v>
       </c>
       <c r="D1033">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E1033" t="s">
         <v>30</v>
@@ -21658,7 +21658,7 @@
         <v>29</v>
       </c>
       <c r="D1034">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1034" t="s">
         <v>30</v>
@@ -21675,7 +21675,7 @@
         <v>29</v>
       </c>
       <c r="D1035">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1035" t="s">
         <v>30</v>
@@ -21692,7 +21692,7 @@
         <v>29</v>
       </c>
       <c r="D1036">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1036" t="s">
         <v>30</v>
@@ -21709,7 +21709,7 @@
         <v>29</v>
       </c>
       <c r="D1037">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1037" t="s">
         <v>30</v>
@@ -21726,7 +21726,7 @@
         <v>29</v>
       </c>
       <c r="D1038">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1038" t="s">
         <v>30</v>
@@ -21743,7 +21743,7 @@
         <v>29</v>
       </c>
       <c r="D1039">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1039" t="s">
         <v>30</v>
@@ -21777,7 +21777,7 @@
         <v>29</v>
       </c>
       <c r="D1041">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1041" t="s">
         <v>30</v>
@@ -21794,7 +21794,7 @@
         <v>29</v>
       </c>
       <c r="D1042">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1042" t="s">
         <v>30</v>
@@ -21811,7 +21811,7 @@
         <v>29</v>
       </c>
       <c r="D1043">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1043" t="s">
         <v>30</v>
@@ -21828,7 +21828,7 @@
         <v>29</v>
       </c>
       <c r="D1044">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1044" t="s">
         <v>30</v>
@@ -21845,7 +21845,7 @@
         <v>29</v>
       </c>
       <c r="D1045">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E1045" t="s">
         <v>30</v>
@@ -21862,7 +21862,7 @@
         <v>29</v>
       </c>
       <c r="D1046">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1046" t="s">
         <v>30</v>
@@ -21879,7 +21879,7 @@
         <v>29</v>
       </c>
       <c r="D1047">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1047" t="s">
         <v>30</v>
@@ -21896,7 +21896,7 @@
         <v>29</v>
       </c>
       <c r="D1048">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E1048" t="s">
         <v>30</v>
@@ -21913,7 +21913,7 @@
         <v>29</v>
       </c>
       <c r="D1049">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E1049" t="s">
         <v>30</v>
@@ -21930,7 +21930,7 @@
         <v>29</v>
       </c>
       <c r="D1050">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E1050" t="s">
         <v>30</v>
@@ -21947,7 +21947,7 @@
         <v>29</v>
       </c>
       <c r="D1051">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1051" t="s">
         <v>30</v>
@@ -21964,7 +21964,7 @@
         <v>29</v>
       </c>
       <c r="D1052">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1052" t="s">
         <v>30</v>
@@ -21981,7 +21981,7 @@
         <v>29</v>
       </c>
       <c r="D1053">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1053" t="s">
         <v>30</v>
@@ -21998,7 +21998,7 @@
         <v>29</v>
       </c>
       <c r="D1054">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E1054" t="s">
         <v>30</v>
@@ -22015,7 +22015,7 @@
         <v>29</v>
       </c>
       <c r="D1055">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1055" t="s">
         <v>30</v>
@@ -22032,7 +22032,7 @@
         <v>29</v>
       </c>
       <c r="D1056">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1056" t="s">
         <v>30</v>
@@ -22049,7 +22049,7 @@
         <v>29</v>
       </c>
       <c r="D1057">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1057" t="s">
         <v>30</v>
@@ -22066,7 +22066,7 @@
         <v>29</v>
       </c>
       <c r="D1058">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E1058" t="s">
         <v>30</v>
@@ -22083,7 +22083,7 @@
         <v>29</v>
       </c>
       <c r="D1059">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1059" t="s">
         <v>30</v>
@@ -22100,7 +22100,7 @@
         <v>29</v>
       </c>
       <c r="D1060">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E1060" t="s">
         <v>30</v>
@@ -22117,7 +22117,7 @@
         <v>29</v>
       </c>
       <c r="D1061">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1061" t="s">
         <v>30</v>
@@ -22134,7 +22134,7 @@
         <v>29</v>
       </c>
       <c r="D1062">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E1062" t="s">
         <v>30</v>
@@ -22151,7 +22151,7 @@
         <v>29</v>
       </c>
       <c r="D1063">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E1063" t="s">
         <v>30</v>
@@ -22168,7 +22168,7 @@
         <v>29</v>
       </c>
       <c r="D1064">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1064" t="s">
         <v>30</v>
@@ -22185,7 +22185,7 @@
         <v>29</v>
       </c>
       <c r="D1065">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1065" t="s">
         <v>30</v>
@@ -22202,7 +22202,7 @@
         <v>29</v>
       </c>
       <c r="D1066">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1066" t="s">
         <v>30</v>
@@ -22236,7 +22236,7 @@
         <v>29</v>
       </c>
       <c r="D1068">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1068" t="s">
         <v>30</v>
@@ -22253,7 +22253,7 @@
         <v>29</v>
       </c>
       <c r="D1069">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1069" t="s">
         <v>30</v>
@@ -22270,7 +22270,7 @@
         <v>29</v>
       </c>
       <c r="D1070">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E1070" t="s">
         <v>30</v>
@@ -22287,7 +22287,7 @@
         <v>29</v>
       </c>
       <c r="D1071">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1071" t="s">
         <v>30</v>
@@ -22304,7 +22304,7 @@
         <v>29</v>
       </c>
       <c r="D1072">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E1072" t="s">
         <v>30</v>
@@ -22321,7 +22321,7 @@
         <v>29</v>
       </c>
       <c r="D1073">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1073" t="s">
         <v>30</v>
@@ -22338,7 +22338,7 @@
         <v>29</v>
       </c>
       <c r="D1074">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E1074" t="s">
         <v>30</v>
@@ -22355,7 +22355,7 @@
         <v>29</v>
       </c>
       <c r="D1075">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E1075" t="s">
         <v>30</v>
@@ -22372,7 +22372,7 @@
         <v>29</v>
       </c>
       <c r="D1076">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E1076" t="s">
         <v>30</v>
@@ -22389,7 +22389,7 @@
         <v>29</v>
       </c>
       <c r="D1077">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1077" t="s">
         <v>30</v>
@@ -22406,7 +22406,7 @@
         <v>29</v>
       </c>
       <c r="D1078">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1078" t="s">
         <v>30</v>
@@ -22423,7 +22423,7 @@
         <v>29</v>
       </c>
       <c r="D1079">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1079" t="s">
         <v>30</v>
@@ -22440,7 +22440,7 @@
         <v>29</v>
       </c>
       <c r="D1080">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E1080" t="s">
         <v>30</v>
@@ -22457,7 +22457,7 @@
         <v>29</v>
       </c>
       <c r="D1081">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E1081" t="s">
         <v>30</v>
@@ -22474,7 +22474,7 @@
         <v>29</v>
       </c>
       <c r="D1082">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E1082" t="s">
         <v>30</v>
@@ -22491,7 +22491,7 @@
         <v>29</v>
       </c>
       <c r="D1083">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1083" t="s">
         <v>30</v>
@@ -22508,7 +22508,7 @@
         <v>29</v>
       </c>
       <c r="D1084">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E1084" t="s">
         <v>30</v>
@@ -22525,7 +22525,7 @@
         <v>29</v>
       </c>
       <c r="D1085">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E1085" t="s">
         <v>30</v>
@@ -22542,7 +22542,7 @@
         <v>29</v>
       </c>
       <c r="D1086">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1086" t="s">
         <v>30</v>
@@ -22559,7 +22559,7 @@
         <v>29</v>
       </c>
       <c r="D1087">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E1087" t="s">
         <v>30</v>
@@ -22576,7 +22576,7 @@
         <v>29</v>
       </c>
       <c r="D1088">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E1088" t="s">
         <v>30</v>
@@ -22593,7 +22593,7 @@
         <v>29</v>
       </c>
       <c r="D1089">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1089" t="s">
         <v>30</v>
@@ -22610,7 +22610,7 @@
         <v>29</v>
       </c>
       <c r="D1090">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E1090" t="s">
         <v>30</v>
@@ -22627,7 +22627,7 @@
         <v>29</v>
       </c>
       <c r="D1091">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E1091" t="s">
         <v>30</v>
@@ -22644,7 +22644,7 @@
         <v>29</v>
       </c>
       <c r="D1092">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1092" t="s">
         <v>30</v>
@@ -22661,7 +22661,7 @@
         <v>29</v>
       </c>
       <c r="D1093">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E1093" t="s">
         <v>30</v>
@@ -22678,7 +22678,7 @@
         <v>29</v>
       </c>
       <c r="D1094">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1094" t="s">
         <v>30</v>
@@ -22695,7 +22695,7 @@
         <v>29</v>
       </c>
       <c r="D1095">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1095" t="s">
         <v>30</v>
@@ -22712,7 +22712,7 @@
         <v>29</v>
       </c>
       <c r="D1096">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E1096" t="s">
         <v>30</v>
@@ -22729,7 +22729,7 @@
         <v>29</v>
       </c>
       <c r="D1097">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1097" t="s">
         <v>30</v>
@@ -22746,7 +22746,7 @@
         <v>29</v>
       </c>
       <c r="D1098">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1098" t="s">
         <v>30</v>
@@ -22763,7 +22763,7 @@
         <v>29</v>
       </c>
       <c r="D1099">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1099" t="s">
         <v>30</v>
@@ -22780,7 +22780,7 @@
         <v>29</v>
       </c>
       <c r="D1100">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E1100" t="s">
         <v>30</v>
@@ -22797,7 +22797,7 @@
         <v>29</v>
       </c>
       <c r="D1101">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1101" t="s">
         <v>30</v>
@@ -22814,7 +22814,7 @@
         <v>29</v>
       </c>
       <c r="D1102">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E1102" t="s">
         <v>30</v>
@@ -22831,7 +22831,7 @@
         <v>29</v>
       </c>
       <c r="D1103">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E1103" t="s">
         <v>30</v>
@@ -22848,7 +22848,7 @@
         <v>29</v>
       </c>
       <c r="D1104">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1104" t="s">
         <v>30</v>
@@ -22865,7 +22865,7 @@
         <v>29</v>
       </c>
       <c r="D1105">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1105" t="s">
         <v>30</v>
@@ -22882,7 +22882,7 @@
         <v>29</v>
       </c>
       <c r="D1106">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1106" t="s">
         <v>30</v>
@@ -22899,7 +22899,7 @@
         <v>29</v>
       </c>
       <c r="D1107">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1107" t="s">
         <v>30</v>
@@ -22916,7 +22916,7 @@
         <v>29</v>
       </c>
       <c r="D1108">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1108" t="s">
         <v>30</v>
@@ -22933,7 +22933,7 @@
         <v>29</v>
       </c>
       <c r="D1109">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E1109" t="s">
         <v>30</v>
@@ -22950,7 +22950,7 @@
         <v>29</v>
       </c>
       <c r="D1110">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E1110" t="s">
         <v>30</v>
@@ -22967,7 +22967,7 @@
         <v>29</v>
       </c>
       <c r="D1111">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1111" t="s">
         <v>30</v>
@@ -22984,7 +22984,7 @@
         <v>29</v>
       </c>
       <c r="D1112">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E1112" t="s">
         <v>30</v>
